--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -416,15 +416,57 @@
     <t xml:space="preserve">Politica internazionale|Politica di sicurezza|Energia</t>
   </si>
   <si>
+    <t xml:space="preserve">26.7151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feller Olivier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nach den Geldautomaten: Werden die Unternehmen die nächsten Ziele sein?  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après les bancomats, les entreprises seront-elles les prochaines cibles ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;- Après les explosions répétées de bancomats en Suisse, le braquage d’une usine localisée à Courchavon le 5 mars 2026 au cours duquel les auteurs ont également mis le feu à des véhicules accolés au bâtiment, marque-t-il une nouvelle escalade de la criminalité&amp;nbsp;?&amp;nbsp;&lt;br&gt;- La Confédération traitera-t-elle les braquages d’entreprises de la même manière que les explosions de bancomats&amp;nbsp;?&amp;nbsp;&lt;br&gt;- Par exemple en créant un groupe d’experts&amp;nbsp;?&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;- Ist der Raubüberfall auf eine Fabrik in Courchavon am 5.&amp;nbsp;März&amp;nbsp;2026, bei dem die Täter auch zwei neben dem Gebäude geparkte Fahrzeuge in Brand setzten, nach den wiederholten Geldautomat-Sprengungen in der Schweiz ein Zeichen für eine erneute Eskalation der Kriminalität?&amp;nbsp;&lt;br&gt;- Wird der Bund Raubüberfälle auf Unternehmen genauso handhaben wie Sprengungen von Geldautomaten?&amp;nbsp;&lt;br&gt;- Zum Beispiel, indem er eine Expertengruppe einberuft?&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Strafrecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Droit pénal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Diritto penale</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3069</t>
   </si>
   <si>
     <t xml:space="preserve">Sollberger Sandra</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
   </si>
   <si>
@@ -441,48 +483,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feller Olivier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nach den Geldautomaten: Werden die Unternehmen die nächsten Ziele sein?  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Après les bancomats, les entreprises seront-elles les prochaines cibles ? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;- Après les explosions répétées de bancomats en Suisse, le braquage d’une usine localisée à Courchavon le 5 mars 2026 au cours duquel les auteurs ont également mis le feu à des véhicules accolés au bâtiment, marque-t-il une nouvelle escalade de la criminalité&amp;nbsp;?&amp;nbsp;&lt;br&gt;- La Confédération traitera-t-elle les braquages d’entreprises de la même manière que les explosions de bancomats&amp;nbsp;?&amp;nbsp;&lt;br&gt;- Par exemple en créant un groupe d’experts&amp;nbsp;?&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;- Ist der Raubüberfall auf eine Fabrik in Courchavon am 5.&amp;nbsp;März&amp;nbsp;2026, bei dem die Täter auch zwei neben dem Gebäude geparkte Fahrzeuge in Brand setzten, nach den wiederholten Geldautomat-Sprengungen in der Schweiz ein Zeichen für eine erneute Eskalation der Kriminalität?&amp;nbsp;&lt;br&gt;- Wird der Bund Raubüberfälle auf Unternehmen genauso handhaben wie Sprengungen von Geldautomaten?&amp;nbsp;&lt;br&gt;- Zum Beispiel, indem er eine Expertengruppe einberuft?&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conseil fédéral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Strafrecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Droit pénal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Diritto penale</t>
   </si>
   <si>
     <t xml:space="preserve">26.030</t>
@@ -5590,62 +5590,62 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263069</v>
+        <v>20267151</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
         <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="F12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
       </c>
-      <c r="H12"/>
+      <c r="H12" t="s">
+        <v>138</v>
+      </c>
       <c r="I12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>138</v>
-      </c>
-      <c r="K12" t="s">
-        <v>28</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="K12"/>
       <c r="L12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="O12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="R12" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="S12" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="T12" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="U12" t="s">
         <v>37</v>
@@ -5653,62 +5653,62 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20267151</v>
+        <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
       </c>
-      <c r="H13" t="s">
-        <v>146</v>
-      </c>
+      <c r="H13"/>
       <c r="I13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>148</v>
-      </c>
-      <c r="K13"/>
+        <v>152</v>
+      </c>
+      <c r="K13" t="s">
+        <v>28</v>
+      </c>
       <c r="L13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N13" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="O13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="Q13" t="s">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="R13" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="S13" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="T13" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="U13" t="s">
         <v>37</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="G14"/>
       <c r="H14" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I14" t="s">
         <v>160</v>
@@ -5918,7 +5918,7 @@
         <v>41</v>
       </c>
       <c r="H17" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I17" t="s">
         <v>198</v>
@@ -6075,7 +6075,7 @@
         <v>233</v>
       </c>
       <c r="Q19" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R19" t="s">
         <v>234</v>
@@ -6178,7 +6178,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I21" t="s">
         <v>251</v>
@@ -6270,7 +6270,7 @@
         <v>271</v>
       </c>
       <c r="Q22" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R22" t="s">
         <v>272</v>
@@ -6335,7 +6335,7 @@
         <v>283</v>
       </c>
       <c r="Q23" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R23" t="s">
         <v>193</v>
@@ -6501,7 +6501,7 @@
         <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I26" t="s">
         <v>309</v>
@@ -7044,7 +7044,7 @@
         <v>399</v>
       </c>
       <c r="Q34" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R34" t="s">
         <v>400</v>
@@ -7203,7 +7203,7 @@
         <v>431</v>
       </c>
       <c r="E37" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F37" t="s">
         <v>432</v>
@@ -7365,7 +7365,7 @@
         <v>459</v>
       </c>
       <c r="Q39" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R39" t="s">
         <v>460</v>
@@ -7403,7 +7403,7 @@
         <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I40" t="s">
         <v>465</v>
@@ -7676,7 +7676,7 @@
         <v>518</v>
       </c>
       <c r="Q44" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R44" t="s">
         <v>519</v>
@@ -7934,7 +7934,7 @@
         <v>567</v>
       </c>
       <c r="Q48" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R48" t="s">
         <v>568</v>
@@ -8156,7 +8156,7 @@
         <v>605</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F52" t="s">
         <v>606</v>
@@ -8322,7 +8322,7 @@
         <v>634</v>
       </c>
       <c r="Q54" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R54" t="s">
         <v>635</v>
@@ -8645,7 +8645,7 @@
         <v>692</v>
       </c>
       <c r="Q59" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R59" t="s">
         <v>440</v>
@@ -8840,7 +8840,7 @@
         <v>722</v>
       </c>
       <c r="Q62" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R62" t="s">
         <v>723</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I65" t="s">
         <v>502</v>
@@ -9051,7 +9051,7 @@
         <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I66" t="s">
         <v>760</v>
@@ -9273,7 +9273,7 @@
         <v>802</v>
       </c>
       <c r="Q69" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R69" t="s">
         <v>803</v>
@@ -9376,7 +9376,7 @@
         <v>25</v>
       </c>
       <c r="H71" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I71" t="s">
         <v>819</v>
@@ -9403,7 +9403,7 @@
         <v>825</v>
       </c>
       <c r="Q71" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R71" t="s">
         <v>826</v>
@@ -9598,7 +9598,7 @@
         <v>861</v>
       </c>
       <c r="Q74" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R74" t="s">
         <v>862</v>
@@ -9756,7 +9756,7 @@
         <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I77" t="s">
         <v>885</v>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I79" t="s">
         <v>905</v>
@@ -10086,7 +10086,7 @@
         <v>944</v>
       </c>
       <c r="Q82" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R82" t="s">
         <v>945</v>
@@ -10151,7 +10151,7 @@
         <v>957</v>
       </c>
       <c r="Q83" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R83" t="s">
         <v>958</v>
@@ -10411,7 +10411,7 @@
         <v>1000</v>
       </c>
       <c r="Q87" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R87" t="s">
         <v>304</v>
@@ -10449,7 +10449,7 @@
         <v>25</v>
       </c>
       <c r="H88" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I88" t="s">
         <v>1003</v>
@@ -10640,7 +10640,7 @@
         <v>25</v>
       </c>
       <c r="H91" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I91" t="s">
         <v>1027</v>
@@ -10703,7 +10703,7 @@
         <v>25</v>
       </c>
       <c r="H92" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I92" t="s">
         <v>1027</v>
@@ -10766,7 +10766,7 @@
         <v>25</v>
       </c>
       <c r="H93" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I93" t="s">
         <v>1027</v>
@@ -11051,7 +11051,7 @@
         <v>1084</v>
       </c>
       <c r="Q97" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R97" t="s">
         <v>1085</v>
@@ -11177,7 +11177,7 @@
         <v>1107</v>
       </c>
       <c r="Q99" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R99" t="s">
         <v>1108</v>
@@ -11242,7 +11242,7 @@
         <v>1119</v>
       </c>
       <c r="Q100" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R100" t="s">
         <v>1120</v>
@@ -11372,7 +11372,7 @@
         <v>1139</v>
       </c>
       <c r="Q102" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R102" t="s">
         <v>1140</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I109" t="s">
         <v>1203</v>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I110" t="s">
         <v>1214</v>
@@ -12134,7 +12134,7 @@
         <v>1266</v>
       </c>
       <c r="Q114" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R114" t="s">
         <v>1097</v>
@@ -12264,7 +12264,7 @@
         <v>1288</v>
       </c>
       <c r="Q116" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R116" t="s">
         <v>1289</v>
@@ -12459,7 +12459,7 @@
         <v>1321</v>
       </c>
       <c r="Q119" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R119" t="s">
         <v>1322</v>
@@ -12524,7 +12524,7 @@
         <v>1334</v>
       </c>
       <c r="Q120" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R120" t="s">
         <v>646</v>
@@ -12973,7 +12973,7 @@
         <v>1400</v>
       </c>
       <c r="Q127" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R127" t="s">
         <v>1401</v>
@@ -13038,7 +13038,7 @@
         <v>1411</v>
       </c>
       <c r="Q128" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R128" t="s">
         <v>1412</v>
@@ -13103,7 +13103,7 @@
         <v>1424</v>
       </c>
       <c r="Q129" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R129" t="s">
         <v>1425</v>
@@ -13168,7 +13168,7 @@
         <v>1430</v>
       </c>
       <c r="Q130" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R130" t="s">
         <v>1431</v>
@@ -13197,7 +13197,7 @@
         <v>1435</v>
       </c>
       <c r="E131" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F131" t="s">
         <v>1436</v>
@@ -13233,7 +13233,7 @@
         <v>1443</v>
       </c>
       <c r="Q131" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R131" t="s">
         <v>440</v>
@@ -13426,7 +13426,7 @@
         <v>1475</v>
       </c>
       <c r="Q134" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R134" t="s">
         <v>1465</v>
@@ -13518,7 +13518,7 @@
         <v>1484</v>
       </c>
       <c r="E136" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F136" t="s">
         <v>1485</v>
@@ -13615,7 +13615,7 @@
         <v>1499</v>
       </c>
       <c r="Q137" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="R137" t="s">
         <v>1500</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,12 +80,69 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">25.4774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gewalttätiger Extremismus bei Demonstrationen. Veranstalter sollen die Kosten übernehmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrémisme violent lors de manifestations. Prise en charge des frais par les organisateurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estremismo violento durante manifestazioni. Addossare i costi agli organizzatori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d'élaborer une base légale fédérale pour permettre aux collectivités publiques de percevoir auprès des organisateurs d'une manifestation la prise en charge de tout ou partie des frais de sécurité et d'intervention.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, eine bundesrechtliche Grundlage zu schaffen, damit die Veranstalter von Demonstrationen die Sicherheits- und Interventionskosten ganz oder teilweise tragen müssen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Kommission des Nationalrats / En commission du Conseil national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Sicherheitspolitik|Soziale Fragen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Politique de sécurité|Questions sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Politica di sicurezza|Questioni sociali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3374</t>
   </si>
   <si>
-    <t xml:space="preserve">Mo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Grüne Fraktion</t>
   </si>
   <si>
@@ -143,9 +200,6 @@
     <t xml:space="preserve">PS</t>
   </si>
   <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
     <t xml:space="preserve">EDI</t>
   </si>
   <si>
@@ -164,9 +218,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263411</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wirtschaft|Soziale Fragen|Medien und Kommunikation|Gesundheit</t>
   </si>
   <si>
@@ -308,12 +359,6 @@
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
   </si>
   <si>
@@ -332,9 +377,6 @@
     <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
   </si>
   <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Von Dänemark lernen: Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
   </si>
   <si>
@@ -609,48 +651,6 @@
   </si>
   <si>
     <t xml:space="preserve">Finanze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gewalttätiger Extremismus bei Demonstrationen. Veranstalter sollen die Kosten übernehmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extrémisme violent lors de manifestations. Prise en charge des frais par les organisateurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estremismo violento durante manifestazioni. Addossare i costi agli organizzatori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d'élaborer une base légale fédérale pour permettre aux collectivités publiques de percevoir auprès des organisateurs d'une manifestation la prise en charge de tout ou partie des frais de sécurité et d'intervention.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, eine bundesrechtliche Grundlage zu schaffen, damit die Veranstalter von Demonstrationen die Sicherheits- und Interventionskosten ganz oder teilweise tragen müssen.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Kommission des Nationalrats / En commission du Conseil national</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Sicherheitspolitik|Soziale Fragen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Politique de sécurité|Questions sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Politica di sicurezza|Questioni sociali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-02</t>
   </si>
   <si>
     <t xml:space="preserve">25.4836</t>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20263374</v>
+        <v>20254774</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5006,605 +5006,607 @@
       <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2"/>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2"/>
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263411</v>
+        <v>20263374</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E3"/>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3"/>
+        <v>49</v>
+      </c>
+      <c r="L3"/>
+      <c r="M3" t="s">
+        <v>50</v>
+      </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="S3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="T3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="U3" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263454</v>
+        <v>20263411</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M4"/>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="T4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="U4" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263228</v>
+        <v>20263454</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M5"/>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="T5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="U5" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263323</v>
+        <v>20263228</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6"/>
-      <c r="M6" t="s">
-        <v>81</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="L6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M6"/>
       <c r="N6" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="T6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="U6" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263120</v>
+        <v>20263323</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L7"/>
       <c r="M7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="S7" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="T7" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="U7" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263121</v>
+        <v>20263120</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8"/>
+      <c r="M8" t="s">
+        <v>108</v>
+      </c>
+      <c r="N8" t="s">
+        <v>51</v>
+      </c>
+      <c r="O8" t="s">
+        <v>109</v>
+      </c>
+      <c r="P8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" t="s">
+        <v>111</v>
+      </c>
+      <c r="S8" t="s">
+        <v>112</v>
+      </c>
+      <c r="T8" t="s">
+        <v>113</v>
+      </c>
+      <c r="U8" t="s">
         <v>58</v>
-      </c>
-      <c r="I8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" t="s">
-        <v>100</v>
-      </c>
-      <c r="K8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" t="s">
-        <v>101</v>
-      </c>
-      <c r="M8"/>
-      <c r="N8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" t="s">
-        <v>102</v>
-      </c>
-      <c r="P8" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" t="s">
-        <v>73</v>
-      </c>
-      <c r="S8" t="s">
-        <v>74</v>
-      </c>
-      <c r="T8" t="s">
-        <v>75</v>
-      </c>
-      <c r="U8" t="s">
-        <v>39</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263131</v>
+        <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9"/>
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s">
-        <v>108</v>
-      </c>
-      <c r="L9"/>
-      <c r="M9" t="s">
-        <v>109</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="L9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M9"/>
       <c r="N9" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="S9" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="T9" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="U9" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263099</v>
+        <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>99</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E10"/>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="J10" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>119</v>
-      </c>
-      <c r="L10" t="s">
-        <v>120</v>
-      </c>
-      <c r="M10"/>
+        <v>122</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>123</v>
+      </c>
       <c r="N10" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="P10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="S10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="T10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="U10" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20267194</v>
+        <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>131</v>
-      </c>
-      <c r="K11"/>
+        <v>132</v>
+      </c>
+      <c r="K11" t="s">
+        <v>133</v>
+      </c>
       <c r="L11" t="s">
-        <v>132</v>
-      </c>
-      <c r="M11" t="s">
-        <v>133</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M11"/>
       <c r="N11" t="s">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
         <v>135</v>
@@ -5613,7 +5615,7 @@
         <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R11" t="s">
         <v>137</v>
@@ -5625,391 +5627,387 @@
         <v>139</v>
       </c>
       <c r="U11" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263069</v>
+        <v>20267194</v>
       </c>
       <c r="B12" t="s">
         <v>140</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K12"/>
+      <c r="L12" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" t="s">
+        <v>147</v>
+      </c>
+      <c r="N12" t="s">
+        <v>148</v>
+      </c>
+      <c r="O12" t="s">
+        <v>149</v>
+      </c>
+      <c r="P12" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>37</v>
+      </c>
+      <c r="R12" t="s">
+        <v>151</v>
+      </c>
+      <c r="S12" t="s">
+        <v>152</v>
+      </c>
+      <c r="T12" t="s">
+        <v>153</v>
+      </c>
+      <c r="U12" t="s">
         <v>58</v>
-      </c>
-      <c r="I12" t="s">
-        <v>143</v>
-      </c>
-      <c r="J12" t="s">
-        <v>144</v>
-      </c>
-      <c r="K12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" t="s">
-        <v>145</v>
-      </c>
-      <c r="M12" t="s">
-        <v>146</v>
-      </c>
-      <c r="N12" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" t="s">
-        <v>147</v>
-      </c>
-      <c r="P12" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>35</v>
-      </c>
-      <c r="R12" t="s">
-        <v>63</v>
-      </c>
-      <c r="S12" t="s">
-        <v>64</v>
-      </c>
-      <c r="T12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U12" t="s">
-        <v>39</v>
       </c>
       <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20267151</v>
+        <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J13" t="s">
-        <v>153</v>
-      </c>
-      <c r="K13"/>
+        <v>158</v>
+      </c>
+      <c r="K13" t="s">
+        <v>49</v>
+      </c>
       <c r="L13" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Q13" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="R13" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="S13" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="T13" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="U13" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260030</v>
+        <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14"/>
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" t="s">
+        <v>165</v>
+      </c>
       <c r="F14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14"/>
+        <v>156</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
       <c r="H14" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K14" t="s">
         <v>167</v>
       </c>
-      <c r="L14"/>
-      <c r="M14"/>
+      <c r="K14"/>
+      <c r="L14" t="s">
+        <v>168</v>
+      </c>
+      <c r="M14" t="s">
+        <v>169</v>
+      </c>
       <c r="N14" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="O14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q14" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="R14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="S14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="T14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="U14" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20267032</v>
+        <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" t="s">
-        <v>78</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15"/>
       <c r="F15" t="s">
-        <v>176</v>
-      </c>
-      <c r="G15" t="s">
-        <v>26</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G15"/>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J15" t="s">
-        <v>178</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15" t="s">
-        <v>179</v>
-      </c>
-      <c r="M15" t="s">
         <v>180</v>
       </c>
+      <c r="K15" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15"/>
+      <c r="M15"/>
       <c r="N15" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="S15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="T15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="U15" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20263006</v>
+        <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16"/>
+        <v>189</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
       <c r="F16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
-        <v>190</v>
-      </c>
-      <c r="K16" t="s">
-        <v>191</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="K16"/>
       <c r="L16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q16" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20254774</v>
+        <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>99</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="E17"/>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="O17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q17" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="U17" t="s">
-        <v>212</v>
-      </c>
-      <c r="V17" t="s">
-        <v>212</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="V17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6019,7 +6017,7 @@
         <v>213</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
         <v>214</v>
@@ -6028,13 +6026,13 @@
         <v>215</v>
       </c>
       <c r="F18" t="s">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I18" t="s">
         <v>216</v>
@@ -6073,7 +6071,7 @@
         <v>227</v>
       </c>
       <c r="U18" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V18"/>
     </row>
@@ -6085,22 +6083,22 @@
         <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
         <v>229</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s">
         <v>230</v>
@@ -6127,7 +6125,7 @@
         <v>236</v>
       </c>
       <c r="Q19" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R19" t="s">
         <v>237</v>
@@ -6139,7 +6137,7 @@
         <v>239</v>
       </c>
       <c r="U19" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V19"/>
     </row>
@@ -6154,16 +6152,16 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>241</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
         <v>242</v>
@@ -6193,7 +6191,7 @@
         <v>250</v>
       </c>
       <c r="Q20" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R20" t="s">
         <v>251</v>
@@ -6205,7 +6203,7 @@
         <v>253</v>
       </c>
       <c r="U20" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V20"/>
     </row>
@@ -6217,22 +6215,22 @@
         <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
         <v>241</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
         <v>255</v>
@@ -6259,7 +6257,7 @@
         <v>262</v>
       </c>
       <c r="Q21" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R21" t="s">
         <v>263</v>
@@ -6271,7 +6269,7 @@
         <v>265</v>
       </c>
       <c r="U21" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V21"/>
     </row>
@@ -6283,22 +6281,22 @@
         <v>266</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
         <v>267</v>
       </c>
       <c r="E22" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
         <v>268</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I22" t="s">
         <v>269</v>
@@ -6316,7 +6314,7 @@
         <v>273</v>
       </c>
       <c r="N22" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O22" t="s">
         <v>274</v>
@@ -6325,7 +6323,7 @@
         <v>275</v>
       </c>
       <c r="Q22" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R22" t="s">
         <v>276</v>
@@ -6337,7 +6335,7 @@
         <v>278</v>
       </c>
       <c r="U22" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V22"/>
     </row>
@@ -6352,19 +6350,19 @@
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
         <v>280</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I23" t="s">
         <v>281</v>
@@ -6391,19 +6389,19 @@
         <v>287</v>
       </c>
       <c r="Q23" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R23" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="S23" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="T23" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="U23" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V23"/>
     </row>
@@ -6415,22 +6413,22 @@
         <v>288</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
         <v>280</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I24" t="s">
         <v>289</v>
@@ -6457,7 +6455,7 @@
         <v>295</v>
       </c>
       <c r="Q24" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R24" t="s">
         <v>296</v>
@@ -6469,7 +6467,7 @@
         <v>298</v>
       </c>
       <c r="U24" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V24"/>
     </row>
@@ -6481,19 +6479,19 @@
         <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
         <v>300</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
         <v>301</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
         <v>242</v>
@@ -6512,7 +6510,7 @@
         <v>305</v>
       </c>
       <c r="N25" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O25" t="s">
         <v>306</v>
@@ -6521,7 +6519,7 @@
         <v>307</v>
       </c>
       <c r="Q25" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R25" t="s">
         <v>308</v>
@@ -6533,7 +6531,7 @@
         <v>310</v>
       </c>
       <c r="U25" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V25"/>
     </row>
@@ -6545,22 +6543,22 @@
         <v>311</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
         <v>312</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
         <v>301</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H26" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
         <v>313</v>
@@ -6576,7 +6574,7 @@
         <v>316</v>
       </c>
       <c r="N26" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O26" t="s">
         <v>317</v>
@@ -6585,19 +6583,19 @@
         <v>318</v>
       </c>
       <c r="Q26" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="S26" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="T26" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="U26" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V26"/>
     </row>
@@ -6609,7 +6607,7 @@
         <v>319</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>320</v>
@@ -6619,10 +6617,10 @@
         <v>321</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I27" t="s">
         <v>322</v>
@@ -6649,7 +6647,7 @@
         <v>328</v>
       </c>
       <c r="Q27" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R27" t="s">
         <v>329</v>
@@ -6661,7 +6659,7 @@
         <v>331</v>
       </c>
       <c r="U27" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V27"/>
     </row>
@@ -6679,16 +6677,16 @@
         <v>333</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
         <v>334</v>
       </c>
       <c r="G28" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I28" t="s">
         <v>335</v>
@@ -6706,7 +6704,7 @@
         <v>339</v>
       </c>
       <c r="N28" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O28" t="s">
         <v>340</v>
@@ -6715,7 +6713,7 @@
         <v>341</v>
       </c>
       <c r="Q28" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R28" t="s">
         <v>342</v>
@@ -6727,7 +6725,7 @@
         <v>344</v>
       </c>
       <c r="U28" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V28"/>
     </row>
@@ -6739,22 +6737,22 @@
         <v>345</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>346</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s">
         <v>334</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H29" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I29" t="s">
         <v>347</v>
@@ -6781,19 +6779,19 @@
         <v>353</v>
       </c>
       <c r="Q29" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="S29" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="T29" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="U29" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V29"/>
     </row>
@@ -6805,22 +6803,22 @@
         <v>354</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F30" t="s">
         <v>334</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s">
         <v>355</v>
@@ -6850,16 +6848,16 @@
         <v>224</v>
       </c>
       <c r="R30" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="T30" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U30" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V30"/>
     </row>
@@ -6874,19 +6872,19 @@
         <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
         <v>334</v>
       </c>
       <c r="G31" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I31" t="s">
         <v>363</v>
@@ -6913,7 +6911,7 @@
         <v>369</v>
       </c>
       <c r="Q31" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R31" t="s">
         <v>370</v>
@@ -6925,7 +6923,7 @@
         <v>372</v>
       </c>
       <c r="U31" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V31"/>
     </row>
@@ -6937,22 +6935,22 @@
         <v>373</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
         <v>374</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
         <v>375</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I32" t="s">
         <v>376</v>
@@ -6970,7 +6968,7 @@
         <v>380</v>
       </c>
       <c r="N32" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O32" t="s">
         <v>381</v>
@@ -6991,7 +6989,7 @@
         <v>227</v>
       </c>
       <c r="U32" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V32"/>
     </row>
@@ -7003,22 +7001,22 @@
         <v>383</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
         <v>384</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
         <v>385</v>
@@ -7036,7 +7034,7 @@
         <v>389</v>
       </c>
       <c r="N33" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O33" t="s">
         <v>390</v>
@@ -7057,7 +7055,7 @@
         <v>394</v>
       </c>
       <c r="U33" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V33"/>
     </row>
@@ -7069,19 +7067,19 @@
         <v>395</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
         <v>396</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
         <v>384</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H34" t="s">
         <v>242</v>
@@ -7111,7 +7109,7 @@
         <v>403</v>
       </c>
       <c r="Q34" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R34" t="s">
         <v>404</v>
@@ -7123,7 +7121,7 @@
         <v>406</v>
       </c>
       <c r="U34" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V34"/>
     </row>
@@ -7135,22 +7133,22 @@
         <v>407</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
         <v>408</v>
       </c>
       <c r="E35" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
         <v>409</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I35" t="s">
         <v>410</v>
@@ -7168,7 +7166,7 @@
         <v>414</v>
       </c>
       <c r="N35" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O35" t="s">
         <v>415</v>
@@ -7189,7 +7187,7 @@
         <v>419</v>
       </c>
       <c r="U35" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V35"/>
     </row>
@@ -7204,19 +7202,19 @@
         <v>421</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
         <v>422</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I36" t="s">
         <v>423</v>
@@ -7243,7 +7241,7 @@
         <v>430</v>
       </c>
       <c r="Q36" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R36" t="s">
         <v>431</v>
@@ -7255,7 +7253,7 @@
         <v>433</v>
       </c>
       <c r="U36" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V36"/>
     </row>
@@ -7273,16 +7271,16 @@
         <v>435</v>
       </c>
       <c r="E37" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F37" t="s">
         <v>436</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I37" t="s">
         <v>437</v>
@@ -7309,7 +7307,7 @@
         <v>443</v>
       </c>
       <c r="Q37" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R37" t="s">
         <v>444</v>
@@ -7321,7 +7319,7 @@
         <v>446</v>
       </c>
       <c r="U37" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V37"/>
     </row>
@@ -7333,7 +7331,7 @@
         <v>447</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
         <v>448</v>
@@ -7345,10 +7343,10 @@
         <v>436</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H38" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I38" t="s">
         <v>450</v>
@@ -7364,7 +7362,7 @@
         <v>453</v>
       </c>
       <c r="N38" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O38" t="s">
         <v>454</v>
@@ -7385,7 +7383,7 @@
         <v>227</v>
       </c>
       <c r="U38" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V38"/>
     </row>
@@ -7397,22 +7395,22 @@
         <v>456</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
         <v>457</v>
       </c>
       <c r="E39" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>436</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s">
         <v>458</v>
@@ -7428,7 +7426,7 @@
         <v>461</v>
       </c>
       <c r="N39" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O39" t="s">
         <v>462</v>
@@ -7437,7 +7435,7 @@
         <v>463</v>
       </c>
       <c r="Q39" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R39" t="s">
         <v>464</v>
@@ -7449,7 +7447,7 @@
         <v>466</v>
       </c>
       <c r="U39" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V39"/>
     </row>
@@ -7461,22 +7459,22 @@
         <v>467</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
         <v>396</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
         <v>468</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H40" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
         <v>469</v>
@@ -7492,7 +7490,7 @@
         <v>472</v>
       </c>
       <c r="N40" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O40" t="s">
         <v>473</v>
@@ -7513,7 +7511,7 @@
         <v>477</v>
       </c>
       <c r="U40" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V40"/>
     </row>
@@ -7525,19 +7523,19 @@
         <v>478</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
         <v>479</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F41" t="s">
         <v>480</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H41" t="s">
         <v>242</v>
@@ -7567,7 +7565,7 @@
         <v>487</v>
       </c>
       <c r="Q41" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R41" t="s">
         <v>488</v>
@@ -7579,7 +7577,7 @@
         <v>490</v>
       </c>
       <c r="U41" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V41"/>
     </row>
@@ -7591,19 +7589,19 @@
         <v>491</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
         <v>479</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F42" t="s">
         <v>480</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H42" t="s">
         <v>242</v>
@@ -7622,7 +7620,7 @@
         <v>495</v>
       </c>
       <c r="N42" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O42" t="s">
         <v>496</v>
@@ -7631,7 +7629,7 @@
         <v>497</v>
       </c>
       <c r="Q42" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R42" t="s">
         <v>498</v>
@@ -7643,7 +7641,7 @@
         <v>500</v>
       </c>
       <c r="U42" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V42"/>
     </row>
@@ -7693,13 +7691,13 @@
         <v>512</v>
       </c>
       <c r="Q43" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R43"/>
       <c r="S43"/>
       <c r="T43"/>
       <c r="U43" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V43"/>
     </row>
@@ -7711,22 +7709,22 @@
         <v>513</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
         <v>514</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F44" t="s">
         <v>515</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s">
         <v>516</v>
@@ -7753,7 +7751,7 @@
         <v>522</v>
       </c>
       <c r="Q44" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R44" t="s">
         <v>523</v>
@@ -7765,7 +7763,7 @@
         <v>525</v>
       </c>
       <c r="U44" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V44"/>
     </row>
@@ -7777,22 +7775,22 @@
         <v>526</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
         <v>527</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F45" t="s">
         <v>515</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s">
         <v>528</v>
@@ -7819,7 +7817,7 @@
         <v>534</v>
       </c>
       <c r="Q45" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R45" t="s">
         <v>535</v>
@@ -7831,7 +7829,7 @@
         <v>537</v>
       </c>
       <c r="U45" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V45"/>
     </row>
@@ -7843,22 +7841,22 @@
         <v>538</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D46" t="s">
         <v>539</v>
       </c>
       <c r="E46" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
         <v>515</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H46" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I46" t="s">
         <v>540</v>
@@ -7885,7 +7883,7 @@
         <v>547</v>
       </c>
       <c r="Q46" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R46" t="s">
         <v>548</v>
@@ -7897,7 +7895,7 @@
         <v>550</v>
       </c>
       <c r="U46" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V46"/>
     </row>
@@ -7912,17 +7910,17 @@
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
         <v>552</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H47" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I47" t="s">
         <v>553</v>
@@ -7961,7 +7959,7 @@
         <v>562</v>
       </c>
       <c r="U47" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V47"/>
     </row>
@@ -7973,22 +7971,22 @@
         <v>563</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
         <v>564</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F48" t="s">
         <v>552</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H48" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I48" t="s">
         <v>565</v>
@@ -8006,7 +8004,7 @@
         <v>569</v>
       </c>
       <c r="N48" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O48" t="s">
         <v>570</v>
@@ -8015,7 +8013,7 @@
         <v>571</v>
       </c>
       <c r="Q48" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R48" t="s">
         <v>572</v>
@@ -8027,7 +8025,7 @@
         <v>574</v>
       </c>
       <c r="U48" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V48"/>
     </row>
@@ -8039,22 +8037,22 @@
         <v>575</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
         <v>576</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F49" t="s">
         <v>577</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s">
         <v>578</v>
@@ -8072,7 +8070,7 @@
         <v>582</v>
       </c>
       <c r="N49" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O49" t="s">
         <v>583</v>
@@ -8084,16 +8082,16 @@
         <v>224</v>
       </c>
       <c r="R49" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S49" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="T49" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U49" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V49"/>
     </row>
@@ -8105,7 +8103,7 @@
         <v>585</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
         <v>586</v>
@@ -8115,10 +8113,10 @@
         <v>577</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s">
         <v>587</v>
@@ -8145,7 +8143,7 @@
         <v>593</v>
       </c>
       <c r="Q50" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R50" t="s">
         <v>594</v>
@@ -8157,7 +8155,7 @@
         <v>596</v>
       </c>
       <c r="U50" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V50"/>
     </row>
@@ -8169,22 +8167,22 @@
         <v>597</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
         <v>346</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F51" t="s">
         <v>577</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I51" t="s">
         <v>598</v>
@@ -8223,7 +8221,7 @@
         <v>607</v>
       </c>
       <c r="U51" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V51"/>
     </row>
@@ -8235,22 +8233,22 @@
         <v>608</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D52" t="s">
         <v>609</v>
       </c>
       <c r="E52" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F52" t="s">
         <v>610</v>
       </c>
       <c r="G52" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I52" t="s">
         <v>611</v>
@@ -8268,7 +8266,7 @@
         <v>615</v>
       </c>
       <c r="N52" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O52" t="s">
         <v>616</v>
@@ -8277,7 +8275,7 @@
         <v>617</v>
       </c>
       <c r="Q52" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R52" t="s">
         <v>523</v>
@@ -8289,7 +8287,7 @@
         <v>525</v>
       </c>
       <c r="U52" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V52"/>
     </row>
@@ -8307,16 +8305,16 @@
         <v>619</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F53" t="s">
         <v>620</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I53" t="s">
         <v>621</v>
@@ -8343,19 +8341,19 @@
         <v>627</v>
       </c>
       <c r="Q53" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R53" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="S53" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="T53" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="U53" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V53"/>
     </row>
@@ -8379,10 +8377,10 @@
         <v>631</v>
       </c>
       <c r="G54" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H54" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I54" t="s">
         <v>632</v>
@@ -8409,7 +8407,7 @@
         <v>638</v>
       </c>
       <c r="Q54" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R54" t="s">
         <v>639</v>
@@ -8421,7 +8419,7 @@
         <v>641</v>
       </c>
       <c r="U54" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V54"/>
     </row>
@@ -8439,16 +8437,16 @@
         <v>396</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F55" t="s">
         <v>631</v>
       </c>
       <c r="G55" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H55" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I55" t="s">
         <v>643</v>
@@ -8487,7 +8485,7 @@
         <v>652</v>
       </c>
       <c r="U55" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V55"/>
     </row>
@@ -8502,17 +8500,17 @@
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
         <v>654</v>
       </c>
       <c r="G56" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H56" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I56" t="s">
         <v>655</v>
@@ -8551,7 +8549,7 @@
         <v>652</v>
       </c>
       <c r="U56" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V56"/>
     </row>
@@ -8563,19 +8561,19 @@
         <v>662</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s">
         <v>663</v>
       </c>
       <c r="E57" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
         <v>664</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H57" t="s">
         <v>665</v>
@@ -8605,7 +8603,7 @@
         <v>672</v>
       </c>
       <c r="Q57" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R57" t="s">
         <v>673</v>
@@ -8617,7 +8615,7 @@
         <v>675</v>
       </c>
       <c r="U57" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V57"/>
     </row>
@@ -8629,22 +8627,22 @@
         <v>676</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
         <v>677</v>
       </c>
       <c r="E58" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
         <v>664</v>
       </c>
       <c r="G58" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H58" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I58" t="s">
         <v>678</v>
@@ -8671,7 +8669,7 @@
         <v>684</v>
       </c>
       <c r="Q58" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R58" t="s">
         <v>685</v>
@@ -8683,7 +8681,7 @@
         <v>687</v>
       </c>
       <c r="U58" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V58"/>
     </row>
@@ -8695,22 +8693,22 @@
         <v>688</v>
       </c>
       <c r="C59" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D59" t="s">
         <v>689</v>
       </c>
       <c r="E59" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F59" t="s">
         <v>664</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I59" t="s">
         <v>690</v>
@@ -8737,7 +8735,7 @@
         <v>696</v>
       </c>
       <c r="Q59" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R59" t="s">
         <v>444</v>
@@ -8749,7 +8747,7 @@
         <v>446</v>
       </c>
       <c r="U59" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V59"/>
     </row>
@@ -8767,16 +8765,16 @@
         <v>698</v>
       </c>
       <c r="E60" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F60" t="s">
         <v>699</v>
       </c>
       <c r="G60" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H60" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I60" t="s">
         <v>700</v>
@@ -8794,7 +8792,7 @@
         <v>704</v>
       </c>
       <c r="N60" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O60" t="s">
         <v>705</v>
@@ -8815,7 +8813,7 @@
         <v>709</v>
       </c>
       <c r="U60" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V60"/>
     </row>
@@ -8830,19 +8828,19 @@
         <v>23</v>
       </c>
       <c r="D61" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
         <v>699</v>
       </c>
       <c r="G61" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I61" t="s">
         <v>711</v>
@@ -8881,7 +8879,7 @@
         <v>652</v>
       </c>
       <c r="U61" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V61"/>
     </row>
@@ -8893,22 +8891,22 @@
         <v>718</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D62" t="s">
         <v>267</v>
       </c>
       <c r="E62" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F62" t="s">
         <v>719</v>
       </c>
       <c r="G62" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I62" t="s">
         <v>720</v>
@@ -8926,7 +8924,7 @@
         <v>724</v>
       </c>
       <c r="N62" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O62" t="s">
         <v>725</v>
@@ -8935,7 +8933,7 @@
         <v>726</v>
       </c>
       <c r="Q62" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R62" t="s">
         <v>727</v>
@@ -8947,7 +8945,7 @@
         <v>729</v>
       </c>
       <c r="U62" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V62"/>
     </row>
@@ -8959,22 +8957,22 @@
         <v>730</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D63" t="s">
         <v>564</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F63" t="s">
         <v>731</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H63" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I63" t="s">
         <v>732</v>
@@ -9001,7 +8999,7 @@
         <v>738</v>
       </c>
       <c r="Q63" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R63" t="s">
         <v>739</v>
@@ -9013,7 +9011,7 @@
         <v>741</v>
       </c>
       <c r="U63" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V63"/>
     </row>
@@ -9036,7 +9034,7 @@
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s">
         <v>745</v>
@@ -9054,7 +9052,7 @@
         <v>749</v>
       </c>
       <c r="N64" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="O64" t="s">
         <v>750</v>
@@ -9063,13 +9061,13 @@
         <v>751</v>
       </c>
       <c r="Q64" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R64"/>
       <c r="S64"/>
       <c r="T64"/>
       <c r="U64" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V64"/>
     </row>
@@ -9092,7 +9090,7 @@
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I65" t="s">
         <v>506</v>
@@ -9119,13 +9117,13 @@
         <v>759</v>
       </c>
       <c r="Q65" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R65"/>
       <c r="S65"/>
       <c r="T65"/>
       <c r="U65" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V65"/>
     </row>
@@ -9147,10 +9145,10 @@
         <v>762</v>
       </c>
       <c r="G66" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H66" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I66" t="s">
         <v>763</v>
@@ -9168,7 +9166,7 @@
         <v>767</v>
       </c>
       <c r="N66" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="O66" t="s">
         <v>768</v>
@@ -9177,7 +9175,7 @@
         <v>769</v>
       </c>
       <c r="Q66" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R66" t="s">
         <v>770</v>
@@ -9189,7 +9187,7 @@
         <v>772</v>
       </c>
       <c r="U66" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V66"/>
     </row>
@@ -9207,16 +9205,16 @@
         <v>527</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F67" t="s">
         <v>774</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I67" t="s">
         <v>775</v>
@@ -9234,7 +9232,7 @@
         <v>779</v>
       </c>
       <c r="N67" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O67" t="s">
         <v>780</v>
@@ -9243,7 +9241,7 @@
         <v>781</v>
       </c>
       <c r="Q67" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R67" t="s">
         <v>782</v>
@@ -9255,7 +9253,7 @@
         <v>784</v>
       </c>
       <c r="U67" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V67"/>
     </row>
@@ -9267,7 +9265,7 @@
         <v>785</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D68" t="s">
         <v>629</v>
@@ -9279,10 +9277,10 @@
         <v>774</v>
       </c>
       <c r="G68" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H68" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I68" t="s">
         <v>786</v>
@@ -9321,7 +9319,7 @@
         <v>795</v>
       </c>
       <c r="U68" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V68"/>
     </row>
@@ -9333,19 +9331,19 @@
         <v>796</v>
       </c>
       <c r="C69" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D69" t="s">
         <v>797</v>
       </c>
       <c r="E69" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F69" t="s">
         <v>774</v>
       </c>
       <c r="G69" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H69" t="s">
         <v>798</v>
@@ -9366,7 +9364,7 @@
         <v>803</v>
       </c>
       <c r="N69" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O69" t="s">
         <v>804</v>
@@ -9375,7 +9373,7 @@
         <v>805</v>
       </c>
       <c r="Q69" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R69" t="s">
         <v>806</v>
@@ -9387,7 +9385,7 @@
         <v>808</v>
       </c>
       <c r="U69" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V69"/>
     </row>
@@ -9405,16 +9403,16 @@
         <v>346</v>
       </c>
       <c r="E70" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F70" t="s">
         <v>774</v>
       </c>
       <c r="G70" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H70" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I70" t="s">
         <v>810</v>
@@ -9453,7 +9451,7 @@
         <v>819</v>
       </c>
       <c r="U70" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V70"/>
     </row>
@@ -9471,16 +9469,16 @@
         <v>821</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F71" t="s">
         <v>774</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H71" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
         <v>822</v>
@@ -9507,7 +9505,7 @@
         <v>828</v>
       </c>
       <c r="Q71" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R71" t="s">
         <v>829</v>
@@ -9519,7 +9517,7 @@
         <v>831</v>
       </c>
       <c r="U71" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V71"/>
     </row>
@@ -9531,22 +9529,22 @@
         <v>832</v>
       </c>
       <c r="C72" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D72" t="s">
         <v>833</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F72" t="s">
         <v>774</v>
       </c>
       <c r="G72" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H72" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I72" t="s">
         <v>834</v>
@@ -9585,7 +9583,7 @@
         <v>843</v>
       </c>
       <c r="U72" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V72"/>
     </row>
@@ -9597,22 +9595,22 @@
         <v>844</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D73" t="s">
         <v>457</v>
       </c>
       <c r="E73" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
         <v>845</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I73" t="s">
         <v>846</v>
@@ -9630,7 +9628,7 @@
         <v>850</v>
       </c>
       <c r="N73" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O73" t="s">
         <v>851</v>
@@ -9639,7 +9637,7 @@
         <v>852</v>
       </c>
       <c r="Q73" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R73" t="s">
         <v>853</v>
@@ -9651,7 +9649,7 @@
         <v>855</v>
       </c>
       <c r="U73" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V73"/>
     </row>
@@ -9663,22 +9661,22 @@
         <v>856</v>
       </c>
       <c r="C74" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
         <v>857</v>
       </c>
       <c r="E74" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F74" t="s">
         <v>845</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I74" t="s">
         <v>858</v>
@@ -9705,7 +9703,7 @@
         <v>864</v>
       </c>
       <c r="Q74" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R74" t="s">
         <v>865</v>
@@ -9717,7 +9715,7 @@
         <v>867</v>
       </c>
       <c r="U74" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V74"/>
     </row>
@@ -9740,7 +9738,7 @@
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I75" t="s">
         <v>870</v>
@@ -9767,13 +9765,13 @@
         <v>876</v>
       </c>
       <c r="Q75" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R75"/>
       <c r="S75"/>
       <c r="T75"/>
       <c r="U75" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V75"/>
     </row>
@@ -9788,19 +9786,19 @@
         <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F76" t="s">
         <v>878</v>
       </c>
       <c r="G76" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H76" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I76" t="s">
         <v>335</v>
@@ -9818,7 +9816,7 @@
         <v>882</v>
       </c>
       <c r="N76" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O76" t="s">
         <v>883</v>
@@ -9827,7 +9825,7 @@
         <v>884</v>
       </c>
       <c r="Q76" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R76" t="s">
         <v>342</v>
@@ -9839,7 +9837,7 @@
         <v>344</v>
       </c>
       <c r="U76" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V76"/>
     </row>
@@ -9851,22 +9849,22 @@
         <v>885</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D77" t="s">
         <v>886</v>
       </c>
       <c r="E77" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F77" t="s">
         <v>887</v>
       </c>
       <c r="G77" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H77" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I77" t="s">
         <v>888</v>
@@ -9882,7 +9880,7 @@
         <v>891</v>
       </c>
       <c r="N77" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O77" t="s">
         <v>892</v>
@@ -9891,7 +9889,7 @@
         <v>893</v>
       </c>
       <c r="Q77" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R77" t="s">
         <v>894</v>
@@ -9903,7 +9901,7 @@
         <v>896</v>
       </c>
       <c r="U77" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V77"/>
     </row>
@@ -9915,22 +9913,22 @@
         <v>897</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D78" t="s">
         <v>898</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F78" t="s">
         <v>899</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I78" t="s">
         <v>900</v>
@@ -9946,7 +9944,7 @@
         <v>903</v>
       </c>
       <c r="N78" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O78" t="s">
         <v>904</v>
@@ -9955,7 +9953,7 @@
         <v>905</v>
       </c>
       <c r="Q78" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R78" t="s">
         <v>782</v>
@@ -9967,7 +9965,7 @@
         <v>784</v>
       </c>
       <c r="U78" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V78"/>
     </row>
@@ -9979,7 +9977,7 @@
         <v>906</v>
       </c>
       <c r="C79" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
@@ -9988,7 +9986,7 @@
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
         <v>908</v>
@@ -10002,7 +10000,7 @@
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O79" t="s">
         <v>911</v>
@@ -10011,7 +10009,7 @@
         <v>912</v>
       </c>
       <c r="Q79" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R79" t="s">
         <v>913</v>
@@ -10023,7 +10021,7 @@
         <v>915</v>
       </c>
       <c r="U79" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V79"/>
     </row>
@@ -10046,7 +10044,7 @@
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I80" t="s">
         <v>918</v>
@@ -10064,7 +10062,7 @@
         <v>922</v>
       </c>
       <c r="N80" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="O80" t="s">
         <v>923</v>
@@ -10073,7 +10071,7 @@
         <v>924</v>
       </c>
       <c r="Q80" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R80" t="s">
         <v>925</v>
@@ -10085,7 +10083,7 @@
         <v>927</v>
       </c>
       <c r="U80" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V80"/>
     </row>
@@ -10108,7 +10106,7 @@
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I81" t="s">
         <v>929</v>
@@ -10135,7 +10133,7 @@
         <v>935</v>
       </c>
       <c r="Q81" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R81" t="s">
         <v>936</v>
@@ -10147,7 +10145,7 @@
         <v>938</v>
       </c>
       <c r="U81" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V81"/>
     </row>
@@ -10171,10 +10169,10 @@
         <v>940</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H82" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I82" t="s">
         <v>941</v>
@@ -10201,7 +10199,7 @@
         <v>947</v>
       </c>
       <c r="Q82" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R82" t="s">
         <v>948</v>
@@ -10213,7 +10211,7 @@
         <v>950</v>
       </c>
       <c r="U82" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V82"/>
     </row>
@@ -10231,16 +10229,16 @@
         <v>952</v>
       </c>
       <c r="E83" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F83" t="s">
         <v>953</v>
       </c>
       <c r="G83" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I83" t="s">
         <v>954</v>
@@ -10267,7 +10265,7 @@
         <v>960</v>
       </c>
       <c r="Q83" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R83" t="s">
         <v>961</v>
@@ -10279,7 +10277,7 @@
         <v>963</v>
       </c>
       <c r="U83" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V83"/>
     </row>
@@ -10291,22 +10289,22 @@
         <v>964</v>
       </c>
       <c r="C84" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D84" t="s">
         <v>965</v>
       </c>
       <c r="E84" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F84" t="s">
         <v>953</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I84" t="s">
         <v>966</v>
@@ -10324,7 +10322,7 @@
         <v>970</v>
       </c>
       <c r="N84" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O84" t="s">
         <v>971</v>
@@ -10333,7 +10331,7 @@
         <v>972</v>
       </c>
       <c r="Q84" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R84" t="s">
         <v>605</v>
@@ -10345,7 +10343,7 @@
         <v>607</v>
       </c>
       <c r="U84" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V84"/>
     </row>
@@ -10363,16 +10361,16 @@
         <v>974</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F85" t="s">
         <v>953</v>
       </c>
       <c r="G85" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H85" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I85" t="s">
         <v>975</v>
@@ -10390,7 +10388,7 @@
         <v>979</v>
       </c>
       <c r="N85" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O85" t="s">
         <v>980</v>
@@ -10411,7 +10409,7 @@
         <v>984</v>
       </c>
       <c r="U85" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V85"/>
     </row>
@@ -10423,22 +10421,22 @@
         <v>985</v>
       </c>
       <c r="C86" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D86" t="s">
         <v>986</v>
       </c>
       <c r="E86" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F86" t="s">
         <v>953</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H86" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I86" t="s">
         <v>987</v>
@@ -10477,7 +10475,7 @@
         <v>525</v>
       </c>
       <c r="U86" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V86"/>
     </row>
@@ -10495,16 +10493,16 @@
         <v>995</v>
       </c>
       <c r="E87" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F87" t="s">
         <v>996</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I87" t="s">
         <v>997</v>
@@ -10531,7 +10529,7 @@
         <v>1003</v>
       </c>
       <c r="Q87" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R87" t="s">
         <v>308</v>
@@ -10543,7 +10541,7 @@
         <v>310</v>
       </c>
       <c r="U87" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V87"/>
     </row>
@@ -10555,22 +10553,22 @@
         <v>1004</v>
       </c>
       <c r="C88" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D88" t="s">
         <v>396</v>
       </c>
       <c r="E88" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F88" t="s">
         <v>1005</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H88" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I88" t="s">
         <v>1006</v>
@@ -10586,7 +10584,7 @@
         <v>1009</v>
       </c>
       <c r="N88" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O88" t="s">
         <v>1010</v>
@@ -10598,16 +10596,16 @@
         <v>224</v>
       </c>
       <c r="R88" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="S88" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="T88" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="U88" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V88"/>
     </row>
@@ -10619,22 +10617,22 @@
         <v>1012</v>
       </c>
       <c r="C89" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D89" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E89" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F89" t="s">
         <v>1013</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I89" t="s">
         <v>1014</v>
@@ -10652,7 +10650,7 @@
         <v>1018</v>
       </c>
       <c r="N89" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O89" t="s">
         <v>1019</v>
@@ -10664,16 +10662,16 @@
         <v>224</v>
       </c>
       <c r="R89" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S89" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="T89" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U89" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V89"/>
     </row>
@@ -10685,22 +10683,22 @@
         <v>1021</v>
       </c>
       <c r="C90" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D90" t="s">
         <v>986</v>
       </c>
       <c r="E90" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
         <v>1022</v>
       </c>
       <c r="G90" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I90" t="s">
         <v>1023</v>
@@ -10716,7 +10714,7 @@
         <v>1026</v>
       </c>
       <c r="N90" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O90" t="s">
         <v>1027</v>
@@ -10725,7 +10723,7 @@
         <v>1028</v>
       </c>
       <c r="Q90" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R90" t="s">
         <v>444</v>
@@ -10737,7 +10735,7 @@
         <v>446</v>
       </c>
       <c r="U90" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V90"/>
     </row>
@@ -10749,22 +10747,22 @@
         <v>1029</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D91" t="s">
         <v>396</v>
       </c>
       <c r="E91" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F91" t="s">
         <v>1022</v>
       </c>
       <c r="G91" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H91" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I91" t="s">
         <v>1030</v>
@@ -10780,7 +10778,7 @@
         <v>1033</v>
       </c>
       <c r="N91" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O91" t="s">
         <v>1034</v>
@@ -10792,16 +10790,16 @@
         <v>224</v>
       </c>
       <c r="R91" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="S91" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="T91" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="U91" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V91"/>
     </row>
@@ -10813,22 +10811,22 @@
         <v>1036</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D92" t="s">
         <v>396</v>
       </c>
       <c r="E92" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F92" t="s">
         <v>1022</v>
       </c>
       <c r="G92" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H92" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I92" t="s">
         <v>1030</v>
@@ -10844,7 +10842,7 @@
         <v>1038</v>
       </c>
       <c r="N92" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O92" t="s">
         <v>1039</v>
@@ -10856,16 +10854,16 @@
         <v>224</v>
       </c>
       <c r="R92" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="S92" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="T92" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="U92" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V92"/>
     </row>
@@ -10877,22 +10875,22 @@
         <v>1041</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D93" t="s">
         <v>396</v>
       </c>
       <c r="E93" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F93" t="s">
         <v>1022</v>
       </c>
       <c r="G93" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H93" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I93" t="s">
         <v>1030</v>
@@ -10908,7 +10906,7 @@
         <v>1043</v>
       </c>
       <c r="N93" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O93" t="s">
         <v>1044</v>
@@ -10920,16 +10918,16 @@
         <v>224</v>
       </c>
       <c r="R93" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="S93" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="T93" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="U93" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V93"/>
     </row>
@@ -10941,22 +10939,22 @@
         <v>1046</v>
       </c>
       <c r="C94" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D94" t="s">
         <v>479</v>
       </c>
       <c r="E94" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F94" t="s">
         <v>1047</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H94" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I94" t="s">
         <v>1048</v>
@@ -10983,7 +10981,7 @@
         <v>1054</v>
       </c>
       <c r="Q94" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R94" t="s">
         <v>1055</v>
@@ -10995,7 +10993,7 @@
         <v>1057</v>
       </c>
       <c r="U94" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V94"/>
     </row>
@@ -11007,22 +11005,22 @@
         <v>1058</v>
       </c>
       <c r="C95" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D95" t="s">
         <v>539</v>
       </c>
       <c r="E95" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F95" t="s">
         <v>1059</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H95" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I95" t="s">
         <v>1060</v>
@@ -11040,7 +11038,7 @@
         <v>1064</v>
       </c>
       <c r="N95" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O95" t="s">
         <v>1065</v>
@@ -11049,19 +11047,19 @@
         <v>1066</v>
       </c>
       <c r="Q95" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R95" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="S95" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="T95" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="U95" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V95"/>
     </row>
@@ -11073,22 +11071,22 @@
         <v>1067</v>
       </c>
       <c r="C96" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D96" t="s">
         <v>1068</v>
       </c>
       <c r="E96" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F96" t="s">
         <v>1059</v>
       </c>
       <c r="G96" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I96" t="s">
         <v>1069</v>
@@ -11115,7 +11113,7 @@
         <v>1075</v>
       </c>
       <c r="Q96" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R96" t="s">
         <v>1076</v>
@@ -11127,7 +11125,7 @@
         <v>1078</v>
       </c>
       <c r="U96" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V96"/>
     </row>
@@ -11139,22 +11137,22 @@
         <v>1079</v>
       </c>
       <c r="C97" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D97" t="s">
         <v>1080</v>
       </c>
       <c r="E97" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F97" t="s">
         <v>1059</v>
       </c>
       <c r="G97" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H97" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I97" t="s">
         <v>1081</v>
@@ -11181,7 +11179,7 @@
         <v>1087</v>
       </c>
       <c r="Q97" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R97" t="s">
         <v>1088</v>
@@ -11193,7 +11191,7 @@
         <v>1090</v>
       </c>
       <c r="U97" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V97"/>
     </row>
@@ -11234,7 +11232,7 @@
         <v>1097</v>
       </c>
       <c r="N98" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="O98" t="s">
         <v>1098</v>
@@ -11243,7 +11241,7 @@
         <v>1099</v>
       </c>
       <c r="Q98" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R98" t="s">
         <v>1100</v>
@@ -11255,7 +11253,7 @@
         <v>1102</v>
       </c>
       <c r="U98" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V98"/>
     </row>
@@ -11273,16 +11271,16 @@
         <v>374</v>
       </c>
       <c r="E99" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
         <v>1092</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I99" t="s">
         <v>1104</v>
@@ -11309,7 +11307,7 @@
         <v>1110</v>
       </c>
       <c r="Q99" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R99" t="s">
         <v>1111</v>
@@ -11321,7 +11319,7 @@
         <v>1113</v>
       </c>
       <c r="U99" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V99"/>
     </row>
@@ -11339,16 +11337,16 @@
         <v>1115</v>
       </c>
       <c r="E100" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F100" t="s">
         <v>1092</v>
       </c>
       <c r="G100" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H100" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I100" t="s">
         <v>1116</v>
@@ -11375,7 +11373,7 @@
         <v>1122</v>
       </c>
       <c r="Q100" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R100" t="s">
         <v>1123</v>
@@ -11387,7 +11385,7 @@
         <v>1125</v>
       </c>
       <c r="U100" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V100"/>
     </row>
@@ -11399,22 +11397,22 @@
         <v>1126</v>
       </c>
       <c r="C101" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D101" t="s">
         <v>1127</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F101" t="s">
         <v>1092</v>
       </c>
       <c r="G101" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H101" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I101" t="s">
         <v>1128</v>
@@ -11432,7 +11430,7 @@
         <v>1132</v>
       </c>
       <c r="N101" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O101" t="s">
         <v>1133</v>
@@ -11453,7 +11451,7 @@
         <v>795</v>
       </c>
       <c r="U101" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V101"/>
     </row>
@@ -11471,16 +11469,16 @@
         <v>527</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F102" t="s">
         <v>1092</v>
       </c>
       <c r="G102" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I102" t="s">
         <v>1136</v>
@@ -11507,7 +11505,7 @@
         <v>1142</v>
       </c>
       <c r="Q102" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R102" t="s">
         <v>1143</v>
@@ -11519,7 +11517,7 @@
         <v>1145</v>
       </c>
       <c r="U102" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V102"/>
     </row>
@@ -11537,16 +11535,16 @@
         <v>479</v>
       </c>
       <c r="E103" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F103" t="s">
         <v>1092</v>
       </c>
       <c r="G103" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H103" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I103" t="s">
         <v>1147</v>
@@ -11564,7 +11562,7 @@
         <v>1151</v>
       </c>
       <c r="N103" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="O103" t="s">
         <v>1152</v>
@@ -11573,7 +11571,7 @@
         <v>1153</v>
       </c>
       <c r="Q103" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R103" t="s">
         <v>1154</v>
@@ -11585,7 +11583,7 @@
         <v>1156</v>
       </c>
       <c r="U103" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V103"/>
     </row>
@@ -11597,22 +11595,22 @@
         <v>1157</v>
       </c>
       <c r="C104" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D104" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E104" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F104" t="s">
         <v>1158</v>
       </c>
       <c r="G104" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I104" t="s">
         <v>1159</v>
@@ -11630,7 +11628,7 @@
         <v>1163</v>
       </c>
       <c r="N104" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O104" t="s">
         <v>1164</v>
@@ -11639,19 +11637,19 @@
         <v>1165</v>
       </c>
       <c r="Q104" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R104" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S104" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="T104" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U104" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V104"/>
     </row>
@@ -11669,16 +11667,16 @@
         <v>346</v>
       </c>
       <c r="E105" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F105" t="s">
         <v>1167</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H105" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I105" t="s">
         <v>1168</v>
@@ -11696,7 +11694,7 @@
         <v>1172</v>
       </c>
       <c r="N105" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O105" t="s">
         <v>1173</v>
@@ -11717,7 +11715,7 @@
         <v>652</v>
       </c>
       <c r="U105" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V105"/>
     </row>
@@ -11729,22 +11727,22 @@
         <v>1175</v>
       </c>
       <c r="C106" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D106" t="s">
         <v>1176</v>
       </c>
       <c r="E106" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F106" t="s">
         <v>1177</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H106" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I106" t="s">
         <v>1178</v>
@@ -11760,7 +11758,7 @@
         <v>1181</v>
       </c>
       <c r="N106" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O106" t="s">
         <v>1182</v>
@@ -11769,7 +11767,7 @@
         <v>1183</v>
       </c>
       <c r="Q106" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R106" t="s">
         <v>650</v>
@@ -11781,7 +11779,7 @@
         <v>652</v>
       </c>
       <c r="U106" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V106"/>
     </row>
@@ -11793,22 +11791,22 @@
         <v>1184</v>
       </c>
       <c r="C107" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D107" t="s">
         <v>1185</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F107" t="s">
         <v>1177</v>
       </c>
       <c r="G107" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I107" t="s">
         <v>1186</v>
@@ -11824,7 +11822,7 @@
         <v>1189</v>
       </c>
       <c r="N107" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O107" t="s">
         <v>1190</v>
@@ -11833,7 +11831,7 @@
         <v>1191</v>
       </c>
       <c r="Q107" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R107" t="s">
         <v>1192</v>
@@ -11845,7 +11843,7 @@
         <v>1194</v>
       </c>
       <c r="U107" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V107"/>
     </row>
@@ -11857,22 +11855,22 @@
         <v>1195</v>
       </c>
       <c r="C108" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D108" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F108" t="s">
         <v>1196</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H108" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I108" t="s">
         <v>1197</v>
@@ -11911,7 +11909,7 @@
         <v>729</v>
       </c>
       <c r="U108" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V108"/>
     </row>
@@ -11923,7 +11921,7 @@
         <v>1204</v>
       </c>
       <c r="C109" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
@@ -11932,7 +11930,7 @@
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I109" t="s">
         <v>1206</v>
@@ -11955,7 +11953,7 @@
         <v>1211</v>
       </c>
       <c r="Q109" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R109" t="s">
         <v>1212</v>
@@ -11967,7 +11965,7 @@
         <v>1214</v>
       </c>
       <c r="U109" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V109"/>
     </row>
@@ -11990,7 +11988,7 @@
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I110" t="s">
         <v>1217</v>
@@ -12008,7 +12006,7 @@
         <v>1221</v>
       </c>
       <c r="N110" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="O110" t="s">
         <v>1222</v>
@@ -12017,7 +12015,7 @@
         <v>1223</v>
       </c>
       <c r="Q110" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R110" t="s">
         <v>1224</v>
@@ -12029,7 +12027,7 @@
         <v>1226</v>
       </c>
       <c r="U110" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V110"/>
     </row>
@@ -12041,22 +12039,22 @@
         <v>1227</v>
       </c>
       <c r="C111" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D111" t="s">
         <v>1228</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F111" t="s">
         <v>1229</v>
       </c>
       <c r="G111" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s">
         <v>1230</v>
@@ -12074,7 +12072,7 @@
         <v>1234</v>
       </c>
       <c r="N111" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O111" t="s">
         <v>1235</v>
@@ -12095,7 +12093,7 @@
         <v>1239</v>
       </c>
       <c r="U111" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V111"/>
     </row>
@@ -12107,22 +12105,22 @@
         <v>1240</v>
       </c>
       <c r="C112" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D112" t="s">
         <v>1241</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F112" t="s">
         <v>1242</v>
       </c>
       <c r="G112" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H112" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I112" t="s">
         <v>1243</v>
@@ -12140,7 +12138,7 @@
         <v>1247</v>
       </c>
       <c r="N112" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O112" t="s">
         <v>1248</v>
@@ -12161,7 +12159,7 @@
         <v>1252</v>
       </c>
       <c r="U112" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V112"/>
     </row>
@@ -12173,22 +12171,22 @@
         <v>1253</v>
       </c>
       <c r="C113" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D113" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F113" t="s">
         <v>1242</v>
       </c>
       <c r="G113" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I113" t="s">
         <v>1254</v>
@@ -12206,7 +12204,7 @@
         <v>1258</v>
       </c>
       <c r="N113" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O113" t="s">
         <v>1259</v>
@@ -12215,7 +12213,7 @@
         <v>1260</v>
       </c>
       <c r="Q113" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R113" t="s">
         <v>605</v>
@@ -12227,7 +12225,7 @@
         <v>607</v>
       </c>
       <c r="U113" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V113"/>
     </row>
@@ -12239,22 +12237,22 @@
         <v>1261</v>
       </c>
       <c r="C114" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D114" t="s">
         <v>267</v>
       </c>
       <c r="E114" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
         <v>1262</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I114" t="s">
         <v>1263</v>
@@ -12281,7 +12279,7 @@
         <v>1269</v>
       </c>
       <c r="Q114" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R114" t="s">
         <v>1100</v>
@@ -12293,7 +12291,7 @@
         <v>1102</v>
       </c>
       <c r="U114" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V114"/>
     </row>
@@ -12311,16 +12309,16 @@
         <v>1271</v>
       </c>
       <c r="E115" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F115" t="s">
         <v>1262</v>
       </c>
       <c r="G115" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H115" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s">
         <v>1272</v>
@@ -12359,7 +12357,7 @@
         <v>1281</v>
       </c>
       <c r="U115" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V115"/>
     </row>
@@ -12383,10 +12381,10 @@
         <v>1262</v>
       </c>
       <c r="G116" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H116" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I116" t="s">
         <v>1285</v>
@@ -12404,7 +12402,7 @@
         <v>1289</v>
       </c>
       <c r="N116" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O116" t="s">
         <v>1290</v>
@@ -12413,7 +12411,7 @@
         <v>1291</v>
       </c>
       <c r="Q116" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R116" t="s">
         <v>1292</v>
@@ -12425,7 +12423,7 @@
         <v>1294</v>
       </c>
       <c r="U116" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V116"/>
     </row>
@@ -12437,22 +12435,22 @@
         <v>1295</v>
       </c>
       <c r="C117" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D117" t="s">
         <v>229</v>
       </c>
       <c r="E117" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F117" t="s">
         <v>1262</v>
       </c>
       <c r="G117" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H117" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I117" t="s">
         <v>1296</v>
@@ -12470,7 +12468,7 @@
         <v>1300</v>
       </c>
       <c r="N117" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O117" t="s">
         <v>1301</v>
@@ -12479,7 +12477,7 @@
         <v>1302</v>
       </c>
       <c r="Q117" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R117" t="s">
         <v>1303</v>
@@ -12491,7 +12489,7 @@
         <v>1305</v>
       </c>
       <c r="U117" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V117"/>
     </row>
@@ -12503,22 +12501,22 @@
         <v>1306</v>
       </c>
       <c r="C118" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D118" t="s">
         <v>1271</v>
       </c>
       <c r="E118" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
         <v>1262</v>
       </c>
       <c r="G118" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H118" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I118" t="s">
         <v>1307</v>
@@ -12536,7 +12534,7 @@
         <v>1311</v>
       </c>
       <c r="N118" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O118" t="s">
         <v>1312</v>
@@ -12545,7 +12543,7 @@
         <v>1313</v>
       </c>
       <c r="Q118" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R118" t="s">
         <v>1314</v>
@@ -12557,7 +12555,7 @@
         <v>1316</v>
       </c>
       <c r="U118" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V118"/>
     </row>
@@ -12569,22 +12567,22 @@
         <v>1317</v>
       </c>
       <c r="C119" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D119" t="s">
         <v>974</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F119" t="s">
         <v>1262</v>
       </c>
       <c r="G119" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H119" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I119" t="s">
         <v>1318</v>
@@ -12602,7 +12600,7 @@
         <v>1322</v>
       </c>
       <c r="N119" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O119" t="s">
         <v>1323</v>
@@ -12611,7 +12609,7 @@
         <v>1324</v>
       </c>
       <c r="Q119" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R119" t="s">
         <v>1325</v>
@@ -12623,7 +12621,7 @@
         <v>1327</v>
       </c>
       <c r="U119" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V119"/>
     </row>
@@ -12635,22 +12633,22 @@
         <v>1328</v>
       </c>
       <c r="C120" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D120" t="s">
         <v>1329</v>
       </c>
       <c r="E120" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
         <v>1330</v>
       </c>
       <c r="G120" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H120" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I120" t="s">
         <v>1331</v>
@@ -12668,7 +12666,7 @@
         <v>1335</v>
       </c>
       <c r="N120" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O120" t="s">
         <v>1336</v>
@@ -12677,7 +12675,7 @@
         <v>1337</v>
       </c>
       <c r="Q120" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R120" t="s">
         <v>650</v>
@@ -12689,7 +12687,7 @@
         <v>652</v>
       </c>
       <c r="U120" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V120"/>
     </row>
@@ -12701,22 +12699,22 @@
         <v>1338</v>
       </c>
       <c r="C121" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D121" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="E121" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F121" t="s">
         <v>1339</v>
       </c>
       <c r="G121" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H121" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I121" t="s">
         <v>1340</v>
@@ -12734,7 +12732,7 @@
         <v>1344</v>
       </c>
       <c r="N121" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O121" t="s">
         <v>1345</v>
@@ -12743,7 +12741,7 @@
         <v>1346</v>
       </c>
       <c r="Q121" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R121" t="s">
         <v>225</v>
@@ -12755,7 +12753,7 @@
         <v>227</v>
       </c>
       <c r="U121" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V121"/>
     </row>
@@ -12767,22 +12765,22 @@
         <v>1347</v>
       </c>
       <c r="C122" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D122" t="s">
         <v>1348</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F122" t="s">
         <v>1349</v>
       </c>
       <c r="G122" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I122" t="s">
         <v>1350</v>
@@ -12800,7 +12798,7 @@
         <v>1354</v>
       </c>
       <c r="N122" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O122" t="s">
         <v>1355</v>
@@ -12809,7 +12807,7 @@
         <v>1356</v>
       </c>
       <c r="Q122" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R122" t="s">
         <v>572</v>
@@ -12821,7 +12819,7 @@
         <v>574</v>
       </c>
       <c r="U122" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V122"/>
     </row>
@@ -12833,22 +12831,22 @@
         <v>1357</v>
       </c>
       <c r="C123" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D123" t="s">
         <v>1358</v>
       </c>
       <c r="E123" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F123" t="s">
         <v>1359</v>
       </c>
       <c r="G123" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H123" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I123" t="s">
         <v>1360</v>
@@ -12875,7 +12873,7 @@
         <v>1366</v>
       </c>
       <c r="Q123" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R123" t="s">
         <v>1123</v>
@@ -12887,7 +12885,7 @@
         <v>1125</v>
       </c>
       <c r="U123" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V123"/>
     </row>
@@ -12899,22 +12897,22 @@
         <v>1367</v>
       </c>
       <c r="C124" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D124" t="s">
         <v>479</v>
       </c>
       <c r="E124" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F124" t="s">
         <v>1359</v>
       </c>
       <c r="G124" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H124" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I124" t="s">
         <v>1368</v>
@@ -12930,7 +12928,7 @@
         <v>1371</v>
       </c>
       <c r="N124" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O124" t="s">
         <v>1372</v>
@@ -12942,16 +12940,16 @@
         <v>224</v>
       </c>
       <c r="R124" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S124" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="T124" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U124" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V124"/>
     </row>
@@ -12963,22 +12961,22 @@
         <v>1374</v>
       </c>
       <c r="C125" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F125" t="s">
         <v>1375</v>
       </c>
       <c r="G125" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s">
         <v>1376</v>
@@ -12994,7 +12992,7 @@
         <v>1379</v>
       </c>
       <c r="N125" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O125" t="s">
         <v>1380</v>
@@ -13003,19 +13001,19 @@
         <v>1381</v>
       </c>
       <c r="Q125" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R125" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S125" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="T125" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="U125" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V125"/>
     </row>
@@ -13037,10 +13035,10 @@
         <v>1384</v>
       </c>
       <c r="G126" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H126" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I126" t="s">
         <v>1385</v>
@@ -13079,7 +13077,7 @@
         <v>1394</v>
       </c>
       <c r="U126" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V126"/>
     </row>
@@ -13091,22 +13089,22 @@
         <v>1395</v>
       </c>
       <c r="C127" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D127" t="s">
         <v>689</v>
       </c>
       <c r="E127" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F127" t="s">
         <v>1396</v>
       </c>
       <c r="G127" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I127" t="s">
         <v>1397</v>
@@ -13124,7 +13122,7 @@
         <v>1401</v>
       </c>
       <c r="N127" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O127" t="s">
         <v>1402</v>
@@ -13133,7 +13131,7 @@
         <v>1403</v>
       </c>
       <c r="Q127" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R127" t="s">
         <v>1404</v>
@@ -13145,7 +13143,7 @@
         <v>1406</v>
       </c>
       <c r="U127" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V127"/>
     </row>
@@ -13163,16 +13161,16 @@
         <v>514</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F128" t="s">
         <v>1396</v>
       </c>
       <c r="G128" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H128" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I128" t="s">
         <v>1408</v>
@@ -13190,7 +13188,7 @@
         <v>1412</v>
       </c>
       <c r="N128" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O128" t="s">
         <v>1413</v>
@@ -13199,7 +13197,7 @@
         <v>1414</v>
       </c>
       <c r="Q128" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R128" t="s">
         <v>1415</v>
@@ -13211,7 +13209,7 @@
         <v>1417</v>
       </c>
       <c r="U128" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V128"/>
     </row>
@@ -13229,13 +13227,13 @@
         <v>1419</v>
       </c>
       <c r="E129" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F129" t="s">
         <v>1420</v>
       </c>
       <c r="G129" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H129" t="s">
         <v>665</v>
@@ -13256,7 +13254,7 @@
         <v>1425</v>
       </c>
       <c r="N129" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O129" t="s">
         <v>1426</v>
@@ -13265,7 +13263,7 @@
         <v>1427</v>
       </c>
       <c r="Q129" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R129" t="s">
         <v>1428</v>
@@ -13277,7 +13275,7 @@
         <v>1430</v>
       </c>
       <c r="U129" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V129"/>
     </row>
@@ -13295,13 +13293,13 @@
         <v>821</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F130" t="s">
         <v>1420</v>
       </c>
       <c r="G130" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H130" t="s">
         <v>665</v>
@@ -13322,7 +13320,7 @@
         <v>1425</v>
       </c>
       <c r="N130" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O130" t="s">
         <v>1432</v>
@@ -13331,7 +13329,7 @@
         <v>1433</v>
       </c>
       <c r="Q130" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R130" t="s">
         <v>1434</v>
@@ -13343,7 +13341,7 @@
         <v>1436</v>
       </c>
       <c r="U130" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V130"/>
     </row>
@@ -13355,22 +13353,22 @@
         <v>1437</v>
       </c>
       <c r="C131" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D131" t="s">
         <v>1438</v>
       </c>
       <c r="E131" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F131" t="s">
         <v>1439</v>
       </c>
       <c r="G131" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H131" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I131" t="s">
         <v>1440</v>
@@ -13388,7 +13386,7 @@
         <v>1444</v>
       </c>
       <c r="N131" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O131" t="s">
         <v>1445</v>
@@ -13397,7 +13395,7 @@
         <v>1446</v>
       </c>
       <c r="Q131" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R131" t="s">
         <v>444</v>
@@ -13409,7 +13407,7 @@
         <v>446</v>
       </c>
       <c r="U131" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V131"/>
     </row>
@@ -13421,22 +13419,22 @@
         <v>1447</v>
       </c>
       <c r="C132" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D132" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F132" t="s">
         <v>1448</v>
       </c>
       <c r="G132" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I132" t="s">
         <v>1449</v>
@@ -13454,7 +13452,7 @@
         <v>1453</v>
       </c>
       <c r="N132" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O132" t="s">
         <v>1454</v>
@@ -13463,7 +13461,7 @@
         <v>1455</v>
       </c>
       <c r="Q132" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R132" t="s">
         <v>1456</v>
@@ -13475,7 +13473,7 @@
         <v>1458</v>
       </c>
       <c r="U132" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V132"/>
     </row>
@@ -13487,22 +13485,22 @@
         <v>1459</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D133" t="s">
         <v>479</v>
       </c>
       <c r="E133" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F133" t="s">
         <v>1460</v>
       </c>
       <c r="G133" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I133" t="s">
         <v>1461</v>
@@ -13520,7 +13518,7 @@
         <v>1465</v>
       </c>
       <c r="N133" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O133" t="s">
         <v>1466</v>
@@ -13529,7 +13527,7 @@
         <v>1467</v>
       </c>
       <c r="Q133" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R133" t="s">
         <v>1468</v>
@@ -13541,7 +13539,7 @@
         <v>1470</v>
       </c>
       <c r="U133" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V133"/>
     </row>
@@ -13553,22 +13551,22 @@
         <v>1471</v>
       </c>
       <c r="C134" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D134" t="s">
         <v>1472</v>
       </c>
       <c r="E134" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F134" t="s">
         <v>1460</v>
       </c>
       <c r="G134" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H134" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I134" t="s">
         <v>1473</v>
@@ -13584,7 +13582,7 @@
         <v>1476</v>
       </c>
       <c r="N134" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O134" t="s">
         <v>1477</v>
@@ -13593,7 +13591,7 @@
         <v>1478</v>
       </c>
       <c r="Q134" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R134" t="s">
         <v>1468</v>
@@ -13605,7 +13603,7 @@
         <v>1470</v>
       </c>
       <c r="U134" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V134"/>
     </row>
@@ -13617,22 +13615,22 @@
         <v>1479</v>
       </c>
       <c r="C135" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D135" t="s">
         <v>1472</v>
       </c>
       <c r="E135" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F135" t="s">
         <v>1460</v>
       </c>
       <c r="G135" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H135" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I135" t="s">
         <v>1480</v>
@@ -13648,7 +13646,7 @@
         <v>1483</v>
       </c>
       <c r="N135" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O135" t="s">
         <v>1484</v>
@@ -13669,7 +13667,7 @@
         <v>1470</v>
       </c>
       <c r="U135" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V135"/>
     </row>
@@ -13681,22 +13679,22 @@
         <v>1486</v>
       </c>
       <c r="C136" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D136" t="s">
         <v>1487</v>
       </c>
       <c r="E136" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F136" t="s">
         <v>1488</v>
       </c>
       <c r="G136" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H136" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I136" t="s">
         <v>1489</v>
@@ -13712,7 +13710,7 @@
         <v>1492</v>
       </c>
       <c r="N136" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O136" t="s">
         <v>1493</v>
@@ -13733,7 +13731,7 @@
         <v>446</v>
       </c>
       <c r="U136" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V136"/>
     </row>
@@ -13745,22 +13743,22 @@
         <v>1495</v>
       </c>
       <c r="C137" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D137" t="s">
         <v>1271</v>
       </c>
       <c r="E137" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="F137" t="s">
         <v>1496</v>
       </c>
       <c r="G137" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H137" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I137" t="s">
         <v>1497</v>
@@ -13776,7 +13774,7 @@
         <v>1500</v>
       </c>
       <c r="N137" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O137" t="s">
         <v>1501</v>
@@ -13785,7 +13783,7 @@
         <v>1502</v>
       </c>
       <c r="Q137" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="R137" t="s">
         <v>1503</v>
@@ -13797,7 +13795,7 @@
         <v>1505</v>
       </c>
       <c r="U137" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V137"/>
     </row>
@@ -13820,7 +13818,7 @@
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I138" t="s">
         <v>1508</v>
@@ -13838,7 +13836,7 @@
         <v>1512</v>
       </c>
       <c r="N138" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O138" t="s">
         <v>1513</v>
@@ -13847,7 +13845,7 @@
         <v>1514</v>
       </c>
       <c r="Q138" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="R138" t="s">
         <v>1515</v>
@@ -13859,7 +13857,7 @@
         <v>1517</v>
       </c>
       <c r="U138" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="V138"/>
     </row>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -263,15 +263,48 @@
     <t xml:space="preserve">Trasporti</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brenzikofer Florence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERT-E-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschulfinanzierung mit alternativen Finanzierungsmodellen sichern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;In diesem Zusammenhang stellen sich folgende Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche der aufgeführten Varianten erachtet der Bundesrat als rechtlich umsetzbar, finanzpolitisch nachhaltig und föderal ausgewogen und wie begründet er seine Einschätzung?&lt;/li&gt;&lt;li&gt;Welche Kombination von Instrumenten erscheint geeignet, um die langfristige Stabilität der Hochschulfinanzierung sicherzustellen?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat im Rahmen des nationalen Finanzausgleichs (NFA) die Möglichkeit, die Unterdeckung zu den Vollkosten für einen Studierenden aus einem Nichthochschulkanton zu einem vereinbarten Teil zur Verrechnung zu bringen? Und zu welchem Teil?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat in einer Fondslösung, gespiesen aus allfälligen Ausschüttungsüberschüssen der&amp;nbsp;Schweizerischen Nationalbank, unter Wahrung der Unabhängigkeit der Nationalbank und der geltenden Ausschüttungsmechanismen, einen möglichen Weg, den es sich zu prüfen lohnt?&amp;nbsp;Falls nein, wieso nicht?&lt;/li&gt;&lt;li&gt;Könnte die Schaffung eines zweckgebundenen Ausgleichs- und Stabilitätsfonds zur Abfederung finanzpolitischer und struktureller Schwankungen in der Hochschulfinanzierung ausgleichend wirken?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanzwesen|Bildung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finances|Éducation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finanze|Formazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3228</t>
   </si>
   <si>
     <t xml:space="preserve">Tuosto Brenda</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">Planification ferroviaire : Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
   </si>
   <si>
@@ -293,39 +326,6 @@
     <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brenzikofer Florence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERT-E-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hochschulfinanzierung mit alternativen Finanzierungsmodellen sichern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;In diesem Zusammenhang stellen sich folgende Fragen:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche der aufgeführten Varianten erachtet der Bundesrat als rechtlich umsetzbar, finanzpolitisch nachhaltig und föderal ausgewogen und wie begründet er seine Einschätzung?&lt;/li&gt;&lt;li&gt;Welche Kombination von Instrumenten erscheint geeignet, um die langfristige Stabilität der Hochschulfinanzierung sicherzustellen?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat im Rahmen des nationalen Finanzausgleichs (NFA) die Möglichkeit, die Unterdeckung zu den Vollkosten für einen Studierenden aus einem Nichthochschulkanton zu einem vereinbarten Teil zur Verrechnung zu bringen? Und zu welchem Teil?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat in einer Fondslösung, gespiesen aus allfälligen Ausschüttungsüberschüssen der&amp;nbsp;Schweizerischen Nationalbank, unter Wahrung der Unabhängigkeit der Nationalbank und der geltenden Ausschüttungsmechanismen, einen möglichen Weg, den es sich zu prüfen lohnt?&amp;nbsp;Falls nein, wieso nicht?&lt;/li&gt;&lt;li&gt;Könnte die Schaffung eines zweckgebundenen Ausgleichs- und Stabilitätsfonds zur Abfederung finanzpolitischer und struktureller Schwankungen in der Hochschulfinanzierung ausgleichend wirken?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanzwesen|Bildung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finances|Éducation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finanze|Formazione</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3120</t>
   </si>
   <si>
@@ -356,6 +356,36 @@
     <t xml:space="preserve">Politica nazionale|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Dänemark lernen: Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imparare dalla Danimarca: espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strafrecht|Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diritto penale|Migrazione</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
@@ -369,36 +399,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraktion der Schweizerischen Volkspartei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von Dänemark lernen: Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imparare dalla Danimarca: espulsione obbligatoria in caso di pene detentive di lunga durata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strafrecht|Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droit pénal|Politique migratoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diritto penale|Migrazione</t>
   </si>
   <si>
     <t xml:space="preserve">26.3099</t>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263228</v>
+        <v>20263323</v>
       </c>
       <c r="B6" t="s">
         <v>83</v>
@@ -5263,50 +5263,50 @@
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s">
         <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s">
         <v>49</v>
       </c>
-      <c r="L6" t="s">
-        <v>87</v>
-      </c>
-      <c r="M6"/>
+      <c r="L6"/>
+      <c r="M6" t="s">
+        <v>89</v>
+      </c>
       <c r="N6" t="s">
         <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q6" t="s">
         <v>54</v>
       </c>
       <c r="R6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -5315,42 +5315,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263323</v>
+        <v>20263228</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s">
         <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" t="s">
         <v>97</v>
-      </c>
-      <c r="J7" t="s">
-        <v>48</v>
       </c>
       <c r="K7" t="s">
         <v>49</v>
       </c>
-      <c r="L7"/>
-      <c r="M7" t="s">
+      <c r="L7" t="s">
         <v>98</v>
       </c>
+      <c r="M7"/>
       <c r="N7" t="s">
         <v>51</v>
       </c>
@@ -5443,62 +5443,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263121</v>
+        <v>20263131</v>
       </c>
       <c r="B9" t="s">
         <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E9"/>
       <c r="F9" t="s">
         <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="J9" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" t="s">
-        <v>116</v>
-      </c>
-      <c r="M9"/>
+        <v>117</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9" t="s">
+        <v>118</v>
+      </c>
       <c r="N9" t="s">
         <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q9" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R9" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="S9" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="T9" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -5507,60 +5505,62 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263131</v>
+        <v>20263121</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10"/>
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
       <c r="F10" t="s">
         <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="K10" t="s">
-        <v>122</v>
-      </c>
-      <c r="L10"/>
-      <c r="M10" t="s">
-        <v>123</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="L10" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10"/>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q10" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="S10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="T10" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5654,7 +5654,7 @@
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
         <v>144</v>
@@ -5895,7 +5895,7 @@
         <v>189</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
         <v>190</v>
@@ -6586,13 +6586,13 @@
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="S26" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="T26" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6743,7 +6743,7 @@
         <v>346</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
         <v>334</v>
@@ -6806,7 +6806,7 @@
         <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
         <v>61</v>
@@ -7016,7 +7016,7 @@
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I33" t="s">
         <v>385</v>
@@ -7410,7 +7410,7 @@
         <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I39" t="s">
         <v>458</v>
@@ -8173,7 +8173,7 @@
         <v>346</v>
       </c>
       <c r="E51" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
         <v>577</v>
@@ -8344,13 +8344,13 @@
         <v>54</v>
       </c>
       <c r="R53" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="S53" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="T53" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="U53" t="s">
         <v>58</v>
@@ -8699,7 +8699,7 @@
         <v>689</v>
       </c>
       <c r="E59" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F59" t="s">
         <v>664</v>
@@ -9403,7 +9403,7 @@
         <v>346</v>
       </c>
       <c r="E70" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F70" t="s">
         <v>774</v>
@@ -10238,7 +10238,7 @@
         <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I83" t="s">
         <v>954</v>
@@ -10436,7 +10436,7 @@
         <v>45</v>
       </c>
       <c r="H86" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I86" t="s">
         <v>987</v>
@@ -10493,7 +10493,7 @@
         <v>995</v>
       </c>
       <c r="E87" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F87" t="s">
         <v>996</v>
@@ -10502,7 +10502,7 @@
         <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I87" t="s">
         <v>997</v>
@@ -10620,10 +10620,10 @@
         <v>72</v>
       </c>
       <c r="D89" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E89" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F89" t="s">
         <v>1013</v>
@@ -11143,7 +11143,7 @@
         <v>1080</v>
       </c>
       <c r="E97" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F97" t="s">
         <v>1059</v>
@@ -11280,7 +11280,7 @@
         <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I99" t="s">
         <v>1104</v>
@@ -11337,7 +11337,7 @@
         <v>1115</v>
       </c>
       <c r="E100" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F100" t="s">
         <v>1092</v>
@@ -11667,7 +11667,7 @@
         <v>346</v>
       </c>
       <c r="E105" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F105" t="s">
         <v>1167</v>
@@ -11858,7 +11858,7 @@
         <v>130</v>
       </c>
       <c r="D108" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E108" t="s">
         <v>61</v>
@@ -12384,7 +12384,7 @@
         <v>45</v>
       </c>
       <c r="H116" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I116" t="s">
         <v>1285</v>
@@ -12964,7 +12964,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E125" t="s">
         <v>61</v>
@@ -13095,7 +13095,7 @@
         <v>689</v>
       </c>
       <c r="E127" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F127" t="s">
         <v>1396</v>
@@ -13368,7 +13368,7 @@
         <v>45</v>
       </c>
       <c r="H131" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I131" t="s">
         <v>1440</v>
@@ -13557,7 +13557,7 @@
         <v>1472</v>
       </c>
       <c r="E134" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F134" t="s">
         <v>1460</v>
@@ -13621,7 +13621,7 @@
         <v>1472</v>
       </c>
       <c r="E135" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F135" t="s">
         <v>1460</v>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I138" t="s">
         <v>1508</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -263,6 +263,36 @@
     <t xml:space="preserve">Trasporti</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuosto Brenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planification ferroviaire : Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3323</t>
   </si>
   <si>
@@ -272,9 +302,6 @@
     <t xml:space="preserve">VERT-E-S</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">WBF</t>
   </si>
   <si>
@@ -299,33 +326,6 @@
     <t xml:space="preserve">Finanze|Formazione</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuosto Brenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planification ferroviaire : Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3120</t>
   </si>
   <si>
@@ -356,6 +356,21 @@
     <t xml:space="preserve">Politica nazionale|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les paramètres du programme « Transports ’45 »dans lequel le projet d’amélioration structurelle de la liaison routière Delémont- Bâle a été retenu. Mais, le report au-delà de 2055 des projets routiers le long de la N18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufen (horizon 2055) – suscite une forte incompréhension de la part des élus, des populations et des milieux économiques en particulier. Ce renoncement de fait à une meilleure accessibilité et à de réelles perspectives de développement économique contredit directement les résultats de l’étude de corridor N18 menée sous la direction de l’OFROU selon les méthodes les plus récentes. C’est aussi une question de crédibilité des institutions par un respect de la cohérence des politiques publiques.&lt;/p&gt;&lt;p&gt;La N18 est un élément essentiel du réseau routier national : elle relie l’agglomération bâloise à l’Arc lémanique et unit deux espaces culturels et&amp;nbsp;économiques majeurs. Elle connecte&amp;nbsp;également le Laufonnais, région dynamique, ainsi que la capitale cantonale Delémont au réseau à haute performance. Elle contribue ainsi&amp;nbsp;à la cohésion nationale et au rapprochement des communautés linguistiques.&lt;/p&gt;&lt;p&gt;Sous l’effet de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, avec l’une des plus fortes densités de bouchons du pays. De plus, le trafic actuel porte atteinte à la qualité de vie dans les centres et compromet la sécurité du trafic motorisé et cycliste. Une modernisation rapide du corridor est donc prioritaire.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il la nécessité d’éliminer les goulets d’étranglement sur la N18 entre Angenstein et Delémont ?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel du Muggenberg comme une mesure durable pour améliorer la sécurité au point noir d’Angenstein ?&lt;/li&gt;&lt;li&gt;Comment apprécie-t-il l’utilité des projets recommandés dans l’étude de corridor N18 (tunnel du Muggenberg, contournements Laufen–Zwingen et Delémont, décharge de Laufen) pour renforcer la connexion des entreprises de la région Laufonnais–Thierstein–Delémont ?&lt;/li&gt;&lt;li&gt;Estime-t-il que les contournements Laufen–Zwingen et Delémont constituent des mesures appropriées pour soulager les zones habitées concernées ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3131</t>
   </si>
   <si>
@@ -384,21 +399,6 @@
   </si>
   <si>
     <t xml:space="preserve">Diritto penale|Migrazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les paramètres du programme « Transports ’45 »dans lequel le projet d’amélioration structurelle de la liaison routière Delémont- Bâle a été retenu. Mais, le report au-delà de 2055 des projets routiers le long de la N18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufen (horizon 2055) – suscite une forte incompréhension de la part des élus, des populations et des milieux économiques en particulier. Ce renoncement de fait à une meilleure accessibilité et à de réelles perspectives de développement économique contredit directement les résultats de l’étude de corridor N18 menée sous la direction de l’OFROU selon les méthodes les plus récentes. C’est aussi une question de crédibilité des institutions par un respect de la cohérence des politiques publiques.&lt;/p&gt;&lt;p&gt;La N18 est un élément essentiel du réseau routier national : elle relie l’agglomération bâloise à l’Arc lémanique et unit deux espaces culturels et&amp;nbsp;économiques majeurs. Elle connecte&amp;nbsp;également le Laufonnais, région dynamique, ainsi que la capitale cantonale Delémont au réseau à haute performance. Elle contribue ainsi&amp;nbsp;à la cohésion nationale et au rapprochement des communautés linguistiques.&lt;/p&gt;&lt;p&gt;Sous l’effet de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, avec l’une des plus fortes densités de bouchons du pays. De plus, le trafic actuel porte atteinte à la qualité de vie dans les centres et compromet la sécurité du trafic motorisé et cycliste. Une modernisation rapide du corridor est donc prioritaire.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il la nécessité d’éliminer les goulets d’étranglement sur la N18 entre Angenstein et Delémont ?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel du Muggenberg comme une mesure durable pour améliorer la sécurité au point noir d’Angenstein ?&lt;/li&gt;&lt;li&gt;Comment apprécie-t-il l’utilité des projets recommandés dans l’étude de corridor N18 (tunnel du Muggenberg, contournements Laufen–Zwingen et Delémont, décharge de Laufen) pour renforcer la connexion des entreprises de la région Laufonnais–Thierstein–Delémont ?&lt;/li&gt;&lt;li&gt;Estime-t-il que les contournements Laufen–Zwingen et Delémont constituent des mesures appropriées pour soulager les zones habitées concernées ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
   </si>
   <si>
     <t xml:space="preserve">26.3099</t>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263323</v>
+        <v>20263228</v>
       </c>
       <c r="B6" t="s">
         <v>83</v>
@@ -5263,50 +5263,50 @@
         <v>84</v>
       </c>
       <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
         <v>85</v>
-      </c>
-      <c r="F6" t="s">
-        <v>86</v>
       </c>
       <c r="G6" t="s">
         <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="K6" t="s">
         <v>49</v>
       </c>
-      <c r="L6"/>
-      <c r="M6" t="s">
-        <v>89</v>
-      </c>
+      <c r="L6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M6"/>
       <c r="N6" t="s">
         <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="s">
         <v>54</v>
       </c>
       <c r="R6" t="s">
+        <v>90</v>
+      </c>
+      <c r="S6" t="s">
+        <v>91</v>
+      </c>
+      <c r="T6" t="s">
         <v>92</v>
-      </c>
-      <c r="S6" t="s">
-        <v>93</v>
-      </c>
-      <c r="T6" t="s">
-        <v>94</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -5315,42 +5315,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263228</v>
+        <v>20263323</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
         <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J7" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s">
         <v>49</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7"/>
+      <c r="M7" t="s">
         <v>98</v>
       </c>
-      <c r="M7"/>
       <c r="N7" t="s">
         <v>51</v>
       </c>
@@ -5443,60 +5443,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263131</v>
+        <v>20263121</v>
       </c>
       <c r="B9" t="s">
         <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9"/>
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
       <c r="F9" t="s">
         <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s">
+        <v>115</v>
+      </c>
+      <c r="K9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" t="s">
         <v>116</v>
       </c>
-      <c r="J9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" t="s">
-        <v>117</v>
-      </c>
-      <c r="L9"/>
-      <c r="M9" t="s">
-        <v>118</v>
-      </c>
+      <c r="M9"/>
       <c r="N9" t="s">
         <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="S9" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="T9" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -5505,62 +5507,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263121</v>
+        <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E10"/>
       <c r="F10" t="s">
         <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="J10" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" t="s">
-        <v>126</v>
-      </c>
-      <c r="M10"/>
+        <v>122</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>123</v>
+      </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
+        <v>124</v>
+      </c>
+      <c r="P10" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" t="s">
+        <v>126</v>
+      </c>
+      <c r="S10" t="s">
         <v>127</v>
       </c>
-      <c r="P10" t="s">
+      <c r="T10" t="s">
         <v>128</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>37</v>
-      </c>
-      <c r="R10" t="s">
-        <v>101</v>
-      </c>
-      <c r="S10" t="s">
-        <v>102</v>
-      </c>
-      <c r="T10" t="s">
-        <v>103</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5654,7 +5654,7 @@
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I12" t="s">
         <v>144</v>
@@ -5895,7 +5895,7 @@
         <v>189</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
         <v>190</v>
@@ -6586,13 +6586,13 @@
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="S26" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="T26" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6743,7 +6743,7 @@
         <v>346</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s">
         <v>334</v>
@@ -6806,7 +6806,7 @@
         <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
         <v>61</v>
@@ -7016,7 +7016,7 @@
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
         <v>385</v>
@@ -7410,7 +7410,7 @@
         <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s">
         <v>458</v>
@@ -8173,7 +8173,7 @@
         <v>346</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F51" t="s">
         <v>577</v>
@@ -8344,13 +8344,13 @@
         <v>54</v>
       </c>
       <c r="R53" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="S53" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="T53" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="U53" t="s">
         <v>58</v>
@@ -8699,7 +8699,7 @@
         <v>689</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F59" t="s">
         <v>664</v>
@@ -9403,7 +9403,7 @@
         <v>346</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F70" t="s">
         <v>774</v>
@@ -10238,7 +10238,7 @@
         <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I83" t="s">
         <v>954</v>
@@ -10436,7 +10436,7 @@
         <v>45</v>
       </c>
       <c r="H86" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I86" t="s">
         <v>987</v>
@@ -10493,7 +10493,7 @@
         <v>995</v>
       </c>
       <c r="E87" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F87" t="s">
         <v>996</v>
@@ -10502,7 +10502,7 @@
         <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I87" t="s">
         <v>997</v>
@@ -10620,10 +10620,10 @@
         <v>72</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E89" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F89" t="s">
         <v>1013</v>
@@ -11143,7 +11143,7 @@
         <v>1080</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F97" t="s">
         <v>1059</v>
@@ -11280,7 +11280,7 @@
         <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I99" t="s">
         <v>1104</v>
@@ -11337,7 +11337,7 @@
         <v>1115</v>
       </c>
       <c r="E100" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F100" t="s">
         <v>1092</v>
@@ -11667,7 +11667,7 @@
         <v>346</v>
       </c>
       <c r="E105" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F105" t="s">
         <v>1167</v>
@@ -11858,7 +11858,7 @@
         <v>130</v>
       </c>
       <c r="D108" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E108" t="s">
         <v>61</v>
@@ -12384,7 +12384,7 @@
         <v>45</v>
       </c>
       <c r="H116" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I116" t="s">
         <v>1285</v>
@@ -12964,7 +12964,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E125" t="s">
         <v>61</v>
@@ -13095,7 +13095,7 @@
         <v>689</v>
       </c>
       <c r="E127" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F127" t="s">
         <v>1396</v>
@@ -13368,7 +13368,7 @@
         <v>45</v>
       </c>
       <c r="H131" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I131" t="s">
         <v>1440</v>
@@ -13557,7 +13557,7 @@
         <v>1472</v>
       </c>
       <c r="E134" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F134" t="s">
         <v>1460</v>
@@ -13621,7 +13621,7 @@
         <v>1472</v>
       </c>
       <c r="E135" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F135" t="s">
         <v>1460</v>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I138" t="s">
         <v>1508</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="1537">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -422,7 +422,13 @@
     <t xml:space="preserve">Von Dänemark lernen: Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein</t>
   </si>
   <si>
+    <t xml:space="preserve">Inspirons-nous du Danemark. Rendons réellement obligatoire l’expulsion en cas de peine privative de liberté de longue durée</t>
+  </si>
+  <si>
     <t xml:space="preserve">Imparare dalla Danimarca: espulsione obbligatoria in caso di pene detentive di lunga durata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter les modifications législatives nécessaires pour que lorsqu’un délinquant étranger est condamné à une peine privative de liberté de longue durée (un an au moins), que cette peine soit ferme ou assortie d’un sursis ou d’un sursis partiel, une expulsion soit obligatoirement ordonnée et exécutée.&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Gesetzesanpassungen vorzulegen, so dass für kriminelle Ausländer bei einer längerfristigen Freiheitsstrafe ab einem Jahr – unabhängig davon, ob diese unbedingt, teilbedingt oder bedingt ausfällt – in jedem Fall zwingend eine Landesverweisung angeordnet und vollzogen werden muss.&amp;nbsp;&lt;/p&gt;</t>
@@ -5593,35 +5599,37 @@
         <v>135</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="K10" t="s">
-        <v>136</v>
-      </c>
-      <c r="L10"/>
+        <v>137</v>
+      </c>
+      <c r="L10" t="s">
+        <v>138</v>
+      </c>
       <c r="M10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N10" t="s">
         <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q10" t="s">
         <v>54</v>
       </c>
       <c r="R10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="S10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="T10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -5633,10 +5641,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5645,7 +5653,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5654,40 +5662,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s">
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="S11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -5699,19 +5707,19 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
@@ -5720,38 +5728,38 @@
         <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="S12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="T12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -5763,19 +5771,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5784,28 +5792,28 @@
         <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N13" t="s">
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q13" t="s">
         <v>54</v>
@@ -5829,19 +5837,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5850,38 +5858,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="S14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -5893,51 +5901,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -5949,19 +5957,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5970,38 +5978,38 @@
         <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q16" t="s">
         <v>54</v>
       </c>
       <c r="R16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="S16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="T16" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -6013,17 +6021,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6032,40 +6040,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q17" t="s">
         <v>54</v>
       </c>
       <c r="R17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S17" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="T17" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -6077,16 +6085,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6098,40 +6106,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R18" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T18" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -6143,13 +6151,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E19" t="s">
         <v>75</v>
@@ -6164,40 +6172,40 @@
         <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O19" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="S19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="T19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -6209,7 +6217,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6221,49 +6229,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O20" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="T20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -6275,10 +6283,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6287,7 +6295,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6296,40 +6304,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="S21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -6341,19 +6349,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6362,40 +6370,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O22" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P22" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R22" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="S22" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="T22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="U22" t="s">
         <v>58</v>
@@ -6407,7 +6415,7 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -6419,7 +6427,7 @@
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6428,40 +6436,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M23" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N23" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="T23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="U23" t="s">
         <v>58</v>
@@ -6473,19 +6481,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
         <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6494,40 +6502,40 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P24" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="S24" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="T24" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="U24" t="s">
         <v>58</v>
@@ -6539,59 +6547,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O25" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P25" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q25" t="s">
         <v>54</v>
       </c>
       <c r="R25" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="S25" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T25" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="U25" t="s">
         <v>58</v>
@@ -6603,19 +6611,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6624,38 +6632,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J26" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M26" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O26" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P26" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q26" t="s">
         <v>54</v>
       </c>
       <c r="R26" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="S26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="T26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="U26" t="s">
         <v>58</v>
@@ -6667,17 +6675,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6686,40 +6694,40 @@
         <v>62</v>
       </c>
       <c r="I27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J27" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K27" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L27" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M27" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N27" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P27" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q27" t="s">
         <v>54</v>
       </c>
       <c r="R27" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="S27" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="T27" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="U27" t="s">
         <v>58</v>
@@ -6731,19 +6739,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E28" t="s">
         <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6752,40 +6760,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K28" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L28" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O28" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q28" t="s">
         <v>54</v>
       </c>
       <c r="R28" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="S28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T28" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="U28" t="s">
         <v>58</v>
@@ -6797,19 +6805,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6818,40 +6826,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J29" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K29" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L29" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M29" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N29" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O29" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P29" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q29" t="s">
         <v>54</v>
       </c>
       <c r="R29" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T29" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U29" t="s">
         <v>58</v>
@@ -6863,7 +6871,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
@@ -6875,7 +6883,7 @@
         <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6884,31 +6892,31 @@
         <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J30" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K30" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L30" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M30" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N30" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O30" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P30" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R30" t="s">
         <v>83</v>
@@ -6929,7 +6937,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6941,7 +6949,7 @@
         <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6950,40 +6958,40 @@
         <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="S31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="T31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="U31" t="s">
         <v>58</v>
@@ -6995,19 +7003,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -7016,40 +7024,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K32" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M32" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P32" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R32" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S32" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T32" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U32" t="s">
         <v>58</v>
@@ -7061,7 +7069,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -7073,7 +7081,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -7082,40 +7090,40 @@
         <v>101</v>
       </c>
       <c r="I33" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L33" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M33" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O33" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P33" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R33" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="S33" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="T33" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="U33" t="s">
         <v>58</v>
@@ -7127,61 +7135,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C34" t="s">
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E34" t="s">
         <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I34" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J34" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K34" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L34" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M34" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O34" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P34" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R34" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="S34" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="T34" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="U34" t="s">
         <v>58</v>
@@ -7193,19 +7201,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7214,40 +7222,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J35" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K35" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L35" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M35" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N35" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O35" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="P35" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R35" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="S35" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="T35" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="U35" t="s">
         <v>58</v>
@@ -7259,10 +7267,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C36" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D36" t="s">
         <v>74</v>
@@ -7271,7 +7279,7 @@
         <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7280,40 +7288,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J36" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K36" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M36" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N36" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O36" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P36" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="S36" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="T36" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="U36" t="s">
         <v>58</v>
@@ -7325,19 +7333,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7346,40 +7354,40 @@
         <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J37" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K37" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L37" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M37" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N37" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O37" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P37" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q37" t="s">
         <v>54</v>
       </c>
       <c r="R37" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="S37" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="T37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U37" t="s">
         <v>58</v>
@@ -7391,19 +7399,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E38" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7412,38 +7420,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J38" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M38" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O38" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="P38" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Q38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S38" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T38" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U38" t="s">
         <v>58</v>
@@ -7455,19 +7463,19 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D39" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
@@ -7476,38 +7484,38 @@
         <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J39" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M39" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N39" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O39" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P39" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Q39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R39" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="S39" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="T39" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="U39" t="s">
         <v>58</v>
@@ -7519,19 +7527,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D40" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E40" t="s">
         <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7540,38 +7548,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J40" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M40" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N40" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O40" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P40" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Q40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R40" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="S40" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="T40" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="U40" t="s">
         <v>58</v>
@@ -7583,61 +7591,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C41" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E41" t="s">
         <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I41" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J41" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K41" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L41" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M41" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N41" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O41" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="P41" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Q41" t="s">
         <v>54</v>
       </c>
       <c r="R41" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="S41" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="T41" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="U41" t="s">
         <v>58</v>
@@ -7649,59 +7657,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E42" t="s">
         <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I42" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J42" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M42" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N42" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O42" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P42" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Q42" t="s">
         <v>54</v>
       </c>
       <c r="R42" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="S42" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="T42" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="U42" t="s">
         <v>58</v>
@@ -7713,45 +7721,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C43" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D43" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I43" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="J43" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K43" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L43" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M43" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N43" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O43" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="P43" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="Q43" t="s">
         <v>54</v>
@@ -7769,19 +7777,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7790,40 +7798,40 @@
         <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J44" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K44" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L44" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M44" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N44" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O44" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P44" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="Q44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R44" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="S44" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="T44" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="U44" t="s">
         <v>58</v>
@@ -7835,19 +7843,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7856,40 +7864,40 @@
         <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J45" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K45" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L45" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M45" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N45" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O45" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="P45" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="Q45" t="s">
         <v>54</v>
       </c>
       <c r="R45" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="S45" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="T45" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="U45" t="s">
         <v>58</v>
@@ -7901,19 +7909,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7922,40 +7930,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J46" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K46" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L46" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M46" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N46" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O46" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P46" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="Q46" t="s">
         <v>54</v>
       </c>
       <c r="R46" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="S46" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="T46" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="U46" t="s">
         <v>58</v>
@@ -7967,7 +7975,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7977,7 +7985,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -7986,40 +7994,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J47" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K47" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L47" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M47" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N47" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O47" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P47" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Q47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R47" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="S47" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="T47" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U47" t="s">
         <v>58</v>
@@ -8031,19 +8039,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C48" t="s">
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E48" t="s">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8052,40 +8060,40 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J48" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K48" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L48" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M48" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O48" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P48" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Q48" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R48" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="S48" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="T48" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="U48" t="s">
         <v>58</v>
@@ -8097,19 +8105,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C49" t="s">
         <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8118,31 +8126,31 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J49" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K49" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L49" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M49" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O49" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="P49" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Q49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R49" t="s">
         <v>83</v>
@@ -8163,17 +8171,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8182,40 +8190,40 @@
         <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L50" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M50" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N50" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O50" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P50" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="Q50" t="s">
         <v>54</v>
       </c>
       <c r="R50" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="S50" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="T50" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="U50" t="s">
         <v>58</v>
@@ -8227,19 +8235,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C51" t="s">
         <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E51" t="s">
         <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8248,40 +8256,40 @@
         <v>76</v>
       </c>
       <c r="I51" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="J51" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="K51" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L51" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M51" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N51" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O51" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P51" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Q51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R51" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="S51" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="T51" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="U51" t="s">
         <v>58</v>
@@ -8293,19 +8301,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C52" t="s">
         <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F52" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8314,40 +8322,40 @@
         <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J52" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K52" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L52" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M52" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N52" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O52" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P52" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="Q52" t="s">
         <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="S52" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="T52" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="U52" t="s">
         <v>58</v>
@@ -8359,19 +8367,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E53" t="s">
         <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8380,28 +8388,28 @@
         <v>76</v>
       </c>
       <c r="I53" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="J53" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K53" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L53" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M53" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N53" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O53" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="P53" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="Q53" t="s">
         <v>54</v>
@@ -8425,19 +8433,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E54" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F54" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8446,40 +8454,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J54" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K54" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L54" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M54" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N54" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O54" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="P54" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="Q54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R54" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="S54" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="T54" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="U54" t="s">
         <v>58</v>
@@ -8491,19 +8499,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E55" t="s">
         <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8512,40 +8520,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="J55" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K55" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L55" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M55" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O55" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="P55" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="Q55" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R55" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="S55" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="T55" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="U55" t="s">
         <v>58</v>
@@ -8557,17 +8565,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8576,40 +8584,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="J56" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K56" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L56" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M56" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N56" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O56" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="P56" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Q56" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R56" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="S56" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="T56" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="U56" t="s">
         <v>58</v>
@@ -8621,61 +8629,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I57" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J57" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K57" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L57" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M57" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N57" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O57" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="P57" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="Q57" t="s">
         <v>54</v>
       </c>
       <c r="R57" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="S57" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="T57" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U57" t="s">
         <v>58</v>
@@ -8687,19 +8695,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8708,40 +8716,40 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J58" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="K58" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="L58" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M58" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N58" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O58" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="P58" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="Q58" t="s">
         <v>54</v>
       </c>
       <c r="R58" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="S58" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="T58" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="U58" t="s">
         <v>58</v>
@@ -8753,19 +8761,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E59" t="s">
         <v>100</v>
       </c>
       <c r="F59" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8774,40 +8782,40 @@
         <v>76</v>
       </c>
       <c r="I59" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="J59" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K59" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L59" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M59" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N59" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O59" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="P59" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="Q59" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R59" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="S59" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="T59" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U59" t="s">
         <v>58</v>
@@ -8819,19 +8827,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8840,40 +8848,40 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="J60" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="K60" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="L60" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M60" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N60" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O60" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P60" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="Q60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R60" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="S60" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="T60" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="U60" t="s">
         <v>58</v>
@@ -8885,7 +8893,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8897,7 +8905,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8906,40 +8914,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J61" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="K61" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="L61" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="M61" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="N61" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O61" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="P61" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="Q61" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R61" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="S61" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="T61" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="U61" t="s">
         <v>58</v>
@@ -8951,19 +8959,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8972,40 +8980,40 @@
         <v>76</v>
       </c>
       <c r="I62" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="J62" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K62" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="L62" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="M62" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="N62" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O62" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="P62" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="Q62" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R62" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="S62" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="T62" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="U62" t="s">
         <v>58</v>
@@ -9017,19 +9025,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9038,40 +9046,40 @@
         <v>62</v>
       </c>
       <c r="I63" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="J63" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="K63" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="L63" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="M63" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="N63" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O63" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="P63" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="Q63" t="s">
         <v>54</v>
       </c>
       <c r="R63" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="S63" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="T63" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="U63" t="s">
         <v>58</v>
@@ -9083,45 +9091,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C64" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D64" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J64" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="K64" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="L64" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="M64" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="P64" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="Q64" t="s">
         <v>54</v>
@@ -9139,45 +9147,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C65" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D65" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="J65" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K65" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L65" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M65" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="N65" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="O65" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="P65" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="Q65" t="s">
         <v>54</v>
@@ -9195,17 +9203,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C66" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D66" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9214,40 +9222,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="J66" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="K66" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="L66" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="M66" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="P66" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="Q66" t="s">
         <v>54</v>
       </c>
       <c r="R66" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="S66" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="T66" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="U66" t="s">
         <v>58</v>
@@ -9259,19 +9267,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C67" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D67" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9280,40 +9288,40 @@
         <v>76</v>
       </c>
       <c r="I67" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="J67" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="K67" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="L67" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="M67" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="N67" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O67" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="P67" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="Q67" t="s">
         <v>54</v>
       </c>
       <c r="R67" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="S67" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="T67" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="U67" t="s">
         <v>58</v>
@@ -9325,19 +9333,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C68" t="s">
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E68" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F68" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9346,40 +9354,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="J68" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="K68" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="L68" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="M68" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="N68" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O68" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="P68" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="Q68" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R68" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="S68" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="T68" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="U68" t="s">
         <v>58</v>
@@ -9391,61 +9399,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C69" t="s">
         <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="I69" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J69" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="K69" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L69" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="M69" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="N69" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O69" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="P69" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="Q69" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R69" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="S69" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="T69" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="U69" t="s">
         <v>58</v>
@@ -9457,19 +9465,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E70" t="s">
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9478,40 +9486,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J70" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="K70" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="L70" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="M70" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="N70" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O70" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="P70" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="Q70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R70" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="S70" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="T70" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="U70" t="s">
         <v>58</v>
@@ -9523,19 +9531,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9544,40 +9552,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="J71" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="K71" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="L71" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="M71" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N71" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O71" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="P71" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="Q71" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R71" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="S71" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="T71" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="U71" t="s">
         <v>58</v>
@@ -9589,19 +9597,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9610,40 +9618,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="J72" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="K72" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="L72" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="M72" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="N72" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O72" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="P72" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="Q72" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R72" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="S72" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="T72" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="U72" t="s">
         <v>58</v>
@@ -9655,19 +9663,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D73" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9676,40 +9684,40 @@
         <v>76</v>
       </c>
       <c r="I73" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="J73" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="K73" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="L73" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="M73" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="N73" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O73" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="P73" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="Q73" t="s">
         <v>54</v>
       </c>
       <c r="R73" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="S73" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="T73" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="U73" t="s">
         <v>58</v>
@@ -9721,19 +9729,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9742,40 +9750,40 @@
         <v>76</v>
       </c>
       <c r="I74" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="J74" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K74" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="L74" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="M74" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="N74" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O74" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="P74" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="Q74" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R74" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="S74" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="T74" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="U74" t="s">
         <v>58</v>
@@ -9787,45 +9795,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C75" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D75" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>76</v>
       </c>
       <c r="I75" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="J75" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="K75" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="L75" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="M75" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="N75" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="O75" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="P75" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="Q75" t="s">
         <v>54</v>
@@ -9843,7 +9851,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9855,7 +9863,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9864,40 +9872,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J76" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="K76" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="L76" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="M76" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="N76" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O76" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="P76" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="Q76" t="s">
         <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="S76" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T76" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="U76" t="s">
         <v>58</v>
@@ -9909,19 +9917,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D77" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E77" t="s">
         <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9930,38 +9938,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J77" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="M77" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="N77" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O77" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="P77" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="Q77" t="s">
         <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="S77" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="T77" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="U77" t="s">
         <v>58</v>
@@ -9973,19 +9981,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D78" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -9994,38 +10002,38 @@
         <v>76</v>
       </c>
       <c r="I78" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="J78" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="M78" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="N78" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O78" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="P78" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="Q78" t="s">
         <v>54</v>
       </c>
       <c r="R78" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="S78" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="T78" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="U78" t="s">
         <v>58</v>
@@ -10037,51 +10045,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C79" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="J79" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="K79" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O79" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="P79" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="S79" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="T79" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="U79" t="s">
         <v>58</v>
@@ -10093,57 +10101,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C80" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D80" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="J80" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="K80" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L80" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="M80" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="P80" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="Q80" t="s">
         <v>54</v>
       </c>
       <c r="R80" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="S80" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="T80" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="U80" t="s">
         <v>58</v>
@@ -10155,57 +10163,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C81" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D81" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="J81" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="K81" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="L81" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="M81" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="N81" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="O81" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="P81" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="S81" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="T81" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="U81" t="s">
         <v>58</v>
@@ -10217,19 +10225,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E82" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F82" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10238,40 +10246,40 @@
         <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="J82" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="K82" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="L82" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="M82" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="N82" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O82" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="P82" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="Q82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R82" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="S82" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="T82" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="U82" t="s">
         <v>58</v>
@@ -10283,19 +10291,19 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
@@ -10304,40 +10312,40 @@
         <v>101</v>
       </c>
       <c r="I83" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="J83" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="K83" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L83" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="M83" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="N83" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O83" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="P83" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="Q83" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R83" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="S83" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="T83" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="U83" t="s">
         <v>58</v>
@@ -10349,19 +10357,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="E84" t="s">
         <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10370,40 +10378,40 @@
         <v>76</v>
       </c>
       <c r="I84" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="J84" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="K84" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="L84" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="M84" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="N84" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O84" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="P84" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="Q84" t="s">
         <v>54</v>
       </c>
       <c r="R84" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="S84" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="T84" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="U84" t="s">
         <v>58</v>
@@ -10415,19 +10423,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10436,40 +10444,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="J85" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="K85" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="L85" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="M85" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="N85" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O85" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="P85" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="Q85" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R85" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="S85" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="T85" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="U85" t="s">
         <v>58</v>
@@ -10481,19 +10489,19 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
@@ -10502,40 +10510,40 @@
         <v>101</v>
       </c>
       <c r="I86" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="J86" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="K86" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="L86" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="M86" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="N86" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O86" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="P86" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q86" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R86" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="S86" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="T86" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="U86" t="s">
         <v>58</v>
@@ -10547,19 +10555,19 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="E87" t="s">
         <v>100</v>
       </c>
       <c r="F87" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
@@ -10568,40 +10576,40 @@
         <v>101</v>
       </c>
       <c r="I87" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="J87" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="K87" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="L87" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="M87" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="N87" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O87" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="P87" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="Q87" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R87" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="S87" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T87" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="U87" t="s">
         <v>58</v>
@@ -10613,19 +10621,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C88" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D88" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E88" t="s">
         <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10634,38 +10642,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="J88" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="M88" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="N88" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O88" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="P88" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="Q88" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R88" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S88" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T88" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U88" t="s">
         <v>58</v>
@@ -10677,7 +10685,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
@@ -10689,7 +10697,7 @@
         <v>100</v>
       </c>
       <c r="F89" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10698,31 +10706,31 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="J89" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="K89" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="L89" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="M89" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="N89" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O89" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="P89" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="Q89" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R89" t="s">
         <v>83</v>
@@ -10743,19 +10751,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C90" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D90" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10764,38 +10772,38 @@
         <v>76</v>
       </c>
       <c r="I90" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J90" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="M90" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N90" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O90" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="P90" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="Q90" t="s">
         <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="S90" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="T90" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U90" t="s">
         <v>58</v>
@@ -10807,19 +10815,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C91" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D91" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E91" t="s">
         <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10828,38 +10836,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="J91" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="M91" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="N91" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O91" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="P91" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="Q91" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R91" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S91" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T91" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U91" t="s">
         <v>58</v>
@@ -10871,19 +10879,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D92" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E92" t="s">
         <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10892,38 +10900,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="J92" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="M92" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="N92" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O92" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="P92" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="Q92" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R92" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S92" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T92" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U92" t="s">
         <v>58</v>
@@ -10935,19 +10943,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C93" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D93" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E93" t="s">
         <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10956,38 +10964,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="J93" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="M93" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="N93" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O93" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="P93" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="Q93" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R93" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S93" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="T93" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U93" t="s">
         <v>58</v>
@@ -10999,19 +11007,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
       </c>
       <c r="F94" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -11020,40 +11028,40 @@
         <v>62</v>
       </c>
       <c r="I94" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J94" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="K94" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="L94" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M94" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="N94" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O94" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="P94" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="Q94" t="s">
         <v>54</v>
       </c>
       <c r="R94" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="S94" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="T94" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="U94" t="s">
         <v>58</v>
@@ -11065,19 +11073,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11086,28 +11094,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="J95" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="K95" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="L95" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="M95" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="N95" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O95" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="P95" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="Q95" t="s">
         <v>54</v>
@@ -11131,19 +11139,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E96" t="s">
         <v>75</v>
       </c>
       <c r="F96" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11152,40 +11160,40 @@
         <v>76</v>
       </c>
       <c r="I96" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="J96" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="K96" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="L96" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="M96" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="N96" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O96" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="P96" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="Q96" t="s">
         <v>54</v>
       </c>
       <c r="R96" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="S96" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="T96" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="U96" t="s">
         <v>58</v>
@@ -11197,19 +11205,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C97" t="s">
         <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="E97" t="s">
         <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11218,40 +11226,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="J97" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="K97" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="L97" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="M97" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="N97" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O97" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="P97" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="Q97" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R97" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="S97" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="T97" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="U97" t="s">
         <v>58</v>
@@ -11263,57 +11271,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C98" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D98" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I98" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="J98" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="K98" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="L98" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="M98" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="P98" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="Q98" t="s">
         <v>54</v>
       </c>
       <c r="R98" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="S98" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="T98" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="U98" t="s">
         <v>58</v>
@@ -11325,19 +11333,19 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
@@ -11346,40 +11354,40 @@
         <v>101</v>
       </c>
       <c r="I99" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="J99" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="K99" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="L99" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="M99" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="N99" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O99" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="P99" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="Q99" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R99" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="S99" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="T99" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="U99" t="s">
         <v>58</v>
@@ -11391,19 +11399,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E100" t="s">
         <v>100</v>
       </c>
       <c r="F100" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11412,40 +11420,40 @@
         <v>62</v>
       </c>
       <c r="I100" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="J100" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="K100" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="L100" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="M100" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="N100" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O100" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="P100" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="Q100" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R100" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="S100" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="T100" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="U100" t="s">
         <v>58</v>
@@ -11457,19 +11465,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11478,40 +11486,40 @@
         <v>62</v>
       </c>
       <c r="I101" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="J101" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K101" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="L101" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="M101" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="N101" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O101" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="P101" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="Q101" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R101" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="S101" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="T101" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="U101" t="s">
         <v>58</v>
@@ -11523,19 +11531,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11544,40 +11552,40 @@
         <v>76</v>
       </c>
       <c r="I102" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="J102" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="K102" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="L102" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="M102" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="N102" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O102" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="P102" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="Q102" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R102" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="S102" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="T102" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="U102" t="s">
         <v>58</v>
@@ -11589,19 +11597,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E103" t="s">
         <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11610,40 +11618,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="J103" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="K103" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="L103" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="M103" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="N103" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O103" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="P103" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="Q103" t="s">
         <v>54</v>
       </c>
       <c r="R103" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="S103" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="T103" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="U103" t="s">
         <v>58</v>
@@ -11655,7 +11663,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
@@ -11667,7 +11675,7 @@
         <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11676,28 +11684,28 @@
         <v>76</v>
       </c>
       <c r="I104" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="J104" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="K104" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="L104" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="M104" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="N104" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O104" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="P104" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="Q104" t="s">
         <v>54</v>
@@ -11721,19 +11729,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E105" t="s">
         <v>100</v>
       </c>
       <c r="F105" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11742,40 +11750,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="J105" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="K105" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="L105" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="M105" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="N105" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O105" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="P105" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="Q105" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R105" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="S105" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="T105" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="U105" t="s">
         <v>58</v>
@@ -11787,19 +11795,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C106" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D106" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="E106" t="s">
         <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11808,38 +11816,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="J106" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="M106" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="N106" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O106" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="P106" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="Q106" t="s">
         <v>54</v>
       </c>
       <c r="R106" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="S106" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="T106" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="U106" t="s">
         <v>58</v>
@@ -11851,19 +11859,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D107" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11872,38 +11880,38 @@
         <v>76</v>
       </c>
       <c r="I107" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="J107" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="M107" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="N107" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O107" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="P107" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="Q107" t="s">
         <v>54</v>
       </c>
       <c r="R107" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="S107" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="T107" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="U107" t="s">
         <v>58</v>
@@ -11915,10 +11923,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C108" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D108" t="s">
         <v>87</v>
@@ -11927,7 +11935,7 @@
         <v>61</v>
       </c>
       <c r="F108" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11936,40 +11944,40 @@
         <v>76</v>
       </c>
       <c r="I108" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="J108" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="K108" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="L108" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="M108" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="N108" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O108" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="P108" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="Q108" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R108" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="S108" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="T108" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="U108" t="s">
         <v>58</v>
@@ -11981,51 +11989,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="C109" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="J109" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="K109" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="O109" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="P109" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="S109" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="T109" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="U109" t="s">
         <v>58</v>
@@ -12037,57 +12045,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C110" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D110" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="J110" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="K110" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="L110" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="M110" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="N110" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O110" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="P110" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="Q110" t="s">
         <v>54</v>
       </c>
       <c r="R110" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="S110" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="T110" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="U110" t="s">
         <v>58</v>
@@ -12099,19 +12107,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C111" t="s">
         <v>73</v>
       </c>
       <c r="D111" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E111" t="s">
         <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12120,40 +12128,40 @@
         <v>76</v>
       </c>
       <c r="I111" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="J111" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="K111" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="L111" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="M111" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="N111" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O111" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="P111" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="Q111" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R111" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="S111" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="T111" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="U111" t="s">
         <v>58</v>
@@ -12165,19 +12173,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="C112" t="s">
         <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E112" t="s">
         <v>61</v>
       </c>
       <c r="F112" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12186,40 +12194,40 @@
         <v>62</v>
       </c>
       <c r="I112" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="J112" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="K112" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="L112" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="M112" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="N112" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O112" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="P112" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="Q112" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R112" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="S112" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="T112" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="U112" t="s">
         <v>58</v>
@@ -12231,7 +12239,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
@@ -12243,7 +12251,7 @@
         <v>61</v>
       </c>
       <c r="F113" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12252,40 +12260,40 @@
         <v>76</v>
       </c>
       <c r="I113" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="J113" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="K113" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="L113" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="M113" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="N113" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O113" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="P113" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="Q113" t="s">
         <v>54</v>
       </c>
       <c r="R113" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="S113" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="T113" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="U113" t="s">
         <v>58</v>
@@ -12297,19 +12305,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12318,40 +12326,40 @@
         <v>62</v>
       </c>
       <c r="I114" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="J114" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="K114" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="L114" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="M114" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="N114" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O114" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="P114" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="Q114" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R114" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="S114" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="T114" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="U114" t="s">
         <v>58</v>
@@ -12363,19 +12371,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12384,40 +12392,40 @@
         <v>76</v>
       </c>
       <c r="I115" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="J115" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="K115" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="L115" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="M115" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="N115" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O115" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="P115" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="Q115" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R115" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="S115" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="T115" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="U115" t="s">
         <v>58</v>
@@ -12429,19 +12437,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E116" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="F116" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12450,40 +12458,40 @@
         <v>101</v>
       </c>
       <c r="I116" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="J116" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="K116" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="L116" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="M116" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="N116" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O116" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="P116" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="Q116" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R116" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="S116" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="T116" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="U116" t="s">
         <v>58</v>
@@ -12495,19 +12503,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="C117" t="s">
         <v>73</v>
       </c>
       <c r="D117" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E117" t="s">
         <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12516,40 +12524,40 @@
         <v>76</v>
       </c>
       <c r="I117" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="J117" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="K117" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="L117" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="M117" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="N117" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O117" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="P117" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="Q117" t="s">
         <v>54</v>
       </c>
       <c r="R117" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="S117" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="T117" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="U117" t="s">
         <v>58</v>
@@ -12561,19 +12569,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C118" t="s">
         <v>73</v>
       </c>
       <c r="D118" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12582,40 +12590,40 @@
         <v>62</v>
       </c>
       <c r="I118" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="J118" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="K118" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="L118" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="M118" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="N118" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O118" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="P118" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="Q118" t="s">
         <v>54</v>
       </c>
       <c r="R118" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="S118" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="T118" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="U118" t="s">
         <v>58</v>
@@ -12627,19 +12635,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="C119" t="s">
         <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E119" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12648,40 +12656,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="J119" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="K119" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="L119" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="M119" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="N119" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O119" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="P119" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="Q119" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R119" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="S119" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="T119" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="U119" t="s">
         <v>58</v>
@@ -12693,19 +12701,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C120" t="s">
         <v>73</v>
       </c>
       <c r="D120" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12714,40 +12722,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="J120" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="K120" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="L120" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="M120" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="N120" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O120" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="P120" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="Q120" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R120" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="S120" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="T120" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="U120" t="s">
         <v>58</v>
@@ -12759,7 +12767,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C121" t="s">
         <v>73</v>
@@ -12771,7 +12779,7 @@
         <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12780,40 +12788,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="J121" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="K121" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="L121" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="M121" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="N121" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O121" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="P121" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="Q121" t="s">
         <v>54</v>
       </c>
       <c r="R121" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S121" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T121" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U121" t="s">
         <v>58</v>
@@ -12825,19 +12833,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="C122" t="s">
         <v>73</v>
       </c>
       <c r="D122" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E122" t="s">
         <v>61</v>
       </c>
       <c r="F122" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12846,40 +12854,40 @@
         <v>62</v>
       </c>
       <c r="I122" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="J122" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="K122" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="L122" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="M122" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="N122" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O122" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="P122" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="Q122" t="s">
         <v>54</v>
       </c>
       <c r="R122" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="S122" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="T122" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="U122" t="s">
         <v>58</v>
@@ -12891,19 +12899,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="C123" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D123" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="E123" t="s">
         <v>61</v>
       </c>
       <c r="F123" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12912,40 +12920,40 @@
         <v>62</v>
       </c>
       <c r="I123" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="J123" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="K123" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="L123" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="M123" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="N123" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O123" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="P123" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="Q123" t="s">
         <v>54</v>
       </c>
       <c r="R123" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="S123" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="T123" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="U123" t="s">
         <v>58</v>
@@ -12957,19 +12965,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C124" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D124" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E124" t="s">
         <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12978,29 +12986,29 @@
         <v>76</v>
       </c>
       <c r="I124" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="J124" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="M124" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="N124" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O124" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="P124" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="Q124" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R124" t="s">
         <v>83</v>
@@ -13021,10 +13029,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="C125" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D125" t="s">
         <v>87</v>
@@ -13033,7 +13041,7 @@
         <v>61</v>
       </c>
       <c r="F125" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13042,26 +13050,26 @@
         <v>76</v>
       </c>
       <c r="I125" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="J125" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="M125" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="N125" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O125" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="P125" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="Q125" t="s">
         <v>54</v>
@@ -13085,17 +13093,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13104,40 +13112,40 @@
         <v>62</v>
       </c>
       <c r="I126" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="J126" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="K126" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="L126" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="M126" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="N126" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O126" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="P126" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="Q126" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R126" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="S126" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="T126" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="U126" t="s">
         <v>58</v>
@@ -13149,19 +13157,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="C127" t="s">
         <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E127" t="s">
         <v>100</v>
       </c>
       <c r="F127" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13170,40 +13178,40 @@
         <v>76</v>
       </c>
       <c r="I127" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="J127" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="K127" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="L127" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="M127" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="N127" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O127" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="P127" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="Q127" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R127" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="S127" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="T127" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="U127" t="s">
         <v>58</v>
@@ -13215,19 +13223,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E128" t="s">
         <v>61</v>
       </c>
       <c r="F128" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13236,40 +13244,40 @@
         <v>62</v>
       </c>
       <c r="I128" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="J128" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="K128" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="L128" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="M128" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="N128" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O128" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="P128" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="Q128" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R128" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="S128" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="T128" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="U128" t="s">
         <v>58</v>
@@ -13281,61 +13289,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E129" t="s">
         <v>61</v>
       </c>
       <c r="F129" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I129" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="J129" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="K129" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="L129" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="M129" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="N129" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O129" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="P129" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="Q129" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R129" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="S129" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="T129" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="U129" t="s">
         <v>58</v>
@@ -13347,61 +13355,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E130" t="s">
         <v>61</v>
       </c>
       <c r="F130" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I130" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="J130" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="K130" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="L130" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="M130" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="N130" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O130" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="P130" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="Q130" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R130" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="S130" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="T130" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="U130" t="s">
         <v>58</v>
@@ -13413,19 +13421,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="C131" t="s">
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="E131" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F131" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13434,40 +13442,40 @@
         <v>101</v>
       </c>
       <c r="I131" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="J131" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="K131" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="L131" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="M131" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="N131" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O131" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="P131" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="Q131" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R131" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="S131" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="T131" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U131" t="s">
         <v>58</v>
@@ -13479,7 +13487,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C132" t="s">
         <v>73</v>
@@ -13491,7 +13499,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13500,40 +13508,40 @@
         <v>76</v>
       </c>
       <c r="I132" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="J132" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="K132" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="L132" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="M132" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="N132" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O132" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="P132" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="Q132" t="s">
         <v>54</v>
       </c>
       <c r="R132" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="S132" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="T132" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="U132" t="s">
         <v>58</v>
@@ -13545,19 +13553,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="C133" t="s">
         <v>73</v>
       </c>
       <c r="D133" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E133" t="s">
         <v>75</v>
       </c>
       <c r="F133" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13566,40 +13574,40 @@
         <v>76</v>
       </c>
       <c r="I133" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="J133" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K133" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="L133" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="M133" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="N133" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O133" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="P133" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="Q133" t="s">
         <v>54</v>
       </c>
       <c r="R133" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="S133" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="T133" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="U133" t="s">
         <v>58</v>
@@ -13611,19 +13619,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C134" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D134" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E134" t="s">
         <v>100</v>
       </c>
       <c r="F134" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13632,38 +13640,38 @@
         <v>76</v>
       </c>
       <c r="I134" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="J134" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="M134" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="N134" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O134" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="P134" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="Q134" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R134" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="S134" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="T134" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="U134" t="s">
         <v>58</v>
@@ -13675,19 +13683,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D135" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E135" t="s">
         <v>100</v>
       </c>
       <c r="F135" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13696,38 +13704,38 @@
         <v>76</v>
       </c>
       <c r="I135" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="J135" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="M135" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="N135" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O135" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="P135" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="Q135" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R135" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="S135" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="T135" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="U135" t="s">
         <v>58</v>
@@ -13739,19 +13747,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C136" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D136" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="E136" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F136" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13760,38 +13768,38 @@
         <v>76</v>
       </c>
       <c r="I136" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="J136" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="M136" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="N136" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O136" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="P136" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="Q136" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R136" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="S136" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="T136" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U136" t="s">
         <v>58</v>
@@ -13803,19 +13811,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="C137" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D137" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13824,38 +13832,38 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="J137" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="M137" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="N137" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O137" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="P137" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="Q137" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R137" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="S137" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="T137" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="U137" t="s">
         <v>58</v>
@@ -13867,57 +13875,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="C138" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D138" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>101</v>
       </c>
       <c r="I138" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="J138" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="K138" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="L138" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="M138" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="N138" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O138" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="P138" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="Q138" t="s">
         <v>54</v>
       </c>
       <c r="R138" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="S138" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="T138" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="U138" t="s">
         <v>58</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="1539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1540">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -255,6 +255,9 @@
   </si>
   <si>
     <t xml:space="preserve">Qualité de vie améliorée grâce aux projets de contournement de la N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migliore qualità di vita grazie ai progetti di circonvallazione sulla N18</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les lignes directrices de «&amp;nbsp;&lt;i&gt;Transports ’45&amp;nbsp;»&lt;/i&gt;. Selon ces derniers, les projets routiers prévus le long de la route nationale 18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufon (horizon 2055) – devraient être reportés à une période postérieure à 2055. Cette perspective suscite une vive incompréhension dans la région. Elle équivaut en effet à renoncer, pour plusieurs décennies, à une amélioration de l’accessibilité et, par conséquent, à de réelles perspectives de développement économique. Elle contredit en outre directement les résultats de l’étude de corridor N18, menée sous la conduite de l’OFROU selon les méthodes les plus récentes et soutenue par un large partenariat.&lt;/p&gt;&lt;p&gt;La N18 constitue un maillon essentiel du réseau routier national. Elle relie l’agglomération bâloise à l’Arc lémanique et dessert le Laufonnais, en plein essor, ainsi que Delémont, chef-lieu cantonal. En raison de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, présentant l’une des charges de trafic et densités de bouchons les plus élevées du pays. La situation actuelle affecte par ailleurs fortement la qualité de vie dans les centres des localités et compromet la sécurité du trafic motorisé et cycliste. La population souffre quotidiennement des embouteillages et du trafic intense des poids lourds traversant les localités, comme en témoignent les nombreux participants aux forums de la mobilité de Laufon. Une évolution rapide du corridor apparaît dès lors indispensable.&lt;/p&gt;&lt;p&gt;Dans ce contexte, le Conseil fédéral est prié de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il les effets du trafic de transit – en particulier des poids lourds – sur le développement du milieu bâti ainsi que sur la qualité de séjour et d’habitation à Delémont, Laufon et Zwingen ?&lt;/li&gt;&lt;li&gt;Considère-t-il les projets de contournement Laufon–Zwingen et Delémont comme des mesures appropriées pour réduire les nuisances dans les zones urbanisées concernées ?&lt;/li&gt;&lt;li&gt;Estime-t-il nécessaires des mesures visant à améliorer la desserte des zones d’emplois à Delémont ainsi que dans le Laufonnais ?&lt;/li&gt;&lt;/ol&gt;</t>
@@ -5284,34 +5287,34 @@
         <v>80</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N5" t="s">
         <v>52</v>
       </c>
       <c r="O5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q5" t="s">
         <v>37</v>
       </c>
       <c r="R5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U5" t="s">
         <v>59</v>
@@ -5323,19 +5326,19 @@
         <v>20263228</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G6" t="s">
         <v>45</v>
@@ -5344,40 +5347,40 @@
         <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" t="s">
         <v>66</v>
       </c>
       <c r="L6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N6" t="s">
         <v>52</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q6" t="s">
         <v>55</v>
       </c>
       <c r="R6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -5389,61 +5392,61 @@
         <v>20263323</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G7" t="s">
         <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N7" t="s">
         <v>52</v>
       </c>
       <c r="O7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q7" t="s">
         <v>55</v>
       </c>
       <c r="R7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -5455,19 +5458,19 @@
         <v>20263120</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
         <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G8" t="s">
         <v>45</v>
@@ -5476,40 +5479,40 @@
         <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N8" t="s">
         <v>52</v>
       </c>
       <c r="O8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
       </c>
       <c r="R8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U8" t="s">
         <v>59</v>
@@ -5521,7 +5524,7 @@
         <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
         <v>75</v>
@@ -5533,7 +5536,7 @@
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -5542,40 +5545,40 @@
         <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N9" t="s">
         <v>52</v>
       </c>
       <c r="O9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U9" t="s">
         <v>59</v>
@@ -5587,17 +5590,17 @@
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G10" t="s">
         <v>45</v>
@@ -5606,40 +5609,40 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s">
         <v>52</v>
       </c>
       <c r="O10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q10" t="s">
         <v>55</v>
       </c>
       <c r="R10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="T10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -5651,10 +5654,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5663,7 +5666,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5672,40 +5675,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" t="s">
         <v>52</v>
       </c>
       <c r="O11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -5717,59 +5720,59 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
         <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -5781,19 +5784,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E13" t="s">
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5802,40 +5805,40 @@
         <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N13" t="s">
         <v>52</v>
       </c>
       <c r="O13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q13" t="s">
         <v>55</v>
       </c>
       <c r="R13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U13" t="s">
         <v>59</v>
@@ -5847,19 +5850,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5868,38 +5871,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="S14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -5911,51 +5914,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -5967,19 +5970,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5988,38 +5991,38 @@
         <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16" t="s">
         <v>55</v>
       </c>
       <c r="R16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -6031,17 +6034,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6050,40 +6053,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q17" t="s">
         <v>55</v>
       </c>
       <c r="R17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -6095,16 +6098,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6116,40 +6119,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U18" t="s">
         <v>59</v>
@@ -6161,13 +6164,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C19" t="s">
         <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
@@ -6182,40 +6185,40 @@
         <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -6227,7 +6230,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6239,49 +6242,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -6293,10 +6296,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6305,7 +6308,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6314,40 +6317,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="T21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -6359,19 +6362,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C22" t="s">
         <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6380,40 +6383,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="T22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U22" t="s">
         <v>59</v>
@@ -6425,19 +6428,19 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
         <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6446,40 +6449,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="U23" t="s">
         <v>59</v>
@@ -6491,19 +6494,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
         <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6512,40 +6515,40 @@
         <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="S24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="U24" t="s">
         <v>59</v>
@@ -6557,59 +6560,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D25" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E25" t="s">
         <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J25" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q25" t="s">
         <v>55</v>
       </c>
       <c r="R25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="T25" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="U25" t="s">
         <v>59</v>
@@ -6621,19 +6624,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6642,38 +6645,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P26" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q26" t="s">
         <v>55</v>
       </c>
       <c r="R26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="T26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U26" t="s">
         <v>59</v>
@@ -6685,17 +6688,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6704,40 +6707,40 @@
         <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P27" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q27" t="s">
         <v>55</v>
       </c>
       <c r="R27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="T27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="U27" t="s">
         <v>59</v>
@@ -6749,19 +6752,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E28" t="s">
         <v>77</v>
       </c>
       <c r="F28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6770,40 +6773,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L28" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
       </c>
       <c r="R28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="T28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="U28" t="s">
         <v>59</v>
@@ -6815,19 +6818,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6836,40 +6839,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K29" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
       </c>
       <c r="R29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U29" t="s">
         <v>59</v>
@@ -6881,19 +6884,19 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
         <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6902,40 +6905,40 @@
         <v>78</v>
       </c>
       <c r="I30" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J30" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M30" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U30" t="s">
         <v>59</v>
@@ -6947,7 +6950,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6959,7 +6962,7 @@
         <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6968,40 +6971,40 @@
         <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J31" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K31" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L31" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="S31" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T31" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U31" t="s">
         <v>59</v>
@@ -7013,19 +7016,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C32" t="s">
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -7034,40 +7037,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J32" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U32" t="s">
         <v>59</v>
@@ -7079,7 +7082,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C33" t="s">
         <v>75</v>
@@ -7091,49 +7094,49 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M33" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O33" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q33" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="S33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T33" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="U33" t="s">
         <v>59</v>
@@ -7145,61 +7148,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C34" t="s">
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E34" t="s">
         <v>77</v>
       </c>
       <c r="F34" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I34" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J34" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K34" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L34" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M34" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O34" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P34" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R34" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="S34" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T34" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="U34" t="s">
         <v>59</v>
@@ -7211,19 +7214,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7232,40 +7235,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J35" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K35" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L35" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O35" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P35" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q35" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R35" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="S35" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="T35" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="U35" t="s">
         <v>59</v>
@@ -7277,10 +7280,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C36" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D36" t="s">
         <v>76</v>
@@ -7289,7 +7292,7 @@
         <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7298,40 +7301,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J36" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K36" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L36" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M36" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N36" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O36" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P36" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="S36" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="T36" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="U36" t="s">
         <v>59</v>
@@ -7343,19 +7346,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F37" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7364,40 +7367,40 @@
         <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J37" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K37" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L37" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M37" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O37" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P37" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q37" t="s">
         <v>55</v>
       </c>
       <c r="R37" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S37" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T37" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U37" t="s">
         <v>59</v>
@@ -7409,19 +7412,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D38" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E38" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F38" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7430,38 +7433,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J38" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P38" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U38" t="s">
         <v>59</v>
@@ -7473,59 +7476,59 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I39" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J39" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O39" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P39" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R39" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="S39" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="T39" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="U39" t="s">
         <v>59</v>
@@ -7537,19 +7540,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D40" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E40" t="s">
         <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7558,38 +7561,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J40" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M40" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O40" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P40" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R40" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="S40" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T40" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="U40" t="s">
         <v>59</v>
@@ -7601,61 +7604,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C41" t="s">
         <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E41" t="s">
         <v>77</v>
       </c>
       <c r="F41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I41" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J41" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K41" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L41" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M41" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O41" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P41" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q41" t="s">
         <v>55</v>
       </c>
       <c r="R41" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="S41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="U41" t="s">
         <v>59</v>
@@ -7667,59 +7670,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E42" t="s">
         <v>77</v>
       </c>
       <c r="F42" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I42" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J42" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M42" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N42" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O42" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P42" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Q42" t="s">
         <v>55</v>
       </c>
       <c r="R42" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S42" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T42" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="U42" t="s">
         <v>59</v>
@@ -7731,45 +7734,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C43" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D43" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I43" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J43" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L43" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M43" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N43" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O43" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P43" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Q43" t="s">
         <v>55</v>
@@ -7787,19 +7790,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C44" t="s">
         <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E44" t="s">
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7808,40 +7811,40 @@
         <v>78</v>
       </c>
       <c r="I44" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J44" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K44" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L44" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M44" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O44" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P44" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R44" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="S44" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T44" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U44" t="s">
         <v>59</v>
@@ -7853,19 +7856,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C45" t="s">
         <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E45" t="s">
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7874,40 +7877,40 @@
         <v>78</v>
       </c>
       <c r="I45" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J45" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K45" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L45" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O45" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P45" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q45" t="s">
         <v>55</v>
       </c>
       <c r="R45" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="S45" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="T45" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="U45" t="s">
         <v>59</v>
@@ -7919,19 +7922,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7940,40 +7943,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J46" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K46" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L46" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M46" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N46" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O46" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P46" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Q46" t="s">
         <v>55</v>
       </c>
       <c r="R46" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="S46" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="T46" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="U46" t="s">
         <v>59</v>
@@ -7985,7 +7988,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7995,7 +7998,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -8004,40 +8007,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J47" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K47" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L47" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M47" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O47" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P47" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Q47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R47" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="S47" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T47" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U47" t="s">
         <v>59</v>
@@ -8049,19 +8052,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C48" t="s">
         <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E48" t="s">
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8070,40 +8073,40 @@
         <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J48" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K48" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L48" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M48" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P48" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Q48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R48" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="S48" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="T48" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="U48" t="s">
         <v>59</v>
@@ -8115,19 +8118,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C49" t="s">
         <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E49" t="s">
         <v>62</v>
       </c>
       <c r="F49" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8136,40 +8139,40 @@
         <v>78</v>
       </c>
       <c r="I49" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J49" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="K49" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M49" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P49" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Q49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S49" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U49" t="s">
         <v>59</v>
@@ -8181,17 +8184,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8200,40 +8203,40 @@
         <v>78</v>
       </c>
       <c r="I50" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K50" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M50" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P50" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Q50" t="s">
         <v>55</v>
       </c>
       <c r="R50" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U50" t="s">
         <v>59</v>
@@ -8245,19 +8248,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C51" t="s">
         <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F51" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8266,40 +8269,40 @@
         <v>78</v>
       </c>
       <c r="I51" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J51" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K51" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L51" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M51" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O51" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P51" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Q51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R51" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S51" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="T51" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U51" t="s">
         <v>59</v>
@@ -8311,19 +8314,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C52" t="s">
         <v>75</v>
       </c>
       <c r="D52" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8332,40 +8335,40 @@
         <v>78</v>
       </c>
       <c r="I52" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J52" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K52" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L52" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M52" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O52" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P52" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Q52" t="s">
         <v>55</v>
       </c>
       <c r="R52" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="S52" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T52" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U52" t="s">
         <v>59</v>
@@ -8377,19 +8380,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E53" t="s">
         <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8398,40 +8401,40 @@
         <v>78</v>
       </c>
       <c r="I53" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J53" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L53" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M53" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O53" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P53" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q53" t="s">
         <v>55</v>
       </c>
       <c r="R53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S53" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U53" t="s">
         <v>59</v>
@@ -8443,19 +8446,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E54" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F54" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8464,40 +8467,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J54" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="K54" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L54" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M54" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O54" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P54" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R54" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="S54" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="T54" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="U54" t="s">
         <v>59</v>
@@ -8509,19 +8512,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E55" t="s">
         <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8530,40 +8533,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J55" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K55" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N55" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P55" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Q55" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R55" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S55" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T55" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U55" t="s">
         <v>59</v>
@@ -8575,17 +8578,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8594,40 +8597,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="J56" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K56" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L56" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M56" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N56" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O56" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P56" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="Q56" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R56" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S56" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T56" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U56" t="s">
         <v>59</v>
@@ -8639,61 +8642,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D57" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I57" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J57" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K57" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L57" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M57" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N57" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O57" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P57" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Q57" t="s">
         <v>55</v>
       </c>
       <c r="R57" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="S57" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="T57" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="U57" t="s">
         <v>59</v>
@@ -8705,19 +8708,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C58" t="s">
         <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8726,40 +8729,40 @@
         <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J58" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K58" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L58" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O58" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P58" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q58" t="s">
         <v>55</v>
       </c>
       <c r="R58" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="S58" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="T58" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="U58" t="s">
         <v>59</v>
@@ -8771,19 +8774,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C59" t="s">
         <v>75</v>
       </c>
       <c r="D59" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F59" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8792,40 +8795,40 @@
         <v>78</v>
       </c>
       <c r="I59" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J59" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K59" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M59" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O59" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P59" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="Q59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R59" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S59" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T59" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U59" t="s">
         <v>59</v>
@@ -8837,19 +8840,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8858,40 +8861,40 @@
         <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J60" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K60" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L60" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M60" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O60" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P60" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Q60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R60" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="S60" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="T60" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="U60" t="s">
         <v>59</v>
@@ -8903,7 +8906,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8915,7 +8918,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8924,40 +8927,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J61" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K61" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L61" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M61" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O61" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P61" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Q61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R61" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S61" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T61" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U61" t="s">
         <v>59</v>
@@ -8969,19 +8972,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C62" t="s">
         <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8990,40 +8993,40 @@
         <v>78</v>
       </c>
       <c r="I62" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J62" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K62" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L62" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M62" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O62" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="P62" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="Q62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R62" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="S62" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="T62" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="U62" t="s">
         <v>59</v>
@@ -9035,19 +9038,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C63" t="s">
         <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E63" t="s">
         <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9056,40 +9059,40 @@
         <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J63" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="K63" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="L63" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M63" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N63" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O63" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P63" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Q63" t="s">
         <v>55</v>
       </c>
       <c r="R63" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="S63" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="T63" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="U63" t="s">
         <v>59</v>
@@ -9101,45 +9104,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C64" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D64" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>78</v>
       </c>
       <c r="I64" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J64" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="K64" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="L64" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M64" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P64" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Q64" t="s">
         <v>55</v>
@@ -9157,45 +9160,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C65" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D65" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J65" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K65" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L65" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M65" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N65" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O65" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="P65" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="Q65" t="s">
         <v>55</v>
@@ -9213,17 +9216,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C66" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D66" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9232,40 +9235,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J66" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K66" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="L66" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M66" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P66" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Q66" t="s">
         <v>55</v>
       </c>
       <c r="R66" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="S66" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="T66" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="U66" t="s">
         <v>59</v>
@@ -9277,19 +9280,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C67" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D67" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E67" t="s">
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9298,40 +9301,40 @@
         <v>78</v>
       </c>
       <c r="I67" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="J67" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="K67" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="L67" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M67" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N67" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O67" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P67" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="Q67" t="s">
         <v>55</v>
       </c>
       <c r="R67" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S67" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="T67" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="U67" t="s">
         <v>59</v>
@@ -9343,19 +9346,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C68" t="s">
         <v>75</v>
       </c>
       <c r="D68" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E68" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F68" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9364,40 +9367,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J68" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K68" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="L68" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M68" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O68" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="P68" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="Q68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R68" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="S68" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="T68" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="U68" t="s">
         <v>59</v>
@@ -9409,61 +9412,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C69" t="s">
         <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I69" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="J69" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K69" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L69" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M69" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N69" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O69" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="P69" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="Q69" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R69" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="S69" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="T69" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="U69" t="s">
         <v>59</v>
@@ -9475,19 +9478,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F70" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9496,40 +9499,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J70" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K70" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L70" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M70" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N70" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O70" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="P70" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Q70" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R70" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="S70" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="T70" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="U70" t="s">
         <v>59</v>
@@ -9541,19 +9544,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E71" t="s">
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9562,40 +9565,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J71" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K71" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="L71" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="M71" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O71" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="P71" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="Q71" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R71" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="S71" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="T71" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="U71" t="s">
         <v>59</v>
@@ -9607,19 +9610,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C72" t="s">
         <v>75</v>
       </c>
       <c r="D72" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E72" t="s">
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9628,40 +9631,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J72" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="K72" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="L72" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M72" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O72" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="P72" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R72" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="S72" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="T72" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="U72" t="s">
         <v>59</v>
@@ -9673,19 +9676,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C73" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9694,40 +9697,40 @@
         <v>78</v>
       </c>
       <c r="I73" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J73" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="K73" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="L73" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M73" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O73" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="P73" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q73" t="s">
         <v>55</v>
       </c>
       <c r="R73" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="S73" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="T73" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="U73" t="s">
         <v>59</v>
@@ -9739,19 +9742,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C74" t="s">
         <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E74" t="s">
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9760,40 +9763,40 @@
         <v>78</v>
       </c>
       <c r="I74" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J74" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="K74" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L74" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M74" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="P74" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="Q74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R74" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="S74" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="T74" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="U74" t="s">
         <v>59</v>
@@ -9805,45 +9808,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C75" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D75" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>78</v>
       </c>
       <c r="I75" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="J75" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="K75" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="L75" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="M75" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="N75" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O75" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="P75" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="Q75" t="s">
         <v>55</v>
@@ -9861,7 +9864,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9873,7 +9876,7 @@
         <v>77</v>
       </c>
       <c r="F76" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9882,40 +9885,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J76" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="K76" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="L76" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="M76" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="N76" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O76" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="P76" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="Q76" t="s">
         <v>55</v>
       </c>
       <c r="R76" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S76" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="T76" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="U76" t="s">
         <v>59</v>
@@ -9927,19 +9930,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D77" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E77" t="s">
         <v>77</v>
       </c>
       <c r="F77" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9948,38 +9951,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="J77" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M77" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="N77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O77" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="P77" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="Q77" t="s">
         <v>55</v>
       </c>
       <c r="R77" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="S77" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="T77" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="U77" t="s">
         <v>59</v>
@@ -9991,19 +9994,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D78" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E78" t="s">
         <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -10012,38 +10015,38 @@
         <v>78</v>
       </c>
       <c r="I78" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="J78" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M78" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="N78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O78" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="P78" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="Q78" t="s">
         <v>55</v>
       </c>
       <c r="R78" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S78" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="T78" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="U78" t="s">
         <v>59</v>
@@ -10055,51 +10058,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="J79" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="K79" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O79" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="P79" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="S79" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="T79" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="U79" t="s">
         <v>59</v>
@@ -10111,57 +10114,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C80" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D80" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J80" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K80" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="L80" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M80" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="P80" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="Q80" t="s">
         <v>55</v>
       </c>
       <c r="R80" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="S80" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="T80" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="U80" t="s">
         <v>59</v>
@@ -10173,57 +10176,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C81" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D81" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>78</v>
       </c>
       <c r="I81" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J81" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="K81" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="L81" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M81" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="N81" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O81" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="P81" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="Q81" t="s">
         <v>55</v>
       </c>
       <c r="R81" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="S81" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="T81" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="U81" t="s">
         <v>59</v>
@@ -10235,19 +10238,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E82" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F82" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10256,40 +10259,40 @@
         <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="J82" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="K82" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="L82" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M82" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="N82" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O82" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="P82" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="Q82" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R82" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="S82" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="T82" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="U82" t="s">
         <v>59</v>
@@ -10301,61 +10304,61 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I83" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J83" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="K83" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="L83" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M83" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="N83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O83" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="P83" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="Q83" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R83" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="S83" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="T83" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="U83" t="s">
         <v>59</v>
@@ -10367,19 +10370,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C84" t="s">
         <v>75</v>
       </c>
       <c r="D84" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E84" t="s">
         <v>77</v>
       </c>
       <c r="F84" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10388,40 +10391,40 @@
         <v>78</v>
       </c>
       <c r="I84" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="J84" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="K84" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="L84" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M84" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="N84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O84" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="P84" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="Q84" t="s">
         <v>55</v>
       </c>
       <c r="R84" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S84" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="T84" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U84" t="s">
         <v>59</v>
@@ -10433,19 +10436,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E85" t="s">
         <v>62</v>
       </c>
       <c r="F85" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10454,40 +10457,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J85" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K85" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="L85" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M85" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="N85" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O85" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="P85" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="Q85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R85" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="S85" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="T85" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="U85" t="s">
         <v>59</v>
@@ -10499,61 +10502,61 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C86" t="s">
         <v>75</v>
       </c>
       <c r="D86" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
       </c>
       <c r="H86" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I86" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="J86" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="K86" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="L86" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M86" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="N86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O86" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="P86" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="Q86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R86" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="S86" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="T86" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U86" t="s">
         <v>59</v>
@@ -10565,61 +10568,61 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E87" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F87" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I87" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="J87" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="K87" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="L87" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M87" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="N87" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O87" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="P87" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="Q87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R87" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S87" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="T87" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="U87" t="s">
         <v>59</v>
@@ -10631,19 +10634,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C88" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D88" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E88" t="s">
         <v>77</v>
       </c>
       <c r="F88" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10652,38 +10655,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J88" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="M88" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="N88" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O88" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="P88" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R88" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U88" t="s">
         <v>59</v>
@@ -10695,19 +10698,19 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C89" t="s">
         <v>75</v>
       </c>
       <c r="D89" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E89" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F89" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10716,40 +10719,40 @@
         <v>78</v>
       </c>
       <c r="I89" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J89" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="K89" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L89" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M89" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O89" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="P89" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="Q89" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R89" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T89" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U89" t="s">
         <v>59</v>
@@ -10761,19 +10764,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D90" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10782,38 +10785,38 @@
         <v>78</v>
       </c>
       <c r="I90" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="J90" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="M90" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O90" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="P90" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="Q90" t="s">
         <v>55</v>
       </c>
       <c r="R90" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S90" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T90" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U90" t="s">
         <v>59</v>
@@ -10825,19 +10828,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C91" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D91" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E91" t="s">
         <v>77</v>
       </c>
       <c r="F91" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10846,38 +10849,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="J91" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="M91" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N91" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O91" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="P91" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="Q91" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R91" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U91" t="s">
         <v>59</v>
@@ -10889,19 +10892,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C92" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D92" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E92" t="s">
         <v>77</v>
       </c>
       <c r="F92" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10910,38 +10913,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="J92" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="M92" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N92" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O92" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="P92" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Q92" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R92" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U92" t="s">
         <v>59</v>
@@ -10953,19 +10956,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C93" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D93" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E93" t="s">
         <v>77</v>
       </c>
       <c r="F93" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10974,38 +10977,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="J93" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M93" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N93" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O93" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="P93" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="Q93" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U93" t="s">
         <v>59</v>
@@ -11017,19 +11020,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C94" t="s">
         <v>75</v>
       </c>
       <c r="D94" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E94" t="s">
         <v>77</v>
       </c>
       <c r="F94" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -11038,40 +11041,40 @@
         <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J94" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K94" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="L94" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="M94" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N94" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O94" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="P94" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="Q94" t="s">
         <v>55</v>
       </c>
       <c r="R94" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="S94" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="T94" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="U94" t="s">
         <v>59</v>
@@ -11083,19 +11086,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C95" t="s">
         <v>75</v>
       </c>
       <c r="D95" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11104,28 +11107,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="J95" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="K95" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="L95" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="M95" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="N95" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O95" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="P95" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="Q95" t="s">
         <v>55</v>
@@ -11149,19 +11152,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C96" t="s">
         <v>75</v>
       </c>
       <c r="D96" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E96" t="s">
         <v>77</v>
       </c>
       <c r="F96" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11170,40 +11173,40 @@
         <v>78</v>
       </c>
       <c r="I96" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J96" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="K96" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="L96" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="M96" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="N96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O96" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="P96" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="Q96" t="s">
         <v>55</v>
       </c>
       <c r="R96" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="S96" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="T96" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="U96" t="s">
         <v>59</v>
@@ -11215,19 +11218,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C97" t="s">
         <v>75</v>
       </c>
       <c r="D97" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E97" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F97" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11236,40 +11239,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J97" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="K97" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="L97" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="M97" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="N97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O97" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="P97" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="Q97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R97" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="S97" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="T97" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="U97" t="s">
         <v>59</v>
@@ -11281,57 +11284,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C98" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D98" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I98" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="J98" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="K98" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="L98" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="M98" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="P98" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="Q98" t="s">
         <v>55</v>
       </c>
       <c r="R98" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="S98" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="T98" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="U98" t="s">
         <v>59</v>
@@ -11343,61 +11346,61 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I99" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="J99" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K99" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="L99" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="M99" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="N99" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O99" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="P99" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="Q99" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R99" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="S99" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="T99" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="U99" t="s">
         <v>59</v>
@@ -11409,19 +11412,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E100" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F100" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11430,40 +11433,40 @@
         <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="J100" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="K100" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="L100" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="M100" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="N100" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O100" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="P100" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="Q100" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R100" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="S100" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="T100" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="U100" t="s">
         <v>59</v>
@@ -11475,19 +11478,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C101" t="s">
         <v>75</v>
       </c>
       <c r="D101" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E101" t="s">
         <v>62</v>
       </c>
       <c r="F101" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11496,40 +11499,40 @@
         <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J101" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="K101" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="L101" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="M101" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="N101" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O101" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="P101" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="Q101" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R101" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="S101" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="T101" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="U101" t="s">
         <v>59</v>
@@ -11541,19 +11544,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E102" t="s">
         <v>62</v>
       </c>
       <c r="F102" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11562,40 +11565,40 @@
         <v>78</v>
       </c>
       <c r="I102" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="J102" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K102" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="L102" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="M102" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="N102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O102" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="P102" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="Q102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R102" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="S102" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="T102" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="U102" t="s">
         <v>59</v>
@@ -11607,19 +11610,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E103" t="s">
         <v>77</v>
       </c>
       <c r="F103" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11628,40 +11631,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="J103" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="K103" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="L103" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="M103" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N103" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O103" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="P103" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="Q103" t="s">
         <v>55</v>
       </c>
       <c r="R103" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="S103" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="T103" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="U103" t="s">
         <v>59</v>
@@ -11673,7 +11676,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C104" t="s">
         <v>75</v>
@@ -11685,7 +11688,7 @@
         <v>77</v>
       </c>
       <c r="F104" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11694,40 +11697,40 @@
         <v>78</v>
       </c>
       <c r="I104" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="J104" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="K104" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="L104" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="M104" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="N104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O104" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="P104" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="Q104" t="s">
         <v>55</v>
       </c>
       <c r="R104" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T104" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U104" t="s">
         <v>59</v>
@@ -11739,19 +11742,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F105" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11760,40 +11763,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="J105" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="K105" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L105" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="M105" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N105" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O105" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="P105" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="Q105" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R105" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S105" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T105" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U105" t="s">
         <v>59</v>
@@ -11805,19 +11808,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C106" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D106" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E106" t="s">
         <v>77</v>
       </c>
       <c r="F106" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11826,38 +11829,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="J106" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="M106" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="N106" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O106" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="P106" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="Q106" t="s">
         <v>55</v>
       </c>
       <c r="R106" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S106" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T106" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U106" t="s">
         <v>59</v>
@@ -11869,19 +11872,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C107" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D107" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="E107" t="s">
         <v>62</v>
       </c>
       <c r="F107" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11890,38 +11893,38 @@
         <v>78</v>
       </c>
       <c r="I107" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="J107" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="M107" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N107" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O107" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="P107" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="Q107" t="s">
         <v>55</v>
       </c>
       <c r="R107" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="S107" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="T107" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="U107" t="s">
         <v>59</v>
@@ -11933,19 +11936,19 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C108" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D108" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E108" t="s">
         <v>62</v>
       </c>
       <c r="F108" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11954,40 +11957,40 @@
         <v>78</v>
       </c>
       <c r="I108" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="J108" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="K108" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="L108" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="M108" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="N108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O108" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="P108" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="Q108" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R108" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="S108" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="T108" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="U108" t="s">
         <v>59</v>
@@ -11999,51 +12002,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C109" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="J109" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="K109" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="O109" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="P109" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="S109" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="T109" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="U109" t="s">
         <v>59</v>
@@ -12055,57 +12058,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C110" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D110" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="J110" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="K110" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="L110" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="M110" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N110" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O110" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="P110" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="Q110" t="s">
         <v>55</v>
       </c>
       <c r="R110" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="S110" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="T110" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="U110" t="s">
         <v>59</v>
@@ -12117,19 +12120,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C111" t="s">
         <v>75</v>
       </c>
       <c r="D111" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="E111" t="s">
         <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12138,40 +12141,40 @@
         <v>78</v>
       </c>
       <c r="I111" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="J111" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="K111" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="L111" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M111" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N111" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O111" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="P111" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="Q111" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R111" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="S111" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="T111" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="U111" t="s">
         <v>59</v>
@@ -12183,19 +12186,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C112" t="s">
         <v>75</v>
       </c>
       <c r="D112" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="E112" t="s">
         <v>62</v>
       </c>
       <c r="F112" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12204,40 +12207,40 @@
         <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="J112" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="K112" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="L112" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="M112" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="N112" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O112" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="P112" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="Q112" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R112" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="S112" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="T112" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="U112" t="s">
         <v>59</v>
@@ -12249,7 +12252,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C113" t="s">
         <v>75</v>
@@ -12261,7 +12264,7 @@
         <v>62</v>
       </c>
       <c r="F113" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12270,40 +12273,40 @@
         <v>78</v>
       </c>
       <c r="I113" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="J113" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="K113" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="L113" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="M113" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="N113" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O113" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="P113" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="Q113" t="s">
         <v>55</v>
       </c>
       <c r="R113" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S113" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="T113" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U113" t="s">
         <v>59</v>
@@ -12315,19 +12318,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D114" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12336,40 +12339,40 @@
         <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="J114" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="K114" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="L114" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="M114" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N114" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O114" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="P114" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="Q114" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R114" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="S114" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="T114" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="U114" t="s">
         <v>59</v>
@@ -12381,19 +12384,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12402,40 +12405,40 @@
         <v>78</v>
       </c>
       <c r="I115" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="J115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="K115" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="L115" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="M115" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="N115" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O115" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="P115" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="Q115" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R115" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="S115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="T115" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="U115" t="s">
         <v>59</v>
@@ -12447,61 +12450,61 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="E116" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="F116" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
       </c>
       <c r="H116" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I116" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="J116" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="K116" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="L116" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="M116" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="N116" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O116" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="P116" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="Q116" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R116" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="S116" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="T116" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="U116" t="s">
         <v>59</v>
@@ -12513,19 +12516,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C117" t="s">
         <v>75</v>
       </c>
       <c r="D117" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E117" t="s">
         <v>77</v>
       </c>
       <c r="F117" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12534,40 +12537,40 @@
         <v>78</v>
       </c>
       <c r="I117" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="J117" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="K117" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="L117" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="M117" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="N117" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O117" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="P117" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="Q117" t="s">
         <v>55</v>
       </c>
       <c r="R117" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="S117" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="T117" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="U117" t="s">
         <v>59</v>
@@ -12579,19 +12582,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C118" t="s">
         <v>75</v>
       </c>
       <c r="D118" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12600,40 +12603,40 @@
         <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="J118" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="K118" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="L118" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="M118" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N118" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O118" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="P118" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="Q118" t="s">
         <v>55</v>
       </c>
       <c r="R118" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="S118" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="T118" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="U118" t="s">
         <v>59</v>
@@ -12645,19 +12648,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C119" t="s">
         <v>75</v>
       </c>
       <c r="D119" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E119" t="s">
         <v>62</v>
       </c>
       <c r="F119" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12666,40 +12669,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="J119" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="K119" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="L119" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="M119" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="N119" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O119" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="P119" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="Q119" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R119" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="S119" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="T119" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="U119" t="s">
         <v>59</v>
@@ -12711,19 +12714,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C120" t="s">
         <v>75</v>
       </c>
       <c r="D120" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12732,40 +12735,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="J120" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="K120" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="L120" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="M120" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="N120" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O120" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="P120" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="Q120" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R120" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S120" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T120" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U120" t="s">
         <v>59</v>
@@ -12777,19 +12780,19 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C121" t="s">
         <v>75</v>
       </c>
       <c r="D121" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E121" t="s">
         <v>77</v>
       </c>
       <c r="F121" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12798,40 +12801,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="J121" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="K121" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="L121" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="M121" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="N121" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O121" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="P121" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="Q121" t="s">
         <v>55</v>
       </c>
       <c r="R121" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S121" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T121" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U121" t="s">
         <v>59</v>
@@ -12843,19 +12846,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C122" t="s">
         <v>75</v>
       </c>
       <c r="D122" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E122" t="s">
         <v>62</v>
       </c>
       <c r="F122" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12864,40 +12867,40 @@
         <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="J122" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="K122" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="L122" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="M122" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="N122" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O122" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="P122" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="Q122" t="s">
         <v>55</v>
       </c>
       <c r="R122" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="S122" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="T122" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="U122" t="s">
         <v>59</v>
@@ -12909,19 +12912,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C123" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D123" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E123" t="s">
         <v>62</v>
       </c>
       <c r="F123" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12930,40 +12933,40 @@
         <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="J123" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="K123" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="L123" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="M123" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="N123" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O123" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="P123" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="Q123" t="s">
         <v>55</v>
       </c>
       <c r="R123" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="S123" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="T123" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="U123" t="s">
         <v>59</v>
@@ -12975,19 +12978,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C124" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D124" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E124" t="s">
         <v>77</v>
       </c>
       <c r="F124" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12996,38 +12999,38 @@
         <v>78</v>
       </c>
       <c r="I124" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="J124" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M124" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="N124" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O124" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="P124" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="Q124" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R124" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S124" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T124" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U124" t="s">
         <v>59</v>
@@ -13039,19 +13042,19 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D125" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E125" t="s">
         <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13060,38 +13063,38 @@
         <v>78</v>
       </c>
       <c r="I125" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="J125" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="M125" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="N125" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O125" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="P125" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="Q125" t="s">
         <v>55</v>
       </c>
       <c r="R125" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S125" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T125" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U125" t="s">
         <v>59</v>
@@ -13103,17 +13106,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13122,40 +13125,40 @@
         <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="J126" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="K126" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="L126" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M126" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="N126" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O126" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="P126" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="Q126" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R126" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="S126" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="T126" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="U126" t="s">
         <v>59</v>
@@ -13167,19 +13170,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C127" t="s">
         <v>75</v>
       </c>
       <c r="D127" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E127" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F127" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13188,40 +13191,40 @@
         <v>78</v>
       </c>
       <c r="I127" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="J127" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="K127" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="L127" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="M127" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="N127" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O127" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="P127" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="Q127" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R127" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="S127" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="T127" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="U127" t="s">
         <v>59</v>
@@ -13233,19 +13236,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E128" t="s">
         <v>62</v>
       </c>
       <c r="F128" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13254,40 +13257,40 @@
         <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="J128" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="K128" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="L128" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="M128" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="N128" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O128" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="P128" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="Q128" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R128" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="S128" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="T128" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="U128" t="s">
         <v>59</v>
@@ -13299,61 +13302,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="E129" t="s">
         <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I129" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="J129" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="K129" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="L129" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="M129" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="N129" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O129" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="P129" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="Q129" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R129" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="S129" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="T129" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="U129" t="s">
         <v>59</v>
@@ -13365,61 +13368,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E130" t="s">
         <v>62</v>
       </c>
       <c r="F130" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I130" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="J130" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="K130" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="L130" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="M130" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="N130" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O130" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="P130" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="Q130" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R130" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="S130" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="T130" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="U130" t="s">
         <v>59</v>
@@ -13431,61 +13434,61 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C131" t="s">
         <v>75</v>
       </c>
       <c r="D131" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="E131" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F131" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
       </c>
       <c r="H131" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I131" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="J131" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="K131" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="L131" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="M131" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="N131" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O131" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="P131" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="Q131" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R131" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S131" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T131" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U131" t="s">
         <v>59</v>
@@ -13497,7 +13500,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C132" t="s">
         <v>75</v>
@@ -13509,7 +13512,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13518,40 +13521,40 @@
         <v>78</v>
       </c>
       <c r="I132" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="J132" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="K132" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="L132" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="M132" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="N132" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O132" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="P132" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="Q132" t="s">
         <v>55</v>
       </c>
       <c r="R132" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="S132" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="T132" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="U132" t="s">
         <v>59</v>
@@ -13563,19 +13566,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C133" t="s">
         <v>75</v>
       </c>
       <c r="D133" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E133" t="s">
         <v>77</v>
       </c>
       <c r="F133" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13584,40 +13587,40 @@
         <v>78</v>
       </c>
       <c r="I133" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="J133" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="K133" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="L133" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="M133" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="N133" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O133" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="P133" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="Q133" t="s">
         <v>55</v>
       </c>
       <c r="R133" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="S133" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="T133" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="U133" t="s">
         <v>59</v>
@@ -13629,19 +13632,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C134" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D134" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="E134" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F134" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13650,38 +13653,38 @@
         <v>78</v>
       </c>
       <c r="I134" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="J134" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M134" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="N134" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O134" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="P134" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="Q134" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R134" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="S134" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="T134" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="U134" t="s">
         <v>59</v>
@@ -13693,19 +13696,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C135" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D135" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="E135" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F135" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13714,38 +13717,38 @@
         <v>78</v>
       </c>
       <c r="I135" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="J135" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="M135" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="N135" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O135" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="P135" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="Q135" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R135" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="S135" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="T135" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="U135" t="s">
         <v>59</v>
@@ -13757,19 +13760,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C136" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D136" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="E136" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13778,38 +13781,38 @@
         <v>78</v>
       </c>
       <c r="I136" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="J136" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="M136" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="N136" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O136" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="P136" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="Q136" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R136" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S136" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T136" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U136" t="s">
         <v>59</v>
@@ -13821,19 +13824,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C137" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D137" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13842,38 +13845,38 @@
         <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="J137" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="M137" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="N137" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O137" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="P137" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="Q137" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R137" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="S137" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="T137" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="U137" t="s">
         <v>59</v>
@@ -13885,57 +13888,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C138" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D138" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I138" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="J138" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="K138" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="L138" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="M138" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="N138" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O138" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="P138" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="Q138" t="s">
         <v>55</v>
       </c>
       <c r="R138" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="S138" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="T138" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="U138" t="s">
         <v>59</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="1541">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t xml:space="preserve">Planification ferroviaire : Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pianificazione ferroviaria: il Consiglio federale può ignorare i mandati del Parlamento?</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
@@ -5353,34 +5356,34 @@
         <v>93</v>
       </c>
       <c r="K6" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N6" t="s">
         <v>52</v>
       </c>
       <c r="O6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q6" t="s">
         <v>55</v>
       </c>
       <c r="R6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -5392,16 +5395,16 @@
         <v>20263323</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
         <v>91</v>
@@ -5410,43 +5413,43 @@
         <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N7" t="s">
         <v>52</v>
       </c>
       <c r="O7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="s">
         <v>55</v>
       </c>
       <c r="R7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -5458,19 +5461,19 @@
         <v>20263120</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
         <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G8" t="s">
         <v>45</v>
@@ -5479,40 +5482,40 @@
         <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s">
         <v>52</v>
       </c>
       <c r="O8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
       </c>
       <c r="R8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U8" t="s">
         <v>59</v>
@@ -5524,7 +5527,7 @@
         <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
         <v>75</v>
@@ -5536,7 +5539,7 @@
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -5545,40 +5548,40 @@
         <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s">
         <v>52</v>
       </c>
       <c r="O9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U9" t="s">
         <v>59</v>
@@ -5590,17 +5593,17 @@
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G10" t="s">
         <v>45</v>
@@ -5609,40 +5612,40 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s">
         <v>52</v>
       </c>
       <c r="O10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q10" t="s">
         <v>55</v>
       </c>
       <c r="R10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -5654,10 +5657,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5666,7 +5669,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5675,40 +5678,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N11" t="s">
         <v>52</v>
       </c>
       <c r="O11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -5720,59 +5723,59 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
         <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -5784,19 +5787,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5805,28 +5808,28 @@
         <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N13" t="s">
         <v>52</v>
       </c>
       <c r="O13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q13" t="s">
         <v>55</v>
@@ -5850,19 +5853,19 @@
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5871,38 +5874,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -5914,51 +5917,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -5970,19 +5973,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5991,38 +5994,38 @@
         <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q16" t="s">
         <v>55</v>
       </c>
       <c r="R16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -6034,17 +6037,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6053,40 +6056,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q17" t="s">
         <v>55</v>
       </c>
       <c r="R17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="T17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -6098,16 +6101,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6119,40 +6122,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U18" t="s">
         <v>59</v>
@@ -6164,13 +6167,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
         <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
@@ -6185,40 +6188,40 @@
         <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -6230,7 +6233,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6242,49 +6245,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -6296,10 +6299,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6308,7 +6311,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6317,40 +6320,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="S21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T21" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -6362,19 +6365,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
         <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6383,40 +6386,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U22" t="s">
         <v>59</v>
@@ -6428,19 +6431,19 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
         <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6449,40 +6452,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N23" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="T23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="U23" t="s">
         <v>59</v>
@@ -6494,19 +6497,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E24" t="s">
         <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6515,40 +6518,40 @@
         <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="S24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U24" t="s">
         <v>59</v>
@@ -6560,59 +6563,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E25" t="s">
         <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I25" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q25" t="s">
         <v>55</v>
       </c>
       <c r="R25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S25" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="U25" t="s">
         <v>59</v>
@@ -6624,19 +6627,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D26" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6645,38 +6648,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J26" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O26" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P26" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q26" t="s">
         <v>55</v>
       </c>
       <c r="R26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U26" t="s">
         <v>59</v>
@@ -6688,17 +6691,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6707,40 +6710,40 @@
         <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O27" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q27" t="s">
         <v>55</v>
       </c>
       <c r="R27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="U27" t="s">
         <v>59</v>
@@ -6752,19 +6755,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E28" t="s">
         <v>77</v>
       </c>
       <c r="F28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6773,40 +6776,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K28" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
       </c>
       <c r="R28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="T28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="U28" t="s">
         <v>59</v>
@@ -6818,19 +6821,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6839,40 +6842,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J29" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
       </c>
       <c r="R29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U29" t="s">
         <v>59</v>
@@ -6884,7 +6887,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
@@ -6896,7 +6899,7 @@
         <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6905,31 +6908,31 @@
         <v>78</v>
       </c>
       <c r="I30" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L30" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R30" t="s">
         <v>86</v>
@@ -6950,7 +6953,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6962,7 +6965,7 @@
         <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6971,40 +6974,40 @@
         <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J31" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K31" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="S31" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="T31" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U31" t="s">
         <v>59</v>
@@ -7016,19 +7019,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C32" t="s">
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -7037,40 +7040,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P32" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U32" t="s">
         <v>59</v>
@@ -7082,7 +7085,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C33" t="s">
         <v>75</v>
@@ -7094,49 +7097,49 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L33" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M33" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="S33" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T33" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="U33" t="s">
         <v>59</v>
@@ -7148,61 +7151,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C34" t="s">
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E34" t="s">
         <v>77</v>
       </c>
       <c r="F34" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I34" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J34" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K34" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L34" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M34" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O34" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P34" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q34" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R34" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S34" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="T34" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="U34" t="s">
         <v>59</v>
@@ -7214,19 +7217,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7235,40 +7238,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J35" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K35" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M35" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O35" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P35" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R35" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="S35" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T35" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U35" t="s">
         <v>59</v>
@@ -7280,10 +7283,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C36" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D36" t="s">
         <v>76</v>
@@ -7292,7 +7295,7 @@
         <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7301,40 +7304,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J36" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K36" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L36" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M36" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N36" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O36" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P36" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="S36" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="T36" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="U36" t="s">
         <v>59</v>
@@ -7346,19 +7349,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7367,40 +7370,40 @@
         <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J37" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K37" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L37" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M37" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O37" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P37" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q37" t="s">
         <v>55</v>
       </c>
       <c r="R37" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="S37" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T37" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="U37" t="s">
         <v>59</v>
@@ -7412,19 +7415,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D38" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E38" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F38" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7433,38 +7436,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O38" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P38" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U38" t="s">
         <v>59</v>
@@ -7476,59 +7479,59 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D39" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I39" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M39" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O39" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P39" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R39" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="S39" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="T39" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="U39" t="s">
         <v>59</v>
@@ -7540,19 +7543,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D40" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E40" t="s">
         <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7561,38 +7564,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J40" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M40" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O40" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P40" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R40" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="S40" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="T40" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="U40" t="s">
         <v>59</v>
@@ -7604,61 +7607,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C41" t="s">
         <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E41" t="s">
         <v>77</v>
       </c>
       <c r="F41" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I41" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J41" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K41" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L41" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M41" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O41" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P41" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Q41" t="s">
         <v>55</v>
       </c>
       <c r="R41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="S41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T41" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="U41" t="s">
         <v>59</v>
@@ -7670,59 +7673,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E42" t="s">
         <v>77</v>
       </c>
       <c r="F42" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I42" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J42" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M42" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O42" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P42" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q42" t="s">
         <v>55</v>
       </c>
       <c r="R42" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="S42" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="T42" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="U42" t="s">
         <v>59</v>
@@ -7734,45 +7737,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C43" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D43" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I43" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K43" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L43" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M43" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O43" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P43" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Q43" t="s">
         <v>55</v>
@@ -7790,19 +7793,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C44" t="s">
         <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E44" t="s">
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7811,40 +7814,40 @@
         <v>78</v>
       </c>
       <c r="I44" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J44" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K44" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L44" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M44" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O44" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P44" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R44" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="S44" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T44" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="U44" t="s">
         <v>59</v>
@@ -7856,19 +7859,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C45" t="s">
         <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E45" t="s">
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7877,40 +7880,40 @@
         <v>78</v>
       </c>
       <c r="I45" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J45" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K45" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M45" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O45" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P45" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q45" t="s">
         <v>55</v>
       </c>
       <c r="R45" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S45" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="T45" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="U45" t="s">
         <v>59</v>
@@ -7922,19 +7925,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7943,40 +7946,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J46" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K46" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L46" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M46" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N46" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O46" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P46" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Q46" t="s">
         <v>55</v>
       </c>
       <c r="R46" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="S46" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="T46" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="U46" t="s">
         <v>59</v>
@@ -7988,7 +7991,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -7998,7 +8001,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -8007,40 +8010,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J47" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K47" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L47" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M47" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O47" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P47" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Q47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R47" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="S47" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="T47" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U47" t="s">
         <v>59</v>
@@ -8052,19 +8055,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C48" t="s">
         <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E48" t="s">
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8073,40 +8076,40 @@
         <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J48" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K48" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L48" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M48" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P48" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Q48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R48" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="S48" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="T48" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="U48" t="s">
         <v>59</v>
@@ -8118,19 +8121,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C49" t="s">
         <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E49" t="s">
         <v>62</v>
       </c>
       <c r="F49" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8139,31 +8142,31 @@
         <v>78</v>
       </c>
       <c r="I49" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J49" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L49" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M49" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P49" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R49" t="s">
         <v>86</v>
@@ -8184,17 +8187,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D50" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8203,40 +8206,40 @@
         <v>78</v>
       </c>
       <c r="I50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J50" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L50" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O50" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P50" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="Q50" t="s">
         <v>55</v>
       </c>
       <c r="R50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="T50" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U50" t="s">
         <v>59</v>
@@ -8248,19 +8251,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C51" t="s">
         <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F51" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8269,40 +8272,40 @@
         <v>78</v>
       </c>
       <c r="I51" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J51" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="K51" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L51" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M51" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O51" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P51" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Q51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R51" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S51" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="T51" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="U51" t="s">
         <v>59</v>
@@ -8314,19 +8317,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C52" t="s">
         <v>75</v>
       </c>
       <c r="D52" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E52" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8335,40 +8338,40 @@
         <v>78</v>
       </c>
       <c r="I52" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J52" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K52" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L52" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M52" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O52" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P52" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Q52" t="s">
         <v>55</v>
       </c>
       <c r="R52" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="S52" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T52" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="U52" t="s">
         <v>59</v>
@@ -8380,19 +8383,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E53" t="s">
         <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8401,40 +8404,40 @@
         <v>78</v>
       </c>
       <c r="I53" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K53" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L53" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M53" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N53" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O53" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P53" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Q53" t="s">
         <v>55</v>
       </c>
       <c r="R53" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U53" t="s">
         <v>59</v>
@@ -8446,19 +8449,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E54" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F54" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8467,40 +8470,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="J54" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="K54" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L54" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M54" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N54" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O54" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P54" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Q54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R54" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="S54" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="T54" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="U54" t="s">
         <v>59</v>
@@ -8512,19 +8515,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E55" t="s">
         <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8533,40 +8536,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J55" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="K55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O55" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P55" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Q55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R55" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S55" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T55" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U55" t="s">
         <v>59</v>
@@ -8578,17 +8581,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8597,40 +8600,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J56" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K56" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L56" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M56" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N56" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O56" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P56" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Q56" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R56" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S56" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T56" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U56" t="s">
         <v>59</v>
@@ -8642,61 +8645,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D57" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I57" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J57" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K57" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L57" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M57" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O57" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="P57" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q57" t="s">
         <v>55</v>
       </c>
       <c r="R57" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="S57" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="T57" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="U57" t="s">
         <v>59</v>
@@ -8708,19 +8711,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C58" t="s">
         <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8729,40 +8732,40 @@
         <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J58" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="K58" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M58" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O58" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P58" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Q58" t="s">
         <v>55</v>
       </c>
       <c r="R58" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="S58" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="T58" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="U58" t="s">
         <v>59</v>
@@ -8774,19 +8777,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C59" t="s">
         <v>75</v>
       </c>
       <c r="D59" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F59" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8795,40 +8798,40 @@
         <v>78</v>
       </c>
       <c r="I59" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J59" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="K59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L59" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M59" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O59" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P59" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R59" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="S59" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T59" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="U59" t="s">
         <v>59</v>
@@ -8840,19 +8843,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8861,40 +8864,40 @@
         <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J60" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K60" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L60" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M60" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O60" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P60" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Q60" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R60" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="S60" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="T60" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="U60" t="s">
         <v>59</v>
@@ -8906,7 +8909,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8918,7 +8921,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8927,40 +8930,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J61" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="K61" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L61" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M61" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N61" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O61" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P61" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Q61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R61" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S61" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T61" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U61" t="s">
         <v>59</v>
@@ -8972,19 +8975,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C62" t="s">
         <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8993,40 +8996,40 @@
         <v>78</v>
       </c>
       <c r="I62" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J62" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="K62" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="L62" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M62" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O62" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="P62" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="Q62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R62" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S62" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="T62" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="U62" t="s">
         <v>59</v>
@@ -9038,19 +9041,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C63" t="s">
         <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E63" t="s">
         <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9059,40 +9062,40 @@
         <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J63" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="K63" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="L63" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M63" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O63" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P63" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Q63" t="s">
         <v>55</v>
       </c>
       <c r="R63" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="S63" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="T63" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="U63" t="s">
         <v>59</v>
@@ -9104,45 +9107,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D64" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>78</v>
       </c>
       <c r="I64" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J64" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K64" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="L64" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M64" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="P64" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Q64" t="s">
         <v>55</v>
@@ -9160,45 +9163,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C65" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D65" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J65" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K65" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L65" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M65" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N65" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O65" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P65" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Q65" t="s">
         <v>55</v>
@@ -9216,17 +9219,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C66" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D66" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9235,40 +9238,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="J66" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="K66" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L66" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M66" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P66" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="Q66" t="s">
         <v>55</v>
       </c>
       <c r="R66" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="S66" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="T66" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="U66" t="s">
         <v>59</v>
@@ -9280,19 +9283,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C67" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D67" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E67" t="s">
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9301,40 +9304,40 @@
         <v>78</v>
       </c>
       <c r="I67" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J67" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K67" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L67" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M67" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O67" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P67" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="Q67" t="s">
         <v>55</v>
       </c>
       <c r="R67" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="S67" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="T67" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="U67" t="s">
         <v>59</v>
@@ -9346,19 +9349,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C68" t="s">
         <v>75</v>
       </c>
       <c r="D68" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E68" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F68" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9367,40 +9370,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J68" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K68" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L68" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M68" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O68" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="P68" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="Q68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R68" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="S68" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="T68" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="U68" t="s">
         <v>59</v>
@@ -9412,61 +9415,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C69" t="s">
         <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I69" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J69" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K69" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="L69" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M69" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O69" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="P69" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q69" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R69" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="S69" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="T69" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="U69" t="s">
         <v>59</v>
@@ -9478,19 +9481,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F70" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9499,40 +9502,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J70" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K70" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="L70" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M70" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N70" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O70" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P70" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="Q70" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R70" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="S70" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="T70" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="U70" t="s">
         <v>59</v>
@@ -9544,19 +9547,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E71" t="s">
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9565,40 +9568,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J71" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K71" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="L71" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M71" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O71" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P71" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="Q71" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R71" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="S71" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="T71" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="U71" t="s">
         <v>59</v>
@@ -9610,19 +9613,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C72" t="s">
         <v>75</v>
       </c>
       <c r="D72" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E72" t="s">
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9631,40 +9634,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J72" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K72" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L72" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M72" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O72" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="P72" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="Q72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R72" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="S72" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T72" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="U72" t="s">
         <v>59</v>
@@ -9676,19 +9679,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C73" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D73" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9697,40 +9700,40 @@
         <v>78</v>
       </c>
       <c r="I73" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J73" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="K73" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="L73" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M73" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O73" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="P73" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="Q73" t="s">
         <v>55</v>
       </c>
       <c r="R73" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="S73" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="T73" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="U73" t="s">
         <v>59</v>
@@ -9742,19 +9745,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C74" t="s">
         <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E74" t="s">
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9763,40 +9766,40 @@
         <v>78</v>
       </c>
       <c r="I74" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J74" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="K74" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="L74" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M74" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O74" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="P74" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="Q74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R74" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="S74" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="T74" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="U74" t="s">
         <v>59</v>
@@ -9808,45 +9811,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C75" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D75" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>78</v>
       </c>
       <c r="I75" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J75" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="K75" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="L75" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M75" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="N75" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O75" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="P75" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="Q75" t="s">
         <v>55</v>
@@ -9864,7 +9867,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9876,7 +9879,7 @@
         <v>77</v>
       </c>
       <c r="F76" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9885,40 +9888,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J76" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="K76" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="L76" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M76" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O76" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="P76" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Q76" t="s">
         <v>55</v>
       </c>
       <c r="R76" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S76" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="T76" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="U76" t="s">
         <v>59</v>
@@ -9930,19 +9933,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D77" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E77" t="s">
         <v>77</v>
       </c>
       <c r="F77" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9951,38 +9954,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="J77" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M77" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="N77" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O77" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="P77" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="Q77" t="s">
         <v>55</v>
       </c>
       <c r="R77" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="S77" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="T77" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="U77" t="s">
         <v>59</v>
@@ -9994,19 +9997,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D78" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E78" t="s">
         <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -10015,38 +10018,38 @@
         <v>78</v>
       </c>
       <c r="I78" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="J78" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M78" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="N78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O78" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="P78" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="Q78" t="s">
         <v>55</v>
       </c>
       <c r="R78" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="S78" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="T78" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="U78" t="s">
         <v>59</v>
@@ -10058,51 +10061,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="J79" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K79" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O79" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P79" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="S79" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="T79" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="U79" t="s">
         <v>59</v>
@@ -10114,57 +10117,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C80" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D80" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="J80" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K80" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="L80" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="M80" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="P80" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="Q80" t="s">
         <v>55</v>
       </c>
       <c r="R80" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="S80" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="T80" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="U80" t="s">
         <v>59</v>
@@ -10176,57 +10179,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C81" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D81" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>78</v>
       </c>
       <c r="I81" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J81" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K81" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="L81" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M81" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="N81" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O81" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="P81" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="Q81" t="s">
         <v>55</v>
       </c>
       <c r="R81" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="S81" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="T81" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="U81" t="s">
         <v>59</v>
@@ -10238,19 +10241,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E82" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F82" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10259,40 +10262,40 @@
         <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="J82" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="K82" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="L82" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M82" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="N82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O82" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="P82" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="Q82" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R82" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="S82" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="T82" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="U82" t="s">
         <v>59</v>
@@ -10304,61 +10307,61 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
       </c>
       <c r="H83" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I83" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="J83" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="K83" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="L83" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="M83" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="N83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O83" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="P83" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="Q83" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R83" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="S83" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="T83" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="U83" t="s">
         <v>59</v>
@@ -10370,19 +10373,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C84" t="s">
         <v>75</v>
       </c>
       <c r="D84" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E84" t="s">
         <v>77</v>
       </c>
       <c r="F84" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10391,40 +10394,40 @@
         <v>78</v>
       </c>
       <c r="I84" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J84" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="K84" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="L84" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M84" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="N84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O84" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="P84" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="Q84" t="s">
         <v>55</v>
       </c>
       <c r="R84" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S84" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="T84" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="U84" t="s">
         <v>59</v>
@@ -10436,19 +10439,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E85" t="s">
         <v>62</v>
       </c>
       <c r="F85" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10457,40 +10460,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="J85" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="K85" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="L85" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M85" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="N85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O85" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="P85" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="Q85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R85" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="S85" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="T85" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="U85" t="s">
         <v>59</v>
@@ -10502,61 +10505,61 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C86" t="s">
         <v>75</v>
       </c>
       <c r="D86" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
       </c>
       <c r="H86" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I86" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J86" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K86" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="L86" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M86" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="N86" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O86" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="P86" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="Q86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R86" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="S86" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T86" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="U86" t="s">
         <v>59</v>
@@ -10568,61 +10571,61 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E87" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F87" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I87" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="J87" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="K87" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="L87" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M87" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N87" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O87" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="P87" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q87" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R87" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S87" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T87" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="U87" t="s">
         <v>59</v>
@@ -10634,19 +10637,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D88" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E88" t="s">
         <v>77</v>
       </c>
       <c r="F88" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10655,38 +10658,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J88" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="M88" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="N88" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O88" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="P88" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="Q88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T88" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U88" t="s">
         <v>59</v>
@@ -10698,19 +10701,19 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C89" t="s">
         <v>75</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E89" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F89" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10719,31 +10722,31 @@
         <v>78</v>
       </c>
       <c r="I89" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J89" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K89" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="L89" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M89" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="N89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O89" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P89" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="Q89" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R89" t="s">
         <v>86</v>
@@ -10764,19 +10767,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C90" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D90" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10785,38 +10788,38 @@
         <v>78</v>
       </c>
       <c r="I90" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="J90" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="M90" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O90" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="P90" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="Q90" t="s">
         <v>55</v>
       </c>
       <c r="R90" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="S90" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T90" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="U90" t="s">
         <v>59</v>
@@ -10828,19 +10831,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D91" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E91" t="s">
         <v>77</v>
       </c>
       <c r="F91" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10849,38 +10852,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J91" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="M91" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="N91" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O91" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="P91" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="Q91" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U91" t="s">
         <v>59</v>
@@ -10892,19 +10895,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C92" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D92" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E92" t="s">
         <v>77</v>
       </c>
       <c r="F92" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10913,38 +10916,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J92" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="M92" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N92" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O92" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="P92" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="Q92" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T92" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U92" t="s">
         <v>59</v>
@@ -10956,19 +10959,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C93" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D93" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E93" t="s">
         <v>77</v>
       </c>
       <c r="F93" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10977,38 +10980,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J93" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="M93" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N93" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O93" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="P93" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="Q93" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U93" t="s">
         <v>59</v>
@@ -11020,19 +11023,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C94" t="s">
         <v>75</v>
       </c>
       <c r="D94" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E94" t="s">
         <v>77</v>
       </c>
       <c r="F94" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -11041,40 +11044,40 @@
         <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="J94" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K94" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="L94" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="M94" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="N94" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O94" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="P94" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Q94" t="s">
         <v>55</v>
       </c>
       <c r="R94" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="S94" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="T94" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="U94" t="s">
         <v>59</v>
@@ -11086,19 +11089,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C95" t="s">
         <v>75</v>
       </c>
       <c r="D95" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11107,28 +11110,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J95" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="K95" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="L95" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="M95" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N95" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O95" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="P95" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Q95" t="s">
         <v>55</v>
@@ -11152,19 +11155,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C96" t="s">
         <v>75</v>
       </c>
       <c r="D96" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E96" t="s">
         <v>77</v>
       </c>
       <c r="F96" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11173,40 +11176,40 @@
         <v>78</v>
       </c>
       <c r="I96" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="J96" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K96" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="L96" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="M96" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="N96" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O96" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="P96" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="Q96" t="s">
         <v>55</v>
       </c>
       <c r="R96" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="S96" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="T96" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="U96" t="s">
         <v>59</v>
@@ -11218,19 +11221,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C97" t="s">
         <v>75</v>
       </c>
       <c r="D97" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E97" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F97" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11239,40 +11242,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J97" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="K97" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="L97" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="M97" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="N97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O97" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="P97" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="Q97" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R97" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="S97" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="T97" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="U97" t="s">
         <v>59</v>
@@ -11284,57 +11287,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C98" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D98" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I98" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J98" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="K98" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="L98" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="M98" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="P98" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="Q98" t="s">
         <v>55</v>
       </c>
       <c r="R98" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="S98" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="T98" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="U98" t="s">
         <v>59</v>
@@ -11346,61 +11349,61 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I99" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="J99" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K99" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="L99" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="M99" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="N99" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O99" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="P99" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="Q99" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R99" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="S99" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="T99" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="U99" t="s">
         <v>59</v>
@@ -11412,19 +11415,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E100" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F100" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11433,40 +11436,40 @@
         <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="J100" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="K100" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="L100" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="M100" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="N100" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O100" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="P100" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="Q100" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R100" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="S100" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="T100" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="U100" t="s">
         <v>59</v>
@@ -11478,19 +11481,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C101" t="s">
         <v>75</v>
       </c>
       <c r="D101" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E101" t="s">
         <v>62</v>
       </c>
       <c r="F101" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11499,40 +11502,40 @@
         <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J101" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="K101" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="L101" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="M101" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="N101" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O101" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="P101" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="Q101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R101" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="S101" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="T101" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="U101" t="s">
         <v>59</v>
@@ -11544,19 +11547,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E102" t="s">
         <v>62</v>
       </c>
       <c r="F102" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11565,40 +11568,40 @@
         <v>78</v>
       </c>
       <c r="I102" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J102" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="K102" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="L102" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="M102" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="N102" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O102" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="P102" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="Q102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R102" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="S102" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="T102" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="U102" t="s">
         <v>59</v>
@@ -11610,19 +11613,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E103" t="s">
         <v>77</v>
       </c>
       <c r="F103" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11631,40 +11634,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J103" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K103" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="L103" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="M103" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N103" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O103" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="P103" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="Q103" t="s">
         <v>55</v>
       </c>
       <c r="R103" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="S103" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="T103" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="U103" t="s">
         <v>59</v>
@@ -11676,7 +11679,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C104" t="s">
         <v>75</v>
@@ -11688,7 +11691,7 @@
         <v>77</v>
       </c>
       <c r="F104" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11697,28 +11700,28 @@
         <v>78</v>
       </c>
       <c r="I104" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="J104" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="K104" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="L104" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="M104" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N104" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O104" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="P104" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="Q104" t="s">
         <v>55</v>
@@ -11742,19 +11745,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E105" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F105" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11763,40 +11766,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J105" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="K105" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="L105" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="M105" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="N105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O105" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="P105" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="Q105" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R105" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S105" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T105" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U105" t="s">
         <v>59</v>
@@ -11808,19 +11811,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C106" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D106" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="E106" t="s">
         <v>77</v>
       </c>
       <c r="F106" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11829,38 +11832,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="J106" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="M106" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N106" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O106" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="P106" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="Q106" t="s">
         <v>55</v>
       </c>
       <c r="R106" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S106" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T106" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U106" t="s">
         <v>59</v>
@@ -11872,19 +11875,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C107" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D107" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E107" t="s">
         <v>62</v>
       </c>
       <c r="F107" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11893,38 +11896,38 @@
         <v>78</v>
       </c>
       <c r="I107" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="J107" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="M107" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N107" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O107" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="P107" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="Q107" t="s">
         <v>55</v>
       </c>
       <c r="R107" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="S107" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="T107" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="U107" t="s">
         <v>59</v>
@@ -11936,10 +11939,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C108" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D108" t="s">
         <v>90</v>
@@ -11948,7 +11951,7 @@
         <v>62</v>
       </c>
       <c r="F108" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11957,40 +11960,40 @@
         <v>78</v>
       </c>
       <c r="I108" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="J108" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="K108" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="L108" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="M108" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="N108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O108" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="P108" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="Q108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R108" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S108" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="T108" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="U108" t="s">
         <v>59</v>
@@ -12002,51 +12005,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C109" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="J109" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="K109" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="O109" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="P109" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="S109" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="T109" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="U109" t="s">
         <v>59</v>
@@ -12058,57 +12061,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C110" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D110" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="J110" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="K110" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="L110" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="M110" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N110" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O110" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="P110" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="Q110" t="s">
         <v>55</v>
       </c>
       <c r="R110" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="S110" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="T110" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="U110" t="s">
         <v>59</v>
@@ -12120,19 +12123,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C111" t="s">
         <v>75</v>
       </c>
       <c r="D111" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="E111" t="s">
         <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12141,40 +12144,40 @@
         <v>78</v>
       </c>
       <c r="I111" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="J111" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="K111" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="L111" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="M111" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="N111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O111" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="P111" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="Q111" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R111" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="S111" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="T111" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="U111" t="s">
         <v>59</v>
@@ -12186,19 +12189,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C112" t="s">
         <v>75</v>
       </c>
       <c r="D112" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="E112" t="s">
         <v>62</v>
       </c>
       <c r="F112" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12207,40 +12210,40 @@
         <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="J112" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="K112" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="L112" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="M112" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O112" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="P112" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="Q112" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R112" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="S112" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="T112" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="U112" t="s">
         <v>59</v>
@@ -12252,7 +12255,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C113" t="s">
         <v>75</v>
@@ -12264,7 +12267,7 @@
         <v>62</v>
       </c>
       <c r="F113" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12273,40 +12276,40 @@
         <v>78</v>
       </c>
       <c r="I113" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="J113" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="K113" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="L113" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M113" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N113" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O113" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="P113" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="Q113" t="s">
         <v>55</v>
       </c>
       <c r="R113" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S113" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="T113" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="U113" t="s">
         <v>59</v>
@@ -12318,19 +12321,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12339,40 +12342,40 @@
         <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="J114" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="K114" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="L114" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="M114" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O114" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="P114" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q114" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R114" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="S114" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="T114" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="U114" t="s">
         <v>59</v>
@@ -12384,19 +12387,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12405,40 +12408,40 @@
         <v>78</v>
       </c>
       <c r="I115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="J115" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="K115" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="L115" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="M115" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O115" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="P115" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="Q115" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="S115" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="T115" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="U115" t="s">
         <v>59</v>
@@ -12450,61 +12453,61 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E116" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F116" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
       </c>
       <c r="H116" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I116" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="J116" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="K116" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="L116" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="M116" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N116" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O116" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="P116" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="Q116" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R116" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="S116" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="T116" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="U116" t="s">
         <v>59</v>
@@ -12516,19 +12519,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C117" t="s">
         <v>75</v>
       </c>
       <c r="D117" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E117" t="s">
         <v>77</v>
       </c>
       <c r="F117" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12537,40 +12540,40 @@
         <v>78</v>
       </c>
       <c r="I117" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="J117" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="K117" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="L117" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="M117" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="N117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O117" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="P117" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="Q117" t="s">
         <v>55</v>
       </c>
       <c r="R117" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="S117" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="T117" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="U117" t="s">
         <v>59</v>
@@ -12582,19 +12585,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C118" t="s">
         <v>75</v>
       </c>
       <c r="D118" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12603,40 +12606,40 @@
         <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="J118" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="K118" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="L118" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="M118" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N118" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O118" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="P118" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="Q118" t="s">
         <v>55</v>
       </c>
       <c r="R118" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="S118" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="T118" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="U118" t="s">
         <v>59</v>
@@ -12648,19 +12651,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C119" t="s">
         <v>75</v>
       </c>
       <c r="D119" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E119" t="s">
         <v>62</v>
       </c>
       <c r="F119" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12669,40 +12672,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="J119" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="K119" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="L119" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="M119" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="N119" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O119" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="P119" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="Q119" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R119" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="S119" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="T119" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="U119" t="s">
         <v>59</v>
@@ -12714,19 +12717,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C120" t="s">
         <v>75</v>
       </c>
       <c r="D120" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12735,40 +12738,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J120" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K120" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="L120" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="M120" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="N120" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O120" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="P120" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="Q120" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R120" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="S120" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T120" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U120" t="s">
         <v>59</v>
@@ -12780,19 +12783,19 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C121" t="s">
         <v>75</v>
       </c>
       <c r="D121" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E121" t="s">
         <v>77</v>
       </c>
       <c r="F121" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12801,40 +12804,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="J121" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="K121" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="L121" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="M121" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="N121" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O121" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="P121" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="Q121" t="s">
         <v>55</v>
       </c>
       <c r="R121" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S121" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T121" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U121" t="s">
         <v>59</v>
@@ -12846,19 +12849,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C122" t="s">
         <v>75</v>
       </c>
       <c r="D122" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="E122" t="s">
         <v>62</v>
       </c>
       <c r="F122" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12867,40 +12870,40 @@
         <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="J122" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="K122" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="L122" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="M122" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="N122" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O122" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="P122" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q122" t="s">
         <v>55</v>
       </c>
       <c r="R122" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="S122" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="T122" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="U122" t="s">
         <v>59</v>
@@ -12912,19 +12915,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C123" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D123" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E123" t="s">
         <v>62</v>
       </c>
       <c r="F123" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12933,40 +12936,40 @@
         <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="J123" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="K123" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="L123" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="M123" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="N123" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O123" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="P123" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="Q123" t="s">
         <v>55</v>
       </c>
       <c r="R123" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="S123" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="T123" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="U123" t="s">
         <v>59</v>
@@ -12978,19 +12981,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C124" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D124" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E124" t="s">
         <v>77</v>
       </c>
       <c r="F124" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -12999,29 +13002,29 @@
         <v>78</v>
       </c>
       <c r="I124" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="J124" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="M124" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="N124" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O124" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="P124" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="Q124" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R124" t="s">
         <v>86</v>
@@ -13042,10 +13045,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D125" t="s">
         <v>90</v>
@@ -13054,7 +13057,7 @@
         <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13063,26 +13066,26 @@
         <v>78</v>
       </c>
       <c r="I125" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="J125" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="M125" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="N125" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O125" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="P125" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="Q125" t="s">
         <v>55</v>
@@ -13106,17 +13109,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13125,40 +13128,40 @@
         <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="J126" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K126" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="L126" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="M126" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="N126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O126" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="P126" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="Q126" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R126" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="S126" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="T126" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="U126" t="s">
         <v>59</v>
@@ -13170,19 +13173,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="C127" t="s">
         <v>75</v>
       </c>
       <c r="D127" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E127" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F127" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13191,40 +13194,40 @@
         <v>78</v>
       </c>
       <c r="I127" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="J127" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="K127" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="L127" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="M127" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="N127" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O127" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="P127" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="Q127" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R127" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="S127" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="T127" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="U127" t="s">
         <v>59</v>
@@ -13236,19 +13239,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E128" t="s">
         <v>62</v>
       </c>
       <c r="F128" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13257,40 +13260,40 @@
         <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="J128" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="K128" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="L128" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="M128" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="N128" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O128" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="P128" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="Q128" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R128" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="S128" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="T128" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="U128" t="s">
         <v>59</v>
@@ -13302,61 +13305,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="E129" t="s">
         <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I129" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="J129" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="K129" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="L129" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="M129" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="N129" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O129" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="P129" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="Q129" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R129" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="S129" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="T129" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="U129" t="s">
         <v>59</v>
@@ -13368,61 +13371,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E130" t="s">
         <v>62</v>
       </c>
       <c r="F130" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I130" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="J130" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="K130" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="L130" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="M130" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="N130" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O130" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="P130" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="Q130" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R130" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="S130" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="T130" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="U130" t="s">
         <v>59</v>
@@ -13434,61 +13437,61 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C131" t="s">
         <v>75</v>
       </c>
       <c r="D131" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="E131" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
       </c>
       <c r="H131" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I131" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="J131" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="K131" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="L131" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="M131" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="N131" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O131" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="P131" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="Q131" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R131" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="S131" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T131" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="U131" t="s">
         <v>59</v>
@@ -13500,7 +13503,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="C132" t="s">
         <v>75</v>
@@ -13512,7 +13515,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13521,40 +13524,40 @@
         <v>78</v>
       </c>
       <c r="I132" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="J132" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="K132" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="L132" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="M132" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="N132" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O132" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="P132" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="Q132" t="s">
         <v>55</v>
       </c>
       <c r="R132" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="S132" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="T132" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="U132" t="s">
         <v>59</v>
@@ -13566,19 +13569,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C133" t="s">
         <v>75</v>
       </c>
       <c r="D133" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E133" t="s">
         <v>77</v>
       </c>
       <c r="F133" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13587,40 +13590,40 @@
         <v>78</v>
       </c>
       <c r="I133" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="J133" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="K133" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="L133" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="M133" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="N133" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O133" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="P133" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Q133" t="s">
         <v>55</v>
       </c>
       <c r="R133" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="S133" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="T133" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="U133" t="s">
         <v>59</v>
@@ -13632,19 +13635,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C134" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D134" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="E134" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F134" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13653,38 +13656,38 @@
         <v>78</v>
       </c>
       <c r="I134" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="J134" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="M134" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="N134" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O134" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="P134" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="Q134" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R134" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="S134" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="T134" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="U134" t="s">
         <v>59</v>
@@ -13696,19 +13699,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C135" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D135" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="E135" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F135" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13717,38 +13720,38 @@
         <v>78</v>
       </c>
       <c r="I135" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="J135" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="M135" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="N135" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O135" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="P135" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="Q135" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R135" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="S135" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="T135" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="U135" t="s">
         <v>59</v>
@@ -13760,19 +13763,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="C136" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D136" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="E136" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F136" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13781,38 +13784,38 @@
         <v>78</v>
       </c>
       <c r="I136" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="J136" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="M136" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="N136" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O136" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="P136" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="Q136" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R136" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="S136" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T136" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="U136" t="s">
         <v>59</v>
@@ -13824,19 +13827,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D137" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13845,38 +13848,38 @@
         <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="J137" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="M137" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="N137" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O137" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="P137" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="Q137" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R137" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="S137" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="T137" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="U137" t="s">
         <v>59</v>
@@ -13888,57 +13891,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C138" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D138" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I138" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="J138" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="K138" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="L138" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="M138" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="N138" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O138" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="P138" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="Q138" t="s">
         <v>55</v>
       </c>
       <c r="R138" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="S138" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="T138" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="U138" t="s">
         <v>59</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Pour des laits et aliments infantiles sûrs en tout temps, garantir la prévention et l'information en cas de contamination</t>
   </si>
   <si>
-    <t xml:space="preserve">Titolo segue</t>
+    <t xml:space="preserve">Garantire la prevenzione e l’informazione in caso di contaminazione per far sì che il latte e gli alimenti per la prima infanzia siano sempre sicuri</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre les mesures nécessaires pour assurer la sécurité de la population lors de cas de contaminations alimentaires, en particulier des laits et aliments infantiles. Il s’agit de garantir l’application des articles 26 à 29 de la loi sur les denrées alimentaires (LDAI), qui règlent les obligations des entreprises (autocontrôle, garantie de la protection de la santé, traçabilité, devoir d’assistance et obligation de renseigner). Les mesures prises visent à garantir que les cas de contamination soient communiqués rapidement aux autorités alimentaires et sanitaires ainsi qu'au public, que les rappels soient effectués dans les meilleurs délais et que les produits rappelés le soient effectivement.&lt;/p&gt;</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">2026-03-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Bahnplanung: Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planification ferroviaire : Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pianificazione ferroviaria: il Consiglio federale può ignorare i mandati del Parlamento?</t>
+    <t xml:space="preserve">Bahnplanung. Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planification ferroviaire. Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pianificazione ferroviaria. Il Consiglio federale può ignorare i mandati del Parlamento?</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -206,13 +206,13 @@
     <t xml:space="preserve">EDI</t>
   </si>
   <si>
-    <t xml:space="preserve">Jederzeit sichere Säuglingsnahrung: Prävention und Aufklärung im Fall einer Kontamination gewährleisten</t>
+    <t xml:space="preserve">Jederzeit sichere Säuglingsnahrung. Prävention und Aufklärung im Fall einer Kontamination gewährleisten</t>
   </si>
   <si>
     <t xml:space="preserve">Pour des laits et aliments infantiles sûrs en tout temps, garantir la prévention et l'information en cas de contamination</t>
   </si>
   <si>
-    <t xml:space="preserve">Garantire la prevenzione e l’informazione in caso di contaminazione per far sì che il latte e gli alimenti per la prima infanzia siano sempre sicuri</t>
+    <t xml:space="preserve">Garantire la prevenzione e l'informazione in caso di contaminazione per far sì che il latte e gli alimenti per la prima infanzia siano sempre sicuri</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre les mesures nécessaires pour assurer la sécurité de la population lors de cas de contaminations alimentaires, en particulier des laits et aliments infantiles. Il s’agit de garantir l’application des articles 26 à 29 de la loi sur les denrées alimentaires (LDAI), qui règlent les obligations des entreprises (autocontrôle, garantie de la protection de la santé, traçabilité, devoir d’assistance et obligation de renseigner). Les mesures prises visent à garantir que les cas de contamination soient communiqués rapidement aux autorités alimentaires et sanitaires ainsi qu'au public, que les rappels soient effectués dans les meilleurs délais et que les produits rappelés le soient effectivement.&lt;/p&gt;</t>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1543">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -386,6 +386,9 @@
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, welcher die Streichung von Art. 22 des Epidemiengesetzes (EpG) vorsieht.&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263120</t>
   </si>
   <si>
@@ -401,6 +404,9 @@
     <t xml:space="preserve">Politica nazionale|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
@@ -572,6 +578,9 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
   </si>
   <si>
+    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.7151</t>
   </si>
   <si>
@@ -746,16 +755,10 @@
     <t xml:space="preserve">&lt;p&gt;Der Kanton Genf hat provisorische Steuerrechnungen der vergangenen Jahre teilweise noch nicht ausgestellt und muss dies nun korrigieren. Für den Bund führt dies zu einmaligen Mehreinnahmen von insgesamt rund 600-800 Millionen Franken (Quelle: https://www.news.admin.ch/de/newnsb/Y973XYMqlzrucihcHqlyi)&lt;/p&gt;&lt;p&gt;Der Kanton Genf hat für die Jahre 2019 bis 2024 in einem grösseren Umfang als angenommen keine provisorischen Steuerrechnungen ausgestellt. Dies widerspricht dem Bundesgesetz über die direkte Bundessteuer, wonach mindestens eine provisorische Steuerrechnung ausgestellt werden muss. Das Fehlen von provisorischen Steuerrechnungen hat womöglich auch Einfluss auf die Berechnung des Ressourcenpotenzials im Ressourcenausgleich zwischen Bund und Kantonen, da bei fehlenden definitiven Veranlagungen die in Rechnung gestellten Steuerfaktoren berücksichtigt werden.&lt;/p&gt;&lt;p&gt;Der Bundesrat wird gebeten, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;Welche Auswirkungen haben diese nicht erfassten provisorischen Steuerrechnungen im Kanton Genf auf das Ressourcenpotenzial und die damit berechneten Ausgleichszahlungen?&lt;/li&gt;&lt;li&gt;Sind die Steuerbemessungsgrundlagen, welche die hohen Nachzahlungen bei der Bundessteuer bewirkt haben, in die aggregierte Steuerbemessungsgrundlage für die Ermittlung des Ressourcenpotenzials und des Ressourcenindexes mit eingeflossen oder werden sie noch einfliessen?&lt;/li&gt;&lt;li&gt;Falls das nicht der Fall ist - kann das fehlende Ressourcenpotenzial dem Kanton Genf nachgetragen werden, so dass es in den Folgeperioden noch für die Berechnung der Ausgleichszahlungen mitberücksichtigt wird?&lt;/li&gt;&lt;li&gt;Welches sind die gesetzlichen Grundlagen und Weisungen für die Erfassung der Steuerbemessungsgrundlagen für den Ressourcenausgleich sowie für die Handhabung von fehlerhaften Datenlieferungen und nachträglichen Korrekturen?&lt;/li&gt;&lt;li&gt;Wer prüft die Einhaltung der Regeln für die korrekte Erfassung der Bemessungsgrundlagen des Ressourcenpotenzials durch die Kantone?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Haben die Kantone einen Spielraum, mit verzögerter Rechnungsstellung oder anderen Aktivitäten das Ressourcenpotenzial zu ihren Gunsten zu optimieren?&lt;/li&gt;&lt;li&gt;Gibt es aus anderen Kantonen Hinweise , über Optimierungsmöglichkeiten bei der Bemessung des Ressourcenpotenzials? Wenn ja, welche Optimierungen werden getätigt?&lt;/li&gt;&lt;li&gt;Welche Sanktionsmöglichkeiten hat der Bund gegenüber Kantonen, die sich bei der Datenlieferung für die Berechnung des Ressourcenpotenzials nicht regelkonform verhalten?&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254836</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
   </si>
   <si>
     <t xml:space="preserve">Staatspolitik|Steuer</t>
@@ -5500,37 +5503,39 @@
         <v>123</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="O8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
       </c>
       <c r="R8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U8" t="s">
-        <v>59</v>
-      </c>
-      <c r="V8"/>
+        <v>130</v>
+      </c>
+      <c r="V8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>20263121</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
         <v>75</v>
@@ -5551,28 +5556,28 @@
         <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="O9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="P9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
@@ -5587,22 +5592,24 @@
         <v>101</v>
       </c>
       <c r="U9" t="s">
-        <v>59</v>
-      </c>
-      <c r="V9"/>
+        <v>130</v>
+      </c>
+      <c r="V9" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>20263131</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -5615,40 +5622,40 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s">
         <v>52</v>
       </c>
       <c r="O10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q10" t="s">
         <v>55</v>
       </c>
       <c r="R10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="T10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -5660,10 +5667,10 @@
         <v>20263099</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -5672,7 +5679,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -5681,40 +5688,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N11" t="s">
         <v>52</v>
       </c>
       <c r="O11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="S11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="T11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -5726,19 +5733,19 @@
         <v>20267194</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
         <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G12" t="s">
         <v>45</v>
@@ -5747,38 +5754,38 @@
         <v>105</v>
       </c>
       <c r="I12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q12" t="s">
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="S12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="T12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -5790,19 +5797,19 @@
         <v>20263069</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E13" t="s">
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
@@ -5811,31 +5818,31 @@
         <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N13" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="O13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q13" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="R13" t="s">
         <v>86</v>
@@ -5847,28 +5854,30 @@
         <v>88</v>
       </c>
       <c r="U13" t="s">
-        <v>59</v>
-      </c>
-      <c r="V13"/>
+        <v>130</v>
+      </c>
+      <c r="V13" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>20267151</v>
       </c>
       <c r="B14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -5877,38 +5886,38 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="T14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -5920,51 +5929,51 @@
         <v>20260030</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q15" t="s">
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -5976,19 +5985,19 @@
         <v>20267032</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G16" t="s">
         <v>45</v>
@@ -5997,38 +6006,38 @@
         <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J16" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q16" t="s">
         <v>55</v>
       </c>
       <c r="R16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="S16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="T16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -6040,17 +6049,17 @@
         <v>20263006</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -6059,40 +6068,40 @@
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q17" t="s">
         <v>55</v>
       </c>
       <c r="R17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="S17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="T17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -6104,16 +6113,16 @@
         <v>20254836</v>
       </c>
       <c r="B18" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E18" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -6125,40 +6134,40 @@
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K18" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L18" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M18" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N18" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P18" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q18" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U18" t="s">
         <v>59</v>
@@ -6170,13 +6179,13 @@
         <v>20254860</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C19" t="s">
         <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
@@ -6191,40 +6200,40 @@
         <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N19" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -6236,7 +6245,7 @@
         <v>20254686</v>
       </c>
       <c r="B20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -6248,49 +6257,49 @@
         <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q20" t="s">
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="S20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -6302,10 +6311,10 @@
         <v>20254687</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -6314,7 +6323,7 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6323,40 +6332,40 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q21" t="s">
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S21" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="T21" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -6368,19 +6377,19 @@
         <v>20254564</v>
       </c>
       <c r="B22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C22" t="s">
         <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
@@ -6389,40 +6398,40 @@
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T22" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="U22" t="s">
         <v>59</v>
@@ -6434,7 +6443,7 @@
         <v>20254517</v>
       </c>
       <c r="B23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -6446,7 +6455,7 @@
         <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
@@ -6455,40 +6464,40 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N23" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q23" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R23" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="S23" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="T23" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="U23" t="s">
         <v>59</v>
@@ -6500,19 +6509,19 @@
         <v>20254531</v>
       </c>
       <c r="B24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E24" t="s">
         <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G24" t="s">
         <v>45</v>
@@ -6521,40 +6530,40 @@
         <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N24" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q24" t="s">
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="S24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T24" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="U24" t="s">
         <v>59</v>
@@ -6566,59 +6575,59 @@
         <v>20258254</v>
       </c>
       <c r="B25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E25" t="s">
         <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G25" t="s">
         <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q25" t="s">
         <v>55</v>
       </c>
       <c r="R25" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T25" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="U25" t="s">
         <v>59</v>
@@ -6630,19 +6639,19 @@
         <v>20258286</v>
       </c>
       <c r="B26" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
@@ -6651,38 +6660,38 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M26" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O26" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P26" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q26" t="s">
         <v>55</v>
       </c>
       <c r="R26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S26" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="T26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="U26" t="s">
         <v>59</v>
@@ -6694,17 +6703,17 @@
         <v>20254401</v>
       </c>
       <c r="B27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G27" t="s">
         <v>45</v>
@@ -6713,40 +6722,40 @@
         <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M27" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N27" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q27" t="s">
         <v>55</v>
       </c>
       <c r="R27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="S27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="T27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="U27" t="s">
         <v>59</v>
@@ -6758,19 +6767,19 @@
         <v>20254263</v>
       </c>
       <c r="B28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E28" t="s">
         <v>77</v>
       </c>
       <c r="F28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
@@ -6779,40 +6788,40 @@
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J28" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
       </c>
       <c r="R28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T28" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="U28" t="s">
         <v>59</v>
@@ -6824,19 +6833,19 @@
         <v>20254320</v>
       </c>
       <c r="B29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E29" t="s">
         <v>104</v>
       </c>
       <c r="F29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
@@ -6845,40 +6854,40 @@
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N29" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P29" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
       </c>
       <c r="R29" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T29" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U29" t="s">
         <v>59</v>
@@ -6890,7 +6899,7 @@
         <v>20254352</v>
       </c>
       <c r="B30" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
@@ -6902,7 +6911,7 @@
         <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G30" t="s">
         <v>45</v>
@@ -6911,31 +6920,31 @@
         <v>78</v>
       </c>
       <c r="I30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K30" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N30" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P30" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q30" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R30" t="s">
         <v>86</v>
@@ -6956,7 +6965,7 @@
         <v>20254380</v>
       </c>
       <c r="B31" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -6968,7 +6977,7 @@
         <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G31" t="s">
         <v>27</v>
@@ -6977,40 +6986,40 @@
         <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J31" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N31" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P31" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q31" t="s">
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S31" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T31" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="U31" t="s">
         <v>59</v>
@@ -7022,19 +7031,19 @@
         <v>20254194</v>
       </c>
       <c r="B32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C32" t="s">
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
@@ -7043,40 +7052,40 @@
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O32" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q32" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U32" t="s">
         <v>59</v>
@@ -7088,7 +7097,7 @@
         <v>20254123</v>
       </c>
       <c r="B33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s">
         <v>75</v>
@@ -7100,7 +7109,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
@@ -7109,40 +7118,40 @@
         <v>105</v>
       </c>
       <c r="I33" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K33" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L33" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q33" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R33" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S33" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="T33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="U33" t="s">
         <v>59</v>
@@ -7154,61 +7163,61 @@
         <v>20254132</v>
       </c>
       <c r="B34" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C34" t="s">
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E34" t="s">
         <v>77</v>
       </c>
       <c r="F34" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G34" t="s">
         <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I34" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J34" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K34" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L34" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M34" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N34" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O34" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P34" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q34" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R34" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="S34" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="T34" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U34" t="s">
         <v>59</v>
@@ -7220,19 +7229,19 @@
         <v>20254080</v>
       </c>
       <c r="B35" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
@@ -7241,40 +7250,40 @@
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J35" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L35" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M35" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N35" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O35" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P35" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q35" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R35" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S35" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T35" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U35" t="s">
         <v>59</v>
@@ -7286,10 +7295,10 @@
         <v>20250467</v>
       </c>
       <c r="B36" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C36" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D36" t="s">
         <v>76</v>
@@ -7298,7 +7307,7 @@
         <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G36" t="s">
         <v>45</v>
@@ -7307,40 +7316,40 @@
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J36" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K36" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L36" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M36" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N36" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O36" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P36" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q36" t="s">
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="S36" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T36" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="U36" t="s">
         <v>59</v>
@@ -7352,19 +7361,19 @@
         <v>20254033</v>
       </c>
       <c r="B37" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G37" t="s">
         <v>45</v>
@@ -7373,40 +7382,40 @@
         <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J37" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K37" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L37" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M37" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N37" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O37" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P37" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q37" t="s">
         <v>55</v>
       </c>
       <c r="R37" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S37" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="T37" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U37" t="s">
         <v>59</v>
@@ -7418,19 +7427,19 @@
         <v>20257863</v>
       </c>
       <c r="B38" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D38" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E38" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F38" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G38" t="s">
         <v>45</v>
@@ -7439,38 +7448,38 @@
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K38"/>
       <c r="L38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M38" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N38" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O38" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P38" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q38" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U38" t="s">
         <v>59</v>
@@ -7482,19 +7491,19 @@
         <v>20257867</v>
       </c>
       <c r="B39" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D39" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G39" t="s">
         <v>45</v>
@@ -7503,38 +7512,38 @@
         <v>105</v>
       </c>
       <c r="I39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M39" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O39" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P39" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q39" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R39" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="S39" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T39" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="U39" t="s">
         <v>59</v>
@@ -7546,19 +7555,19 @@
         <v>20257620</v>
       </c>
       <c r="B40" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D40" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E40" t="s">
         <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G40" t="s">
         <v>45</v>
@@ -7567,38 +7576,38 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J40" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M40" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O40" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P40" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q40" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R40" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="S40" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="T40" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="U40" t="s">
         <v>59</v>
@@ -7610,61 +7619,61 @@
         <v>20253960</v>
       </c>
       <c r="B41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C41" t="s">
         <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E41" t="s">
         <v>77</v>
       </c>
       <c r="F41" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G41" t="s">
         <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I41" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J41" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K41" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L41" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M41" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N41" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O41" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q41" t="s">
         <v>55</v>
       </c>
       <c r="R41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="S41" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T41" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="U41" t="s">
         <v>59</v>
@@ -7676,59 +7685,59 @@
         <v>20257581</v>
       </c>
       <c r="B42" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E42" t="s">
         <v>77</v>
       </c>
       <c r="F42" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I42" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J42" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M42" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N42" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O42" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P42" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q42" t="s">
         <v>55</v>
       </c>
       <c r="R42" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="S42" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="T42" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="U42" t="s">
         <v>59</v>
@@ -7740,45 +7749,45 @@
         <v>20250317</v>
       </c>
       <c r="B43" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C43" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D43" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J43" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K43" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L43" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M43" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O43" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P43" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Q43" t="s">
         <v>55</v>
@@ -7796,19 +7805,19 @@
         <v>20253856</v>
       </c>
       <c r="B44" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C44" t="s">
         <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E44" t="s">
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G44" t="s">
         <v>45</v>
@@ -7817,40 +7826,40 @@
         <v>78</v>
       </c>
       <c r="I44" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J44" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K44" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L44" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M44" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N44" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O44" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P44" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Q44" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R44" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="S44" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="T44" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="U44" t="s">
         <v>59</v>
@@ -7862,19 +7871,19 @@
         <v>20253885</v>
       </c>
       <c r="B45" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C45" t="s">
         <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E45" t="s">
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G45" t="s">
         <v>45</v>
@@ -7883,40 +7892,40 @@
         <v>78</v>
       </c>
       <c r="I45" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J45" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L45" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M45" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N45" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O45" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P45" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Q45" t="s">
         <v>55</v>
       </c>
       <c r="R45" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S45" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T45" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="U45" t="s">
         <v>59</v>
@@ -7928,19 +7937,19 @@
         <v>20253904</v>
       </c>
       <c r="B46" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D46" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G46" t="s">
         <v>45</v>
@@ -7949,40 +7958,40 @@
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J46" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K46" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L46" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M46" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N46" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O46" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P46" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q46" t="s">
         <v>55</v>
       </c>
       <c r="R46" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="S46" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="T46" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="U46" t="s">
         <v>59</v>
@@ -7994,7 +8003,7 @@
         <v>20253737</v>
       </c>
       <c r="B47" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -8004,7 +8013,7 @@
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G47" t="s">
         <v>45</v>
@@ -8013,40 +8022,40 @@
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J47" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K47" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L47" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M47" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N47" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O47" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P47" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Q47" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R47" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="S47" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T47" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="U47" t="s">
         <v>59</v>
@@ -8058,19 +8067,19 @@
         <v>20253789</v>
       </c>
       <c r="B48" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C48" t="s">
         <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E48" t="s">
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G48" t="s">
         <v>45</v>
@@ -8079,40 +8088,40 @@
         <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J48" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K48" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L48" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M48" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N48" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O48" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P48" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Q48" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R48" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S48" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="T48" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="U48" t="s">
         <v>59</v>
@@ -8124,19 +8133,19 @@
         <v>20253668</v>
       </c>
       <c r="B49" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C49" t="s">
         <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E49" t="s">
         <v>62</v>
       </c>
       <c r="F49" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -8145,31 +8154,31 @@
         <v>78</v>
       </c>
       <c r="I49" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K49" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L49" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M49" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O49" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P49" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Q49" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R49" t="s">
         <v>86</v>
@@ -8190,17 +8199,17 @@
         <v>20253669</v>
       </c>
       <c r="B50" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E50"/>
       <c r="F50" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G50" t="s">
         <v>45</v>
@@ -8209,40 +8218,40 @@
         <v>78</v>
       </c>
       <c r="I50" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K50" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M50" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O50" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Q50" t="s">
         <v>55</v>
       </c>
       <c r="R50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="S50" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="T50" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="U50" t="s">
         <v>59</v>
@@ -8254,19 +8263,19 @@
         <v>20253691</v>
       </c>
       <c r="B51" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C51" t="s">
         <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E51" t="s">
         <v>104</v>
       </c>
       <c r="F51" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G51" t="s">
         <v>45</v>
@@ -8275,40 +8284,40 @@
         <v>78</v>
       </c>
       <c r="I51" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J51" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K51" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L51" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M51" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N51" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O51" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P51" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Q51" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R51" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S51" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="T51" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="U51" t="s">
         <v>59</v>
@@ -8320,19 +8329,19 @@
         <v>20253576</v>
       </c>
       <c r="B52" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C52" t="s">
         <v>75</v>
       </c>
       <c r="D52" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E52" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F52" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
@@ -8341,40 +8350,40 @@
         <v>78</v>
       </c>
       <c r="I52" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J52" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K52" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L52" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M52" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N52" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O52" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P52" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q52" t="s">
         <v>55</v>
       </c>
       <c r="R52" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="S52" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="T52" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="U52" t="s">
         <v>59</v>
@@ -8386,19 +8395,19 @@
         <v>20253572</v>
       </c>
       <c r="B53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E53" t="s">
         <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G53" t="s">
         <v>45</v>
@@ -8407,28 +8416,28 @@
         <v>78</v>
       </c>
       <c r="I53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J53" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K53" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L53" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M53" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N53" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O53" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P53" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Q53" t="s">
         <v>55</v>
@@ -8452,19 +8461,19 @@
         <v>20253467</v>
       </c>
       <c r="B54" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E54" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F54" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
@@ -8473,40 +8482,40 @@
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J54" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K54" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L54" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M54" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N54" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O54" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P54" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Q54" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R54" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="S54" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="T54" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="U54" t="s">
         <v>59</v>
@@ -8518,19 +8527,19 @@
         <v>20253502</v>
       </c>
       <c r="B55" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E55" t="s">
         <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G55" t="s">
         <v>45</v>
@@ -8539,40 +8548,40 @@
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M55" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N55" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O55" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P55" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Q55" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R55" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S55" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T55" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U55" t="s">
         <v>59</v>
@@ -8584,17 +8593,17 @@
         <v>20253425</v>
       </c>
       <c r="B56" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G56" t="s">
         <v>45</v>
@@ -8603,40 +8612,40 @@
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J56" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="K56" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L56" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M56" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N56" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O56" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P56" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Q56" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R56" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S56" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T56" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U56" t="s">
         <v>59</v>
@@ -8648,61 +8657,61 @@
         <v>20253296</v>
       </c>
       <c r="B57" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I57" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J57" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K57" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L57" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M57" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N57" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O57" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P57" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="Q57" t="s">
         <v>55</v>
       </c>
       <c r="R57" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="S57" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="T57" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="U57" t="s">
         <v>59</v>
@@ -8714,19 +8723,19 @@
         <v>20253360</v>
       </c>
       <c r="B58" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C58" t="s">
         <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G58" t="s">
         <v>45</v>
@@ -8735,40 +8744,40 @@
         <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J58" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L58" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M58" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N58" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O58" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P58" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="Q58" t="s">
         <v>55</v>
       </c>
       <c r="R58" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="S58" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="T58" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="U58" t="s">
         <v>59</v>
@@ -8780,19 +8789,19 @@
         <v>20253380</v>
       </c>
       <c r="B59" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C59" t="s">
         <v>75</v>
       </c>
       <c r="D59" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E59" t="s">
         <v>104</v>
       </c>
       <c r="F59" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G59" t="s">
         <v>45</v>
@@ -8801,40 +8810,40 @@
         <v>78</v>
       </c>
       <c r="I59" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K59" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L59" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M59" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N59" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O59" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P59" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Q59" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R59" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S59" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="T59" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U59" t="s">
         <v>59</v>
@@ -8846,19 +8855,19 @@
         <v>20253153</v>
       </c>
       <c r="B60" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G60" t="s">
         <v>27</v>
@@ -8867,40 +8876,40 @@
         <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="J60" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K60" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L60" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M60" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N60" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O60" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P60" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Q60" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R60" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="S60" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="T60" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="U60" t="s">
         <v>59</v>
@@ -8912,7 +8921,7 @@
         <v>20253165</v>
       </c>
       <c r="B61" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -8924,7 +8933,7 @@
         <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G61" t="s">
         <v>27</v>
@@ -8933,40 +8942,40 @@
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J61" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="K61" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L61" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M61" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O61" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="P61" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Q61" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R61" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S61" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T61" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U61" t="s">
         <v>59</v>
@@ -8978,19 +8987,19 @@
         <v>20253115</v>
       </c>
       <c r="B62" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C62" t="s">
         <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
@@ -8999,40 +9008,40 @@
         <v>78</v>
       </c>
       <c r="I62" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J62" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K62" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="L62" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M62" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O62" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P62" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="Q62" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R62" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="S62" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="T62" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="U62" t="s">
         <v>59</v>
@@ -9044,19 +9053,19 @@
         <v>20253096</v>
       </c>
       <c r="B63" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C63" t="s">
         <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E63" t="s">
         <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G63" t="s">
         <v>45</v>
@@ -9065,40 +9074,40 @@
         <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J63" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="K63" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="L63" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M63" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N63" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O63" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P63" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Q63" t="s">
         <v>55</v>
       </c>
       <c r="R63" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="S63" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="T63" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="U63" t="s">
         <v>59</v>
@@ -9110,45 +9119,45 @@
         <v>20250303</v>
       </c>
       <c r="B64" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C64" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D64" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
         <v>78</v>
       </c>
       <c r="I64" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J64" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K64" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L64" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M64" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P64" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="Q64" t="s">
         <v>55</v>
@@ -9166,45 +9175,45 @@
         <v>20250301</v>
       </c>
       <c r="B65" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C65" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D65" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J65" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K65" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L65" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M65" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N65" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O65" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P65" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Q65" t="s">
         <v>55</v>
@@ -9222,17 +9231,17 @@
         <v>20250401</v>
       </c>
       <c r="B66" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C66" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D66" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
@@ -9241,40 +9250,40 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="J66" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="K66" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L66" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M66" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N66" t="s">
         <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P66" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="Q66" t="s">
         <v>55</v>
       </c>
       <c r="R66" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="S66" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="T66" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="U66" t="s">
         <v>59</v>
@@ -9286,19 +9295,19 @@
         <v>20240477</v>
       </c>
       <c r="B67" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C67" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D67" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E67" t="s">
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G67" t="s">
         <v>45</v>
@@ -9307,40 +9316,40 @@
         <v>78</v>
       </c>
       <c r="I67" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J67" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K67" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L67" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M67" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N67" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O67" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P67" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="Q67" t="s">
         <v>55</v>
       </c>
       <c r="R67" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="S67" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="T67" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="U67" t="s">
         <v>59</v>
@@ -9352,19 +9361,19 @@
         <v>20244553</v>
       </c>
       <c r="B68" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C68" t="s">
         <v>75</v>
       </c>
       <c r="D68" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E68" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F68" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G68" t="s">
         <v>45</v>
@@ -9373,40 +9382,40 @@
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J68" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K68" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L68" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M68" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N68" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O68" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="P68" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="Q68" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R68" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="S68" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="T68" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="U68" t="s">
         <v>59</v>
@@ -9418,61 +9427,61 @@
         <v>20244562</v>
       </c>
       <c r="B69" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C69" t="s">
         <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G69" t="s">
         <v>45</v>
       </c>
       <c r="H69" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I69" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J69" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K69" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="L69" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M69" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N69" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O69" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="P69" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q69" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R69" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="S69" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="T69" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="U69" t="s">
         <v>59</v>
@@ -9484,19 +9493,19 @@
         <v>20244595</v>
       </c>
       <c r="B70" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E70" t="s">
         <v>104</v>
       </c>
       <c r="F70" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G70" t="s">
         <v>45</v>
@@ -9505,40 +9514,40 @@
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J70" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K70" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="L70" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M70" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N70" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O70" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P70" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="Q70" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R70" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="S70" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="T70" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="U70" t="s">
         <v>59</v>
@@ -9550,19 +9559,19 @@
         <v>20244634</v>
       </c>
       <c r="B71" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E71" t="s">
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G71" t="s">
         <v>45</v>
@@ -9571,40 +9580,40 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J71" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K71" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="L71" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M71" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N71" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O71" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P71" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="Q71" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R71" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="S71" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="T71" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="U71" t="s">
         <v>59</v>
@@ -9616,19 +9625,19 @@
         <v>20244660</v>
       </c>
       <c r="B72" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C72" t="s">
         <v>75</v>
       </c>
       <c r="D72" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E72" t="s">
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G72" t="s">
         <v>45</v>
@@ -9637,40 +9646,40 @@
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J72" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K72" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L72" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M72" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N72" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O72" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="P72" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="Q72" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R72" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="S72" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T72" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="U72" t="s">
         <v>59</v>
@@ -9682,19 +9691,19 @@
         <v>20241055</v>
       </c>
       <c r="B73" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C73" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D73" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G73" t="s">
         <v>45</v>
@@ -9703,40 +9712,40 @@
         <v>78</v>
       </c>
       <c r="I73" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J73" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="K73" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="L73" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M73" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N73" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O73" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="P73" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="Q73" t="s">
         <v>55</v>
       </c>
       <c r="R73" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="S73" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="T73" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="U73" t="s">
         <v>59</v>
@@ -9748,19 +9757,19 @@
         <v>20244459</v>
       </c>
       <c r="B74" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C74" t="s">
         <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E74" t="s">
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G74" t="s">
         <v>45</v>
@@ -9769,40 +9778,40 @@
         <v>78</v>
       </c>
       <c r="I74" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="J74" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="K74" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="L74" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M74" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N74" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O74" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="P74" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="Q74" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R74" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="S74" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="T74" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="U74" t="s">
         <v>59</v>
@@ -9814,45 +9823,45 @@
         <v>20240331</v>
       </c>
       <c r="B75" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C75" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D75" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
         <v>78</v>
       </c>
       <c r="I75" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J75" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="K75" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="L75" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M75" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="N75" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="O75" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="P75" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="Q75" t="s">
         <v>55</v>
@@ -9870,7 +9879,7 @@
         <v>20244340</v>
       </c>
       <c r="B76" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -9882,7 +9891,7 @@
         <v>77</v>
       </c>
       <c r="F76" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G76" t="s">
         <v>45</v>
@@ -9891,40 +9900,40 @@
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J76" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="K76" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L76" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M76" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N76" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O76" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="P76" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="Q76" t="s">
         <v>55</v>
       </c>
       <c r="R76" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S76" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T76" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="U76" t="s">
         <v>59</v>
@@ -9936,19 +9945,19 @@
         <v>20247929</v>
       </c>
       <c r="B77" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C77" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D77" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E77" t="s">
         <v>77</v>
       </c>
       <c r="F77" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G77" t="s">
         <v>45</v>
@@ -9957,38 +9966,38 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="J77" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="K77"/>
       <c r="L77" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M77" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="N77" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O77" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="P77" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="Q77" t="s">
         <v>55</v>
       </c>
       <c r="R77" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="S77" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="T77" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="U77" t="s">
         <v>59</v>
@@ -10000,19 +10009,19 @@
         <v>20247903</v>
       </c>
       <c r="B78" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C78" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D78" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E78" t="s">
         <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G78" t="s">
         <v>45</v>
@@ -10021,38 +10030,38 @@
         <v>78</v>
       </c>
       <c r="I78" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="J78" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M78" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N78" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O78" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="P78" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="Q78" t="s">
         <v>55</v>
       </c>
       <c r="R78" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="S78" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="T78" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="U78" t="s">
         <v>59</v>
@@ -10064,51 +10073,51 @@
         <v>20240083</v>
       </c>
       <c r="B79" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C79" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J79" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="K79" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O79" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="P79" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
       </c>
       <c r="R79" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="S79" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="T79" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="U79" t="s">
         <v>59</v>
@@ -10120,57 +10129,57 @@
         <v>20240325</v>
       </c>
       <c r="B80" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C80" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D80" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
         <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J80" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="K80" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="L80" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M80" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N80" t="s">
         <v>34</v>
       </c>
       <c r="O80" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="P80" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="Q80" t="s">
         <v>55</v>
       </c>
       <c r="R80" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="S80" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="T80" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="U80" t="s">
         <v>59</v>
@@ -10182,57 +10191,57 @@
         <v>20240326</v>
       </c>
       <c r="B81" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C81" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D81" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
         <v>78</v>
       </c>
       <c r="I81" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="J81" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K81" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="L81" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M81" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N81" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="O81" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="P81" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="Q81" t="s">
         <v>55</v>
       </c>
       <c r="R81" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="S81" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="T81" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="U81" t="s">
         <v>59</v>
@@ -10244,19 +10253,19 @@
         <v>20244209</v>
       </c>
       <c r="B82" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
       </c>
       <c r="D82" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E82" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F82" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G82" t="s">
         <v>45</v>
@@ -10265,40 +10274,40 @@
         <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="J82" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="K82" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="L82" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M82" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="N82" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O82" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="P82" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="Q82" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R82" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="S82" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="T82" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="U82" t="s">
         <v>59</v>
@@ -10310,19 +10319,19 @@
         <v>20244026</v>
       </c>
       <c r="B83" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G83" t="s">
         <v>45</v>
@@ -10331,40 +10340,40 @@
         <v>105</v>
       </c>
       <c r="I83" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="J83" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="K83" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="L83" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M83" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="N83" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O83" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="P83" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="Q83" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R83" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="S83" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="T83" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="U83" t="s">
         <v>59</v>
@@ -10376,19 +10385,19 @@
         <v>20244044</v>
       </c>
       <c r="B84" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C84" t="s">
         <v>75</v>
       </c>
       <c r="D84" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E84" t="s">
         <v>77</v>
       </c>
       <c r="F84" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G84" t="s">
         <v>45</v>
@@ -10397,40 +10406,40 @@
         <v>78</v>
       </c>
       <c r="I84" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="J84" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K84" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L84" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M84" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="N84" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O84" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="P84" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q84" t="s">
         <v>55</v>
       </c>
       <c r="R84" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S84" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="T84" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="U84" t="s">
         <v>59</v>
@@ -10442,19 +10451,19 @@
         <v>20244134</v>
       </c>
       <c r="B85" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
       </c>
       <c r="D85" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E85" t="s">
         <v>62</v>
       </c>
       <c r="F85" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G85" t="s">
         <v>45</v>
@@ -10463,40 +10472,40 @@
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="J85" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K85" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L85" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M85" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="N85" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O85" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="P85" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="Q85" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R85" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="S85" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="T85" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="U85" t="s">
         <v>59</v>
@@ -10508,19 +10517,19 @@
         <v>20244155</v>
       </c>
       <c r="B86" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C86" t="s">
         <v>75</v>
       </c>
       <c r="D86" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G86" t="s">
         <v>45</v>
@@ -10529,40 +10538,40 @@
         <v>105</v>
       </c>
       <c r="I86" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="J86" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="K86" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L86" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="M86" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="N86" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O86" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="P86" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="Q86" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R86" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="S86" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="T86" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="U86" t="s">
         <v>59</v>
@@ -10574,19 +10583,19 @@
         <v>20243913</v>
       </c>
       <c r="B87" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E87" t="s">
         <v>104</v>
       </c>
       <c r="F87" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G87" t="s">
         <v>45</v>
@@ -10595,40 +10604,40 @@
         <v>105</v>
       </c>
       <c r="I87" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="J87" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="K87" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="L87" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="M87" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="N87" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O87" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="P87" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="Q87" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R87" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S87" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T87" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="U87" t="s">
         <v>59</v>
@@ -10640,19 +10649,19 @@
         <v>20247658</v>
       </c>
       <c r="B88" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C88" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D88" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E88" t="s">
         <v>77</v>
       </c>
       <c r="F88" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G88" t="s">
         <v>45</v>
@@ -10661,38 +10670,38 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J88" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="M88" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N88" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O88" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="P88" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="Q88" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R88" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S88" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T88" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U88" t="s">
         <v>59</v>
@@ -10704,7 +10713,7 @@
         <v>20243865</v>
       </c>
       <c r="B89" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C89" t="s">
         <v>75</v>
@@ -10716,7 +10725,7 @@
         <v>104</v>
       </c>
       <c r="F89" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G89" t="s">
         <v>45</v>
@@ -10725,31 +10734,31 @@
         <v>78</v>
       </c>
       <c r="I89" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J89" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="K89" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="L89" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="M89" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="N89" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O89" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="P89" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="Q89" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R89" t="s">
         <v>86</v>
@@ -10770,19 +10779,19 @@
         <v>20247610</v>
       </c>
       <c r="B90" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C90" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D90" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G90" t="s">
         <v>45</v>
@@ -10791,38 +10800,38 @@
         <v>78</v>
       </c>
       <c r="I90" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J90" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="M90" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="N90" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O90" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="P90" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="Q90" t="s">
         <v>55</v>
       </c>
       <c r="R90" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S90" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="T90" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U90" t="s">
         <v>59</v>
@@ -10834,19 +10843,19 @@
         <v>20247640</v>
       </c>
       <c r="B91" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C91" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D91" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E91" t="s">
         <v>77</v>
       </c>
       <c r="F91" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G91" t="s">
         <v>45</v>
@@ -10855,38 +10864,38 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J91" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M91" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="N91" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O91" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="P91" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="Q91" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R91" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S91" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T91" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U91" t="s">
         <v>59</v>
@@ -10898,19 +10907,19 @@
         <v>20247641</v>
       </c>
       <c r="B92" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C92" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D92" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E92" t="s">
         <v>77</v>
       </c>
       <c r="F92" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G92" t="s">
         <v>45</v>
@@ -10919,38 +10928,38 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J92" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K92"/>
       <c r="L92" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M92" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N92" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O92" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="P92" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="Q92" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R92" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S92" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T92" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U92" t="s">
         <v>59</v>
@@ -10962,19 +10971,19 @@
         <v>20247642</v>
       </c>
       <c r="B93" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C93" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D93" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E93" t="s">
         <v>77</v>
       </c>
       <c r="F93" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G93" t="s">
         <v>45</v>
@@ -10983,38 +10992,38 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J93" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="M93" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N93" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O93" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="P93" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="Q93" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R93" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S93" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T93" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U93" t="s">
         <v>59</v>
@@ -11026,19 +11035,19 @@
         <v>20243832</v>
       </c>
       <c r="B94" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C94" t="s">
         <v>75</v>
       </c>
       <c r="D94" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E94" t="s">
         <v>77</v>
       </c>
       <c r="F94" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G94" t="s">
         <v>45</v>
@@ -11047,40 +11056,40 @@
         <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="J94" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K94" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="L94" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="M94" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N94" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O94" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="P94" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="Q94" t="s">
         <v>55</v>
       </c>
       <c r="R94" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="S94" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="T94" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="U94" t="s">
         <v>59</v>
@@ -11092,19 +11101,19 @@
         <v>20243738</v>
       </c>
       <c r="B95" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C95" t="s">
         <v>75</v>
       </c>
       <c r="D95" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G95" t="s">
         <v>45</v>
@@ -11113,28 +11122,28 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="J95" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K95" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="L95" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="M95" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N95" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O95" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="P95" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Q95" t="s">
         <v>55</v>
@@ -11158,19 +11167,19 @@
         <v>20243769</v>
       </c>
       <c r="B96" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C96" t="s">
         <v>75</v>
       </c>
       <c r="D96" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E96" t="s">
         <v>77</v>
       </c>
       <c r="F96" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G96" t="s">
         <v>45</v>
@@ -11179,40 +11188,40 @@
         <v>78</v>
       </c>
       <c r="I96" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J96" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="K96" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="L96" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M96" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="N96" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O96" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="P96" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="Q96" t="s">
         <v>55</v>
       </c>
       <c r="R96" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="S96" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="T96" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="U96" t="s">
         <v>59</v>
@@ -11224,19 +11233,19 @@
         <v>20243804</v>
       </c>
       <c r="B97" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C97" t="s">
         <v>75</v>
       </c>
       <c r="D97" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="E97" t="s">
         <v>104</v>
       </c>
       <c r="F97" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G97" t="s">
         <v>45</v>
@@ -11245,40 +11254,40 @@
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="J97" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="K97" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="L97" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="M97" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="N97" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O97" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="P97" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="Q97" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R97" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="S97" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="T97" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="U97" t="s">
         <v>59</v>
@@ -11290,57 +11299,57 @@
         <v>20240316</v>
       </c>
       <c r="B98" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C98" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D98" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I98" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="J98" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="K98" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="L98" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="M98" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="N98" t="s">
         <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="P98" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="Q98" t="s">
         <v>55</v>
       </c>
       <c r="R98" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="S98" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="T98" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="U98" t="s">
         <v>59</v>
@@ -11352,19 +11361,19 @@
         <v>20243627</v>
       </c>
       <c r="B99" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G99" t="s">
         <v>45</v>
@@ -11373,40 +11382,40 @@
         <v>105</v>
       </c>
       <c r="I99" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J99" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K99" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="L99" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="M99" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="N99" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O99" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="P99" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="Q99" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R99" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="S99" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="T99" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="U99" t="s">
         <v>59</v>
@@ -11418,19 +11427,19 @@
         <v>20243641</v>
       </c>
       <c r="B100" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
       </c>
       <c r="D100" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E100" t="s">
         <v>104</v>
       </c>
       <c r="F100" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G100" t="s">
         <v>45</v>
@@ -11439,40 +11448,40 @@
         <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="J100" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="K100" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="L100" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="M100" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="N100" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O100" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="P100" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="Q100" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R100" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="S100" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="T100" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="U100" t="s">
         <v>59</v>
@@ -11484,19 +11493,19 @@
         <v>20243664</v>
       </c>
       <c r="B101" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C101" t="s">
         <v>75</v>
       </c>
       <c r="D101" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E101" t="s">
         <v>62</v>
       </c>
       <c r="F101" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G101" t="s">
         <v>45</v>
@@ -11505,40 +11514,40 @@
         <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="J101" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="K101" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="L101" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="M101" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="N101" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O101" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="P101" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="Q101" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R101" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="S101" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="T101" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="U101" t="s">
         <v>59</v>
@@ -11550,19 +11559,19 @@
         <v>20243684</v>
       </c>
       <c r="B102" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E102" t="s">
         <v>62</v>
       </c>
       <c r="F102" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G102" t="s">
         <v>45</v>
@@ -11571,40 +11580,40 @@
         <v>78</v>
       </c>
       <c r="I102" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="J102" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="K102" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="L102" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="M102" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N102" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O102" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="P102" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="Q102" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R102" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="S102" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="T102" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="U102" t="s">
         <v>59</v>
@@ -11616,19 +11625,19 @@
         <v>20243701</v>
       </c>
       <c r="B103" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E103" t="s">
         <v>77</v>
       </c>
       <c r="F103" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G103" t="s">
         <v>45</v>
@@ -11637,40 +11646,40 @@
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="J103" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="K103" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="L103" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="M103" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N103" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="O103" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="P103" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="Q103" t="s">
         <v>55</v>
       </c>
       <c r="R103" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="S103" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="T103" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="U103" t="s">
         <v>59</v>
@@ -11682,7 +11691,7 @@
         <v>20243559</v>
       </c>
       <c r="B104" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C104" t="s">
         <v>75</v>
@@ -11694,7 +11703,7 @@
         <v>77</v>
       </c>
       <c r="F104" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G104" t="s">
         <v>45</v>
@@ -11703,28 +11712,28 @@
         <v>78</v>
       </c>
       <c r="I104" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="J104" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="K104" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="L104" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="M104" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="N104" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O104" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="P104" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="Q104" t="s">
         <v>55</v>
@@ -11748,19 +11757,19 @@
         <v>20243545</v>
       </c>
       <c r="B105" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E105" t="s">
         <v>104</v>
       </c>
       <c r="F105" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="G105" t="s">
         <v>45</v>
@@ -11769,40 +11778,40 @@
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="J105" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="K105" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="L105" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="M105" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="N105" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O105" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="P105" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="Q105" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R105" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S105" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T105" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U105" t="s">
         <v>59</v>
@@ -11814,19 +11823,19 @@
         <v>20247418</v>
       </c>
       <c r="B106" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C106" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D106" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="E106" t="s">
         <v>77</v>
       </c>
       <c r="F106" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G106" t="s">
         <v>45</v>
@@ -11835,38 +11844,38 @@
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="J106" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="K106"/>
       <c r="L106" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="M106" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="N106" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O106" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="P106" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="Q106" t="s">
         <v>55</v>
       </c>
       <c r="R106" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S106" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T106" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U106" t="s">
         <v>59</v>
@@ -11878,19 +11887,19 @@
         <v>20247440</v>
       </c>
       <c r="B107" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C107" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D107" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E107" t="s">
         <v>62</v>
       </c>
       <c r="F107" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G107" t="s">
         <v>45</v>
@@ -11899,38 +11908,38 @@
         <v>78</v>
       </c>
       <c r="I107" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="J107" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="M107" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="N107" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O107" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="P107" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="Q107" t="s">
         <v>55</v>
       </c>
       <c r="R107" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="S107" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="T107" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="U107" t="s">
         <v>59</v>
@@ -11942,10 +11951,10 @@
         <v>20243483</v>
       </c>
       <c r="B108" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C108" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D108" t="s">
         <v>90</v>
@@ -11954,7 +11963,7 @@
         <v>62</v>
       </c>
       <c r="F108" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="G108" t="s">
         <v>45</v>
@@ -11963,40 +11972,40 @@
         <v>78</v>
       </c>
       <c r="I108" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="J108" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="K108" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="L108" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="M108" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N108" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="O108" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="P108" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="Q108" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R108" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="S108" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="T108" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="U108" t="s">
         <v>59</v>
@@ -12008,51 +12017,51 @@
         <v>20240052</v>
       </c>
       <c r="B109" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C109" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D109"/>
       <c r="E109"/>
       <c r="F109" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
         <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="J109" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="K109" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="L109"/>
       <c r="M109"/>
       <c r="N109" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="O109" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="P109" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="Q109" t="s">
         <v>37</v>
       </c>
       <c r="R109" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="S109" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="T109" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="U109" t="s">
         <v>59</v>
@@ -12064,57 +12073,57 @@
         <v>20240310</v>
       </c>
       <c r="B110" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C110" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D110" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
         <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="J110" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="K110" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="L110" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="M110" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N110" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="O110" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="P110" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="Q110" t="s">
         <v>55</v>
       </c>
       <c r="R110" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="S110" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="T110" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="U110" t="s">
         <v>59</v>
@@ -12126,19 +12135,19 @@
         <v>20243428</v>
       </c>
       <c r="B111" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C111" t="s">
         <v>75</v>
       </c>
       <c r="D111" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E111" t="s">
         <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="G111" t="s">
         <v>45</v>
@@ -12147,40 +12156,40 @@
         <v>78</v>
       </c>
       <c r="I111" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="J111" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="K111" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="L111" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="M111" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="N111" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O111" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="P111" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="Q111" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R111" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="S111" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="T111" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="U111" t="s">
         <v>59</v>
@@ -12192,19 +12201,19 @@
         <v>20243366</v>
       </c>
       <c r="B112" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C112" t="s">
         <v>75</v>
       </c>
       <c r="D112" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E112" t="s">
         <v>62</v>
       </c>
       <c r="F112" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G112" t="s">
         <v>45</v>
@@ -12213,40 +12222,40 @@
         <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="J112" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="K112" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="L112" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="M112" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="N112" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O112" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="P112" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="Q112" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R112" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="S112" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="T112" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="U112" t="s">
         <v>59</v>
@@ -12258,7 +12267,7 @@
         <v>20243383</v>
       </c>
       <c r="B113" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C113" t="s">
         <v>75</v>
@@ -12270,7 +12279,7 @@
         <v>62</v>
       </c>
       <c r="F113" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G113" t="s">
         <v>27</v>
@@ -12279,40 +12288,40 @@
         <v>78</v>
       </c>
       <c r="I113" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="J113" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="K113" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="L113" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="M113" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N113" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O113" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="P113" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="Q113" t="s">
         <v>55</v>
       </c>
       <c r="R113" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S113" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="T113" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="U113" t="s">
         <v>59</v>
@@ -12324,19 +12333,19 @@
         <v>20243204</v>
       </c>
       <c r="B114" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D114" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G114" t="s">
         <v>27</v>
@@ -12345,40 +12354,40 @@
         <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="J114" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="K114" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="L114" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="M114" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N114" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O114" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="P114" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="Q114" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R114" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="S114" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="T114" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="U114" t="s">
         <v>59</v>
@@ -12390,19 +12399,19 @@
         <v>20243228</v>
       </c>
       <c r="B115" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
       <c r="D115" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G115" t="s">
         <v>45</v>
@@ -12411,40 +12420,40 @@
         <v>78</v>
       </c>
       <c r="I115" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="J115" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="K115" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="L115" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="M115" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N115" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O115" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P115" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="Q115" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R115" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="S115" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="T115" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="U115" t="s">
         <v>59</v>
@@ -12456,19 +12465,19 @@
         <v>20243244</v>
       </c>
       <c r="B116" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E116" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="F116" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G116" t="s">
         <v>45</v>
@@ -12477,40 +12486,40 @@
         <v>105</v>
       </c>
       <c r="I116" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J116" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="K116" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="L116" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="M116" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="N116" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O116" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="P116" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="Q116" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R116" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="S116" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="T116" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="U116" t="s">
         <v>59</v>
@@ -12522,19 +12531,19 @@
         <v>20243270</v>
       </c>
       <c r="B117" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C117" t="s">
         <v>75</v>
       </c>
       <c r="D117" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E117" t="s">
         <v>77</v>
       </c>
       <c r="F117" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G117" t="s">
         <v>45</v>
@@ -12543,40 +12552,40 @@
         <v>78</v>
       </c>
       <c r="I117" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="J117" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="K117" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="L117" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="M117" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="N117" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O117" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="P117" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="Q117" t="s">
         <v>55</v>
       </c>
       <c r="R117" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="S117" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="T117" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="U117" t="s">
         <v>59</v>
@@ -12588,19 +12597,19 @@
         <v>20243289</v>
       </c>
       <c r="B118" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C118" t="s">
         <v>75</v>
       </c>
       <c r="D118" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G118" t="s">
         <v>45</v>
@@ -12609,40 +12618,40 @@
         <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J118" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="K118" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="L118" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M118" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N118" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O118" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="P118" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="Q118" t="s">
         <v>55</v>
       </c>
       <c r="R118" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="S118" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="T118" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="U118" t="s">
         <v>59</v>
@@ -12654,19 +12663,19 @@
         <v>20243291</v>
       </c>
       <c r="B119" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C119" t="s">
         <v>75</v>
       </c>
       <c r="D119" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E119" t="s">
         <v>62</v>
       </c>
       <c r="F119" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G119" t="s">
         <v>45</v>
@@ -12675,40 +12684,40 @@
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="J119" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="K119" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="L119" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="M119" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="N119" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O119" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="P119" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="Q119" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R119" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="S119" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="T119" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="U119" t="s">
         <v>59</v>
@@ -12720,19 +12729,19 @@
         <v>20243117</v>
       </c>
       <c r="B120" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C120" t="s">
         <v>75</v>
       </c>
       <c r="D120" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="G120" t="s">
         <v>45</v>
@@ -12741,40 +12750,40 @@
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="J120" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="K120" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="L120" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="M120" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="N120" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O120" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="P120" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="Q120" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R120" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S120" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T120" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U120" t="s">
         <v>59</v>
@@ -12786,7 +12795,7 @@
         <v>20243108</v>
       </c>
       <c r="B121" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C121" t="s">
         <v>75</v>
@@ -12798,7 +12807,7 @@
         <v>77</v>
       </c>
       <c r="F121" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G121" t="s">
         <v>45</v>
@@ -12807,40 +12816,40 @@
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="J121" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="K121" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="L121" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="M121" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N121" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O121" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="P121" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="Q121" t="s">
         <v>55</v>
       </c>
       <c r="R121" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S121" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U121" t="s">
         <v>59</v>
@@ -12852,19 +12861,19 @@
         <v>20243102</v>
       </c>
       <c r="B122" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C122" t="s">
         <v>75</v>
       </c>
       <c r="D122" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="E122" t="s">
         <v>62</v>
       </c>
       <c r="F122" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="G122" t="s">
         <v>27</v>
@@ -12873,40 +12882,40 @@
         <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="J122" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="K122" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="L122" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="M122" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="N122" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O122" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="P122" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="Q122" t="s">
         <v>55</v>
       </c>
       <c r="R122" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S122" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="T122" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="U122" t="s">
         <v>59</v>
@@ -12918,19 +12927,19 @@
         <v>20243085</v>
       </c>
       <c r="B123" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C123" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D123" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="E123" t="s">
         <v>62</v>
       </c>
       <c r="F123" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="G123" t="s">
         <v>27</v>
@@ -12939,40 +12948,40 @@
         <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="J123" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="K123" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="L123" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="M123" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="N123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O123" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="P123" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="Q123" t="s">
         <v>55</v>
       </c>
       <c r="R123" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="S123" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="T123" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="U123" t="s">
         <v>59</v>
@@ -12984,19 +12993,19 @@
         <v>20247180</v>
       </c>
       <c r="B124" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C124" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D124" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E124" t="s">
         <v>77</v>
       </c>
       <c r="F124" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="G124" t="s">
         <v>45</v>
@@ -13005,29 +13014,29 @@
         <v>78</v>
       </c>
       <c r="I124" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="J124" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M124" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="N124" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O124" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="P124" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="Q124" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R124" t="s">
         <v>86</v>
@@ -13048,10 +13057,10 @@
         <v>20247151</v>
       </c>
       <c r="B125" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D125" t="s">
         <v>90</v>
@@ -13060,7 +13069,7 @@
         <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
@@ -13069,26 +13078,26 @@
         <v>78</v>
       </c>
       <c r="I125" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="J125" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="M125" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="N125" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O125" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="P125" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="Q125" t="s">
         <v>55</v>
@@ -13112,17 +13121,17 @@
         <v>20243003</v>
       </c>
       <c r="B126" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="E126"/>
       <c r="F126" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="G126" t="s">
         <v>45</v>
@@ -13131,40 +13140,40 @@
         <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="J126" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="K126" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="L126" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="M126" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="N126" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O126" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="P126" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="Q126" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R126" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="S126" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="T126" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="U126" t="s">
         <v>59</v>
@@ -13176,19 +13185,19 @@
         <v>20234512</v>
       </c>
       <c r="B127" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C127" t="s">
         <v>75</v>
       </c>
       <c r="D127" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E127" t="s">
         <v>104</v>
       </c>
       <c r="F127" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="G127" t="s">
         <v>45</v>
@@ -13197,40 +13206,40 @@
         <v>78</v>
       </c>
       <c r="I127" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="J127" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="K127" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="L127" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="M127" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="N127" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O127" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="P127" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="Q127" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R127" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="S127" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="T127" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="U127" t="s">
         <v>59</v>
@@ -13242,19 +13251,19 @@
         <v>20234526</v>
       </c>
       <c r="B128" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E128" t="s">
         <v>62</v>
       </c>
       <c r="F128" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="G128" t="s">
         <v>45</v>
@@ -13263,40 +13272,40 @@
         <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="J128" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="K128" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="L128" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="M128" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="N128" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O128" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="P128" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="Q128" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R128" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="S128" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="T128" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="U128" t="s">
         <v>59</v>
@@ -13308,61 +13317,61 @@
         <v>20234438</v>
       </c>
       <c r="B129" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E129" t="s">
         <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G129" t="s">
         <v>27</v>
       </c>
       <c r="H129" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I129" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="J129" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="K129" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="L129" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="M129" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="N129" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O129" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="P129" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="Q129" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R129" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="S129" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="T129" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="U129" t="s">
         <v>59</v>
@@ -13374,61 +13383,61 @@
         <v>20234469</v>
       </c>
       <c r="B130" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E130" t="s">
         <v>62</v>
       </c>
       <c r="F130" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G130" t="s">
         <v>45</v>
       </c>
       <c r="H130" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I130" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="J130" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="K130" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="L130" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="M130" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="N130" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O130" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="P130" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="Q130" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R130" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="S130" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="T130" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="U130" t="s">
         <v>59</v>
@@ -13440,19 +13449,19 @@
         <v>20234393</v>
       </c>
       <c r="B131" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C131" t="s">
         <v>75</v>
       </c>
       <c r="D131" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="E131" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F131" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
@@ -13461,40 +13470,40 @@
         <v>105</v>
       </c>
       <c r="I131" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="J131" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="K131" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="L131" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="M131" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="N131" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O131" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="P131" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="Q131" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R131" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S131" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="T131" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U131" t="s">
         <v>59</v>
@@ -13506,7 +13515,7 @@
         <v>20234382</v>
       </c>
       <c r="B132" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C132" t="s">
         <v>75</v>
@@ -13518,7 +13527,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G132" t="s">
         <v>27</v>
@@ -13527,40 +13536,40 @@
         <v>78</v>
       </c>
       <c r="I132" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="J132" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="K132" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="L132" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="M132" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="N132" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O132" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="P132" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="Q132" t="s">
         <v>55</v>
       </c>
       <c r="R132" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="S132" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="T132" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="U132" t="s">
         <v>59</v>
@@ -13572,19 +13581,19 @@
         <v>20234372</v>
       </c>
       <c r="B133" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C133" t="s">
         <v>75</v>
       </c>
       <c r="D133" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E133" t="s">
         <v>77</v>
       </c>
       <c r="F133" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="G133" t="s">
         <v>45</v>
@@ -13593,40 +13602,40 @@
         <v>78</v>
       </c>
       <c r="I133" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="J133" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="K133" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="L133" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="M133" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="N133" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O133" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="P133" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="Q133" t="s">
         <v>55</v>
       </c>
       <c r="R133" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="S133" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="T133" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="U133" t="s">
         <v>59</v>
@@ -13638,19 +13647,19 @@
         <v>20237936</v>
       </c>
       <c r="B134" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C134" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D134" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="E134" t="s">
         <v>104</v>
       </c>
       <c r="F134" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="G134" t="s">
         <v>45</v>
@@ -13659,38 +13668,38 @@
         <v>78</v>
       </c>
       <c r="I134" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="J134" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="M134" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="N134" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O134" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="P134" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="Q134" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R134" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="S134" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="T134" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="U134" t="s">
         <v>59</v>
@@ -13702,19 +13711,19 @@
         <v>20237937</v>
       </c>
       <c r="B135" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C135" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D135" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="E135" t="s">
         <v>104</v>
       </c>
       <c r="F135" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="G135" t="s">
         <v>45</v>
@@ -13723,38 +13732,38 @@
         <v>78</v>
       </c>
       <c r="I135" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="J135" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="M135" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="N135" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O135" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="P135" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="Q135" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R135" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="S135" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="T135" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="U135" t="s">
         <v>59</v>
@@ -13766,19 +13775,19 @@
         <v>20237883</v>
       </c>
       <c r="B136" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C136" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D136" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="E136" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F136" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="G136" t="s">
         <v>45</v>
@@ -13787,38 +13796,38 @@
         <v>78</v>
       </c>
       <c r="I136" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="J136" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="K136"/>
       <c r="L136" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="M136" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="N136" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O136" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="P136" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="Q136" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="R136" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S136" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="T136" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U136" t="s">
         <v>59</v>
@@ -13830,19 +13839,19 @@
         <v>20237843</v>
       </c>
       <c r="B137" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C137" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
@@ -13851,38 +13860,38 @@
         <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="J137" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="K137"/>
       <c r="L137" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="M137" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="N137" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O137" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="P137" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="Q137" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R137" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="S137" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="T137" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="U137" t="s">
         <v>59</v>
@@ -13894,57 +13903,57 @@
         <v>20230322</v>
       </c>
       <c r="B138" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C138" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D138" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E138"/>
       <c r="F138" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
         <v>105</v>
       </c>
       <c r="I138" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="J138" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="K138" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="L138" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="M138" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="N138" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O138" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="P138" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="Q138" t="s">
         <v>55</v>
       </c>
       <c r="R138" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="S138" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="T138" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="U138" t="s">
         <v>59</v>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,24 +80,165 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyssmann Rémy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streichung von Artikel 22 des Epidemiengesetzes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abrogation de l'article 22 de la loi sur les épidémies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stralcio dell'articolo 22 della legge sulle epidemie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter à l’Assemblée fédérale un projet d’acte législatif prévoyant l’abrogation de l’art.&amp;nbsp;22 de la loi du 28&amp;nbsp;septembre&amp;nbsp;2012 sur les épidémies (LEp).&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, welcher die Streichung von Art. 22 des Epidemiengesetzes (EpG) vorsieht.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Salute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dank einer leistungsfähigen Nationalstrasse 18 Kultur- und Wirtschaftsräume effektiv miteinander verbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collegare efficacemente spazi culturali ed economici attraverso una strada nazionale N18 efficiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les paramètres du programme « Transports ’45 »dans lequel le projet d’amélioration structurelle de la liaison routière Delémont- Bâle a été retenu. Mais, le report au-delà de 2055 des projets routiers le long de la N18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufen (horizon 2055) – suscite une forte incompréhension de la part des élus, des populations et des milieux économiques en particulier. Ce renoncement de fait à une meilleure accessibilité et à de réelles perspectives de développement économique contredit directement les résultats de l’étude de corridor N18 menée sous la direction de l’OFROU selon les méthodes les plus récentes. C’est aussi une question de crédibilité des institutions par un respect de la cohérence des politiques publiques.&lt;/p&gt;&lt;p&gt;La N18 est un élément essentiel du réseau routier national : elle relie l’agglomération bâloise à l’Arc lémanique et unit deux espaces culturels et&amp;nbsp;économiques majeurs. Elle connecte&amp;nbsp;également le Laufonnais, région dynamique, ainsi que la capitale cantonale Delémont au réseau à haute performance. Elle contribue ainsi&amp;nbsp;à la cohésion nationale et au rapprochement des communautés linguistiques.&lt;/p&gt;&lt;p&gt;Sous l’effet de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, avec l’une des plus fortes densités de bouchons du pays. De plus, le trafic actuel porte atteinte à la qualité de vie dans les centres et compromet la sécurité du trafic motorisé et cycliste. Une modernisation rapide du corridor est donc prioritaire.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il la nécessité d’éliminer les goulets d’étranglement sur la N18 entre Angenstein et Delémont ?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel du Muggenberg comme une mesure durable pour améliorer la sécurité au point noir d’Angenstein ?&lt;/li&gt;&lt;li&gt;Comment apprécie-t-il l’utilité des projets recommandés dans l’étude de corridor N18 (tunnel du Muggenberg, contournements Laufen–Zwingen et Delémont, décharge de Laufen) pour renforcer la connexion des entreprises de la région Laufonnais–Thierstein–Delémont ?&lt;/li&gt;&lt;li&gt;Estime-t-il que les contournements Laufen–Zwingen et Delémont constituent des mesures appropriées pour soulager les zones habitées concernées ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ende Januar&amp;nbsp;2026 hat der Bundesrat die Eckwerte des Programms «Verkehr&amp;nbsp;’45» veröffentlicht. Das Vorhaben einer strukturellen Verbesserung der Strassenverbindung Delémont–Basel wurde darin berücksichtigt. Dass die Strassenbauprojekte entlang der Nationalstrasse&amp;nbsp;18 (N18) zwischen Basel und Delémont – mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont&amp;nbsp;2055) – aber bis nach 2055 aufgeschoben werden sollen, stösst bei Politik, Bevölkerung und insbesondere in Wirtschaftskreisen auf grosses Unverständnis. Diese Entscheidung gegen bessere Erreichbarkeit und wirtschaftliche Entwicklung widerspricht den Ergebnissen der Korridorstudie&amp;nbsp;N18, die unter der Federführung des Bundesamts für Strassen (ASTRA) nach neuesten Methoden durchgeführt wurde. Es geht dabei auch um die Glaubwürdigkeit der Institutionen, von denen eine kohärente öffentliche Politik erwartet wird.&lt;/p&gt;&lt;p&gt;Die N18 ist ein wesentlicher Bestandteil des nationalen Strassennetzes: Sie verbindet den Grossraum Basel mit der Genferseeregion und damit zwei wichtige Kultur- und Wirtschaftsräume. Sie schliesst zudem das dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Damit trägt sie zum nationalen Zusammenhalt und zur Annäherung der Sprachgemeinschaften bei.&lt;/p&gt;&lt;p&gt;Aufgrund des Bevölkerungswachstums entwickelt sich dieser Strassenabschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig leidet die Lebensqualität in den Ortszentren, und die Sicherheit des Auto- und Veloverkehrs wird gefährdet. Eine rasche Modernisierung des Korridors hat daher Priorität.&lt;/p&gt;&lt;p&gt;Daher bitte ich den Bundesrat um Beantwortung folgender Fragen:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie beurteilt er die Notwendigkeit, die Engpässe auf der N18 zwischen Angenstein und Delémont zu beseitigen?&lt;/li&gt;&lt;li&gt;Ist der Muggenbergtunnel seines Erachtens eine nachhaltige Massnahme zur Verbesserung der Sicherheit am Unfallhotspot Angenstein?&lt;/li&gt;&lt;li&gt;Wie bewertet er den Nutzen der in der Korridorstudie&amp;nbsp;N18 empfohlenen Projekte (Muggenbergtunnel, Umfahrungen Laufen–Zwingen und Delémont, Zentrumsentlastung Laufen) für eine verbesserte Anbindung der Unternehmen in der Region Laufen–Thierstein–Delémont?&lt;/li&gt;&lt;li&gt;Sind die Umfahrungen Laufen–Zwingen und Delémont seines Erachtens geeignete Massnahmen zur Entlastung der betroffenen Wohngebiete?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports|Aménagement du territoire et logement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sollberger Sandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafforzare la sicurezza stradale con progetti lungo la N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 wurden vom Bundesrat die Eckwerte zu Verkehr ’45 veröffentlicht. Dass die Strassenprojekte entlang der Nationalstrasse 18 zwischen Basel und Delémont mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont 2055) in einen fernen Zeitraum nach 2055 verschoben werden sollen, stösst in der Region auf Unverständnis. Diese faktische Absage an eine bessere Erreichbarkeit und damit ernsthafte wirtschaftliche Entwicklungsperspektiven steht in direktem Widerspruch zu den Ergebnissen der breit abgestützten Korridorstudie N18, welche unter Federführung des ASTRA nach neuesten Methoden durchgeführt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein zentraler Bestandteil des nationalen Strassennetzes, der den Grossraum Basel mit dem Arc lémanique verbindet. Sie schliesst das wirtschaftlich dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig beeinträchtigt die aktuelle Verkehrsführung die Lebensqualität in den Ortszentren erheblich und gefährdet die Sicherheit des Auto- und Veloverkehrs. So kommt es in Grellingen West sowie beim Knoten Angenstein immer wieder zu Unfällen. Bei Letzterem handelt es sich mit zehn Leichtverletzten und einem Schwerverletzten in den Jahren 2022-2024 gar um den zweitgrössten Unfallhotspot des Kantons Baselland. Erhöhte Unfallraten sind zudem auf allen Ortsdurchfahrten zu beobachten – eine unhaltbare Situation. Eine zeitnahe Weiterentwicklung des Korridors ist daher von höchster Priorität.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit entlang der N18, insbesondere an den Unfallschwerpunkten am Knoten Angenstein sowie am Eggflue-Südportal bzw. Grellingen West?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit bei den Ortsdurchfahrten entlang der N18, insbesondere in Zwingen, Laufen und Delémont?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat den Muggenbergtunnel als Massnahme zur nachhaltigen Verbesserung der Verkehrssicherheit am Unfallschwerpunkt Angenstein?&lt;/li&gt;&lt;li&gt;Würde aus Sicht des Bundesrates eine Umfahrung Laufen-Zwingen zur Verkehrssicherheit entlang der N18 beitragen?&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.4774</t>
   </si>
   <si>
-    <t xml:space="preserve">Mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-12-19</t>
   </si>
   <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
     <t xml:space="preserve">EJPD</t>
   </si>
   <si>
@@ -125,9 +266,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20254774</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Sicherheitspolitik|Soziale Fragen</t>
   </si>
   <si>
@@ -149,9 +287,6 @@
     <t xml:space="preserve">2026-03-20</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">EFD</t>
   </si>
   <si>
@@ -179,9 +314,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263374</t>
   </si>
   <si>
-    <t xml:space="preserve">Élu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Staatspolitik|Finanzwesen|Steuer</t>
   </si>
   <si>
@@ -203,9 +335,6 @@
     <t xml:space="preserve">PS</t>
   </si>
   <si>
-    <t xml:space="preserve">EDI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jederzeit sichere Säuglingsnahrung. Prävention und Aufklärung im Fall einer Kontamination gewährleisten</t>
   </si>
   <si>
@@ -239,18 +368,9 @@
     <t xml:space="preserve">26.3454</t>
   </si>
   <si>
-    <t xml:space="preserve">Ip.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stettler Thomas</t>
   </si>
   <si>
-    <t xml:space="preserve">UDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verbesserte Lebensqualität dank den Umfahrungsprojekten entlang der N18</t>
   </si>
   <si>
@@ -272,15 +392,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
   </si>
   <si>
-    <t xml:space="preserve">Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3228</t>
   </si>
   <si>
@@ -311,15 +422,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
   </si>
   <si>
-    <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports|Aménagement du territoire et logement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti|Pianificazione territoriale e alloggi</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3323</t>
   </si>
   <si>
@@ -362,75 +464,6 @@
     <t xml:space="preserve">Finanze|Formazione</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wyssmann Rémy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streichung von Artikel 22 des Epidemiengesetzes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abrogation de l'article 22 de la loi sur les épidémies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stralcio dell'articolo 22 della legge sulle epidemie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter à l’Assemblée fédérale un projet d’acte législatif prévoyant l’abrogation de l’art.&amp;nbsp;22 de la loi du 28&amp;nbsp;septembre&amp;nbsp;2012 sur les épidémies (LEp).&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Entwurf zu einem Erlass der Bundesversammlung vorzulegen, welcher die Streichung von Art. 22 des Epidemiengesetzes (EpG) vorsieht.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Salute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dank einer leistungsfähigen Nationalstrasse 18 Kultur- und Wirtschaftsräume effektiv miteinander verbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relier efficacement des espaces culturels et économiques grâce à une route nationale N18 performante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collegare efficacemente spazi culturali ed economici attraverso una strada nazionale N18 efficiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les paramètres du programme « Transports ’45 »dans lequel le projet d’amélioration structurelle de la liaison routière Delémont- Bâle a été retenu. Mais, le report au-delà de 2055 des projets routiers le long de la N18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufen (horizon 2055) – suscite une forte incompréhension de la part des élus, des populations et des milieux économiques en particulier. Ce renoncement de fait à une meilleure accessibilité et à de réelles perspectives de développement économique contredit directement les résultats de l’étude de corridor N18 menée sous la direction de l’OFROU selon les méthodes les plus récentes. C’est aussi une question de crédibilité des institutions par un respect de la cohérence des politiques publiques.&lt;/p&gt;&lt;p&gt;La N18 est un élément essentiel du réseau routier national : elle relie l’agglomération bâloise à l’Arc lémanique et unit deux espaces culturels et&amp;nbsp;économiques majeurs. Elle connecte&amp;nbsp;également le Laufonnais, région dynamique, ainsi que la capitale cantonale Delémont au réseau à haute performance. Elle contribue ainsi&amp;nbsp;à la cohésion nationale et au rapprochement des communautés linguistiques.&lt;/p&gt;&lt;p&gt;Sous l’effet de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, avec l’une des plus fortes densités de bouchons du pays. De plus, le trafic actuel porte atteinte à la qualité de vie dans les centres et compromet la sécurité du trafic motorisé et cycliste. Une modernisation rapide du corridor est donc prioritaire.&lt;/p&gt;&lt;p&gt;Dans ce contexte, je prie le Conseil fédéral de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il la nécessité d’éliminer les goulets d’étranglement sur la N18 entre Angenstein et Delémont ?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel du Muggenberg comme une mesure durable pour améliorer la sécurité au point noir d’Angenstein ?&lt;/li&gt;&lt;li&gt;Comment apprécie-t-il l’utilité des projets recommandés dans l’étude de corridor N18 (tunnel du Muggenberg, contournements Laufen–Zwingen et Delémont, décharge de Laufen) pour renforcer la connexion des entreprises de la région Laufonnais–Thierstein–Delémont ?&lt;/li&gt;&lt;li&gt;Estime-t-il que les contournements Laufen–Zwingen et Delémont constituent des mesures appropriées pour soulager les zones habitées concernées ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ende Januar&amp;nbsp;2026 hat der Bundesrat die Eckwerte des Programms «Verkehr&amp;nbsp;’45» veröffentlicht. Das Vorhaben einer strukturellen Verbesserung der Strassenverbindung Delémont–Basel wurde darin berücksichtigt. Dass die Strassenbauprojekte entlang der Nationalstrasse&amp;nbsp;18 (N18) zwischen Basel und Delémont – mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont&amp;nbsp;2055) – aber bis nach 2055 aufgeschoben werden sollen, stösst bei Politik, Bevölkerung und insbesondere in Wirtschaftskreisen auf grosses Unverständnis. Diese Entscheidung gegen bessere Erreichbarkeit und wirtschaftliche Entwicklung widerspricht den Ergebnissen der Korridorstudie&amp;nbsp;N18, die unter der Federführung des Bundesamts für Strassen (ASTRA) nach neuesten Methoden durchgeführt wurde. Es geht dabei auch um die Glaubwürdigkeit der Institutionen, von denen eine kohärente öffentliche Politik erwartet wird.&lt;/p&gt;&lt;p&gt;Die N18 ist ein wesentlicher Bestandteil des nationalen Strassennetzes: Sie verbindet den Grossraum Basel mit der Genferseeregion und damit zwei wichtige Kultur- und Wirtschaftsräume. Sie schliesst zudem das dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Damit trägt sie zum nationalen Zusammenhalt und zur Annäherung der Sprachgemeinschaften bei.&lt;/p&gt;&lt;p&gt;Aufgrund des Bevölkerungswachstums entwickelt sich dieser Strassenabschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig leidet die Lebensqualität in den Ortszentren, und die Sicherheit des Auto- und Veloverkehrs wird gefährdet. Eine rasche Modernisierung des Korridors hat daher Priorität.&lt;/p&gt;&lt;p&gt;Daher bitte ich den Bundesrat um Beantwortung folgender Fragen:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie beurteilt er die Notwendigkeit, die Engpässe auf der N18 zwischen Angenstein und Delémont zu beseitigen?&lt;/li&gt;&lt;li&gt;Ist der Muggenbergtunnel seines Erachtens eine nachhaltige Massnahme zur Verbesserung der Sicherheit am Unfallhotspot Angenstein?&lt;/li&gt;&lt;li&gt;Wie bewertet er den Nutzen der in der Korridorstudie&amp;nbsp;N18 empfohlenen Projekte (Muggenbergtunnel, Umfahrungen Laufen–Zwingen und Delémont, Zentrumsentlastung Laufen) für eine verbesserte Anbindung der Unternehmen in der Region Laufen–Thierstein–Delémont?&lt;/li&gt;&lt;li&gt;Sind die Umfahrungen Laufen–Zwingen und Delémont seines Erachtens geeignete Massnahmen zur Entlastung der betroffenen Wohngebiete?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3131</t>
   </si>
   <si>
@@ -546,39 +579,6 @@
   </si>
   <si>
     <t xml:space="preserve">Politica internazionale|Politica di sicurezza|Energia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sollberger Sandra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehrssicherheit stärken mit Projekten entlang der N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projets le long de la N18 pour renforcer la sécurité routière</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafforzare la sicurezza stradale con progetti lungo la N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les grandes lignes du programme Transports ’45. Le fait que les projets routiers le long de la N18 entre Bâle et Delémont, à l’exception du désengorgement du centre de Laufon (horizon de réalisation 2055), soient reportés à une date lointaine après 2055 suscite de l’incompréhension. Ce refus d’améliorer dans les faits l’accessibilité de la région et, par conséquent, ses perspectives de développement économique est en contradiction flagrante avec les résultats de la vaste étude menée sur le corridor&amp;nbsp;N1 sous la direction de l’OFROU selon les méthodes les plus récentes.&lt;/p&gt;&lt;p&gt;La N18 est un élément central du réseau routier national entre la région de Bâle et l’arc lémanique. Elle relie Delémont, le chef-lieu du Jura, et la vallée de Laufon, qui présente un bon dynamisme économique, au réseau routier à grand débit. Cependant, en raison de la croissance démographique, ce tronçon devient toujours plus un goulet d’étranglement. Il affiche même l’un des taux d’embouteillage les plus élevés de Suisse. Parallèlement, la gestion actuelle du trafic nuit considérablement à la qualité de vie dans le cœur des localités et compromet la sécurité des automobilistes et des cyclistes. Les accidents sont notamment fréquents à Grellingen Ouest et au carrefour d’Angenstein. Avec dix blessés légers et un blessé grave entre 2022 et 2024, ce carrefour est même le deuxième endroit le plus accidentogène du canton de Bâle-Campagne. Le nombre d’accidents est aussi élevé dans toutes les localités traversées, ce qui rend la situation intenable. Il est donc primordial de poursuivre rapidement le développement du corridor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Quel est l’avis du Conseil fédéral sur le besoin d’agir rapidement pour améliorer la sécurité routière le long de la N18, en particulier aux points noirs suivants&amp;nbsp;: carrefour d’Angenstein et Grellingen Ouest (portail sud d’Eggflue)&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Idem en ce qui concerne les traversées de localités, en particulier à Zwingen, Laufon et Delémont&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Considère-t-il le tunnel de Muggenberg comme une mesure qui permettrait d’améliorer durablement la sécurité routière au niveau d’Angenstein&amp;nbsp;?&lt;/li&gt;&lt;li&gt;Du point de vue du Conseil fédéral, un contournement de Laufon et Zwingen contribuerait-il à la sécurité routière le long de la N18&amp;nbsp;?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 wurden vom Bundesrat die Eckwerte zu Verkehr ’45 veröffentlicht. Dass die Strassenprojekte entlang der Nationalstrasse 18 zwischen Basel und Delémont mit Ausnahme der Zentrumsentlastung Laufen (Realisierungshorizont 2055) in einen fernen Zeitraum nach 2055 verschoben werden sollen, stösst in der Region auf Unverständnis. Diese faktische Absage an eine bessere Erreichbarkeit und damit ernsthafte wirtschaftliche Entwicklungsperspektiven steht in direktem Widerspruch zu den Ergebnissen der breit abgestützten Korridorstudie N18, welche unter Federführung des ASTRA nach neuesten Methoden durchgeführt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein zentraler Bestandteil des nationalen Strassennetzes, der den Grossraum Basel mit dem Arc lémanique verbindet. Sie schliesst das wirtschaftlich dynamische Laufental und den Kantonshauptort Delémont an das Hochleistungsstrassennetz an. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zunehmend zu einem Engpass – mit einer der schweizweit höchsten Staudichten. Gleichzeitig beeinträchtigt die aktuelle Verkehrsführung die Lebensqualität in den Ortszentren erheblich und gefährdet die Sicherheit des Auto- und Veloverkehrs. So kommt es in Grellingen West sowie beim Knoten Angenstein immer wieder zu Unfällen. Bei Letzterem handelt es sich mit zehn Leichtverletzten und einem Schwerverletzten in den Jahren 2022-2024 gar um den zweitgrössten Unfallhotspot des Kantons Baselland. Erhöhte Unfallraten sind zudem auf allen Ortsdurchfahrten zu beobachten – eine unhaltbare Situation. Eine zeitnahe Weiterentwicklung des Korridors ist daher von höchster Priorität.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit entlang der N18, insbesondere an den Unfallschwerpunkten am Knoten Angenstein sowie am Eggflue-Südportal bzw. Grellingen West?&lt;/li&gt;&lt;li&gt;Wie beurteilt der Bundesrat den Handlungsbedarf zur Verbesserung der Verkehrssicherheit bei den Ortsdurchfahrten entlang der N18, insbesondere in Zwingen, Laufen und Delémont?&lt;/li&gt;&lt;li&gt;Sieht der Bundesrat den Muggenbergtunnel als Massnahme zur nachhaltigen Verbesserung der Verkehrssicherheit am Unfallschwerpunkt Angenstein?&lt;/li&gt;&lt;li&gt;Würde aus Sicht des Bundesrates eine Umfahrung Laufen-Zwingen zur Verkehrssicherheit entlang der N18 beitragen?&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
   </si>
   <si>
     <t xml:space="preserve">26.7151</t>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20254774</v>
+        <v>20263120</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5136,44 +5136,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263374</v>
+        <v>20263121</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3"/>
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N3" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="O3" t="s">
         <v>53</v>
@@ -5194,166 +5196,164 @@
         <v>58</v>
       </c>
       <c r="U3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263411</v>
+        <v>20263069</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
         <v>61</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>64</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>65</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>66</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" t="s">
         <v>67</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>68</v>
       </c>
-      <c r="N4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>69</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>71</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>72</v>
       </c>
-      <c r="T4" t="s">
-        <v>73</v>
-      </c>
       <c r="U4" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263454</v>
+        <v>20254774</v>
       </c>
       <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s">
         <v>74</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" t="s">
         <v>75</v>
       </c>
-      <c r="D5" t="s">
+      <c r="I5" t="s">
         <v>76</v>
       </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>77</v>
       </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>78</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>79</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>80</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>81</v>
       </c>
-      <c r="L5" t="s">
+      <c r="O5" t="s">
         <v>82</v>
       </c>
-      <c r="M5" t="s">
+      <c r="P5" t="s">
         <v>83</v>
       </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" t="s">
         <v>84</v>
       </c>
-      <c r="P5" t="s">
+      <c r="S5" t="s">
         <v>85</v>
       </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>86</v>
       </c>
-      <c r="S5" t="s">
+      <c r="U5" t="s">
         <v>87</v>
-      </c>
-      <c r="T5" t="s">
-        <v>88</v>
-      </c>
-      <c r="U5" t="s">
-        <v>59</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263228</v>
+        <v>20263374</v>
       </c>
       <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>89</v>
       </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6"/>
+      <c r="F6" t="s">
         <v>90</v>
       </c>
-      <c r="E6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
         <v>91</v>
-      </c>
-      <c r="G6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" t="s">
-        <v>78</v>
       </c>
       <c r="I6" t="s">
         <v>92</v>
@@ -5371,121 +5371,121 @@
         <v>96</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="O6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U6" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263323</v>
+        <v>20263411</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="O7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="s">
         <v>55</v>
       </c>
       <c r="R7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U7" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263120</v>
+        <v>20263454</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
         <v>119</v>
@@ -5503,362 +5503,356 @@
         <v>123</v>
       </c>
       <c r="N8" t="s">
+        <v>97</v>
+      </c>
+      <c r="O8" t="s">
         <v>124</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>125</v>
-      </c>
-      <c r="P8" t="s">
-        <v>126</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
       </c>
       <c r="R8" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="S8" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="T8" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="U8" t="s">
-        <v>130</v>
-      </c>
-      <c r="V8" t="s">
-        <v>130</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263121</v>
+        <v>20263228</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" t="s">
+        <v>130</v>
+      </c>
+      <c r="K9" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s">
         <v>132</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>133</v>
       </c>
-      <c r="K9" t="s">
+      <c r="N9" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" t="s">
         <v>134</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
         <v>135</v>
-      </c>
-      <c r="M9" t="s">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s">
-        <v>124</v>
-      </c>
-      <c r="O9" t="s">
-        <v>137</v>
-      </c>
-      <c r="P9" t="s">
-        <v>138</v>
       </c>
       <c r="Q9" t="s">
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="S9" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="T9" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="U9" t="s">
-        <v>130</v>
-      </c>
-      <c r="V9" t="s">
-        <v>130</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263131</v>
+        <v>20263323</v>
       </c>
       <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" t="s">
         <v>139</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="I10" t="s">
         <v>140</v>
       </c>
-      <c r="E10"/>
-      <c r="F10" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>141</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>142</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>143</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>144</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
+        <v>97</v>
+      </c>
+      <c r="O10" t="s">
         <v>145</v>
       </c>
-      <c r="N10" t="s">
-        <v>52</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>146</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" t="s">
         <v>147</v>
       </c>
-      <c r="Q10" t="s">
-        <v>55</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>148</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>149</v>
       </c>
-      <c r="T10" t="s">
-        <v>150</v>
-      </c>
       <c r="U10" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20263099</v>
+        <v>20263131</v>
       </c>
       <c r="B11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
         <v>151</v>
       </c>
-      <c r="C11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
+      <c r="E11"/>
       <c r="F11" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
+        <v>152</v>
+      </c>
+      <c r="J11" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" t="s">
         <v>154</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>155</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>156</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" t="s">
         <v>157</v>
       </c>
-      <c r="M11" t="s">
+      <c r="P11" t="s">
         <v>158</v>
-      </c>
-      <c r="N11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O11" t="s">
-        <v>159</v>
-      </c>
-      <c r="P11" t="s">
-        <v>160</v>
       </c>
       <c r="Q11" t="s">
         <v>37</v>
       </c>
       <c r="R11" t="s">
+        <v>159</v>
+      </c>
+      <c r="S11" t="s">
+        <v>160</v>
+      </c>
+      <c r="T11" t="s">
         <v>161</v>
       </c>
-      <c r="S11" t="s">
-        <v>162</v>
-      </c>
-      <c r="T11" t="s">
-        <v>163</v>
-      </c>
       <c r="U11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20267194</v>
+        <v>20263099</v>
       </c>
       <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
         <v>164</v>
       </c>
-      <c r="C12" t="s">
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
         <v>165</v>
       </c>
-      <c r="D12" t="s">
+      <c r="J12" t="s">
         <v>166</v>
       </c>
-      <c r="E12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="K12" t="s">
         <v>167</v>
       </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>168</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>169</v>
       </c>
-      <c r="K12"/>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
+        <v>97</v>
+      </c>
+      <c r="O12" t="s">
         <v>170</v>
       </c>
-      <c r="M12" t="s">
+      <c r="P12" t="s">
         <v>171</v>
       </c>
-      <c r="N12" t="s">
+      <c r="Q12" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" t="s">
         <v>172</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>173</v>
       </c>
-      <c r="P12" t="s">
+      <c r="T12" t="s">
         <v>174</v>
       </c>
-      <c r="Q12" t="s">
-        <v>37</v>
-      </c>
-      <c r="R12" t="s">
-        <v>175</v>
-      </c>
-      <c r="S12" t="s">
-        <v>176</v>
-      </c>
-      <c r="T12" t="s">
-        <v>177</v>
-      </c>
       <c r="U12" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263069</v>
+        <v>20267194</v>
       </c>
       <c r="B13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" t="s">
         <v>178</v>
       </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" t="s">
         <v>179</v>
       </c>
-      <c r="E13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="J13" t="s">
         <v>180</v>
       </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13"/>
+      <c r="L13" t="s">
         <v>181</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>182</v>
       </c>
-      <c r="K13" t="s">
+      <c r="N13" t="s">
         <v>183</v>
       </c>
-      <c r="L13" t="s">
+      <c r="O13" t="s">
         <v>184</v>
       </c>
-      <c r="M13" t="s">
+      <c r="P13" t="s">
         <v>185</v>
       </c>
-      <c r="N13" t="s">
-        <v>124</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
+        <v>55</v>
+      </c>
+      <c r="R13" t="s">
         <v>186</v>
       </c>
-      <c r="P13" t="s">
+      <c r="S13" t="s">
         <v>187</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="T13" t="s">
         <v>188</v>
       </c>
-      <c r="R13" t="s">
-        <v>86</v>
-      </c>
-      <c r="S13" t="s">
-        <v>87</v>
-      </c>
-      <c r="T13" t="s">
-        <v>88</v>
-      </c>
       <c r="U13" t="s">
-        <v>130</v>
-      </c>
-      <c r="V13" t="s">
-        <v>130</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5868,7 +5862,7 @@
         <v>189</v>
       </c>
       <c r="C14" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
         <v>190</v>
@@ -5877,13 +5871,13 @@
         <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I14" t="s">
         <v>192</v>
@@ -5899,7 +5893,7 @@
         <v>195</v>
       </c>
       <c r="N14" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O14" t="s">
         <v>196</v>
@@ -5920,7 +5914,7 @@
         <v>201</v>
       </c>
       <c r="U14" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V14"/>
     </row>
@@ -5941,7 +5935,7 @@
       </c>
       <c r="G15"/>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
         <v>205</v>
@@ -5964,7 +5958,7 @@
         <v>210</v>
       </c>
       <c r="Q15" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R15" t="s">
         <v>211</v>
@@ -5976,7 +5970,7 @@
         <v>213</v>
       </c>
       <c r="U15" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V15"/>
     </row>
@@ -5988,22 +5982,22 @@
         <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D16" t="s">
         <v>215</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F16" t="s">
         <v>216</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>217</v>
@@ -6019,7 +6013,7 @@
         <v>220</v>
       </c>
       <c r="N16" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O16" t="s">
         <v>221</v>
@@ -6028,7 +6022,7 @@
         <v>222</v>
       </c>
       <c r="Q16" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R16" t="s">
         <v>223</v>
@@ -6040,7 +6034,7 @@
         <v>225</v>
       </c>
       <c r="U16" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V16"/>
     </row>
@@ -6062,10 +6056,10 @@
         <v>228</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
         <v>229</v>
@@ -6083,7 +6077,7 @@
         <v>233</v>
       </c>
       <c r="N17" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O17" t="s">
         <v>234</v>
@@ -6092,7 +6086,7 @@
         <v>235</v>
       </c>
       <c r="Q17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R17" t="s">
         <v>236</v>
@@ -6104,7 +6098,7 @@
         <v>238</v>
       </c>
       <c r="U17" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V17"/>
     </row>
@@ -6116,7 +6110,7 @@
         <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
         <v>240</v>
@@ -6125,13 +6119,13 @@
         <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
         <v>242</v>
@@ -6149,7 +6143,7 @@
         <v>246</v>
       </c>
       <c r="N18" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
         <v>247</v>
@@ -6158,7 +6152,7 @@
         <v>248</v>
       </c>
       <c r="Q18" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R18" t="s">
         <v>249</v>
@@ -6170,7 +6164,7 @@
         <v>251</v>
       </c>
       <c r="U18" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V18"/>
     </row>
@@ -6182,22 +6176,22 @@
         <v>252</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
         <v>253</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I19" t="s">
         <v>254</v>
@@ -6215,7 +6209,7 @@
         <v>258</v>
       </c>
       <c r="N19" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
         <v>259</v>
@@ -6236,7 +6230,7 @@
         <v>263</v>
       </c>
       <c r="U19" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V19"/>
     </row>
@@ -6251,16 +6245,16 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>265</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H20" t="s">
         <v>266</v>
@@ -6290,7 +6284,7 @@
         <v>274</v>
       </c>
       <c r="Q20" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R20" t="s">
         <v>275</v>
@@ -6302,7 +6296,7 @@
         <v>277</v>
       </c>
       <c r="U20" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V20"/>
     </row>
@@ -6314,22 +6308,22 @@
         <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>265</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
         <v>279</v>
@@ -6356,7 +6350,7 @@
         <v>286</v>
       </c>
       <c r="Q21" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R21" t="s">
         <v>287</v>
@@ -6368,7 +6362,7 @@
         <v>289</v>
       </c>
       <c r="U21" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V21"/>
     </row>
@@ -6380,22 +6374,22 @@
         <v>290</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
         <v>291</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
         <v>292</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
         <v>293</v>
@@ -6413,7 +6407,7 @@
         <v>297</v>
       </c>
       <c r="N22" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O22" t="s">
         <v>298</v>
@@ -6434,7 +6428,7 @@
         <v>302</v>
       </c>
       <c r="U22" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V22"/>
     </row>
@@ -6449,19 +6443,19 @@
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
         <v>304</v>
       </c>
       <c r="G23" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s">
         <v>305</v>
@@ -6479,7 +6473,7 @@
         <v>309</v>
       </c>
       <c r="N23" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O23" t="s">
         <v>310</v>
@@ -6500,7 +6494,7 @@
         <v>238</v>
       </c>
       <c r="U23" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V23"/>
     </row>
@@ -6512,22 +6506,22 @@
         <v>312</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
         <v>304</v>
       </c>
       <c r="G24" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I24" t="s">
         <v>313</v>
@@ -6545,7 +6539,7 @@
         <v>317</v>
       </c>
       <c r="N24" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O24" t="s">
         <v>318</v>
@@ -6554,7 +6548,7 @@
         <v>319</v>
       </c>
       <c r="Q24" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R24" t="s">
         <v>320</v>
@@ -6566,7 +6560,7 @@
         <v>322</v>
       </c>
       <c r="U24" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V24"/>
     </row>
@@ -6578,19 +6572,19 @@
         <v>323</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s">
         <v>324</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
         <v>325</v>
       </c>
       <c r="G25" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H25" t="s">
         <v>266</v>
@@ -6609,7 +6603,7 @@
         <v>329</v>
       </c>
       <c r="N25" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O25" t="s">
         <v>330</v>
@@ -6618,7 +6612,7 @@
         <v>331</v>
       </c>
       <c r="Q25" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R25" t="s">
         <v>332</v>
@@ -6630,7 +6624,7 @@
         <v>334</v>
       </c>
       <c r="U25" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V25"/>
     </row>
@@ -6642,22 +6636,22 @@
         <v>335</v>
       </c>
       <c r="C26" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
         <v>336</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
         <v>325</v>
       </c>
       <c r="G26" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I26" t="s">
         <v>337</v>
@@ -6673,7 +6667,7 @@
         <v>340</v>
       </c>
       <c r="N26" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O26" t="s">
         <v>341</v>
@@ -6682,19 +6676,19 @@
         <v>342</v>
       </c>
       <c r="Q26" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R26" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="S26" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="T26" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="U26" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V26"/>
     </row>
@@ -6706,7 +6700,7 @@
         <v>343</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D27" t="s">
         <v>344</v>
@@ -6716,10 +6710,10 @@
         <v>345</v>
       </c>
       <c r="G27" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I27" t="s">
         <v>346</v>
@@ -6746,7 +6740,7 @@
         <v>352</v>
       </c>
       <c r="Q27" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R27" t="s">
         <v>353</v>
@@ -6758,7 +6752,7 @@
         <v>355</v>
       </c>
       <c r="U27" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V27"/>
     </row>
@@ -6776,16 +6770,16 @@
         <v>357</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>358</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H28" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s">
         <v>359</v>
@@ -6803,7 +6797,7 @@
         <v>363</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O28" t="s">
         <v>364</v>
@@ -6812,7 +6806,7 @@
         <v>365</v>
       </c>
       <c r="Q28" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R28" t="s">
         <v>366</v>
@@ -6824,7 +6818,7 @@
         <v>368</v>
       </c>
       <c r="U28" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V28"/>
     </row>
@@ -6836,22 +6830,22 @@
         <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D29" t="s">
         <v>370</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
         <v>358</v>
       </c>
       <c r="G29" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H29" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s">
         <v>371</v>
@@ -6869,7 +6863,7 @@
         <v>375</v>
       </c>
       <c r="N29" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O29" t="s">
         <v>376</v>
@@ -6878,7 +6872,7 @@
         <v>377</v>
       </c>
       <c r="Q29" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R29" t="s">
         <v>211</v>
@@ -6890,7 +6884,7 @@
         <v>213</v>
       </c>
       <c r="U29" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V29"/>
     </row>
@@ -6902,22 +6896,22 @@
         <v>378</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F30" t="s">
         <v>358</v>
       </c>
       <c r="G30" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H30" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I30" t="s">
         <v>379</v>
@@ -6935,7 +6929,7 @@
         <v>383</v>
       </c>
       <c r="N30" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O30" t="s">
         <v>384</v>
@@ -6944,19 +6938,19 @@
         <v>385</v>
       </c>
       <c r="Q30" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R30" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="S30" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T30" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="U30" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V30"/>
     </row>
@@ -6971,19 +6965,19 @@
         <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s">
         <v>358</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H31" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I31" t="s">
         <v>387</v>
@@ -7010,7 +7004,7 @@
         <v>393</v>
       </c>
       <c r="Q31" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R31" t="s">
         <v>394</v>
@@ -7022,7 +7016,7 @@
         <v>396</v>
       </c>
       <c r="U31" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V31"/>
     </row>
@@ -7034,22 +7028,22 @@
         <v>397</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
         <v>398</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
         <v>399</v>
       </c>
       <c r="G32" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s">
         <v>400</v>
@@ -7067,7 +7061,7 @@
         <v>404</v>
       </c>
       <c r="N32" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O32" t="s">
         <v>405</v>
@@ -7076,7 +7070,7 @@
         <v>406</v>
       </c>
       <c r="Q32" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R32" t="s">
         <v>249</v>
@@ -7088,7 +7082,7 @@
         <v>251</v>
       </c>
       <c r="U32" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V32"/>
     </row>
@@ -7100,22 +7094,22 @@
         <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
         <v>408</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H33" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I33" t="s">
         <v>409</v>
@@ -7133,7 +7127,7 @@
         <v>413</v>
       </c>
       <c r="N33" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O33" t="s">
         <v>414</v>
@@ -7142,7 +7136,7 @@
         <v>415</v>
       </c>
       <c r="Q33" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R33" t="s">
         <v>416</v>
@@ -7154,7 +7148,7 @@
         <v>418</v>
       </c>
       <c r="U33" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V33"/>
     </row>
@@ -7166,19 +7160,19 @@
         <v>419</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
         <v>420</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
         <v>408</v>
       </c>
       <c r="G34" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H34" t="s">
         <v>266</v>
@@ -7199,7 +7193,7 @@
         <v>425</v>
       </c>
       <c r="N34" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O34" t="s">
         <v>426</v>
@@ -7220,7 +7214,7 @@
         <v>430</v>
       </c>
       <c r="U34" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V34"/>
     </row>
@@ -7232,22 +7226,22 @@
         <v>431</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
         <v>432</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F35" t="s">
         <v>433</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H35" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s">
         <v>434</v>
@@ -7265,7 +7259,7 @@
         <v>438</v>
       </c>
       <c r="N35" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O35" t="s">
         <v>439</v>
@@ -7274,7 +7268,7 @@
         <v>440</v>
       </c>
       <c r="Q35" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R35" t="s">
         <v>441</v>
@@ -7286,7 +7280,7 @@
         <v>443</v>
       </c>
       <c r="U35" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V35"/>
     </row>
@@ -7301,19 +7295,19 @@
         <v>445</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
         <v>446</v>
       </c>
       <c r="G36" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H36" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s">
         <v>447</v>
@@ -7340,7 +7334,7 @@
         <v>454</v>
       </c>
       <c r="Q36" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R36" t="s">
         <v>455</v>
@@ -7352,7 +7346,7 @@
         <v>457</v>
       </c>
       <c r="U36" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V36"/>
     </row>
@@ -7376,10 +7370,10 @@
         <v>460</v>
       </c>
       <c r="G37" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I37" t="s">
         <v>461</v>
@@ -7397,7 +7391,7 @@
         <v>465</v>
       </c>
       <c r="N37" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O37" t="s">
         <v>466</v>
@@ -7406,7 +7400,7 @@
         <v>467</v>
       </c>
       <c r="Q37" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R37" t="s">
         <v>468</v>
@@ -7418,7 +7412,7 @@
         <v>470</v>
       </c>
       <c r="U37" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V37"/>
     </row>
@@ -7430,7 +7424,7 @@
         <v>471</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
         <v>472</v>
@@ -7442,10 +7436,10 @@
         <v>460</v>
       </c>
       <c r="G38" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s">
         <v>474</v>
@@ -7461,7 +7455,7 @@
         <v>477</v>
       </c>
       <c r="N38" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O38" t="s">
         <v>478</v>
@@ -7470,7 +7464,7 @@
         <v>479</v>
       </c>
       <c r="Q38" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R38" t="s">
         <v>249</v>
@@ -7482,7 +7476,7 @@
         <v>251</v>
       </c>
       <c r="U38" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V38"/>
     </row>
@@ -7494,22 +7488,22 @@
         <v>480</v>
       </c>
       <c r="C39" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D39" t="s">
         <v>481</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F39" t="s">
         <v>460</v>
       </c>
       <c r="G39" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I39" t="s">
         <v>482</v>
@@ -7525,7 +7519,7 @@
         <v>485</v>
       </c>
       <c r="N39" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O39" t="s">
         <v>486</v>
@@ -7546,7 +7540,7 @@
         <v>490</v>
       </c>
       <c r="U39" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V39"/>
     </row>
@@ -7558,22 +7552,22 @@
         <v>491</v>
       </c>
       <c r="C40" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
         <v>420</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>492</v>
       </c>
       <c r="G40" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I40" t="s">
         <v>493</v>
@@ -7589,7 +7583,7 @@
         <v>496</v>
       </c>
       <c r="N40" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O40" t="s">
         <v>497</v>
@@ -7598,7 +7592,7 @@
         <v>498</v>
       </c>
       <c r="Q40" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R40" t="s">
         <v>499</v>
@@ -7610,7 +7604,7 @@
         <v>501</v>
       </c>
       <c r="U40" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V40"/>
     </row>
@@ -7622,19 +7616,19 @@
         <v>502</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
         <v>503</v>
       </c>
       <c r="E41" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
         <v>504</v>
       </c>
       <c r="G41" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
         <v>266</v>
@@ -7655,7 +7649,7 @@
         <v>509</v>
       </c>
       <c r="N41" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O41" t="s">
         <v>510</v>
@@ -7664,7 +7658,7 @@
         <v>511</v>
       </c>
       <c r="Q41" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R41" t="s">
         <v>512</v>
@@ -7676,7 +7670,7 @@
         <v>514</v>
       </c>
       <c r="U41" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V41"/>
     </row>
@@ -7688,19 +7682,19 @@
         <v>515</v>
       </c>
       <c r="C42" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
         <v>503</v>
       </c>
       <c r="E42" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
         <v>504</v>
       </c>
       <c r="G42" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H42" t="s">
         <v>266</v>
@@ -7719,7 +7713,7 @@
         <v>519</v>
       </c>
       <c r="N42" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O42" t="s">
         <v>520</v>
@@ -7728,7 +7722,7 @@
         <v>521</v>
       </c>
       <c r="Q42" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R42" t="s">
         <v>522</v>
@@ -7740,7 +7734,7 @@
         <v>524</v>
       </c>
       <c r="U42" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V42"/>
     </row>
@@ -7790,13 +7784,13 @@
         <v>536</v>
       </c>
       <c r="Q43" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R43"/>
       <c r="S43"/>
       <c r="T43"/>
       <c r="U43" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V43"/>
     </row>
@@ -7808,22 +7802,22 @@
         <v>537</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
         <v>538</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s">
         <v>539</v>
       </c>
       <c r="G44" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I44" t="s">
         <v>540</v>
@@ -7841,7 +7835,7 @@
         <v>544</v>
       </c>
       <c r="N44" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O44" t="s">
         <v>545</v>
@@ -7862,7 +7856,7 @@
         <v>549</v>
       </c>
       <c r="U44" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V44"/>
     </row>
@@ -7874,22 +7868,22 @@
         <v>550</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
         <v>551</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F45" t="s">
         <v>539</v>
       </c>
       <c r="G45" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I45" t="s">
         <v>552</v>
@@ -7907,7 +7901,7 @@
         <v>556</v>
       </c>
       <c r="N45" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O45" t="s">
         <v>557</v>
@@ -7916,7 +7910,7 @@
         <v>558</v>
       </c>
       <c r="Q45" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R45" t="s">
         <v>559</v>
@@ -7928,7 +7922,7 @@
         <v>561</v>
       </c>
       <c r="U45" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V45"/>
     </row>
@@ -7940,22 +7934,22 @@
         <v>562</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D46" t="s">
         <v>563</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F46" t="s">
         <v>539</v>
       </c>
       <c r="G46" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H46" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s">
         <v>564</v>
@@ -7982,7 +7976,7 @@
         <v>571</v>
       </c>
       <c r="Q46" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R46" t="s">
         <v>572</v>
@@ -7994,7 +7988,7 @@
         <v>574</v>
       </c>
       <c r="U46" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V46"/>
     </row>
@@ -8009,17 +8003,17 @@
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E47"/>
       <c r="F47" t="s">
         <v>576</v>
       </c>
       <c r="G47" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s">
         <v>577</v>
@@ -8037,7 +8031,7 @@
         <v>581</v>
       </c>
       <c r="N47" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O47" t="s">
         <v>582</v>
@@ -8046,7 +8040,7 @@
         <v>583</v>
       </c>
       <c r="Q47" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R47" t="s">
         <v>584</v>
@@ -8058,7 +8052,7 @@
         <v>586</v>
       </c>
       <c r="U47" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V47"/>
     </row>
@@ -8070,22 +8064,22 @@
         <v>587</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
         <v>588</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F48" t="s">
         <v>576</v>
       </c>
       <c r="G48" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H48" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
         <v>589</v>
@@ -8103,7 +8097,7 @@
         <v>593</v>
       </c>
       <c r="N48" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O48" t="s">
         <v>594</v>
@@ -8124,7 +8118,7 @@
         <v>598</v>
       </c>
       <c r="U48" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V48"/>
     </row>
@@ -8136,22 +8130,22 @@
         <v>599</v>
       </c>
       <c r="C49" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
         <v>600</v>
       </c>
       <c r="E49" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F49" t="s">
         <v>601</v>
       </c>
       <c r="G49" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I49" t="s">
         <v>602</v>
@@ -8169,7 +8163,7 @@
         <v>606</v>
       </c>
       <c r="N49" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O49" t="s">
         <v>607</v>
@@ -8178,19 +8172,19 @@
         <v>608</v>
       </c>
       <c r="Q49" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R49" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="S49" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T49" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="U49" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V49"/>
     </row>
@@ -8202,7 +8196,7 @@
         <v>609</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
         <v>610</v>
@@ -8212,10 +8206,10 @@
         <v>601</v>
       </c>
       <c r="G50" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H50" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I50" t="s">
         <v>611</v>
@@ -8242,7 +8236,7 @@
         <v>617</v>
       </c>
       <c r="Q50" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R50" t="s">
         <v>618</v>
@@ -8254,7 +8248,7 @@
         <v>620</v>
       </c>
       <c r="U50" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V50"/>
     </row>
@@ -8266,22 +8260,22 @@
         <v>621</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
         <v>370</v>
       </c>
       <c r="E51" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F51" t="s">
         <v>601</v>
       </c>
       <c r="G51" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H51" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I51" t="s">
         <v>622</v>
@@ -8299,7 +8293,7 @@
         <v>626</v>
       </c>
       <c r="N51" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O51" t="s">
         <v>627</v>
@@ -8308,7 +8302,7 @@
         <v>628</v>
       </c>
       <c r="Q51" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R51" t="s">
         <v>629</v>
@@ -8320,7 +8314,7 @@
         <v>631</v>
       </c>
       <c r="U51" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V51"/>
     </row>
@@ -8332,7 +8326,7 @@
         <v>632</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D52" t="s">
         <v>633</v>
@@ -8344,10 +8338,10 @@
         <v>634</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H52" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I52" t="s">
         <v>635</v>
@@ -8365,7 +8359,7 @@
         <v>639</v>
       </c>
       <c r="N52" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O52" t="s">
         <v>640</v>
@@ -8374,7 +8368,7 @@
         <v>641</v>
       </c>
       <c r="Q52" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R52" t="s">
         <v>547</v>
@@ -8386,7 +8380,7 @@
         <v>549</v>
       </c>
       <c r="U52" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V52"/>
     </row>
@@ -8404,16 +8398,16 @@
         <v>643</v>
       </c>
       <c r="E53" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F53" t="s">
         <v>644</v>
       </c>
       <c r="G53" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I53" t="s">
         <v>645</v>
@@ -8431,7 +8425,7 @@
         <v>649</v>
       </c>
       <c r="N53" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O53" t="s">
         <v>650</v>
@@ -8440,19 +8434,19 @@
         <v>651</v>
       </c>
       <c r="Q53" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R53" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="S53" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="T53" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="U53" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V53"/>
     </row>
@@ -8476,10 +8470,10 @@
         <v>655</v>
       </c>
       <c r="G54" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s">
         <v>656</v>
@@ -8497,7 +8491,7 @@
         <v>660</v>
       </c>
       <c r="N54" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O54" t="s">
         <v>661</v>
@@ -8518,7 +8512,7 @@
         <v>665</v>
       </c>
       <c r="U54" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V54"/>
     </row>
@@ -8536,16 +8530,16 @@
         <v>420</v>
       </c>
       <c r="E55" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F55" t="s">
         <v>655</v>
       </c>
       <c r="G55" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s">
         <v>667</v>
@@ -8563,7 +8557,7 @@
         <v>671</v>
       </c>
       <c r="N55" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O55" t="s">
         <v>672</v>
@@ -8572,7 +8566,7 @@
         <v>673</v>
       </c>
       <c r="Q55" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R55" t="s">
         <v>674</v>
@@ -8584,7 +8578,7 @@
         <v>676</v>
       </c>
       <c r="U55" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V55"/>
     </row>
@@ -8606,10 +8600,10 @@
         <v>678</v>
       </c>
       <c r="G56" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H56" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s">
         <v>679</v>
@@ -8636,7 +8630,7 @@
         <v>685</v>
       </c>
       <c r="Q56" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R56" t="s">
         <v>674</v>
@@ -8648,7 +8642,7 @@
         <v>676</v>
       </c>
       <c r="U56" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V56"/>
     </row>
@@ -8660,19 +8654,19 @@
         <v>686</v>
       </c>
       <c r="C57" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D57" t="s">
         <v>687</v>
       </c>
       <c r="E57" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F57" t="s">
         <v>688</v>
       </c>
       <c r="G57" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H57" t="s">
         <v>689</v>
@@ -8702,7 +8696,7 @@
         <v>696</v>
       </c>
       <c r="Q57" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R57" t="s">
         <v>697</v>
@@ -8714,7 +8708,7 @@
         <v>699</v>
       </c>
       <c r="U57" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V57"/>
     </row>
@@ -8726,22 +8720,22 @@
         <v>700</v>
       </c>
       <c r="C58" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
         <v>701</v>
       </c>
       <c r="E58" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F58" t="s">
         <v>688</v>
       </c>
       <c r="G58" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H58" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I58" t="s">
         <v>702</v>
@@ -8759,7 +8753,7 @@
         <v>706</v>
       </c>
       <c r="N58" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O58" t="s">
         <v>707</v>
@@ -8768,7 +8762,7 @@
         <v>708</v>
       </c>
       <c r="Q58" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R58" t="s">
         <v>709</v>
@@ -8780,7 +8774,7 @@
         <v>711</v>
       </c>
       <c r="U58" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V58"/>
     </row>
@@ -8792,22 +8786,22 @@
         <v>712</v>
       </c>
       <c r="C59" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D59" t="s">
         <v>713</v>
       </c>
       <c r="E59" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F59" t="s">
         <v>688</v>
       </c>
       <c r="G59" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H59" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I59" t="s">
         <v>714</v>
@@ -8825,7 +8819,7 @@
         <v>718</v>
       </c>
       <c r="N59" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O59" t="s">
         <v>719</v>
@@ -8846,7 +8840,7 @@
         <v>470</v>
       </c>
       <c r="U59" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V59"/>
     </row>
@@ -8864,16 +8858,16 @@
         <v>722</v>
       </c>
       <c r="E60" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
         <v>723</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H60" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
         <v>724</v>
@@ -8891,7 +8885,7 @@
         <v>728</v>
       </c>
       <c r="N60" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O60" t="s">
         <v>729</v>
@@ -8900,7 +8894,7 @@
         <v>730</v>
       </c>
       <c r="Q60" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R60" t="s">
         <v>731</v>
@@ -8912,7 +8906,7 @@
         <v>733</v>
       </c>
       <c r="U60" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V60"/>
     </row>
@@ -8927,19 +8921,19 @@
         <v>23</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F61" t="s">
         <v>723</v>
       </c>
       <c r="G61" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H61" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s">
         <v>735</v>
@@ -8966,7 +8960,7 @@
         <v>741</v>
       </c>
       <c r="Q61" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R61" t="s">
         <v>674</v>
@@ -8978,7 +8972,7 @@
         <v>676</v>
       </c>
       <c r="U61" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V61"/>
     </row>
@@ -8990,22 +8984,22 @@
         <v>742</v>
       </c>
       <c r="C62" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D62" t="s">
         <v>291</v>
       </c>
       <c r="E62" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
         <v>743</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H62" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I62" t="s">
         <v>744</v>
@@ -9023,7 +9017,7 @@
         <v>748</v>
       </c>
       <c r="N62" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O62" t="s">
         <v>749</v>
@@ -9044,7 +9038,7 @@
         <v>753</v>
       </c>
       <c r="U62" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V62"/>
     </row>
@@ -9056,22 +9050,22 @@
         <v>754</v>
       </c>
       <c r="C63" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D63" t="s">
         <v>588</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F63" t="s">
         <v>755</v>
       </c>
       <c r="G63" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I63" t="s">
         <v>756</v>
@@ -9089,7 +9083,7 @@
         <v>760</v>
       </c>
       <c r="N63" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O63" t="s">
         <v>761</v>
@@ -9098,7 +9092,7 @@
         <v>762</v>
       </c>
       <c r="Q63" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R63" t="s">
         <v>763</v>
@@ -9110,7 +9104,7 @@
         <v>765</v>
       </c>
       <c r="U63" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V63"/>
     </row>
@@ -9133,7 +9127,7 @@
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I64" t="s">
         <v>769</v>
@@ -9151,7 +9145,7 @@
         <v>773</v>
       </c>
       <c r="N64" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="O64" t="s">
         <v>774</v>
@@ -9160,13 +9154,13 @@
         <v>775</v>
       </c>
       <c r="Q64" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R64"/>
       <c r="S64"/>
       <c r="T64"/>
       <c r="U64" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V64"/>
     </row>
@@ -9189,7 +9183,7 @@
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I65" t="s">
         <v>530</v>
@@ -9207,7 +9201,7 @@
         <v>780</v>
       </c>
       <c r="N65" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O65" t="s">
         <v>781</v>
@@ -9216,13 +9210,13 @@
         <v>782</v>
       </c>
       <c r="Q65" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R65"/>
       <c r="S65"/>
       <c r="T65"/>
       <c r="U65" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V65"/>
     </row>
@@ -9244,10 +9238,10 @@
         <v>785</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H66" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I66" t="s">
         <v>786</v>
@@ -9265,7 +9259,7 @@
         <v>790</v>
       </c>
       <c r="N66" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="O66" t="s">
         <v>791</v>
@@ -9274,7 +9268,7 @@
         <v>792</v>
       </c>
       <c r="Q66" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R66" t="s">
         <v>793</v>
@@ -9286,7 +9280,7 @@
         <v>795</v>
       </c>
       <c r="U66" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V66"/>
     </row>
@@ -9304,16 +9298,16 @@
         <v>551</v>
       </c>
       <c r="E67" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F67" t="s">
         <v>797</v>
       </c>
       <c r="G67" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H67" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I67" t="s">
         <v>798</v>
@@ -9331,7 +9325,7 @@
         <v>802</v>
       </c>
       <c r="N67" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O67" t="s">
         <v>803</v>
@@ -9340,7 +9334,7 @@
         <v>804</v>
       </c>
       <c r="Q67" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R67" t="s">
         <v>805</v>
@@ -9352,7 +9346,7 @@
         <v>807</v>
       </c>
       <c r="U67" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V67"/>
     </row>
@@ -9364,7 +9358,7 @@
         <v>808</v>
       </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
         <v>653</v>
@@ -9376,10 +9370,10 @@
         <v>797</v>
       </c>
       <c r="G68" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s">
         <v>809</v>
@@ -9397,7 +9391,7 @@
         <v>813</v>
       </c>
       <c r="N68" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O68" t="s">
         <v>814</v>
@@ -9406,7 +9400,7 @@
         <v>815</v>
       </c>
       <c r="Q68" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R68" t="s">
         <v>816</v>
@@ -9418,7 +9412,7 @@
         <v>818</v>
       </c>
       <c r="U68" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V68"/>
     </row>
@@ -9430,19 +9424,19 @@
         <v>819</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s">
         <v>820</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F69" t="s">
         <v>797</v>
       </c>
       <c r="G69" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H69" t="s">
         <v>821</v>
@@ -9463,7 +9457,7 @@
         <v>826</v>
       </c>
       <c r="N69" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O69" t="s">
         <v>827</v>
@@ -9484,7 +9478,7 @@
         <v>831</v>
       </c>
       <c r="U69" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V69"/>
     </row>
@@ -9502,16 +9496,16 @@
         <v>370</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F70" t="s">
         <v>797</v>
       </c>
       <c r="G70" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s">
         <v>833</v>
@@ -9538,7 +9532,7 @@
         <v>839</v>
       </c>
       <c r="Q70" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R70" t="s">
         <v>840</v>
@@ -9550,7 +9544,7 @@
         <v>842</v>
       </c>
       <c r="U70" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V70"/>
     </row>
@@ -9568,16 +9562,16 @@
         <v>844</v>
       </c>
       <c r="E71" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F71" t="s">
         <v>797</v>
       </c>
       <c r="G71" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H71" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I71" t="s">
         <v>845</v>
@@ -9595,7 +9589,7 @@
         <v>849</v>
       </c>
       <c r="N71" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O71" t="s">
         <v>850</v>
@@ -9616,7 +9610,7 @@
         <v>854</v>
       </c>
       <c r="U71" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V71"/>
     </row>
@@ -9628,22 +9622,22 @@
         <v>855</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
         <v>856</v>
       </c>
       <c r="E72" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F72" t="s">
         <v>797</v>
       </c>
       <c r="G72" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s">
         <v>857</v>
@@ -9661,7 +9655,7 @@
         <v>861</v>
       </c>
       <c r="N72" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O72" t="s">
         <v>862</v>
@@ -9670,7 +9664,7 @@
         <v>863</v>
       </c>
       <c r="Q72" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R72" t="s">
         <v>864</v>
@@ -9682,7 +9676,7 @@
         <v>866</v>
       </c>
       <c r="U72" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V72"/>
     </row>
@@ -9694,22 +9688,22 @@
         <v>867</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
         <v>481</v>
       </c>
       <c r="E73" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F73" t="s">
         <v>868</v>
       </c>
       <c r="G73" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H73" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I73" t="s">
         <v>869</v>
@@ -9727,7 +9721,7 @@
         <v>873</v>
       </c>
       <c r="N73" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O73" t="s">
         <v>874</v>
@@ -9736,7 +9730,7 @@
         <v>875</v>
       </c>
       <c r="Q73" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R73" t="s">
         <v>876</v>
@@ -9748,7 +9742,7 @@
         <v>878</v>
       </c>
       <c r="U73" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V73"/>
     </row>
@@ -9760,22 +9754,22 @@
         <v>879</v>
       </c>
       <c r="C74" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D74" t="s">
         <v>880</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F74" t="s">
         <v>868</v>
       </c>
       <c r="G74" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H74" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I74" t="s">
         <v>881</v>
@@ -9793,7 +9787,7 @@
         <v>885</v>
       </c>
       <c r="N74" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O74" t="s">
         <v>886</v>
@@ -9814,7 +9808,7 @@
         <v>890</v>
       </c>
       <c r="U74" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V74"/>
     </row>
@@ -9837,7 +9831,7 @@
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I75" t="s">
         <v>893</v>
@@ -9864,13 +9858,13 @@
         <v>900</v>
       </c>
       <c r="Q75" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R75"/>
       <c r="S75"/>
       <c r="T75"/>
       <c r="U75" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V75"/>
     </row>
@@ -9885,19 +9879,19 @@
         <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E76" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
         <v>902</v>
       </c>
       <c r="G76" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s">
         <v>359</v>
@@ -9915,7 +9909,7 @@
         <v>906</v>
       </c>
       <c r="N76" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O76" t="s">
         <v>907</v>
@@ -9924,7 +9918,7 @@
         <v>908</v>
       </c>
       <c r="Q76" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R76" t="s">
         <v>366</v>
@@ -9936,7 +9930,7 @@
         <v>368</v>
       </c>
       <c r="U76" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V76"/>
     </row>
@@ -9948,22 +9942,22 @@
         <v>909</v>
       </c>
       <c r="C77" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D77" t="s">
         <v>910</v>
       </c>
       <c r="E77" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
         <v>911</v>
       </c>
       <c r="G77" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I77" t="s">
         <v>912</v>
@@ -9979,7 +9973,7 @@
         <v>915</v>
       </c>
       <c r="N77" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O77" t="s">
         <v>916</v>
@@ -9988,7 +9982,7 @@
         <v>917</v>
       </c>
       <c r="Q77" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R77" t="s">
         <v>918</v>
@@ -10000,7 +9994,7 @@
         <v>920</v>
       </c>
       <c r="U77" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V77"/>
     </row>
@@ -10012,22 +10006,22 @@
         <v>921</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D78" t="s">
         <v>922</v>
       </c>
       <c r="E78" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F78" t="s">
         <v>923</v>
       </c>
       <c r="G78" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I78" t="s">
         <v>924</v>
@@ -10043,7 +10037,7 @@
         <v>927</v>
       </c>
       <c r="N78" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O78" t="s">
         <v>928</v>
@@ -10052,7 +10046,7 @@
         <v>929</v>
       </c>
       <c r="Q78" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R78" t="s">
         <v>805</v>
@@ -10064,7 +10058,7 @@
         <v>807</v>
       </c>
       <c r="U78" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V78"/>
     </row>
@@ -10085,7 +10079,7 @@
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I79" t="s">
         <v>932</v>
@@ -10099,7 +10093,7 @@
       <c r="L79"/>
       <c r="M79"/>
       <c r="N79" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O79" t="s">
         <v>935</v>
@@ -10108,7 +10102,7 @@
         <v>936</v>
       </c>
       <c r="Q79" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R79" t="s">
         <v>937</v>
@@ -10120,7 +10114,7 @@
         <v>939</v>
       </c>
       <c r="U79" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V79"/>
     </row>
@@ -10143,7 +10137,7 @@
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I80" t="s">
         <v>942</v>
@@ -10161,7 +10155,7 @@
         <v>946</v>
       </c>
       <c r="N80" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="O80" t="s">
         <v>947</v>
@@ -10170,7 +10164,7 @@
         <v>948</v>
       </c>
       <c r="Q80" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R80" t="s">
         <v>949</v>
@@ -10182,7 +10176,7 @@
         <v>951</v>
       </c>
       <c r="U80" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V80"/>
     </row>
@@ -10205,7 +10199,7 @@
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I81" t="s">
         <v>953</v>
@@ -10232,7 +10226,7 @@
         <v>959</v>
       </c>
       <c r="Q81" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R81" t="s">
         <v>960</v>
@@ -10244,7 +10238,7 @@
         <v>962</v>
       </c>
       <c r="U81" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V81"/>
     </row>
@@ -10268,10 +10262,10 @@
         <v>964</v>
       </c>
       <c r="G82" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H82" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
         <v>965</v>
@@ -10289,7 +10283,7 @@
         <v>969</v>
       </c>
       <c r="N82" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O82" t="s">
         <v>970</v>
@@ -10310,7 +10304,7 @@
         <v>974</v>
       </c>
       <c r="U82" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V82"/>
     </row>
@@ -10328,16 +10322,16 @@
         <v>976</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F83" t="s">
         <v>977</v>
       </c>
       <c r="G83" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H83" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I83" t="s">
         <v>978</v>
@@ -10355,7 +10349,7 @@
         <v>982</v>
       </c>
       <c r="N83" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O83" t="s">
         <v>983</v>
@@ -10376,7 +10370,7 @@
         <v>987</v>
       </c>
       <c r="U83" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V83"/>
     </row>
@@ -10388,22 +10382,22 @@
         <v>988</v>
       </c>
       <c r="C84" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
         <v>989</v>
       </c>
       <c r="E84" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
         <v>977</v>
       </c>
       <c r="G84" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H84" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I84" t="s">
         <v>990</v>
@@ -10421,7 +10415,7 @@
         <v>994</v>
       </c>
       <c r="N84" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O84" t="s">
         <v>995</v>
@@ -10430,7 +10424,7 @@
         <v>996</v>
       </c>
       <c r="Q84" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R84" t="s">
         <v>629</v>
@@ -10442,7 +10436,7 @@
         <v>631</v>
       </c>
       <c r="U84" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V84"/>
     </row>
@@ -10460,16 +10454,16 @@
         <v>998</v>
       </c>
       <c r="E85" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F85" t="s">
         <v>977</v>
       </c>
       <c r="G85" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H85" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I85" t="s">
         <v>999</v>
@@ -10487,7 +10481,7 @@
         <v>1003</v>
       </c>
       <c r="N85" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O85" t="s">
         <v>1004</v>
@@ -10496,7 +10490,7 @@
         <v>1005</v>
       </c>
       <c r="Q85" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R85" t="s">
         <v>1006</v>
@@ -10508,7 +10502,7 @@
         <v>1008</v>
       </c>
       <c r="U85" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V85"/>
     </row>
@@ -10520,22 +10514,22 @@
         <v>1009</v>
       </c>
       <c r="C86" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D86" t="s">
         <v>1010</v>
       </c>
       <c r="E86" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F86" t="s">
         <v>977</v>
       </c>
       <c r="G86" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I86" t="s">
         <v>1011</v>
@@ -10553,7 +10547,7 @@
         <v>1015</v>
       </c>
       <c r="N86" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O86" t="s">
         <v>1016</v>
@@ -10562,7 +10556,7 @@
         <v>1017</v>
       </c>
       <c r="Q86" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R86" t="s">
         <v>547</v>
@@ -10574,7 +10568,7 @@
         <v>549</v>
       </c>
       <c r="U86" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V86"/>
     </row>
@@ -10592,16 +10586,16 @@
         <v>1019</v>
       </c>
       <c r="E87" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F87" t="s">
         <v>1020</v>
       </c>
       <c r="G87" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I87" t="s">
         <v>1021</v>
@@ -10619,7 +10613,7 @@
         <v>1025</v>
       </c>
       <c r="N87" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O87" t="s">
         <v>1026</v>
@@ -10640,7 +10634,7 @@
         <v>334</v>
       </c>
       <c r="U87" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V87"/>
     </row>
@@ -10652,22 +10646,22 @@
         <v>1028</v>
       </c>
       <c r="C88" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D88" t="s">
         <v>420</v>
       </c>
       <c r="E88" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F88" t="s">
         <v>1029</v>
       </c>
       <c r="G88" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H88" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I88" t="s">
         <v>1030</v>
@@ -10683,7 +10677,7 @@
         <v>1033</v>
       </c>
       <c r="N88" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O88" t="s">
         <v>1034</v>
@@ -10692,7 +10686,7 @@
         <v>1035</v>
       </c>
       <c r="Q88" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R88" t="s">
         <v>211</v>
@@ -10704,7 +10698,7 @@
         <v>213</v>
       </c>
       <c r="U88" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V88"/>
     </row>
@@ -10716,22 +10710,22 @@
         <v>1036</v>
       </c>
       <c r="C89" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D89" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="E89" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F89" t="s">
         <v>1037</v>
       </c>
       <c r="G89" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I89" t="s">
         <v>1038</v>
@@ -10749,7 +10743,7 @@
         <v>1042</v>
       </c>
       <c r="N89" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O89" t="s">
         <v>1043</v>
@@ -10758,19 +10752,19 @@
         <v>1044</v>
       </c>
       <c r="Q89" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R89" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="S89" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T89" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="U89" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V89"/>
     </row>
@@ -10782,22 +10776,22 @@
         <v>1045</v>
       </c>
       <c r="C90" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D90" t="s">
         <v>1010</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F90" t="s">
         <v>1046</v>
       </c>
       <c r="G90" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H90" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I90" t="s">
         <v>1047</v>
@@ -10813,7 +10807,7 @@
         <v>1050</v>
       </c>
       <c r="N90" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O90" t="s">
         <v>1051</v>
@@ -10822,7 +10816,7 @@
         <v>1052</v>
       </c>
       <c r="Q90" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R90" t="s">
         <v>468</v>
@@ -10834,7 +10828,7 @@
         <v>470</v>
       </c>
       <c r="U90" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V90"/>
     </row>
@@ -10846,22 +10840,22 @@
         <v>1053</v>
       </c>
       <c r="C91" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D91" t="s">
         <v>420</v>
       </c>
       <c r="E91" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
         <v>1046</v>
       </c>
       <c r="G91" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H91" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I91" t="s">
         <v>1054</v>
@@ -10877,7 +10871,7 @@
         <v>1057</v>
       </c>
       <c r="N91" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O91" t="s">
         <v>1058</v>
@@ -10886,7 +10880,7 @@
         <v>1059</v>
       </c>
       <c r="Q91" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R91" t="s">
         <v>211</v>
@@ -10898,7 +10892,7 @@
         <v>213</v>
       </c>
       <c r="U91" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V91"/>
     </row>
@@ -10910,22 +10904,22 @@
         <v>1060</v>
       </c>
       <c r="C92" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D92" t="s">
         <v>420</v>
       </c>
       <c r="E92" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F92" t="s">
         <v>1046</v>
       </c>
       <c r="G92" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I92" t="s">
         <v>1054</v>
@@ -10941,7 +10935,7 @@
         <v>1062</v>
       </c>
       <c r="N92" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O92" t="s">
         <v>1063</v>
@@ -10950,7 +10944,7 @@
         <v>1064</v>
       </c>
       <c r="Q92" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R92" t="s">
         <v>211</v>
@@ -10962,7 +10956,7 @@
         <v>213</v>
       </c>
       <c r="U92" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V92"/>
     </row>
@@ -10974,22 +10968,22 @@
         <v>1065</v>
       </c>
       <c r="C93" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D93" t="s">
         <v>420</v>
       </c>
       <c r="E93" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F93" t="s">
         <v>1046</v>
       </c>
       <c r="G93" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H93" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I93" t="s">
         <v>1054</v>
@@ -11005,7 +10999,7 @@
         <v>1067</v>
       </c>
       <c r="N93" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O93" t="s">
         <v>1068</v>
@@ -11014,7 +11008,7 @@
         <v>1069</v>
       </c>
       <c r="Q93" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R93" t="s">
         <v>211</v>
@@ -11026,7 +11020,7 @@
         <v>213</v>
       </c>
       <c r="U93" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V93"/>
     </row>
@@ -11038,22 +11032,22 @@
         <v>1070</v>
       </c>
       <c r="C94" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D94" t="s">
         <v>503</v>
       </c>
       <c r="E94" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F94" t="s">
         <v>1071</v>
       </c>
       <c r="G94" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H94" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I94" t="s">
         <v>1072</v>
@@ -11071,7 +11065,7 @@
         <v>1076</v>
       </c>
       <c r="N94" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O94" t="s">
         <v>1077</v>
@@ -11080,7 +11074,7 @@
         <v>1078</v>
       </c>
       <c r="Q94" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R94" t="s">
         <v>1079</v>
@@ -11092,7 +11086,7 @@
         <v>1081</v>
       </c>
       <c r="U94" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V94"/>
     </row>
@@ -11104,22 +11098,22 @@
         <v>1082</v>
       </c>
       <c r="C95" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D95" t="s">
         <v>563</v>
       </c>
       <c r="E95" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F95" t="s">
         <v>1083</v>
       </c>
       <c r="G95" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H95" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s">
         <v>1084</v>
@@ -11137,7 +11131,7 @@
         <v>1088</v>
       </c>
       <c r="N95" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O95" t="s">
         <v>1089</v>
@@ -11146,19 +11140,19 @@
         <v>1090</v>
       </c>
       <c r="Q95" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R95" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="S95" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="T95" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="U95" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V95"/>
     </row>
@@ -11170,22 +11164,22 @@
         <v>1091</v>
       </c>
       <c r="C96" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D96" t="s">
         <v>1092</v>
       </c>
       <c r="E96" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F96" t="s">
         <v>1083</v>
       </c>
       <c r="G96" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H96" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I96" t="s">
         <v>1093</v>
@@ -11203,7 +11197,7 @@
         <v>1097</v>
       </c>
       <c r="N96" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O96" t="s">
         <v>1098</v>
@@ -11212,7 +11206,7 @@
         <v>1099</v>
       </c>
       <c r="Q96" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R96" t="s">
         <v>1100</v>
@@ -11224,7 +11218,7 @@
         <v>1102</v>
       </c>
       <c r="U96" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V96"/>
     </row>
@@ -11236,22 +11230,22 @@
         <v>1103</v>
       </c>
       <c r="C97" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D97" t="s">
         <v>1104</v>
       </c>
       <c r="E97" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F97" t="s">
         <v>1083</v>
       </c>
       <c r="G97" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s">
         <v>1105</v>
@@ -11269,7 +11263,7 @@
         <v>1109</v>
       </c>
       <c r="N97" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O97" t="s">
         <v>1110</v>
@@ -11290,7 +11284,7 @@
         <v>1114</v>
       </c>
       <c r="U97" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V97"/>
     </row>
@@ -11331,7 +11325,7 @@
         <v>1121</v>
       </c>
       <c r="N98" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="O98" t="s">
         <v>1122</v>
@@ -11340,7 +11334,7 @@
         <v>1123</v>
       </c>
       <c r="Q98" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R98" t="s">
         <v>1124</v>
@@ -11352,7 +11346,7 @@
         <v>1126</v>
       </c>
       <c r="U98" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V98"/>
     </row>
@@ -11370,16 +11364,16 @@
         <v>398</v>
       </c>
       <c r="E99" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F99" t="s">
         <v>1116</v>
       </c>
       <c r="G99" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H99" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I99" t="s">
         <v>1128</v>
@@ -11397,7 +11391,7 @@
         <v>1132</v>
       </c>
       <c r="N99" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O99" t="s">
         <v>1133</v>
@@ -11418,7 +11412,7 @@
         <v>1137</v>
       </c>
       <c r="U99" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V99"/>
     </row>
@@ -11436,16 +11430,16 @@
         <v>1139</v>
       </c>
       <c r="E100" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F100" t="s">
         <v>1116</v>
       </c>
       <c r="G100" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H100" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I100" t="s">
         <v>1140</v>
@@ -11463,7 +11457,7 @@
         <v>1144</v>
       </c>
       <c r="N100" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O100" t="s">
         <v>1145</v>
@@ -11484,7 +11478,7 @@
         <v>1149</v>
       </c>
       <c r="U100" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V100"/>
     </row>
@@ -11496,22 +11490,22 @@
         <v>1150</v>
       </c>
       <c r="C101" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D101" t="s">
         <v>1151</v>
       </c>
       <c r="E101" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F101" t="s">
         <v>1116</v>
       </c>
       <c r="G101" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H101" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I101" t="s">
         <v>1152</v>
@@ -11529,7 +11523,7 @@
         <v>1156</v>
       </c>
       <c r="N101" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O101" t="s">
         <v>1157</v>
@@ -11538,7 +11532,7 @@
         <v>1158</v>
       </c>
       <c r="Q101" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R101" t="s">
         <v>816</v>
@@ -11550,7 +11544,7 @@
         <v>818</v>
       </c>
       <c r="U101" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V101"/>
     </row>
@@ -11568,16 +11562,16 @@
         <v>551</v>
       </c>
       <c r="E102" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F102" t="s">
         <v>1116</v>
       </c>
       <c r="G102" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I102" t="s">
         <v>1160</v>
@@ -11595,7 +11589,7 @@
         <v>1164</v>
       </c>
       <c r="N102" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O102" t="s">
         <v>1165</v>
@@ -11616,7 +11610,7 @@
         <v>1169</v>
       </c>
       <c r="U102" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V102"/>
     </row>
@@ -11634,16 +11628,16 @@
         <v>503</v>
       </c>
       <c r="E103" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F103" t="s">
         <v>1116</v>
       </c>
       <c r="G103" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H103" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I103" t="s">
         <v>1171</v>
@@ -11670,7 +11664,7 @@
         <v>1178</v>
       </c>
       <c r="Q103" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R103" t="s">
         <v>1179</v>
@@ -11682,7 +11676,7 @@
         <v>1181</v>
       </c>
       <c r="U103" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V103"/>
     </row>
@@ -11694,22 +11688,22 @@
         <v>1182</v>
       </c>
       <c r="C104" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D104" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E104" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
         <v>1183</v>
       </c>
       <c r="G104" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H104" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I104" t="s">
         <v>1184</v>
@@ -11727,7 +11721,7 @@
         <v>1188</v>
       </c>
       <c r="N104" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O104" t="s">
         <v>1189</v>
@@ -11736,19 +11730,19 @@
         <v>1190</v>
       </c>
       <c r="Q104" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R104" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="S104" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T104" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="U104" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V104"/>
     </row>
@@ -11766,16 +11760,16 @@
         <v>370</v>
       </c>
       <c r="E105" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F105" t="s">
         <v>1192</v>
       </c>
       <c r="G105" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H105" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I105" t="s">
         <v>1193</v>
@@ -11793,7 +11787,7 @@
         <v>1197</v>
       </c>
       <c r="N105" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O105" t="s">
         <v>1198</v>
@@ -11802,7 +11796,7 @@
         <v>1199</v>
       </c>
       <c r="Q105" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R105" t="s">
         <v>674</v>
@@ -11814,7 +11808,7 @@
         <v>676</v>
       </c>
       <c r="U105" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V105"/>
     </row>
@@ -11826,22 +11820,22 @@
         <v>1200</v>
       </c>
       <c r="C106" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D106" t="s">
         <v>1201</v>
       </c>
       <c r="E106" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F106" t="s">
         <v>1202</v>
       </c>
       <c r="G106" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H106" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I106" t="s">
         <v>1203</v>
@@ -11857,7 +11851,7 @@
         <v>1206</v>
       </c>
       <c r="N106" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O106" t="s">
         <v>1207</v>
@@ -11866,7 +11860,7 @@
         <v>1208</v>
       </c>
       <c r="Q106" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R106" t="s">
         <v>674</v>
@@ -11878,7 +11872,7 @@
         <v>676</v>
       </c>
       <c r="U106" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V106"/>
     </row>
@@ -11890,22 +11884,22 @@
         <v>1209</v>
       </c>
       <c r="C107" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D107" t="s">
         <v>1210</v>
       </c>
       <c r="E107" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F107" t="s">
         <v>1202</v>
       </c>
       <c r="G107" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H107" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I107" t="s">
         <v>1211</v>
@@ -11921,7 +11915,7 @@
         <v>1214</v>
       </c>
       <c r="N107" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O107" t="s">
         <v>1215</v>
@@ -11930,7 +11924,7 @@
         <v>1216</v>
       </c>
       <c r="Q107" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R107" t="s">
         <v>1217</v>
@@ -11942,7 +11936,7 @@
         <v>1219</v>
       </c>
       <c r="U107" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V107"/>
     </row>
@@ -11954,22 +11948,22 @@
         <v>1220</v>
       </c>
       <c r="C108" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D108" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="E108" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F108" t="s">
         <v>1221</v>
       </c>
       <c r="G108" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H108" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I108" t="s">
         <v>1222</v>
@@ -11987,7 +11981,7 @@
         <v>1226</v>
       </c>
       <c r="N108" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="O108" t="s">
         <v>1227</v>
@@ -11996,7 +11990,7 @@
         <v>1228</v>
       </c>
       <c r="Q108" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R108" t="s">
         <v>751</v>
@@ -12008,7 +12002,7 @@
         <v>753</v>
       </c>
       <c r="U108" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V108"/>
     </row>
@@ -12029,7 +12023,7 @@
       </c>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I109" t="s">
         <v>1231</v>
@@ -12052,7 +12046,7 @@
         <v>1236</v>
       </c>
       <c r="Q109" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R109" t="s">
         <v>1237</v>
@@ -12064,7 +12058,7 @@
         <v>1239</v>
       </c>
       <c r="U109" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V109"/>
     </row>
@@ -12087,7 +12081,7 @@
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I110" t="s">
         <v>1242</v>
@@ -12114,7 +12108,7 @@
         <v>1248</v>
       </c>
       <c r="Q110" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R110" t="s">
         <v>1249</v>
@@ -12126,7 +12120,7 @@
         <v>1251</v>
       </c>
       <c r="U110" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V110"/>
     </row>
@@ -12138,22 +12132,22 @@
         <v>1252</v>
       </c>
       <c r="C111" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D111" t="s">
         <v>1253</v>
       </c>
       <c r="E111" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F111" t="s">
         <v>1254</v>
       </c>
       <c r="G111" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H111" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I111" t="s">
         <v>1255</v>
@@ -12171,7 +12165,7 @@
         <v>1259</v>
       </c>
       <c r="N111" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O111" t="s">
         <v>1260</v>
@@ -12180,7 +12174,7 @@
         <v>1261</v>
       </c>
       <c r="Q111" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R111" t="s">
         <v>1262</v>
@@ -12192,7 +12186,7 @@
         <v>1264</v>
       </c>
       <c r="U111" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V111"/>
     </row>
@@ -12204,22 +12198,22 @@
         <v>1265</v>
       </c>
       <c r="C112" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D112" t="s">
         <v>1266</v>
       </c>
       <c r="E112" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F112" t="s">
         <v>1267</v>
       </c>
       <c r="G112" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H112" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I112" t="s">
         <v>1268</v>
@@ -12237,7 +12231,7 @@
         <v>1272</v>
       </c>
       <c r="N112" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O112" t="s">
         <v>1273</v>
@@ -12246,7 +12240,7 @@
         <v>1274</v>
       </c>
       <c r="Q112" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R112" t="s">
         <v>1275</v>
@@ -12258,7 +12252,7 @@
         <v>1277</v>
       </c>
       <c r="U112" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V112"/>
     </row>
@@ -12270,22 +12264,22 @@
         <v>1278</v>
       </c>
       <c r="C113" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="E113" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F113" t="s">
         <v>1267</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H113" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I113" t="s">
         <v>1279</v>
@@ -12303,7 +12297,7 @@
         <v>1283</v>
       </c>
       <c r="N113" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O113" t="s">
         <v>1284</v>
@@ -12312,7 +12306,7 @@
         <v>1285</v>
       </c>
       <c r="Q113" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R113" t="s">
         <v>629</v>
@@ -12324,7 +12318,7 @@
         <v>631</v>
       </c>
       <c r="U113" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V113"/>
     </row>
@@ -12336,22 +12330,22 @@
         <v>1286</v>
       </c>
       <c r="C114" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D114" t="s">
         <v>291</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F114" t="s">
         <v>1287</v>
       </c>
       <c r="G114" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H114" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I114" t="s">
         <v>1288</v>
@@ -12390,7 +12384,7 @@
         <v>1126</v>
       </c>
       <c r="U114" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V114"/>
     </row>
@@ -12408,16 +12402,16 @@
         <v>1296</v>
       </c>
       <c r="E115" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F115" t="s">
         <v>1287</v>
       </c>
       <c r="G115" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I115" t="s">
         <v>1297</v>
@@ -12444,7 +12438,7 @@
         <v>1303</v>
       </c>
       <c r="Q115" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R115" t="s">
         <v>1304</v>
@@ -12456,7 +12450,7 @@
         <v>1306</v>
       </c>
       <c r="U115" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V115"/>
     </row>
@@ -12480,10 +12474,10 @@
         <v>1287</v>
       </c>
       <c r="G116" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H116" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I116" t="s">
         <v>1310</v>
@@ -12501,7 +12495,7 @@
         <v>1314</v>
       </c>
       <c r="N116" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O116" t="s">
         <v>1315</v>
@@ -12522,7 +12516,7 @@
         <v>1319</v>
       </c>
       <c r="U116" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V116"/>
     </row>
@@ -12534,22 +12528,22 @@
         <v>1320</v>
       </c>
       <c r="C117" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D117" t="s">
         <v>253</v>
       </c>
       <c r="E117" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
         <v>1287</v>
       </c>
       <c r="G117" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I117" t="s">
         <v>1321</v>
@@ -12567,7 +12561,7 @@
         <v>1325</v>
       </c>
       <c r="N117" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O117" t="s">
         <v>1326</v>
@@ -12576,7 +12570,7 @@
         <v>1327</v>
       </c>
       <c r="Q117" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R117" t="s">
         <v>1328</v>
@@ -12588,7 +12582,7 @@
         <v>1330</v>
       </c>
       <c r="U117" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V117"/>
     </row>
@@ -12600,22 +12594,22 @@
         <v>1331</v>
       </c>
       <c r="C118" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D118" t="s">
         <v>1296</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F118" t="s">
         <v>1287</v>
       </c>
       <c r="G118" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I118" t="s">
         <v>1332</v>
@@ -12633,7 +12627,7 @@
         <v>1336</v>
       </c>
       <c r="N118" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O118" t="s">
         <v>1337</v>
@@ -12642,7 +12636,7 @@
         <v>1338</v>
       </c>
       <c r="Q118" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R118" t="s">
         <v>1339</v>
@@ -12654,7 +12648,7 @@
         <v>1341</v>
       </c>
       <c r="U118" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V118"/>
     </row>
@@ -12666,22 +12660,22 @@
         <v>1342</v>
       </c>
       <c r="C119" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D119" t="s">
         <v>998</v>
       </c>
       <c r="E119" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F119" t="s">
         <v>1287</v>
       </c>
       <c r="G119" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H119" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I119" t="s">
         <v>1343</v>
@@ -12699,7 +12693,7 @@
         <v>1347</v>
       </c>
       <c r="N119" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O119" t="s">
         <v>1348</v>
@@ -12720,7 +12714,7 @@
         <v>1352</v>
       </c>
       <c r="U119" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V119"/>
     </row>
@@ -12732,22 +12726,22 @@
         <v>1353</v>
       </c>
       <c r="C120" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D120" t="s">
         <v>1354</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F120" t="s">
         <v>1355</v>
       </c>
       <c r="G120" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I120" t="s">
         <v>1356</v>
@@ -12765,7 +12759,7 @@
         <v>1360</v>
       </c>
       <c r="N120" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O120" t="s">
         <v>1361</v>
@@ -12786,7 +12780,7 @@
         <v>676</v>
       </c>
       <c r="U120" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V120"/>
     </row>
@@ -12798,22 +12792,22 @@
         <v>1363</v>
       </c>
       <c r="C121" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D121" t="s">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F121" t="s">
         <v>1364</v>
       </c>
       <c r="G121" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="I121" t="s">
         <v>1365</v>
@@ -12831,7 +12825,7 @@
         <v>1369</v>
       </c>
       <c r="N121" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O121" t="s">
         <v>1370</v>
@@ -12840,7 +12834,7 @@
         <v>1371</v>
       </c>
       <c r="Q121" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R121" t="s">
         <v>249</v>
@@ -12852,7 +12846,7 @@
         <v>251</v>
       </c>
       <c r="U121" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V121"/>
     </row>
@@ -12864,22 +12858,22 @@
         <v>1372</v>
       </c>
       <c r="C122" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D122" t="s">
         <v>1373</v>
       </c>
       <c r="E122" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F122" t="s">
         <v>1374</v>
       </c>
       <c r="G122" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H122" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I122" t="s">
         <v>1375</v>
@@ -12897,7 +12891,7 @@
         <v>1379</v>
       </c>
       <c r="N122" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O122" t="s">
         <v>1380</v>
@@ -12906,7 +12900,7 @@
         <v>1381</v>
       </c>
       <c r="Q122" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R122" t="s">
         <v>596</v>
@@ -12918,7 +12912,7 @@
         <v>598</v>
       </c>
       <c r="U122" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V122"/>
     </row>
@@ -12930,22 +12924,22 @@
         <v>1382</v>
       </c>
       <c r="C123" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D123" t="s">
         <v>1383</v>
       </c>
       <c r="E123" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F123" t="s">
         <v>1384</v>
       </c>
       <c r="G123" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H123" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I123" t="s">
         <v>1385</v>
@@ -12972,7 +12966,7 @@
         <v>1391</v>
       </c>
       <c r="Q123" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R123" t="s">
         <v>1147</v>
@@ -12984,7 +12978,7 @@
         <v>1149</v>
       </c>
       <c r="U123" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V123"/>
     </row>
@@ -12996,22 +12990,22 @@
         <v>1392</v>
       </c>
       <c r="C124" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D124" t="s">
         <v>503</v>
       </c>
       <c r="E124" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>1384</v>
       </c>
       <c r="G124" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H124" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I124" t="s">
         <v>1393</v>
@@ -13027,7 +13021,7 @@
         <v>1396</v>
       </c>
       <c r="N124" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O124" t="s">
         <v>1397</v>
@@ -13036,19 +13030,19 @@
         <v>1398</v>
       </c>
       <c r="Q124" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R124" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="S124" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T124" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="U124" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V124"/>
     </row>
@@ -13060,22 +13054,22 @@
         <v>1399</v>
       </c>
       <c r="C125" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D125" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="E125" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F125" t="s">
         <v>1400</v>
       </c>
       <c r="G125" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H125" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I125" t="s">
         <v>1401</v>
@@ -13091,7 +13085,7 @@
         <v>1404</v>
       </c>
       <c r="N125" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O125" t="s">
         <v>1405</v>
@@ -13100,19 +13094,19 @@
         <v>1406</v>
       </c>
       <c r="Q125" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R125" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="S125" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="T125" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="U125" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V125"/>
     </row>
@@ -13134,10 +13128,10 @@
         <v>1409</v>
       </c>
       <c r="G126" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I126" t="s">
         <v>1410</v>
@@ -13164,7 +13158,7 @@
         <v>1416</v>
       </c>
       <c r="Q126" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R126" t="s">
         <v>1417</v>
@@ -13176,7 +13170,7 @@
         <v>1419</v>
       </c>
       <c r="U126" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V126"/>
     </row>
@@ -13188,22 +13182,22 @@
         <v>1420</v>
       </c>
       <c r="C127" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D127" t="s">
         <v>713</v>
       </c>
       <c r="E127" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F127" t="s">
         <v>1421</v>
       </c>
       <c r="G127" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H127" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I127" t="s">
         <v>1422</v>
@@ -13221,7 +13215,7 @@
         <v>1426</v>
       </c>
       <c r="N127" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O127" t="s">
         <v>1427</v>
@@ -13242,7 +13236,7 @@
         <v>1431</v>
       </c>
       <c r="U127" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V127"/>
     </row>
@@ -13260,16 +13254,16 @@
         <v>538</v>
       </c>
       <c r="E128" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F128" t="s">
         <v>1421</v>
       </c>
       <c r="G128" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H128" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I128" t="s">
         <v>1433</v>
@@ -13287,7 +13281,7 @@
         <v>1437</v>
       </c>
       <c r="N128" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O128" t="s">
         <v>1438</v>
@@ -13308,7 +13302,7 @@
         <v>1442</v>
       </c>
       <c r="U128" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V128"/>
     </row>
@@ -13326,13 +13320,13 @@
         <v>1444</v>
       </c>
       <c r="E129" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F129" t="s">
         <v>1445</v>
       </c>
       <c r="G129" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H129" t="s">
         <v>689</v>
@@ -13353,7 +13347,7 @@
         <v>1450</v>
       </c>
       <c r="N129" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O129" t="s">
         <v>1451</v>
@@ -13374,7 +13368,7 @@
         <v>1455</v>
       </c>
       <c r="U129" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V129"/>
     </row>
@@ -13392,13 +13386,13 @@
         <v>844</v>
       </c>
       <c r="E130" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F130" t="s">
         <v>1445</v>
       </c>
       <c r="G130" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H130" t="s">
         <v>689</v>
@@ -13419,7 +13413,7 @@
         <v>1450</v>
       </c>
       <c r="N130" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O130" t="s">
         <v>1457</v>
@@ -13440,7 +13434,7 @@
         <v>1461</v>
       </c>
       <c r="U130" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V130"/>
     </row>
@@ -13452,7 +13446,7 @@
         <v>1462</v>
       </c>
       <c r="C131" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D131" t="s">
         <v>1463</v>
@@ -13464,10 +13458,10 @@
         <v>1464</v>
       </c>
       <c r="G131" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H131" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I131" t="s">
         <v>1465</v>
@@ -13485,7 +13479,7 @@
         <v>1469</v>
       </c>
       <c r="N131" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O131" t="s">
         <v>1470</v>
@@ -13506,7 +13500,7 @@
         <v>470</v>
       </c>
       <c r="U131" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V131"/>
     </row>
@@ -13518,22 +13512,22 @@
         <v>1472</v>
       </c>
       <c r="C132" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D132" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E132" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F132" t="s">
         <v>1473</v>
       </c>
       <c r="G132" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H132" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I132" t="s">
         <v>1474</v>
@@ -13551,7 +13545,7 @@
         <v>1478</v>
       </c>
       <c r="N132" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O132" t="s">
         <v>1479</v>
@@ -13560,7 +13554,7 @@
         <v>1480</v>
       </c>
       <c r="Q132" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R132" t="s">
         <v>1481</v>
@@ -13572,7 +13566,7 @@
         <v>1483</v>
       </c>
       <c r="U132" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V132"/>
     </row>
@@ -13584,22 +13578,22 @@
         <v>1484</v>
       </c>
       <c r="C133" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D133" t="s">
         <v>503</v>
       </c>
       <c r="E133" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F133" t="s">
         <v>1485</v>
       </c>
       <c r="G133" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H133" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I133" t="s">
         <v>1486</v>
@@ -13617,7 +13611,7 @@
         <v>1490</v>
       </c>
       <c r="N133" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O133" t="s">
         <v>1491</v>
@@ -13626,7 +13620,7 @@
         <v>1492</v>
       </c>
       <c r="Q133" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R133" t="s">
         <v>1493</v>
@@ -13638,7 +13632,7 @@
         <v>1495</v>
       </c>
       <c r="U133" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V133"/>
     </row>
@@ -13650,22 +13644,22 @@
         <v>1496</v>
       </c>
       <c r="C134" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D134" t="s">
         <v>1497</v>
       </c>
       <c r="E134" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F134" t="s">
         <v>1485</v>
       </c>
       <c r="G134" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H134" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I134" t="s">
         <v>1498</v>
@@ -13681,7 +13675,7 @@
         <v>1501</v>
       </c>
       <c r="N134" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O134" t="s">
         <v>1502</v>
@@ -13702,7 +13696,7 @@
         <v>1495</v>
       </c>
       <c r="U134" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V134"/>
     </row>
@@ -13714,22 +13708,22 @@
         <v>1504</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D135" t="s">
         <v>1497</v>
       </c>
       <c r="E135" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F135" t="s">
         <v>1485</v>
       </c>
       <c r="G135" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H135" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I135" t="s">
         <v>1505</v>
@@ -13745,7 +13739,7 @@
         <v>1508</v>
       </c>
       <c r="N135" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O135" t="s">
         <v>1509</v>
@@ -13754,7 +13748,7 @@
         <v>1510</v>
       </c>
       <c r="Q135" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R135" t="s">
         <v>1493</v>
@@ -13766,7 +13760,7 @@
         <v>1495</v>
       </c>
       <c r="U135" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V135"/>
     </row>
@@ -13778,7 +13772,7 @@
         <v>1511</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D136" t="s">
         <v>1512</v>
@@ -13790,10 +13784,10 @@
         <v>1513</v>
       </c>
       <c r="G136" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H136" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I136" t="s">
         <v>1514</v>
@@ -13809,7 +13803,7 @@
         <v>1517</v>
       </c>
       <c r="N136" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O136" t="s">
         <v>1518</v>
@@ -13818,7 +13812,7 @@
         <v>1519</v>
       </c>
       <c r="Q136" t="s">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="R136" t="s">
         <v>468</v>
@@ -13830,7 +13824,7 @@
         <v>470</v>
       </c>
       <c r="U136" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V136"/>
     </row>
@@ -13842,22 +13836,22 @@
         <v>1520</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D137" t="s">
         <v>1296</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F137" t="s">
         <v>1521</v>
       </c>
       <c r="G137" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H137" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I137" t="s">
         <v>1522</v>
@@ -13873,7 +13867,7 @@
         <v>1525</v>
       </c>
       <c r="N137" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O137" t="s">
         <v>1526</v>
@@ -13894,7 +13888,7 @@
         <v>1530</v>
       </c>
       <c r="U137" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V137"/>
     </row>
@@ -13917,7 +13911,7 @@
       </c>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I138" t="s">
         <v>1533</v>
@@ -13935,7 +13929,7 @@
         <v>1537</v>
       </c>
       <c r="N138" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O138" t="s">
         <v>1538</v>
@@ -13944,7 +13938,7 @@
         <v>1539</v>
       </c>
       <c r="Q138" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R138" t="s">
         <v>1540</v>
@@ -13956,7 +13950,7 @@
         <v>1542</v>
       </c>
       <c r="U138" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="V138"/>
     </row>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -80,6 +80,111 @@
     <t xml:space="preserve">Statut_Change_Date</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grüne Fraktion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kantonsanteile an der direkten Bundessteuer als zusätzliches Instrument des Finanzausgleichs einsetzen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utiliser la part des cantons au produit de l'impôt fédéral direct comme instrument supplémentaire de la péréquation financière </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote cantonali sulle entrate dell'imposta federale diretta. Un ulteriore strumento di perequazione finanziaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer une modification de la loi fédérale sur l’impôt fédéral direct (LIFD&amp;nbsp;; RS 642.11) afin que les parts des cantons au produit de l’impôt fédéral direct soient échelonnées en fonction du potentiel de ressources du canton. L’échelonnement sera structuré de sorte qu’un canton dont l’indice des ressources se situe dans la moyenne reçoive au moins 17&amp;nbsp;% et que tous les cantons aient droit à au moins 15&amp;nbsp;%.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, eine Änderung des Bundesgesetzes über die direkte Bundessteuer (DBG; SR 642.11) auszuarbeiten, welches folgende Auswirkung hat: Die Kantonsanteile an der direkten Bundessteuer werden je nach Ressourcenstärke des Kantons abgestuft. Die Abstufung soll so ausgestaltet sein, dass einem Kanton mit durchschnittlichem Ressourcenindex mindestens 17 Prozent zustehen und dass keinem Kanton weniger als 15 Prozent zustehen.&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staatspolitik|Finanzwesen|Steuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique d'Etat|Finances|Fiscalité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica nazionale|Finanze|Imposte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jederzeit sichere Säuglingsnahrung. Prävention und Aufklärung im Fall einer Kontamination gewährleisten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour des laits et aliments infantiles sûrs en tout temps, garantir la prévention et l'information en cas de contamination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantire la prevenzione e l'informazione in caso di contaminazione per far sì che il latte e gli alimenti per la prima infanzia siano sempre sicuri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre les mesures nécessaires pour assurer la sécurité de la population lors de cas de contaminations alimentaires, en particulier des laits et aliments infantiles. Il s’agit de garantir l’application des articles 26 à 29 de la loi sur les denrées alimentaires (LDAI), qui règlent les obligations des entreprises (autocontrôle, garantie de la protection de la santé, traçabilité, devoir d’assistance et obligation de renseigner). Les mesures prises visent à garantir que les cas de contamination soient communiqués rapidement aux autorités alimentaires et sanitaires ainsi qu'au public, que les rappels soient effectués dans les meilleurs délais et que les produits rappelés le soient effectivement.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Massnahmen zu ergreifen, um die Sicherheit der Bevölkerung bei Lebensmittelkontaminationen zu gewährleisten, insbesondere wenn Säuglingsnahrung von der Kontamination betroffen ist. Damit soll die Umsetzung der Artikel 26 bis 29 des Lebensmittelgesetzes (LMG) sichergestellt werden, welche die Pflichten der Unternehmen regeln (Selbstkontrolle, Sicherstellung des Gesundheitsschutzes, Rückverfolgbarkeit, Unterstützungs- und Auskunftspflicht). Die Massnahmen sollen sicherstellen, dass Lebensmittel- und Gesundheitsbehörden sowie die Öffentlichkeit umgehend über festgestellte Kontaminationen informiert werden, betroffene Produkte so schnell wie möglich zurückgerufen werden und zurückgerufene Produkte tatsächlich vom Markt entfernt werden.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titre uniquement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft|Soziale Fragen|Medien und Kommunikation|Gesundheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Économie|Questions sociales|Médias et communication|Santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economia|Questioni sociali|Media e comunicazione|Salute</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3192</t>
   </si>
   <si>
@@ -95,9 +200,6 @@
     <t xml:space="preserve">2026-03-18</t>
   </si>
   <si>
-    <t xml:space="preserve">NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">BK</t>
   </si>
   <si>
@@ -116,9 +218,6 @@
     <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird gebeten, die folgenden Fragen zu beantworten:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wer hat entschieden, dass SP-Bundesrat Jans an der Medienkonferenz vom 16. März 2026 durch Verbandsvertreter, Gewerkschafter und politische Akteure bei der Bundesratsinformation zur Nachhaltigkeitsinitiative «Keine 10-Millionen-Schweiz!» unterstützt wird? Der Gesamtbundesrat oder SP-Bundesrat Jans?&lt;/li&gt;&lt;li&gt;Weshalb hat SP-Bundesrat Jans die Vorgabe verletzt, dass &lt;i&gt;«am besten keine Gäste von ausserhalb der Bundesverwaltung»&lt;/i&gt; an bundesrätlichen Medienkonferenzen teilnehmen? Haben die externen Teilnehmer die gesetzlichen Vorgaben eingehalten?&lt;/li&gt;&lt;li&gt;Der Bundesrat wird gebeten, seit 2000 alle bundesrätlichen Medienkonferenzen aufzulisten, die zusammen mit Verbandsvertretern, Gewerkschaften und politischen Akteuren stattgefunden haben.&lt;/li&gt;&lt;li&gt;Gemäss den bundesrätlichen Leitlinien hat SP-Bundesrat Jans offensichtlich eine Kampagne geführt (&lt;i&gt;«Die Grenze zur Kampagne wird insbesondere überschritten, wenn: Verbände, politische Akteure oder Vertreter und Vertreterinnen aus Wirtschaft und Zivilgesellschaft bei der Kampagnentätigkeit unterstützt werden; die Informationstätigkeit mit kampagnenführenden Organisationen koordiniert wird»&lt;/i&gt;). Wie beurteilt der Bundesrat dieses Verhalten von SP-Bundesrat Jans?&lt;/li&gt;&lt;li&gt;Die bundesrätliche Medienkonferenz dauert bis zu Beginn der Fragerunde 34 Minuten. Während wie vielen Minuten wurde dabei über die Argumente der Befürworter der Initiative informiert?&amp;nbsp;&lt;/li&gt;&lt;li&gt;Da die Argumente der Befürworter mit keinem Satz erwähnt wurden: Teilt der Bundesrat die Einschätzung, dass die bundesrätlichen Leitlinien (&lt;i&gt;«die Gegenpositionen berücksichtigend», «Vorteile ohne Nachteile erwähnen», «die Gegenseite in angemessener Weise berücksichtigen»&lt;/i&gt;) verletzt werden?&lt;/li&gt;&lt;li&gt;Wäre vorgängig zur Abstimmung über den Ausbau der Nationalstrassen vom 24. November 2024 eine Medienkonferenz mit Bundesrat Albert Rösti und Verbandsvertretern von strasseschweiz, auto-schweiz, ACS, TCS, ASTAG und dem Auto Gewerbe Verband Schweiz, AGVS mit den bundesrätlichen Leitlinien konform gewesen?&lt;/li&gt;&lt;li&gt;Welche Sanktionen ergreift der Gesamtbundesrat gegen SP-Bundesrat Jans? Ist der Bundesrat bereit, zukünftig an bundesrätlichen Medienkonferenzen die Argumente der Gegenseite in angemessener Weise zu berücksichtigen?&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Stellungnahme zum Vorstoss liegt vor / L’avis relatif à l’intervention est disponible</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263192</t>
   </si>
   <si>
@@ -137,24 +236,63 @@
     <t xml:space="preserve">Politica nazionale</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-13</t>
+    <t xml:space="preserve">26.3099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Po.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rechtliche Abklärungen und Potenzial von künstlicher Intelligenz in den Bereichen Polizei und innere Sicherheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarifications juridiques et potentiel de l'utilisation de l'intelligence artificielle (IA) dans les domaines de la police et de la sécurité intérieure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiarimenti giuridici e potenzialità dell'impiego dell'intelligenza artificiale (IA) nei settori della polizia e della sicurezza interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un rapport concernant l’utilisation de l’intelligence artificielle (IA) dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale exposant le potentiel, les bases légales et les limites constitutionnelles, notamment pour la protection de la vie privée. Sur la base de ces conclusions, il devra soumettre au Parlement des lignes directrices pour une utilisation cohérente et conforme aux droits fondamentaux de l’IA dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale, tout en respectant la souveraineté numérique de la Suisse. Le rapport devra notamment :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Démontrer le potentiel et les domaines d’application des technologies d’IA pour rendre la lutte contre la criminalité plus efficace et contribuer à la sauvegarde de la sécurité intérieure.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Analyser le cadre juridique existant pour l’utilisation des technologies d’IA dans le domaine de la sécurité et identifier les éventuelles lacunes du cadre juridique.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Expliquer les limites constitutionnelles à l’utilisation des technologies d’IA dans les domaines de la police et de la sécurité et définir des conditions cadre et les lignes directrices pour l’utilisation de ces technologies.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Démontrer comment les exigences en matière de protection de la vie privée peuvent être satisfaites lors de l'utilisation des technologies d'IA dans les domaines de la police et de la sécurité.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Expliquer comment la souveraineté numérique de la Suisse peut être préservée et la dépendance vis-à-vis des prestataires externes évitée lors de l'acquisition et de l'exploitation des technologies d'IA dans le secteur de la sécurité.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Bericht über den Einsatz künstlicher Intelligenz (KI) in den Bereichen Polizei, innere Sicherheit und Strafverfolgung vorzulegen. Der Bericht soll insbesondere das Potenzial, die rechtlichen Grundlagen sowie die verfassungsrechtlichen Grenzen von KI – namentlich in Bezug auf den Schutz der Privatsphäre – darlegen. Auf der Grundlage des Berichts soll der Bundesrat dem Parlament Leitlinien für einen kohärenten und grundrechtskonformen Einsatz von KI in den Bereichen Polizei, innere Sicherheit und Strafverfolgung vorlegen, wobei die digitale Souveränität der Schweiz gewahrt werden soll. Der Bericht soll insbesondere:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. das Potenzial und die Anwendungsbereiche von KI-Technologien aufzeigen, um die Bekämpfung der Kriminalität effizienter zu gestalten und die innere Sicherheit zu stärken;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. den bestehenden Rechtsrahmen für den Einsatz von KI-Technologien im Sicherheitsbereich analysieren und allfällige Lücken identifizieren;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. die verfassungsrechtlichen Grenzen für den Einsatz von KI-Technologien in den Bereichen Polizei und Sicherheit erläutern sowie Rahmenbedingungen und Leitlinien für den Einsatz von KI definieren;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. aufzeigen, wie die Anforderungen an den Schutz der Privatsphäre beim Einsatz von KI-Technologien im Polizei- und Sicherheitsbereich erfüllt werden können;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. erläutern, wie die digitale Souveränität der Schweiz gewahrt und Abhängigkeiten von externen Anbietern bei der Beschaffung und beim Betrieb von KI-Technologien im Sicherheitsbereich vermieden werden können.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspolitik|Recht Allgemein|Medien und Kommunikation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politique de sécurité|Droit|Médias et communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Politica di sicurezza|Diritto generale|Media e comunicazione</t>
   </si>
   <si>
     <t xml:space="preserve">26.3120</t>
   </si>
   <si>
-    <t xml:space="preserve">Mo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wyssmann Rémy</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16</t>
   </si>
   <si>
-    <t xml:space="preserve">EDI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Streichung von Artikel 22 des Epidemiengesetzes</t>
   </si>
   <si>
@@ -194,15 +332,6 @@
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
-    <t xml:space="preserve">Juillard Charles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Centre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
     <t xml:space="preserve">UVEK</t>
   </si>
   <si>
@@ -227,9 +356,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263121</t>
   </si>
   <si>
-    <t xml:space="preserve">Titre uniquement</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verkehr|Raumplanung und Wohnungswesen</t>
   </si>
   <si>
@@ -269,9 +395,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
   </si>
   <si>
-    <t xml:space="preserve">Élu &amp; Conseil fédéral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verkehr</t>
   </si>
   <si>
@@ -287,9 +410,6 @@
     <t xml:space="preserve">2025-12-19</t>
   </si>
   <si>
-    <t xml:space="preserve">EJPD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gewalttätiger Extremismus bei Demonstrationen. Veranstalter sollen die Kosten übernehmen</t>
   </si>
   <si>
@@ -326,87 +446,6 @@
     <t xml:space="preserve">2026-04-02</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grüne Fraktion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kantonsanteile an der direkten Bundessteuer als zusätzliches Instrument des Finanzausgleichs einsetzen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utiliser la part des cantons au produit de l'impôt fédéral direct comme instrument supplémentaire de la péréquation financière </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quote cantonali sulle entrate dell'imposta federale diretta. Un ulteriore strumento di perequazione finanziaria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé d’élaborer une modification de la loi fédérale sur l’impôt fédéral direct (LIFD&amp;nbsp;; RS 642.11) afin que les parts des cantons au produit de l’impôt fédéral direct soient échelonnées en fonction du potentiel de ressources du canton. L’échelonnement sera structuré de sorte qu’un canton dont l’indice des ressources se situe dans la moyenne reçoive au moins 17&amp;nbsp;% et que tous les cantons aient droit à au moins 15&amp;nbsp;%.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, eine Änderung des Bundesgesetzes über die direkte Bundessteuer (DBG; SR 642.11) auszuarbeiten, welches folgende Auswirkung hat: Die Kantonsanteile an der direkten Bundessteuer werden je nach Ressourcenstärke des Kantons abgestuft. Die Abstufung soll so ausgestaltet sein, dass einem Kanton mit durchschnittlichem Ressourcenindex mindestens 17 Prozent zustehen und dass keinem Kanton weniger als 15 Prozent zustehen.&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staatspolitik|Finanzwesen|Steuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique d'Etat|Finances|Fiscalité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica nazionale|Finanze|Imposte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jederzeit sichere Säuglingsnahrung. Prävention und Aufklärung im Fall einer Kontamination gewährleisten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour des laits et aliments infantiles sûrs en tout temps, garantir la prévention et l'information en cas de contamination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantire la prevenzione e l'informazione in caso di contaminazione per far sì che il latte e gli alimenti per la prima infanzia siano sempre sicuri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de prendre les mesures nécessaires pour assurer la sécurité de la population lors de cas de contaminations alimentaires, en particulier des laits et aliments infantiles. Il s’agit de garantir l’application des articles 26 à 29 de la loi sur les denrées alimentaires (LDAI), qui règlent les obligations des entreprises (autocontrôle, garantie de la protection de la santé, traçabilité, devoir d’assistance et obligation de renseigner). Les mesures prises visent à garantir que les cas de contamination soient communiqués rapidement aux autorités alimentaires et sanitaires ainsi qu'au public, que les rappels soient effectués dans les meilleurs délais et que les produits rappelés le soient effectivement.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, die erforderlichen Massnahmen zu ergreifen, um die Sicherheit der Bevölkerung bei Lebensmittelkontaminationen zu gewährleisten, insbesondere wenn Säuglingsnahrung von der Kontamination betroffen ist. Damit soll die Umsetzung der Artikel 26 bis 29 des Lebensmittelgesetzes (LMG) sichergestellt werden, welche die Pflichten der Unternehmen regeln (Selbstkontrolle, Sicherstellung des Gesundheitsschutzes, Rückverfolgbarkeit, Unterstützungs- und Auskunftspflicht). Die Massnahmen sollen sicherstellen, dass Lebensmittel- und Gesundheitsbehörden sowie die Öffentlichkeit umgehend über festgestellte Kontaminationen informiert werden, betroffene Produkte so schnell wie möglich zurückgerufen werden und zurückgerufene Produkte tatsächlich vom Markt entfernt werden.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft|Soziale Fragen|Medien und Kommunikation|Gesundheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Économie|Questions sociales|Médias et communication|Santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economia|Questioni sociali|Media e comunicazione|Salute</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3454</t>
   </si>
   <si>
@@ -428,48 +467,48 @@
     <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 veröffentlichte der Bundesrat die Eckwerte von &lt;i&gt;«Verkehr ’45»&lt;/i&gt;. Die geplanten Strassenbauprojekte entlang der Nationalstrasse 18 zwischen Basel und Delsberg – mit Ausnahme der Entlastung des Zentrums von Laufen (bis 2055) – sollen auf einen Zeitpunkt nach 2055 verschoben werden. Diese Aussichten stossen in der Region auf grosses Unverständnis. Der Entscheid bedeutet nämlich, dass für mehrere Jahrzehnte auf eine Verbesserung der Erreichbarkeit und damit auf echte Perspektiven für die wirtschaftliche Entwicklung verzichtet wird. Zudem steht er in direktem Widerspruch zu den Ergebnissen der Korridorstudie N18, die unter der Leitung des ASTRA nach den neuesten Methoden durchgeführt und von einer breiten Partnerschaft unterstützt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein wesentlicher Abschnitt des nationalen Strassennetzes. Sie verbindet den Grossraum Basel mit der Genferseeregion und bedient das aufstrebende Laufental sowie die Kantonshauptstadt Delsberg. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zu einem Engpass und weist eine der höchsten Verkehrsbelastungen und Staudichten des Landes auf. Die derzeitige Situation beeinträchtigt zudem erheblich die Lebensqualität in den Ortskernen und gefährdet die Sicherheit des motorisierten Verkers und des Veloverkehrs. Die Bevölkerung leidet täglich unter den Staus und dem starken Lastwagenverkehr, der durch die Ortschaften rollt, wie die zahlreichen Teilnehmer und Teilnehmerinnen der Mobilitätsforen in Laufen bezeugen. Eine rasche Weiterentwicklung des Korridors erscheint daher unerlässlich.&lt;/p&gt;&lt;p&gt;Vor diesem Hintergrund bitte ich den Bundesrat um die Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie bewertet er die Auswirkungen des Transitverkehrs – insbesondere des Schwerverkehrs – auf die Siedlungsentwicklung sowie auf die Lebens- und Wohnqualität in Delsberg, Laufen und Zwingen?&lt;/li&gt;&lt;li&gt;Erachtet er die Umfahrungsprojekte Laufen–Zwingen und Delsberg als geeignete Massnahmen zur Verringerung der Belastungen in den betroffenen Siedlungsgebieten?&lt;/li&gt;&lt;li&gt;Hält er Massnahmen zur Verbesserung der Verkehrsanbindung der Arbeitszonen in Delsberg sowie im Laufental für notwendig?&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuosto Brenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahnplanung. Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planification ferroviaire. Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pianificazione ferroviaria. Il Consiglio federale può ignorare i mandati del Parlamento?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Der Bundesrat hat Ende Januar 2026 die Eckwerte für den Ausbau der Verkehrsinfrastruktur im Rahmen von «Verkehr 45» veröffentlicht. Obwohl die politischen Instanzen bereits klare Leitlinien festgelegt haben – insbesondere haben beide Kammern am 11. März 2026 die Motion &lt;strong&gt;24.4042&lt;/strong&gt; «Entwicklung eines Angebotskonzepts 2050 auf nationaler und internationaler Ebene» und am 11. März 2024 &lt;strong&gt;die Motion 23.3668&lt;/strong&gt; «Redundanz und Zuverlässigkeit auf der Eisenbahnachse Lausanne–Genf» angenommen – scheint dies im Dossier &lt;strong&gt;«Verkehr 45»&lt;/strong&gt; in keiner Weise berücksichtigt worden zu sein.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Wird sich die Botschaft 2027 auf diese beiden Motionen abstützen und klar aufzeigen, dass prioritär die Redundanz in der Genferseeregion sowie ein Angebotskonzept, das den nationalen Hauptstrecken Vorrang einräumt, schnellstmöglich geprüft und umgesetzt werden müssen? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Wird die Botschaft 2027 eine Erhöhung der Taktfrequenz, kürzere Fahrzeiten, mehr Kapazitäten und eine robustere Eisenbahninfrastruktur vorsehen, insbesondere für die Westschweiz?&lt;/p&gt;&lt;p&gt;3. Wie gedenkt der Bundesrat angesichts bestimmter neuer Projekte, die im Rahmen von «Verkehr&amp;nbsp;45» vorgesehen sind, die Tragfähigkeit des Bahninfrastrukturfonds zu gewährleisten, ohne dabei die Regionen zu benachteiligen, die bereits einen Investitionsrückstand aufweisen (Jura und Genferseeregion)?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Kann der Bundesrat die territorialen und wirtschaftlichen Auswirkungen eines mangelnden Ausbaus des Schienenverkehrs darlegen und die geplanten Massnahmen zur Gewährleistung der Gleichbehandlung erläutern?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Hält es der Bundesrat im Hinblick auf die Eindämmung der öffentlichen Ausgaben nicht für notwendig, die Baustandards der SBB zu vereinfachen?&lt;/p&gt;&lt;p&gt;6. Sind konkret Verbesserungen auf der Strecke Biel–Lausanne/Genf sowie die endgültige Wiederaufnahme der direkten (pünktlichen) Verbindung Basel/Zürich–Biel–Genf (ohne Umsteigen in Renens) vorgesehen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Ist der Bundesrat nicht der Ansicht, dass er neben den Grossprojekten auch Projekten mit hohem Mehrwert und geringen Kosten Vorrang einräumen sollte, wie beispielsweise der &lt;strong&gt;Bahnhaltestelle «Y-Parc» in Yverdon&lt;/strong&gt;? Die Investitionen sind für das Bundesamt für Verkehr lächerlich gering, gewährleisten jedoch eine Verkehrsverlagerung für Tausende von Arbeitsplätzen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Wenn die Beschlüsse des Parlaments bei der technischen Planung ausser Kraft gesetzt werden können, was bringen die Sessionen dann noch?&lt;/strong&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eingereicht / Déposé</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-26</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuosto Brenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bahnplanung. Darf der Bundesrat die Aufträge des Parlaments ignorieren?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planification ferroviaire. Le Conseil fédéral peut-il ignorer les mandats du Parlement ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pianificazione ferroviaria. Il Consiglio federale può ignorare i mandati del Parlamento?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral a publié fin janvier 2026 les grandes lignes du développement des infrastructures de transport dans le cadre de Transport 45. Bien que les autorités politiques aient déjà fixé des orientations claires — notamment via l'approbation par les deux Chambres des motions &lt;strong&gt;24.4042&lt;/strong&gt; "Concept d’offre 2050" le 11 mars 2026 et &lt;strong&gt;23.3668&lt;/strong&gt; "Redondance et fiabilité de l’axe Lausanne-Genève" le 11 mars 2024 — le dossier &lt;strong&gt;"Transport 45"&lt;/strong&gt; semble n'en avoir nullement tenu compte.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Dès lors, le Conseil fédéral est prié de répondre aux questions suivantes:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Le message 2027 reposera-t-il sur ces deux motions montrant clairement la priorité d'étudier et de réaliser au plus vite la redondance sur l'arc lémanique, ainsi qu'un concept d'offre donnant la priorité aux grandes lignes nationales ? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Le message 2027, proposera-t-il des gains en cadence, des temps de parcours réduits, une plus grande capacité et une robustesse du réseau ferroviaire, notamment pour la Suisse romande ?&lt;/p&gt;&lt;p&gt;3. Au vu de certains nouveaux projets prévus par le T45, comment le Conseil fédéral compte-il assurer la viabilité du FIF sans prétériter les régions déjà en retard d'investissements (Jura et Arc lémanique) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Le Conseil fédéral peut-il présenter l’impact territorial et économique d'un manque de développement du ferroviaire et les mesures prévues pour garantir l’équité de traitement ?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Dans une optique de maîtrise des dépenses publiques, le Conseil fédéral n'estime-t-il pas nécessaire de simplifier les normes de construction des CFF ?&lt;/p&gt;&lt;p&gt;6. Plus concrètement, des améliorations sont-elles prévues sur l’axe Bienne-Lausanne/Genève et la restauration définitive de liaison (à l'heure) directe Bâle/Zurich-Bienne-Genève (sans changement à Renens) ?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Enfin, au-delà des grands chantiers, le Conseil fédéral ne pense-t-il pas prioriser des projets à haute valeur ajoutée et à faible coût, tels que la &lt;strong&gt;halte ferroviaire d'Y-Parc à Yverdon&lt;/strong&gt; ? Son investissement dérisoire pour l’OFT garantit pourtant un report modal pour des milliers d'emplois.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Si une planification technique peut balayer les décisions du Parlement, à quoi sert-il encore de siéger ?&lt;/strong&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat hat Ende Januar 2026 die Eckwerte für den Ausbau der Verkehrsinfrastruktur im Rahmen von «Verkehr 45» veröffentlicht. Obwohl die politischen Instanzen bereits klare Leitlinien festgelegt haben – insbesondere haben beide Kammern am 11. März 2026 die Motion &lt;strong&gt;24.4042&lt;/strong&gt; «Entwicklung eines Angebotskonzepts 2050 auf nationaler und internationaler Ebene» und am 11. März 2024 &lt;strong&gt;die Motion 23.3668&lt;/strong&gt; «Redundanz und Zuverlässigkeit auf der Eisenbahnachse Lausanne–Genf» angenommen – scheint dies im Dossier &lt;strong&gt;«Verkehr 45»&lt;/strong&gt; in keiner Weise berücksichtigt worden zu sein.&amp;nbsp;&lt;/p&gt;&lt;p&gt;Ich bitte daher den Bundesrat, folgende Fragen zu beantworten:&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Wird sich die Botschaft 2027 auf diese beiden Motionen abstützen und klar aufzeigen, dass prioritär die Redundanz in der Genferseeregion sowie ein Angebotskonzept, das den nationalen Hauptstrecken Vorrang einräumt, schnellstmöglich geprüft und umgesetzt werden müssen? &amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Wird die Botschaft 2027 eine Erhöhung der Taktfrequenz, kürzere Fahrzeiten, mehr Kapazitäten und eine robustere Eisenbahninfrastruktur vorsehen, insbesondere für die Westschweiz?&lt;/p&gt;&lt;p&gt;3. Wie gedenkt der Bundesrat angesichts bestimmter neuer Projekte, die im Rahmen von «Verkehr&amp;nbsp;45» vorgesehen sind, die Tragfähigkeit des Bahninfrastrukturfonds zu gewährleisten, ohne dabei die Regionen zu benachteiligen, die bereits einen Investitionsrückstand aufweisen (Jura und Genferseeregion)?&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Kann der Bundesrat die territorialen und wirtschaftlichen Auswirkungen eines mangelnden Ausbaus des Schienenverkehrs darlegen und die geplanten Massnahmen zur Gewährleistung der Gleichbehandlung erläutern?&amp;nbsp;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Hält es der Bundesrat im Hinblick auf die Eindämmung der öffentlichen Ausgaben nicht für notwendig, die Baustandards der SBB zu vereinfachen?&lt;/p&gt;&lt;p&gt;6. Sind konkret Verbesserungen auf der Strecke Biel–Lausanne/Genf sowie die endgültige Wiederaufnahme der direkten (pünktlichen) Verbindung Basel/Zürich–Biel–Genf (ohne Umsteigen in Renens) vorgesehen?&amp;nbsp;&lt;/p&gt;&lt;p&gt;7. Ist der Bundesrat nicht der Ansicht, dass er neben den Grossprojekten auch Projekten mit hohem Mehrwert und geringen Kosten Vorrang einräumen sollte, wie beispielsweise der &lt;strong&gt;Bahnhaltestelle «Y-Parc» in Yverdon&lt;/strong&gt;? Die Investitionen sind für das Bundesamt für Verkehr lächerlich gering, gewährleisten jedoch eine Verkehrsverlagerung für Tausende von Arbeitsplätzen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Wenn die Beschlüsse des Parlaments bei der technischen Planung ausser Kraft gesetzt werden können, was bringen die Sessionen dann noch?&lt;/strong&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263228</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.3323</t>
   </si>
   <si>
@@ -546,45 +585,6 @@
   </si>
   <si>
     <t xml:space="preserve">Diritto penale|Migrazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Po.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechtliche Abklärungen und Potenzial von künstlicher Intelligenz in den Bereichen Polizei und innere Sicherheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarifications juridiques et potentiel de l'utilisation de l'intelligence artificielle (IA) dans les domaines de la police et de la sécurité intérieure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiarimenti giuridici e potenzialità dell'impiego dell'intelligenza artificiale (IA) nei settori della polizia e della sicurezza interna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Le Conseil fédéral est chargé de présenter un rapport concernant l’utilisation de l’intelligence artificielle (IA) dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale exposant le potentiel, les bases légales et les limites constitutionnelles, notamment pour la protection de la vie privée. Sur la base de ces conclusions, il devra soumettre au Parlement des lignes directrices pour une utilisation cohérente et conforme aux droits fondamentaux de l’IA dans les domaines de la police, de la sécurité intérieure et de la poursuite pénale, tout en respectant la souveraineté numérique de la Suisse. Le rapport devra notamment :&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. Démontrer le potentiel et les domaines d’application des technologies d’IA pour rendre la lutte contre la criminalité plus efficace et contribuer à la sauvegarde de la sécurité intérieure.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. Analyser le cadre juridique existant pour l’utilisation des technologies d’IA dans le domaine de la sécurité et identifier les éventuelles lacunes du cadre juridique.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. Expliquer les limites constitutionnelles à l’utilisation des technologies d’IA dans les domaines de la police et de la sécurité et définir des conditions cadre et les lignes directrices pour l’utilisation de ces technologies.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. Démontrer comment les exigences en matière de protection de la vie privée peuvent être satisfaites lors de l'utilisation des technologies d'IA dans les domaines de la police et de la sécurité.&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. Expliquer comment la souveraineté numérique de la Suisse peut être préservée et la dépendance vis-à-vis des prestataires externes évitée lors de l'acquisition et de l'exploitation des technologies d'IA dans le secteur de la sécurité.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Der Bundesrat wird beauftragt, einen Bericht über den Einsatz künstlicher Intelligenz (KI) in den Bereichen Polizei, innere Sicherheit und Strafverfolgung vorzulegen. Der Bericht soll insbesondere das Potenzial, die rechtlichen Grundlagen sowie die verfassungsrechtlichen Grenzen von KI – namentlich in Bezug auf den Schutz der Privatsphäre – darlegen. Auf der Grundlage des Berichts soll der Bundesrat dem Parlament Leitlinien für einen kohärenten und grundrechtskonformen Einsatz von KI in den Bereichen Polizei, innere Sicherheit und Strafverfolgung vorlegen, wobei die digitale Souveränität der Schweiz gewahrt werden soll. Der Bericht soll insbesondere:&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;1. das Potenzial und die Anwendungsbereiche von KI-Technologien aufzeigen, um die Bekämpfung der Kriminalität effizienter zu gestalten und die innere Sicherheit zu stärken;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;2. den bestehenden Rechtsrahmen für den Einsatz von KI-Technologien im Sicherheitsbereich analysieren und allfällige Lücken identifizieren;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;3. die verfassungsrechtlichen Grenzen für den Einsatz von KI-Technologien in den Bereichen Polizei und Sicherheit erläutern sowie Rahmenbedingungen und Leitlinien für den Einsatz von KI definieren;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;4. aufzeigen, wie die Anforderungen an den Schutz der Privatsphäre beim Einsatz von KI-Technologien im Polizei- und Sicherheitsbereich erfüllt werden können;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;5. erläutern, wie die digitale Souveränität der Schweiz gewahrt und Abhängigkeiten von externen Anbietern bei der Beschaffung und beim Betrieb von KI-Technologien im Sicherheitsbereich vermieden werden können.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspolitik|Recht Allgemein|Medien und Kommunikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politique de sécurité|Droit|Médias et communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Politica di sicurezza|Diritto generale|Media e comunicazione</t>
   </si>
   <si>
     <t xml:space="preserve">26.7194</t>
@@ -5100,7 +5100,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20263192</v>
+        <v>20263374</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -5111,299 +5111,297 @@
       <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2"/>
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>32</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>33</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>35</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>38</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>40</v>
-      </c>
-      <c r="U2" t="s">
-        <v>41</v>
       </c>
       <c r="V2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20263120</v>
+        <v>20263411</v>
       </c>
       <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>45</v>
       </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>46</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>47</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>48</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>49</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>50</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
         <v>51</v>
       </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>52</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>54</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>55</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>56</v>
       </c>
-      <c r="T3" t="s">
-        <v>57</v>
-      </c>
       <c r="U3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="V3"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263121</v>
+        <v>20263192</v>
       </c>
       <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>60</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>61</v>
       </c>
-      <c r="F4" t="s">
-        <v>45</v>
-      </c>
       <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>62</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>64</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>65</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>66</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>67</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
         <v>68</v>
       </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>69</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>71</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>72</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>73</v>
       </c>
-      <c r="T4" t="s">
-        <v>74</v>
-      </c>
       <c r="U4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="V4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263069</v>
+        <v>20263099</v>
       </c>
       <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
         <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q5" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="R5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="V5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20254774</v>
+        <v>20263120</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
-        <v>61</v>
-      </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
         <v>98</v>
@@ -5412,312 +5410,312 @@
         <v>99</v>
       </c>
       <c r="Q6" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="R6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263374</v>
+        <v>20263121</v>
       </c>
       <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" t="s">
+        <v>112</v>
+      </c>
+      <c r="P7" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R7" t="s">
+        <v>114</v>
+      </c>
+      <c r="S7" t="s">
+        <v>115</v>
+      </c>
+      <c r="T7" t="s">
+        <v>116</v>
+      </c>
+      <c r="U7" t="s">
         <v>104</v>
       </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J7" t="s">
-        <v>109</v>
-      </c>
-      <c r="K7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L7" t="s">
-        <v>111</v>
-      </c>
-      <c r="M7" t="s">
-        <v>112</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-      <c r="O7" t="s">
-        <v>113</v>
-      </c>
-      <c r="P7" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>85</v>
-      </c>
-      <c r="R7" t="s">
-        <v>115</v>
-      </c>
-      <c r="S7" t="s">
-        <v>116</v>
-      </c>
-      <c r="T7" t="s">
-        <v>117</v>
-      </c>
-      <c r="U7" t="s">
-        <v>41</v>
-      </c>
-      <c r="V7" t="s">
-        <v>41</v>
-      </c>
+      <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263411</v>
+        <v>20263069</v>
       </c>
       <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
         <v>118</v>
       </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
         <v>119</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" t="s">
         <v>120</v>
       </c>
-      <c r="F8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>121</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>122</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>123</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>124</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" t="s">
         <v>125</v>
       </c>
-      <c r="N8" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>126</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
         <v>127</v>
       </c>
-      <c r="Q8" t="s">
-        <v>71</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>128</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>129</v>
       </c>
-      <c r="T8" t="s">
-        <v>130</v>
-      </c>
       <c r="U8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V8" t="s">
-        <v>41</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20263454</v>
+        <v>20254774</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" t="s">
         <v>132</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>133</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>134</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>135</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>136</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>137</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>138</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>139</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R9" t="s">
         <v>140</v>
       </c>
-      <c r="Q9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R9" t="s">
-        <v>86</v>
-      </c>
       <c r="S9" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="T9" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="U9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263228</v>
+        <v>20263454</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R10" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="S10" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="T10" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="U10" t="s">
-        <v>141</v>
-      </c>
-      <c r="V10"/>
+        <v>40</v>
+      </c>
+      <c r="V10" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20263323</v>
+        <v>20263228</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
         <v>156</v>
@@ -5735,119 +5733,119 @@
         <v>160</v>
       </c>
       <c r="N11" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="O11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q11" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R11" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="S11" t="s">
+        <v>115</v>
+      </c>
+      <c r="T11" t="s">
+        <v>116</v>
+      </c>
+      <c r="U11" t="s">
         <v>164</v>
-      </c>
-      <c r="T11" t="s">
-        <v>165</v>
-      </c>
-      <c r="U11" t="s">
-        <v>141</v>
       </c>
       <c r="V11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20263131</v>
+        <v>20263323</v>
       </c>
       <c r="B12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
         <v>166</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>167</v>
       </c>
-      <c r="E12"/>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="I12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N12" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U12" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20263099</v>
+        <v>20263131</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>61</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="E13"/>
       <c r="F13" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s">
         <v>181</v>
@@ -5865,7 +5863,7 @@
         <v>185</v>
       </c>
       <c r="N13" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s">
         <v>186</v>
@@ -5874,7 +5872,7 @@
         <v>187</v>
       </c>
       <c r="Q13" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="R13" t="s">
         <v>188</v>
@@ -5886,11 +5884,9 @@
         <v>190</v>
       </c>
       <c r="U13" t="s">
-        <v>41</v>
-      </c>
-      <c r="V13" t="s">
-        <v>41</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="V13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5906,16 +5902,16 @@
         <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
         <v>194</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I14" t="s">
         <v>195</v>
@@ -5940,7 +5936,7 @@
         <v>201</v>
       </c>
       <c r="Q14" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R14" t="s">
         <v>202</v>
@@ -5952,7 +5948,7 @@
         <v>204</v>
       </c>
       <c r="U14" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V14"/>
     </row>
@@ -5973,13 +5969,13 @@
         <v>207</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
         <v>208</v>
@@ -6004,7 +6000,7 @@
         <v>213</v>
       </c>
       <c r="Q15" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R15" t="s">
         <v>214</v>
@@ -6016,7 +6012,7 @@
         <v>216</v>
       </c>
       <c r="U15" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V15"/>
     </row>
@@ -6037,7 +6033,7 @@
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
         <v>220</v>
@@ -6060,19 +6056,19 @@
         <v>225</v>
       </c>
       <c r="Q16" t="s">
+        <v>53</v>
+      </c>
+      <c r="R16" t="s">
         <v>71</v>
       </c>
-      <c r="R16" t="s">
-        <v>38</v>
-      </c>
       <c r="S16" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="T16" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U16" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V16"/>
     </row>
@@ -6090,16 +6086,16 @@
         <v>227</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
         <v>228</v>
       </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
         <v>229</v>
@@ -6124,7 +6120,7 @@
         <v>234</v>
       </c>
       <c r="Q17" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R17" t="s">
         <v>235</v>
@@ -6136,7 +6132,7 @@
         <v>237</v>
       </c>
       <c r="U17" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V17"/>
     </row>
@@ -6148,7 +6144,7 @@
         <v>238</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>239</v>
@@ -6158,10 +6154,10 @@
         <v>240</v>
       </c>
       <c r="G18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="s">
         <v>27</v>
-      </c>
-      <c r="H18" t="s">
-        <v>107</v>
       </c>
       <c r="I18" t="s">
         <v>241</v>
@@ -6188,7 +6184,7 @@
         <v>247</v>
       </c>
       <c r="Q18" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R18" t="s">
         <v>248</v>
@@ -6200,7 +6196,7 @@
         <v>250</v>
       </c>
       <c r="U18" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V18"/>
     </row>
@@ -6212,7 +6208,7 @@
         <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
         <v>252</v>
@@ -6221,13 +6217,13 @@
         <v>253</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="s">
         <v>27</v>
-      </c>
-      <c r="H19" t="s">
-        <v>107</v>
       </c>
       <c r="I19" t="s">
         <v>254</v>
@@ -6245,7 +6241,7 @@
         <v>258</v>
       </c>
       <c r="N19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O19" t="s">
         <v>259</v>
@@ -6254,7 +6250,7 @@
         <v>260</v>
       </c>
       <c r="Q19" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
         <v>261</v>
@@ -6266,7 +6262,7 @@
         <v>263</v>
       </c>
       <c r="U19" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V19"/>
     </row>
@@ -6278,22 +6274,22 @@
         <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>265</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I20" t="s">
         <v>266</v>
@@ -6311,7 +6307,7 @@
         <v>270</v>
       </c>
       <c r="N20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O20" t="s">
         <v>271</v>
@@ -6320,7 +6316,7 @@
         <v>272</v>
       </c>
       <c r="Q20" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R20" t="s">
         <v>273</v>
@@ -6332,7 +6328,7 @@
         <v>275</v>
       </c>
       <c r="U20" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V20"/>
     </row>
@@ -6344,19 +6340,19 @@
         <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
         <v>277</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H21" t="s">
         <v>278</v>
@@ -6386,7 +6382,7 @@
         <v>286</v>
       </c>
       <c r="Q21" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R21" t="s">
         <v>287</v>
@@ -6398,7 +6394,7 @@
         <v>289</v>
       </c>
       <c r="U21" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V21"/>
     </row>
@@ -6410,22 +6406,22 @@
         <v>290</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
         <v>277</v>
       </c>
       <c r="G22" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s">
         <v>291</v>
@@ -6452,7 +6448,7 @@
         <v>298</v>
       </c>
       <c r="Q22" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R22" t="s">
         <v>299</v>
@@ -6464,7 +6460,7 @@
         <v>301</v>
       </c>
       <c r="U22" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V22"/>
     </row>
@@ -6476,22 +6472,22 @@
         <v>302</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
         <v>303</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s">
         <v>304</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I23" t="s">
         <v>305</v>
@@ -6518,7 +6514,7 @@
         <v>311</v>
       </c>
       <c r="Q23" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R23" t="s">
         <v>312</v>
@@ -6530,7 +6526,7 @@
         <v>314</v>
       </c>
       <c r="U23" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V23"/>
     </row>
@@ -6542,22 +6538,22 @@
         <v>315</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
         <v>316</v>
       </c>
       <c r="G24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" t="s">
         <v>27</v>
-      </c>
-      <c r="H24" t="s">
-        <v>107</v>
       </c>
       <c r="I24" t="s">
         <v>317</v>
@@ -6575,7 +6571,7 @@
         <v>321</v>
       </c>
       <c r="N24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O24" t="s">
         <v>322</v>
@@ -6584,7 +6580,7 @@
         <v>323</v>
       </c>
       <c r="Q24" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R24" t="s">
         <v>248</v>
@@ -6596,7 +6592,7 @@
         <v>250</v>
       </c>
       <c r="U24" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V24"/>
     </row>
@@ -6608,22 +6604,22 @@
         <v>324</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
         <v>193</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
         <v>316</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I25" t="s">
         <v>325</v>
@@ -6641,7 +6637,7 @@
         <v>329</v>
       </c>
       <c r="N25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O25" t="s">
         <v>330</v>
@@ -6650,7 +6646,7 @@
         <v>331</v>
       </c>
       <c r="Q25" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R25" t="s">
         <v>332</v>
@@ -6662,7 +6658,7 @@
         <v>334</v>
       </c>
       <c r="U25" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V25"/>
     </row>
@@ -6680,13 +6676,13 @@
         <v>336</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
         <v>337</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
         <v>278</v>
@@ -6714,7 +6710,7 @@
         <v>343</v>
       </c>
       <c r="Q26" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R26" t="s">
         <v>344</v>
@@ -6726,7 +6722,7 @@
         <v>346</v>
       </c>
       <c r="U26" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V26"/>
     </row>
@@ -6741,19 +6737,19 @@
         <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
         <v>337</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s">
         <v>348</v>
@@ -6778,19 +6774,19 @@
         <v>353</v>
       </c>
       <c r="Q27" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R27" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="S27" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="T27" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="U27" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V27"/>
     </row>
@@ -6802,7 +6798,7 @@
         <v>354</v>
       </c>
       <c r="C28" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>355</v>
@@ -6812,10 +6808,10 @@
         <v>356</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I28" t="s">
         <v>357</v>
@@ -6842,7 +6838,7 @@
         <v>363</v>
       </c>
       <c r="Q28" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R28" t="s">
         <v>364</v>
@@ -6854,7 +6850,7 @@
         <v>366</v>
       </c>
       <c r="U28" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V28"/>
     </row>
@@ -6866,22 +6862,22 @@
         <v>367</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
         <v>368</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
         <v>369</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H29" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I29" t="s">
         <v>370</v>
@@ -6908,7 +6904,7 @@
         <v>376</v>
       </c>
       <c r="Q29" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R29" t="s">
         <v>377</v>
@@ -6920,7 +6916,7 @@
         <v>379</v>
       </c>
       <c r="U29" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V29"/>
     </row>
@@ -6932,22 +6928,22 @@
         <v>380</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
         <v>381</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F30" t="s">
         <v>369</v>
       </c>
       <c r="G30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" t="s">
         <v>27</v>
-      </c>
-      <c r="H30" t="s">
-        <v>107</v>
       </c>
       <c r="I30" t="s">
         <v>382</v>
@@ -6965,7 +6961,7 @@
         <v>386</v>
       </c>
       <c r="N30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O30" t="s">
         <v>387</v>
@@ -6974,19 +6970,19 @@
         <v>388</v>
       </c>
       <c r="Q30" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R30" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="S30" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="T30" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U30" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V30"/>
     </row>
@@ -6998,22 +6994,22 @@
         <v>389</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
         <v>369</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H31" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I31" t="s">
         <v>390</v>
@@ -7031,7 +7027,7 @@
         <v>394</v>
       </c>
       <c r="N31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O31" t="s">
         <v>395</v>
@@ -7040,19 +7036,19 @@
         <v>396</v>
       </c>
       <c r="Q31" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R31" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="S31" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="T31" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="U31" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V31"/>
     </row>
@@ -7064,22 +7060,22 @@
         <v>397</v>
       </c>
       <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
         <v>43</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" t="s">
-        <v>120</v>
       </c>
       <c r="F32" t="s">
         <v>369</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I32" t="s">
         <v>398</v>
@@ -7106,7 +7102,7 @@
         <v>404</v>
       </c>
       <c r="Q32" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R32" t="s">
         <v>405</v>
@@ -7118,7 +7114,7 @@
         <v>407</v>
       </c>
       <c r="U32" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V32"/>
     </row>
@@ -7130,22 +7126,22 @@
         <v>408</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
         <v>409</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
         <v>410</v>
       </c>
       <c r="G33" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" t="s">
         <v>27</v>
-      </c>
-      <c r="H33" t="s">
-        <v>107</v>
       </c>
       <c r="I33" t="s">
         <v>411</v>
@@ -7172,7 +7168,7 @@
         <v>417</v>
       </c>
       <c r="Q33" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R33" t="s">
         <v>261</v>
@@ -7184,7 +7180,7 @@
         <v>263</v>
       </c>
       <c r="U33" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V33"/>
     </row>
@@ -7196,22 +7192,22 @@
         <v>418</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F34" t="s">
         <v>419</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s">
         <v>420</v>
@@ -7238,7 +7234,7 @@
         <v>426</v>
       </c>
       <c r="Q34" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R34" t="s">
         <v>427</v>
@@ -7250,7 +7246,7 @@
         <v>429</v>
       </c>
       <c r="U34" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V34"/>
     </row>
@@ -7262,19 +7258,19 @@
         <v>430</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
         <v>431</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F35" t="s">
         <v>419</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H35" t="s">
         <v>278</v>
@@ -7295,7 +7291,7 @@
         <v>436</v>
       </c>
       <c r="N35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O35" t="s">
         <v>437</v>
@@ -7304,7 +7300,7 @@
         <v>438</v>
       </c>
       <c r="Q35" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R35" t="s">
         <v>439</v>
@@ -7316,7 +7312,7 @@
         <v>441</v>
       </c>
       <c r="U35" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V35"/>
     </row>
@@ -7328,22 +7324,22 @@
         <v>442</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
         <v>443</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
         <v>444</v>
       </c>
       <c r="G36" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H36" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I36" t="s">
         <v>445</v>
@@ -7370,7 +7366,7 @@
         <v>451</v>
       </c>
       <c r="Q36" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R36" t="s">
         <v>452</v>
@@ -7382,7 +7378,7 @@
         <v>454</v>
       </c>
       <c r="U36" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V36"/>
     </row>
@@ -7397,19 +7393,19 @@
         <v>456</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F37" t="s">
         <v>457</v>
       </c>
       <c r="G37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" t="s">
         <v>27</v>
-      </c>
-      <c r="H37" t="s">
-        <v>107</v>
       </c>
       <c r="I37" t="s">
         <v>458</v>
@@ -7436,7 +7432,7 @@
         <v>465</v>
       </c>
       <c r="Q37" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R37" t="s">
         <v>466</v>
@@ -7448,7 +7444,7 @@
         <v>468</v>
       </c>
       <c r="U37" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V37"/>
     </row>
@@ -7460,7 +7456,7 @@
         <v>469</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
         <v>470</v>
@@ -7472,10 +7468,10 @@
         <v>471</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H38" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I38" t="s">
         <v>472</v>
@@ -7493,7 +7489,7 @@
         <v>476</v>
       </c>
       <c r="N38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O38" t="s">
         <v>477</v>
@@ -7502,7 +7498,7 @@
         <v>478</v>
       </c>
       <c r="Q38" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R38" t="s">
         <v>479</v>
@@ -7514,7 +7510,7 @@
         <v>481</v>
       </c>
       <c r="U38" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V38"/>
     </row>
@@ -7538,10 +7534,10 @@
         <v>471</v>
       </c>
       <c r="G39" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" t="s">
         <v>27</v>
-      </c>
-      <c r="H39" t="s">
-        <v>107</v>
       </c>
       <c r="I39" t="s">
         <v>485</v>
@@ -7566,7 +7562,7 @@
         <v>490</v>
       </c>
       <c r="Q39" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R39" t="s">
         <v>261</v>
@@ -7578,7 +7574,7 @@
         <v>263</v>
       </c>
       <c r="U39" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V39"/>
     </row>
@@ -7596,16 +7592,16 @@
         <v>492</v>
       </c>
       <c r="E40" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
         <v>471</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s">
         <v>493</v>
@@ -7630,7 +7626,7 @@
         <v>498</v>
       </c>
       <c r="Q40" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R40" t="s">
         <v>499</v>
@@ -7642,7 +7638,7 @@
         <v>501</v>
       </c>
       <c r="U40" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V40"/>
     </row>
@@ -7660,16 +7656,16 @@
         <v>431</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F41" t="s">
         <v>503</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I41" t="s">
         <v>504</v>
@@ -7694,7 +7690,7 @@
         <v>509</v>
       </c>
       <c r="Q41" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R41" t="s">
         <v>510</v>
@@ -7706,7 +7702,7 @@
         <v>512</v>
       </c>
       <c r="U41" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V41"/>
     </row>
@@ -7718,19 +7714,19 @@
         <v>513</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
         <v>514</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
         <v>515</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H42" t="s">
         <v>278</v>
@@ -7751,7 +7747,7 @@
         <v>520</v>
       </c>
       <c r="N42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O42" t="s">
         <v>521</v>
@@ -7760,7 +7756,7 @@
         <v>522</v>
       </c>
       <c r="Q42" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R42" t="s">
         <v>523</v>
@@ -7772,7 +7768,7 @@
         <v>525</v>
       </c>
       <c r="U42" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V42"/>
     </row>
@@ -7790,13 +7786,13 @@
         <v>514</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
         <v>515</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H43" t="s">
         <v>278</v>
@@ -7824,7 +7820,7 @@
         <v>532</v>
       </c>
       <c r="Q43" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R43" t="s">
         <v>533</v>
@@ -7836,7 +7832,7 @@
         <v>535</v>
       </c>
       <c r="U43" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V43"/>
     </row>
@@ -7886,13 +7882,13 @@
         <v>547</v>
       </c>
       <c r="Q44" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R44"/>
       <c r="S44"/>
       <c r="T44"/>
       <c r="U44" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V44"/>
     </row>
@@ -7904,22 +7900,22 @@
         <v>548</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
         <v>549</v>
       </c>
       <c r="E45" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F45" t="s">
         <v>550</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H45" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I45" t="s">
         <v>551</v>
@@ -7937,7 +7933,7 @@
         <v>555</v>
       </c>
       <c r="N45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O45" t="s">
         <v>556</v>
@@ -7946,7 +7942,7 @@
         <v>557</v>
       </c>
       <c r="Q45" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R45" t="s">
         <v>558</v>
@@ -7958,7 +7954,7 @@
         <v>560</v>
       </c>
       <c r="U45" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V45"/>
     </row>
@@ -7970,22 +7966,22 @@
         <v>561</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
         <v>562</v>
       </c>
       <c r="E46" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F46" t="s">
         <v>550</v>
       </c>
       <c r="G46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I46" t="s">
         <v>563</v>
@@ -8003,7 +7999,7 @@
         <v>567</v>
       </c>
       <c r="N46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O46" t="s">
         <v>568</v>
@@ -8012,7 +8008,7 @@
         <v>569</v>
       </c>
       <c r="Q46" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R46" t="s">
         <v>570</v>
@@ -8024,7 +8020,7 @@
         <v>572</v>
       </c>
       <c r="U46" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V46"/>
     </row>
@@ -8036,22 +8032,22 @@
         <v>573</v>
       </c>
       <c r="C47" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
         <v>574</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F47" t="s">
         <v>550</v>
       </c>
       <c r="G47" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" t="s">
         <v>27</v>
-      </c>
-      <c r="H47" t="s">
-        <v>107</v>
       </c>
       <c r="I47" t="s">
         <v>575</v>
@@ -8078,7 +8074,7 @@
         <v>582</v>
       </c>
       <c r="Q47" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R47" t="s">
         <v>583</v>
@@ -8090,7 +8086,7 @@
         <v>585</v>
       </c>
       <c r="U47" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V47"/>
     </row>
@@ -8102,20 +8098,20 @@
         <v>586</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="E48"/>
       <c r="F48" t="s">
         <v>587</v>
       </c>
       <c r="G48" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" t="s">
         <v>27</v>
-      </c>
-      <c r="H48" t="s">
-        <v>107</v>
       </c>
       <c r="I48" t="s">
         <v>588</v>
@@ -8133,7 +8129,7 @@
         <v>592</v>
       </c>
       <c r="N48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O48" t="s">
         <v>593</v>
@@ -8142,7 +8138,7 @@
         <v>594</v>
       </c>
       <c r="Q48" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R48" t="s">
         <v>595</v>
@@ -8154,7 +8150,7 @@
         <v>597</v>
       </c>
       <c r="U48" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V48"/>
     </row>
@@ -8166,22 +8162,22 @@
         <v>598</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
         <v>599</v>
       </c>
       <c r="E49" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F49" t="s">
         <v>587</v>
       </c>
       <c r="G49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I49" t="s">
         <v>600</v>
@@ -8208,7 +8204,7 @@
         <v>606</v>
       </c>
       <c r="Q49" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R49" t="s">
         <v>607</v>
@@ -8220,7 +8216,7 @@
         <v>609</v>
       </c>
       <c r="U49" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V49"/>
     </row>
@@ -8232,22 +8228,22 @@
         <v>610</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
         <v>611</v>
       </c>
       <c r="E50" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F50" t="s">
         <v>612</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H50" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I50" t="s">
         <v>613</v>
@@ -8274,19 +8270,19 @@
         <v>619</v>
       </c>
       <c r="Q50" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R50" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="S50" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="T50" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="U50" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V50"/>
     </row>
@@ -8298,7 +8294,7 @@
         <v>620</v>
       </c>
       <c r="C51" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D51" t="s">
         <v>621</v>
@@ -8308,10 +8304,10 @@
         <v>612</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H51" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I51" t="s">
         <v>622</v>
@@ -8338,7 +8334,7 @@
         <v>628</v>
       </c>
       <c r="Q51" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R51" t="s">
         <v>629</v>
@@ -8350,7 +8346,7 @@
         <v>631</v>
       </c>
       <c r="U51" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V51"/>
     </row>
@@ -8362,22 +8358,22 @@
         <v>632</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
         <v>381</v>
       </c>
       <c r="E52" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F52" t="s">
         <v>612</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I52" t="s">
         <v>633</v>
@@ -8395,7 +8391,7 @@
         <v>637</v>
       </c>
       <c r="N52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O52" t="s">
         <v>638</v>
@@ -8404,7 +8400,7 @@
         <v>639</v>
       </c>
       <c r="Q52" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R52" t="s">
         <v>640</v>
@@ -8416,7 +8412,7 @@
         <v>642</v>
       </c>
       <c r="U52" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V52"/>
     </row>
@@ -8428,7 +8424,7 @@
         <v>643</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
         <v>644</v>
@@ -8440,10 +8436,10 @@
         <v>645</v>
       </c>
       <c r="G53" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H53" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I53" t="s">
         <v>646</v>
@@ -8470,7 +8466,7 @@
         <v>652</v>
       </c>
       <c r="Q53" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R53" t="s">
         <v>558</v>
@@ -8482,7 +8478,7 @@
         <v>560</v>
       </c>
       <c r="U53" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V53"/>
     </row>
@@ -8494,22 +8490,22 @@
         <v>653</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
         <v>654</v>
       </c>
       <c r="E54" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
         <v>655</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H54" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I54" t="s">
         <v>656</v>
@@ -8527,7 +8523,7 @@
         <v>660</v>
       </c>
       <c r="N54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O54" t="s">
         <v>661</v>
@@ -8536,19 +8532,19 @@
         <v>662</v>
       </c>
       <c r="Q54" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R54" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="S54" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="T54" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="U54" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V54"/>
     </row>
@@ -8560,7 +8556,7 @@
         <v>663</v>
       </c>
       <c r="C55" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
         <v>664</v>
@@ -8572,10 +8568,10 @@
         <v>666</v>
       </c>
       <c r="G55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" t="s">
         <v>27</v>
-      </c>
-      <c r="H55" t="s">
-        <v>107</v>
       </c>
       <c r="I55" t="s">
         <v>667</v>
@@ -8593,7 +8589,7 @@
         <v>671</v>
       </c>
       <c r="N55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O55" t="s">
         <v>672</v>
@@ -8602,7 +8598,7 @@
         <v>673</v>
       </c>
       <c r="Q55" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R55" t="s">
         <v>674</v>
@@ -8614,7 +8610,7 @@
         <v>676</v>
       </c>
       <c r="U55" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V55"/>
     </row>
@@ -8626,22 +8622,22 @@
         <v>677</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
         <v>431</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F56" t="s">
         <v>666</v>
       </c>
       <c r="G56" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" t="s">
         <v>27</v>
-      </c>
-      <c r="H56" t="s">
-        <v>107</v>
       </c>
       <c r="I56" t="s">
         <v>678</v>
@@ -8659,7 +8655,7 @@
         <v>682</v>
       </c>
       <c r="N56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O56" t="s">
         <v>683</v>
@@ -8668,7 +8664,7 @@
         <v>684</v>
       </c>
       <c r="Q56" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R56" t="s">
         <v>685</v>
@@ -8680,7 +8676,7 @@
         <v>687</v>
       </c>
       <c r="U56" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V56"/>
     </row>
@@ -8692,7 +8688,7 @@
         <v>688</v>
       </c>
       <c r="C57" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
         <v>239</v>
@@ -8702,10 +8698,10 @@
         <v>689</v>
       </c>
       <c r="G57" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" t="s">
         <v>27</v>
-      </c>
-      <c r="H57" t="s">
-        <v>107</v>
       </c>
       <c r="I57" t="s">
         <v>690</v>
@@ -8732,7 +8728,7 @@
         <v>696</v>
       </c>
       <c r="Q57" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R57" t="s">
         <v>685</v>
@@ -8744,7 +8740,7 @@
         <v>687</v>
       </c>
       <c r="U57" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V57"/>
     </row>
@@ -8756,19 +8752,19 @@
         <v>697</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
         <v>698</v>
       </c>
       <c r="E58" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F58" t="s">
         <v>699</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H58" t="s">
         <v>700</v>
@@ -8798,7 +8794,7 @@
         <v>707</v>
       </c>
       <c r="Q58" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R58" t="s">
         <v>708</v>
@@ -8810,7 +8806,7 @@
         <v>710</v>
       </c>
       <c r="U58" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V58"/>
     </row>
@@ -8822,22 +8818,22 @@
         <v>711</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
         <v>712</v>
       </c>
       <c r="E59" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F59" t="s">
         <v>699</v>
       </c>
       <c r="G59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I59" t="s">
         <v>713</v>
@@ -8855,7 +8851,7 @@
         <v>717</v>
       </c>
       <c r="N59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O59" t="s">
         <v>718</v>
@@ -8864,7 +8860,7 @@
         <v>719</v>
       </c>
       <c r="Q59" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R59" t="s">
         <v>720</v>
@@ -8876,7 +8872,7 @@
         <v>722</v>
       </c>
       <c r="U59" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V59"/>
     </row>
@@ -8888,22 +8884,22 @@
         <v>723</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
         <v>724</v>
       </c>
       <c r="E60" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F60" t="s">
         <v>699</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H60" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I60" t="s">
         <v>725</v>
@@ -8921,7 +8917,7 @@
         <v>729</v>
       </c>
       <c r="N60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O60" t="s">
         <v>730</v>
@@ -8930,7 +8926,7 @@
         <v>731</v>
       </c>
       <c r="Q60" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R60" t="s">
         <v>479</v>
@@ -8942,7 +8938,7 @@
         <v>481</v>
       </c>
       <c r="U60" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V60"/>
     </row>
@@ -8954,22 +8950,22 @@
         <v>732</v>
       </c>
       <c r="C61" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D61" t="s">
         <v>733</v>
       </c>
       <c r="E61" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F61" t="s">
         <v>734</v>
       </c>
       <c r="G61" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I61" t="s">
         <v>735</v>
@@ -8996,7 +8992,7 @@
         <v>741</v>
       </c>
       <c r="Q61" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R61" t="s">
         <v>742</v>
@@ -9008,7 +9004,7 @@
         <v>744</v>
       </c>
       <c r="U61" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V61"/>
     </row>
@@ -9020,22 +9016,22 @@
         <v>745</v>
       </c>
       <c r="C62" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F62" t="s">
         <v>734</v>
       </c>
       <c r="G62" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H62" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I62" t="s">
         <v>746</v>
@@ -9062,7 +9058,7 @@
         <v>752</v>
       </c>
       <c r="Q62" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R62" t="s">
         <v>685</v>
@@ -9074,7 +9070,7 @@
         <v>687</v>
       </c>
       <c r="U62" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V62"/>
     </row>
@@ -9086,22 +9082,22 @@
         <v>753</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
         <v>303</v>
       </c>
       <c r="E63" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F63" t="s">
         <v>754</v>
       </c>
       <c r="G63" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H63" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I63" t="s">
         <v>755</v>
@@ -9128,7 +9124,7 @@
         <v>761</v>
       </c>
       <c r="Q63" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R63" t="s">
         <v>762</v>
@@ -9140,7 +9136,7 @@
         <v>764</v>
       </c>
       <c r="U63" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V63"/>
     </row>
@@ -9152,22 +9148,22 @@
         <v>765</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
         <v>599</v>
       </c>
       <c r="E64" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F64" t="s">
         <v>766</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I64" t="s">
         <v>767</v>
@@ -9185,7 +9181,7 @@
         <v>771</v>
       </c>
       <c r="N64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O64" t="s">
         <v>772</v>
@@ -9194,7 +9190,7 @@
         <v>773</v>
       </c>
       <c r="Q64" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R64" t="s">
         <v>774</v>
@@ -9206,7 +9202,7 @@
         <v>776</v>
       </c>
       <c r="U64" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V64"/>
     </row>
@@ -9229,7 +9225,7 @@
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I65" t="s">
         <v>780</v>
@@ -9247,7 +9243,7 @@
         <v>784</v>
       </c>
       <c r="N65" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="O65" t="s">
         <v>785</v>
@@ -9256,13 +9252,13 @@
         <v>786</v>
       </c>
       <c r="Q65" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R65"/>
       <c r="S65"/>
       <c r="T65"/>
       <c r="U65" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V65"/>
     </row>
@@ -9285,7 +9281,7 @@
       </c>
       <c r="G66"/>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I66" t="s">
         <v>541</v>
@@ -9312,13 +9308,13 @@
         <v>793</v>
       </c>
       <c r="Q66" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R66"/>
       <c r="S66"/>
       <c r="T66"/>
       <c r="U66" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V66"/>
     </row>
@@ -9340,10 +9336,10 @@
         <v>796</v>
       </c>
       <c r="G67" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H67" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I67" t="s">
         <v>797</v>
@@ -9361,7 +9357,7 @@
         <v>801</v>
       </c>
       <c r="N67" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="O67" t="s">
         <v>802</v>
@@ -9370,7 +9366,7 @@
         <v>803</v>
       </c>
       <c r="Q67" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R67" t="s">
         <v>804</v>
@@ -9382,7 +9378,7 @@
         <v>806</v>
       </c>
       <c r="U67" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V67"/>
     </row>
@@ -9400,16 +9396,16 @@
         <v>562</v>
       </c>
       <c r="E68" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F68" t="s">
         <v>808</v>
       </c>
       <c r="G68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H68" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I68" t="s">
         <v>809</v>
@@ -9436,7 +9432,7 @@
         <v>815</v>
       </c>
       <c r="Q68" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R68" t="s">
         <v>816</v>
@@ -9448,7 +9444,7 @@
         <v>818</v>
       </c>
       <c r="U68" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V68"/>
     </row>
@@ -9460,7 +9456,7 @@
         <v>819</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
         <v>664</v>
@@ -9472,10 +9468,10 @@
         <v>808</v>
       </c>
       <c r="G69" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" t="s">
         <v>27</v>
-      </c>
-      <c r="H69" t="s">
-        <v>107</v>
       </c>
       <c r="I69" t="s">
         <v>820</v>
@@ -9493,7 +9489,7 @@
         <v>824</v>
       </c>
       <c r="N69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O69" t="s">
         <v>825</v>
@@ -9502,7 +9498,7 @@
         <v>826</v>
       </c>
       <c r="Q69" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R69" t="s">
         <v>827</v>
@@ -9514,7 +9510,7 @@
         <v>829</v>
       </c>
       <c r="U69" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V69"/>
     </row>
@@ -9526,22 +9522,22 @@
         <v>830</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D70" t="s">
         <v>831</v>
       </c>
       <c r="E70" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F70" t="s">
         <v>808</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H70" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="I70" t="s">
         <v>832</v>
@@ -9568,7 +9564,7 @@
         <v>838</v>
       </c>
       <c r="Q70" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R70" t="s">
         <v>839</v>
@@ -9580,7 +9576,7 @@
         <v>841</v>
       </c>
       <c r="U70" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V70"/>
     </row>
@@ -9592,22 +9588,22 @@
         <v>842</v>
       </c>
       <c r="C71" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
         <v>381</v>
       </c>
       <c r="E71" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F71" t="s">
         <v>808</v>
       </c>
       <c r="G71" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" t="s">
         <v>27</v>
-      </c>
-      <c r="H71" t="s">
-        <v>107</v>
       </c>
       <c r="I71" t="s">
         <v>843</v>
@@ -9634,7 +9630,7 @@
         <v>849</v>
       </c>
       <c r="Q71" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R71" t="s">
         <v>850</v>
@@ -9646,7 +9642,7 @@
         <v>852</v>
       </c>
       <c r="U71" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V71"/>
     </row>
@@ -9658,22 +9654,22 @@
         <v>853</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D72" t="s">
         <v>854</v>
       </c>
       <c r="E72" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F72" t="s">
         <v>808</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H72" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I72" t="s">
         <v>855</v>
@@ -9691,7 +9687,7 @@
         <v>859</v>
       </c>
       <c r="N72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O72" t="s">
         <v>860</v>
@@ -9700,7 +9696,7 @@
         <v>861</v>
       </c>
       <c r="Q72" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R72" t="s">
         <v>862</v>
@@ -9712,7 +9708,7 @@
         <v>864</v>
       </c>
       <c r="U72" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V72"/>
     </row>
@@ -9724,22 +9720,22 @@
         <v>865</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
         <v>866</v>
       </c>
       <c r="E73" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F73" t="s">
         <v>808</v>
       </c>
       <c r="G73" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" t="s">
         <v>27</v>
-      </c>
-      <c r="H73" t="s">
-        <v>107</v>
       </c>
       <c r="I73" t="s">
         <v>867</v>
@@ -9757,7 +9753,7 @@
         <v>871</v>
       </c>
       <c r="N73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O73" t="s">
         <v>872</v>
@@ -9766,7 +9762,7 @@
         <v>873</v>
       </c>
       <c r="Q73" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R73" t="s">
         <v>874</v>
@@ -9778,7 +9774,7 @@
         <v>876</v>
       </c>
       <c r="U73" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V73"/>
     </row>
@@ -9796,16 +9792,16 @@
         <v>492</v>
       </c>
       <c r="E74" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F74" t="s">
         <v>878</v>
       </c>
       <c r="G74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H74" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I74" t="s">
         <v>879</v>
@@ -9832,7 +9828,7 @@
         <v>885</v>
       </c>
       <c r="Q74" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R74" t="s">
         <v>886</v>
@@ -9844,7 +9840,7 @@
         <v>888</v>
       </c>
       <c r="U74" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V74"/>
     </row>
@@ -9856,22 +9852,22 @@
         <v>889</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D75" t="s">
         <v>890</v>
       </c>
       <c r="E75" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F75" t="s">
         <v>878</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H75" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I75" t="s">
         <v>891</v>
@@ -9889,7 +9885,7 @@
         <v>895</v>
       </c>
       <c r="N75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O75" t="s">
         <v>896</v>
@@ -9898,7 +9894,7 @@
         <v>897</v>
       </c>
       <c r="Q75" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R75" t="s">
         <v>898</v>
@@ -9910,7 +9906,7 @@
         <v>900</v>
       </c>
       <c r="U75" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V75"/>
     </row>
@@ -9933,7 +9929,7 @@
       </c>
       <c r="G76"/>
       <c r="H76" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I76" t="s">
         <v>903</v>
@@ -9960,13 +9956,13 @@
         <v>910</v>
       </c>
       <c r="Q76" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R76"/>
       <c r="S76"/>
       <c r="T76"/>
       <c r="U76" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V76"/>
     </row>
@@ -9978,22 +9974,22 @@
         <v>911</v>
       </c>
       <c r="C77" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F77" t="s">
         <v>912</v>
       </c>
       <c r="G77" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" t="s">
         <v>27</v>
-      </c>
-      <c r="H77" t="s">
-        <v>107</v>
       </c>
       <c r="I77" t="s">
         <v>370</v>
@@ -10020,7 +10016,7 @@
         <v>918</v>
       </c>
       <c r="Q77" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R77" t="s">
         <v>377</v>
@@ -10032,7 +10028,7 @@
         <v>379</v>
       </c>
       <c r="U77" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V77"/>
     </row>
@@ -10050,16 +10046,16 @@
         <v>920</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F78" t="s">
         <v>921</v>
       </c>
       <c r="G78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s">
         <v>922</v>
@@ -10084,7 +10080,7 @@
         <v>927</v>
       </c>
       <c r="Q78" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R78" t="s">
         <v>928</v>
@@ -10096,7 +10092,7 @@
         <v>930</v>
       </c>
       <c r="U78" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V78"/>
     </row>
@@ -10114,16 +10110,16 @@
         <v>932</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F79" t="s">
         <v>933</v>
       </c>
       <c r="G79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H79" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I79" t="s">
         <v>934</v>
@@ -10148,7 +10144,7 @@
         <v>939</v>
       </c>
       <c r="Q79" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R79" t="s">
         <v>816</v>
@@ -10160,7 +10156,7 @@
         <v>818</v>
       </c>
       <c r="U79" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V79"/>
     </row>
@@ -10181,7 +10177,7 @@
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I80" t="s">
         <v>942</v>
@@ -10204,7 +10200,7 @@
         <v>946</v>
       </c>
       <c r="Q80" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R80" t="s">
         <v>947</v>
@@ -10216,7 +10212,7 @@
         <v>949</v>
       </c>
       <c r="U80" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V80"/>
     </row>
@@ -10239,7 +10235,7 @@
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I81" t="s">
         <v>952</v>
@@ -10257,7 +10253,7 @@
         <v>956</v>
       </c>
       <c r="N81" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="O81" t="s">
         <v>957</v>
@@ -10266,7 +10262,7 @@
         <v>958</v>
       </c>
       <c r="Q81" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R81" t="s">
         <v>959</v>
@@ -10278,7 +10274,7 @@
         <v>961</v>
       </c>
       <c r="U81" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V81"/>
     </row>
@@ -10301,7 +10297,7 @@
       </c>
       <c r="G82"/>
       <c r="H82" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I82" t="s">
         <v>963</v>
@@ -10328,7 +10324,7 @@
         <v>969</v>
       </c>
       <c r="Q82" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R82" t="s">
         <v>970</v>
@@ -10340,7 +10336,7 @@
         <v>972</v>
       </c>
       <c r="U82" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V82"/>
     </row>
@@ -10352,7 +10348,7 @@
         <v>973</v>
       </c>
       <c r="C83" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D83" t="s">
         <v>664</v>
@@ -10364,10 +10360,10 @@
         <v>974</v>
       </c>
       <c r="G83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I83" t="s">
         <v>975</v>
@@ -10385,7 +10381,7 @@
         <v>979</v>
       </c>
       <c r="N83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O83" t="s">
         <v>980</v>
@@ -10394,7 +10390,7 @@
         <v>981</v>
       </c>
       <c r="Q83" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R83" t="s">
         <v>982</v>
@@ -10406,7 +10402,7 @@
         <v>984</v>
       </c>
       <c r="U83" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V83"/>
     </row>
@@ -10418,22 +10414,22 @@
         <v>985</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D84" t="s">
         <v>986</v>
       </c>
       <c r="E84" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F84" t="s">
         <v>987</v>
       </c>
       <c r="G84" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H84" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I84" t="s">
         <v>988</v>
@@ -10451,7 +10447,7 @@
         <v>992</v>
       </c>
       <c r="N84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O84" t="s">
         <v>993</v>
@@ -10460,7 +10456,7 @@
         <v>994</v>
       </c>
       <c r="Q84" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R84" t="s">
         <v>995</v>
@@ -10472,7 +10468,7 @@
         <v>997</v>
       </c>
       <c r="U84" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V84"/>
     </row>
@@ -10484,22 +10480,22 @@
         <v>998</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D85" t="s">
         <v>999</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F85" t="s">
         <v>987</v>
       </c>
       <c r="G85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I85" t="s">
         <v>1000</v>
@@ -10526,7 +10522,7 @@
         <v>1006</v>
       </c>
       <c r="Q85" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R85" t="s">
         <v>640</v>
@@ -10538,7 +10534,7 @@
         <v>642</v>
       </c>
       <c r="U85" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V85"/>
     </row>
@@ -10550,22 +10546,22 @@
         <v>1007</v>
       </c>
       <c r="C86" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
         <v>1008</v>
       </c>
       <c r="E86" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F86" t="s">
         <v>987</v>
       </c>
       <c r="G86" t="s">
+        <v>26</v>
+      </c>
+      <c r="H86" t="s">
         <v>27</v>
-      </c>
-      <c r="H86" t="s">
-        <v>107</v>
       </c>
       <c r="I86" t="s">
         <v>1009</v>
@@ -10592,7 +10588,7 @@
         <v>1015</v>
       </c>
       <c r="Q86" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R86" t="s">
         <v>1016</v>
@@ -10604,7 +10600,7 @@
         <v>1018</v>
       </c>
       <c r="U86" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V86"/>
     </row>
@@ -10616,22 +10612,22 @@
         <v>1019</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D87" t="s">
         <v>1020</v>
       </c>
       <c r="E87" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F87" t="s">
         <v>987</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H87" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I87" t="s">
         <v>1021</v>
@@ -10649,7 +10645,7 @@
         <v>1025</v>
       </c>
       <c r="N87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O87" t="s">
         <v>1026</v>
@@ -10658,7 +10654,7 @@
         <v>1027</v>
       </c>
       <c r="Q87" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R87" t="s">
         <v>558</v>
@@ -10670,7 +10666,7 @@
         <v>560</v>
       </c>
       <c r="U87" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V87"/>
     </row>
@@ -10682,22 +10678,22 @@
         <v>1028</v>
       </c>
       <c r="C88" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D88" t="s">
         <v>1029</v>
       </c>
       <c r="E88" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F88" t="s">
         <v>1030</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H88" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I88" t="s">
         <v>1031</v>
@@ -10715,7 +10711,7 @@
         <v>1035</v>
       </c>
       <c r="N88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O88" t="s">
         <v>1036</v>
@@ -10724,7 +10720,7 @@
         <v>1037</v>
       </c>
       <c r="Q88" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R88" t="s">
         <v>344</v>
@@ -10736,7 +10732,7 @@
         <v>346</v>
       </c>
       <c r="U88" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V88"/>
     </row>
@@ -10754,16 +10750,16 @@
         <v>431</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F89" t="s">
         <v>1039</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I89" t="s">
         <v>1040</v>
@@ -10788,19 +10784,19 @@
         <v>1045</v>
       </c>
       <c r="Q89" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R89" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="S89" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="T89" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U89" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V89"/>
     </row>
@@ -10812,22 +10808,22 @@
         <v>1046</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D90" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E90" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F90" t="s">
         <v>1047</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H90" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I90" t="s">
         <v>1048</v>
@@ -10854,19 +10850,19 @@
         <v>1054</v>
       </c>
       <c r="Q90" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R90" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="S90" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="T90" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="U90" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V90"/>
     </row>
@@ -10884,16 +10880,16 @@
         <v>1020</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F91" t="s">
         <v>1056</v>
       </c>
       <c r="G91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H91" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I91" t="s">
         <v>1057</v>
@@ -10918,7 +10914,7 @@
         <v>1062</v>
       </c>
       <c r="Q91" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R91" t="s">
         <v>479</v>
@@ -10930,7 +10926,7 @@
         <v>481</v>
       </c>
       <c r="U91" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V91"/>
     </row>
@@ -10948,16 +10944,16 @@
         <v>431</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F92" t="s">
         <v>1056</v>
       </c>
       <c r="G92" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H92" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I92" t="s">
         <v>1064</v>
@@ -10982,19 +10978,19 @@
         <v>1069</v>
       </c>
       <c r="Q92" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R92" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="S92" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="T92" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U92" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V92"/>
     </row>
@@ -11012,16 +11008,16 @@
         <v>431</v>
       </c>
       <c r="E93" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F93" t="s">
         <v>1056</v>
       </c>
       <c r="G93" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H93" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I93" t="s">
         <v>1064</v>
@@ -11046,19 +11042,19 @@
         <v>1074</v>
       </c>
       <c r="Q93" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R93" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="S93" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="T93" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U93" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V93"/>
     </row>
@@ -11076,16 +11072,16 @@
         <v>431</v>
       </c>
       <c r="E94" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F94" t="s">
         <v>1056</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H94" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I94" t="s">
         <v>1064</v>
@@ -11110,19 +11106,19 @@
         <v>1079</v>
       </c>
       <c r="Q94" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R94" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="S94" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="T94" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U94" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V94"/>
     </row>
@@ -11134,22 +11130,22 @@
         <v>1080</v>
       </c>
       <c r="C95" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D95" t="s">
         <v>514</v>
       </c>
       <c r="E95" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F95" t="s">
         <v>1081</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H95" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I95" t="s">
         <v>1082</v>
@@ -11167,7 +11163,7 @@
         <v>1086</v>
       </c>
       <c r="N95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O95" t="s">
         <v>1087</v>
@@ -11176,7 +11172,7 @@
         <v>1088</v>
       </c>
       <c r="Q95" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R95" t="s">
         <v>1089</v>
@@ -11188,7 +11184,7 @@
         <v>1091</v>
       </c>
       <c r="U95" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V95"/>
     </row>
@@ -11200,22 +11196,22 @@
         <v>1092</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D96" t="s">
         <v>574</v>
       </c>
       <c r="E96" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F96" t="s">
         <v>1093</v>
       </c>
       <c r="G96" t="s">
+        <v>26</v>
+      </c>
+      <c r="H96" t="s">
         <v>27</v>
-      </c>
-      <c r="H96" t="s">
-        <v>107</v>
       </c>
       <c r="I96" t="s">
         <v>1094</v>
@@ -11242,19 +11238,19 @@
         <v>1100</v>
       </c>
       <c r="Q96" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R96" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="S96" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="T96" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="U96" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V96"/>
     </row>
@@ -11266,22 +11262,22 @@
         <v>1101</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D97" t="s">
         <v>1102</v>
       </c>
       <c r="E97" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F97" t="s">
         <v>1093</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H97" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I97" t="s">
         <v>1103</v>
@@ -11299,7 +11295,7 @@
         <v>1107</v>
       </c>
       <c r="N97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O97" t="s">
         <v>1108</v>
@@ -11308,7 +11304,7 @@
         <v>1109</v>
       </c>
       <c r="Q97" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R97" t="s">
         <v>1110</v>
@@ -11320,7 +11316,7 @@
         <v>1112</v>
       </c>
       <c r="U97" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V97"/>
     </row>
@@ -11332,22 +11328,22 @@
         <v>1113</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D98" t="s">
         <v>1114</v>
       </c>
       <c r="E98" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F98" t="s">
         <v>1093</v>
       </c>
       <c r="G98" t="s">
+        <v>26</v>
+      </c>
+      <c r="H98" t="s">
         <v>27</v>
-      </c>
-      <c r="H98" t="s">
-        <v>107</v>
       </c>
       <c r="I98" t="s">
         <v>1115</v>
@@ -11365,7 +11361,7 @@
         <v>1119</v>
       </c>
       <c r="N98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O98" t="s">
         <v>1120</v>
@@ -11374,7 +11370,7 @@
         <v>1121</v>
       </c>
       <c r="Q98" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R98" t="s">
         <v>1122</v>
@@ -11386,7 +11382,7 @@
         <v>1124</v>
       </c>
       <c r="U98" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V98"/>
     </row>
@@ -11427,7 +11423,7 @@
         <v>1131</v>
       </c>
       <c r="N99" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="O99" t="s">
         <v>1132</v>
@@ -11436,7 +11432,7 @@
         <v>1133</v>
       </c>
       <c r="Q99" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R99" t="s">
         <v>1134</v>
@@ -11448,7 +11444,7 @@
         <v>1136</v>
       </c>
       <c r="U99" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V99"/>
     </row>
@@ -11460,22 +11456,22 @@
         <v>1137</v>
       </c>
       <c r="C100" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D100" t="s">
         <v>409</v>
       </c>
       <c r="E100" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F100" t="s">
         <v>1126</v>
       </c>
       <c r="G100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H100" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I100" t="s">
         <v>1138</v>
@@ -11493,7 +11489,7 @@
         <v>1142</v>
       </c>
       <c r="N100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O100" t="s">
         <v>1143</v>
@@ -11502,7 +11498,7 @@
         <v>1144</v>
       </c>
       <c r="Q100" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R100" t="s">
         <v>1145</v>
@@ -11514,7 +11510,7 @@
         <v>1147</v>
       </c>
       <c r="U100" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V100"/>
     </row>
@@ -11526,22 +11522,22 @@
         <v>1148</v>
       </c>
       <c r="C101" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D101" t="s">
         <v>1149</v>
       </c>
       <c r="E101" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F101" t="s">
         <v>1126</v>
       </c>
       <c r="G101" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H101" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I101" t="s">
         <v>1150</v>
@@ -11559,7 +11555,7 @@
         <v>1154</v>
       </c>
       <c r="N101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O101" t="s">
         <v>1155</v>
@@ -11568,7 +11564,7 @@
         <v>1156</v>
       </c>
       <c r="Q101" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R101" t="s">
         <v>1157</v>
@@ -11580,7 +11576,7 @@
         <v>1159</v>
       </c>
       <c r="U101" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V101"/>
     </row>
@@ -11592,22 +11588,22 @@
         <v>1160</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D102" t="s">
         <v>1161</v>
       </c>
       <c r="E102" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F102" t="s">
         <v>1126</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H102" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I102" t="s">
         <v>1162</v>
@@ -11634,7 +11630,7 @@
         <v>1168</v>
       </c>
       <c r="Q102" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R102" t="s">
         <v>827</v>
@@ -11646,7 +11642,7 @@
         <v>829</v>
       </c>
       <c r="U102" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V102"/>
     </row>
@@ -11658,22 +11654,22 @@
         <v>1169</v>
       </c>
       <c r="C103" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D103" t="s">
         <v>562</v>
       </c>
       <c r="E103" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F103" t="s">
         <v>1126</v>
       </c>
       <c r="G103" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I103" t="s">
         <v>1170</v>
@@ -11691,7 +11687,7 @@
         <v>1174</v>
       </c>
       <c r="N103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O103" t="s">
         <v>1175</v>
@@ -11700,7 +11696,7 @@
         <v>1176</v>
       </c>
       <c r="Q103" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R103" t="s">
         <v>1177</v>
@@ -11712,7 +11708,7 @@
         <v>1179</v>
       </c>
       <c r="U103" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V103"/>
     </row>
@@ -11724,22 +11720,22 @@
         <v>1180</v>
       </c>
       <c r="C104" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D104" t="s">
         <v>514</v>
       </c>
       <c r="E104" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F104" t="s">
         <v>1126</v>
       </c>
       <c r="G104" t="s">
+        <v>26</v>
+      </c>
+      <c r="H104" t="s">
         <v>27</v>
-      </c>
-      <c r="H104" t="s">
-        <v>107</v>
       </c>
       <c r="I104" t="s">
         <v>1181</v>
@@ -11766,7 +11762,7 @@
         <v>1188</v>
       </c>
       <c r="Q104" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R104" t="s">
         <v>1189</v>
@@ -11778,7 +11774,7 @@
         <v>1191</v>
       </c>
       <c r="U104" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V104"/>
     </row>
@@ -11790,22 +11786,22 @@
         <v>1192</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D105" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E105" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F105" t="s">
         <v>1193</v>
       </c>
       <c r="G105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I105" t="s">
         <v>1194</v>
@@ -11832,19 +11828,19 @@
         <v>1200</v>
       </c>
       <c r="Q105" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R105" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="S105" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="T105" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="U105" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V105"/>
     </row>
@@ -11856,22 +11852,22 @@
         <v>1201</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D106" t="s">
         <v>381</v>
       </c>
       <c r="E106" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F106" t="s">
         <v>1202</v>
       </c>
       <c r="G106" t="s">
+        <v>26</v>
+      </c>
+      <c r="H106" t="s">
         <v>27</v>
-      </c>
-      <c r="H106" t="s">
-        <v>107</v>
       </c>
       <c r="I106" t="s">
         <v>1203</v>
@@ -11898,7 +11894,7 @@
         <v>1209</v>
       </c>
       <c r="Q106" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R106" t="s">
         <v>685</v>
@@ -11910,7 +11906,7 @@
         <v>687</v>
       </c>
       <c r="U106" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V106"/>
     </row>
@@ -11928,16 +11924,16 @@
         <v>1211</v>
       </c>
       <c r="E107" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F107" t="s">
         <v>1212</v>
       </c>
       <c r="G107" t="s">
+        <v>26</v>
+      </c>
+      <c r="H107" t="s">
         <v>27</v>
-      </c>
-      <c r="H107" t="s">
-        <v>107</v>
       </c>
       <c r="I107" t="s">
         <v>1213</v>
@@ -11962,7 +11958,7 @@
         <v>1218</v>
       </c>
       <c r="Q107" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R107" t="s">
         <v>685</v>
@@ -11974,7 +11970,7 @@
         <v>687</v>
       </c>
       <c r="U107" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V107"/>
     </row>
@@ -11992,16 +11988,16 @@
         <v>1220</v>
       </c>
       <c r="E108" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F108" t="s">
         <v>1212</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H108" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I108" t="s">
         <v>1221</v>
@@ -12026,7 +12022,7 @@
         <v>1226</v>
       </c>
       <c r="Q108" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R108" t="s">
         <v>1227</v>
@@ -12038,7 +12034,7 @@
         <v>1229</v>
       </c>
       <c r="U108" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V108"/>
     </row>
@@ -12050,22 +12046,22 @@
         <v>1230</v>
       </c>
       <c r="C109" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D109" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E109" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F109" t="s">
         <v>1231</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I109" t="s">
         <v>1232</v>
@@ -12083,7 +12079,7 @@
         <v>1236</v>
       </c>
       <c r="N109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O109" t="s">
         <v>1237</v>
@@ -12092,7 +12088,7 @@
         <v>1238</v>
       </c>
       <c r="Q109" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R109" t="s">
         <v>762</v>
@@ -12104,7 +12100,7 @@
         <v>764</v>
       </c>
       <c r="U109" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V109"/>
     </row>
@@ -12125,7 +12121,7 @@
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I110" t="s">
         <v>1241</v>
@@ -12148,7 +12144,7 @@
         <v>1246</v>
       </c>
       <c r="Q110" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="R110" t="s">
         <v>1247</v>
@@ -12160,7 +12156,7 @@
         <v>1249</v>
       </c>
       <c r="U110" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V110"/>
     </row>
@@ -12183,7 +12179,7 @@
       </c>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I111" t="s">
         <v>1252</v>
@@ -12210,7 +12206,7 @@
         <v>1258</v>
       </c>
       <c r="Q111" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R111" t="s">
         <v>1259</v>
@@ -12222,7 +12218,7 @@
         <v>1261</v>
       </c>
       <c r="U111" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V111"/>
     </row>
@@ -12234,22 +12230,22 @@
         <v>1262</v>
       </c>
       <c r="C112" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D112" t="s">
         <v>1263</v>
       </c>
       <c r="E112" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F112" t="s">
         <v>1264</v>
       </c>
       <c r="G112" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H112" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I112" t="s">
         <v>1265</v>
@@ -12276,7 +12272,7 @@
         <v>1271</v>
       </c>
       <c r="Q112" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R112" t="s">
         <v>1272</v>
@@ -12288,7 +12284,7 @@
         <v>1274</v>
       </c>
       <c r="U112" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V112"/>
     </row>
@@ -12300,22 +12296,22 @@
         <v>1275</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D113" t="s">
         <v>1276</v>
       </c>
       <c r="E113" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F113" t="s">
         <v>1277</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H113" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I113" t="s">
         <v>1278</v>
@@ -12342,7 +12338,7 @@
         <v>1284</v>
       </c>
       <c r="Q113" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R113" t="s">
         <v>1285</v>
@@ -12354,7 +12350,7 @@
         <v>1287</v>
       </c>
       <c r="U113" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V113"/>
     </row>
@@ -12366,22 +12362,22 @@
         <v>1288</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D114" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="E114" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F114" t="s">
         <v>1277</v>
       </c>
       <c r="G114" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H114" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I114" t="s">
         <v>1289</v>
@@ -12408,7 +12404,7 @@
         <v>1295</v>
       </c>
       <c r="Q114" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R114" t="s">
         <v>640</v>
@@ -12420,7 +12416,7 @@
         <v>642</v>
       </c>
       <c r="U114" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V114"/>
     </row>
@@ -12432,22 +12428,22 @@
         <v>1296</v>
       </c>
       <c r="C115" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D115" t="s">
         <v>303</v>
       </c>
       <c r="E115" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F115" t="s">
         <v>1297</v>
       </c>
       <c r="G115" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I115" t="s">
         <v>1298</v>
@@ -12474,7 +12470,7 @@
         <v>1304</v>
       </c>
       <c r="Q115" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R115" t="s">
         <v>1134</v>
@@ -12486,7 +12482,7 @@
         <v>1136</v>
       </c>
       <c r="U115" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V115"/>
     </row>
@@ -12498,22 +12494,22 @@
         <v>1305</v>
       </c>
       <c r="C116" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D116" t="s">
         <v>1306</v>
       </c>
       <c r="E116" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F116" t="s">
         <v>1297</v>
       </c>
       <c r="G116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H116" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I116" t="s">
         <v>1307</v>
@@ -12540,7 +12536,7 @@
         <v>1313</v>
       </c>
       <c r="Q116" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R116" t="s">
         <v>1314</v>
@@ -12552,7 +12548,7 @@
         <v>1316</v>
       </c>
       <c r="U116" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V116"/>
     </row>
@@ -12564,7 +12560,7 @@
         <v>1317</v>
       </c>
       <c r="C117" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D117" t="s">
         <v>1318</v>
@@ -12576,10 +12572,10 @@
         <v>1297</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H117" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I117" t="s">
         <v>1320</v>
@@ -12606,7 +12602,7 @@
         <v>1326</v>
       </c>
       <c r="Q117" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R117" t="s">
         <v>1327</v>
@@ -12618,7 +12614,7 @@
         <v>1329</v>
       </c>
       <c r="U117" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V117"/>
     </row>
@@ -12630,22 +12626,22 @@
         <v>1330</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D118" t="s">
         <v>265</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F118" t="s">
         <v>1297</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H118" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I118" t="s">
         <v>1331</v>
@@ -12672,7 +12668,7 @@
         <v>1337</v>
       </c>
       <c r="Q118" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R118" t="s">
         <v>1338</v>
@@ -12684,7 +12680,7 @@
         <v>1340</v>
       </c>
       <c r="U118" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V118"/>
     </row>
@@ -12696,22 +12692,22 @@
         <v>1341</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D119" t="s">
         <v>1306</v>
       </c>
       <c r="E119" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F119" t="s">
         <v>1297</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I119" t="s">
         <v>1342</v>
@@ -12738,7 +12734,7 @@
         <v>1348</v>
       </c>
       <c r="Q119" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R119" t="s">
         <v>1349</v>
@@ -12750,7 +12746,7 @@
         <v>1351</v>
       </c>
       <c r="U119" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V119"/>
     </row>
@@ -12762,22 +12758,22 @@
         <v>1352</v>
       </c>
       <c r="C120" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D120" t="s">
         <v>1008</v>
       </c>
       <c r="E120" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F120" t="s">
         <v>1297</v>
       </c>
       <c r="G120" t="s">
+        <v>26</v>
+      </c>
+      <c r="H120" t="s">
         <v>27</v>
-      </c>
-      <c r="H120" t="s">
-        <v>107</v>
       </c>
       <c r="I120" t="s">
         <v>1353</v>
@@ -12804,7 +12800,7 @@
         <v>1359</v>
       </c>
       <c r="Q120" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R120" t="s">
         <v>1360</v>
@@ -12816,7 +12812,7 @@
         <v>1362</v>
       </c>
       <c r="U120" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V120"/>
     </row>
@@ -12828,22 +12824,22 @@
         <v>1363</v>
       </c>
       <c r="C121" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D121" t="s">
         <v>1364</v>
       </c>
       <c r="E121" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F121" t="s">
         <v>1365</v>
       </c>
       <c r="G121" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" t="s">
         <v>27</v>
-      </c>
-      <c r="H121" t="s">
-        <v>107</v>
       </c>
       <c r="I121" t="s">
         <v>1366</v>
@@ -12870,7 +12866,7 @@
         <v>1372</v>
       </c>
       <c r="Q121" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R121" t="s">
         <v>685</v>
@@ -12882,7 +12878,7 @@
         <v>687</v>
       </c>
       <c r="U121" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V121"/>
     </row>
@@ -12894,22 +12890,22 @@
         <v>1373</v>
       </c>
       <c r="C122" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D122" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="E122" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F122" t="s">
         <v>1374</v>
       </c>
       <c r="G122" t="s">
+        <v>26</v>
+      </c>
+      <c r="H122" t="s">
         <v>27</v>
-      </c>
-      <c r="H122" t="s">
-        <v>107</v>
       </c>
       <c r="I122" t="s">
         <v>1375</v>
@@ -12936,7 +12932,7 @@
         <v>1381</v>
       </c>
       <c r="Q122" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R122" t="s">
         <v>261</v>
@@ -12948,7 +12944,7 @@
         <v>263</v>
       </c>
       <c r="U122" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V122"/>
     </row>
@@ -12960,22 +12956,22 @@
         <v>1382</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D123" t="s">
         <v>1383</v>
       </c>
       <c r="E123" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
         <v>1384</v>
       </c>
       <c r="G123" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H123" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I123" t="s">
         <v>1385</v>
@@ -13002,7 +12998,7 @@
         <v>1391</v>
       </c>
       <c r="Q123" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R123" t="s">
         <v>607</v>
@@ -13014,7 +13010,7 @@
         <v>609</v>
       </c>
       <c r="U123" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V123"/>
     </row>
@@ -13026,22 +13022,22 @@
         <v>1392</v>
       </c>
       <c r="C124" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="D124" t="s">
         <v>1393</v>
       </c>
       <c r="E124" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F124" t="s">
         <v>1394</v>
       </c>
       <c r="G124" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H124" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I124" t="s">
         <v>1395</v>
@@ -13068,7 +13064,7 @@
         <v>1401</v>
       </c>
       <c r="Q124" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R124" t="s">
         <v>1157</v>
@@ -13080,7 +13076,7 @@
         <v>1159</v>
       </c>
       <c r="U124" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V124"/>
     </row>
@@ -13098,16 +13094,16 @@
         <v>514</v>
       </c>
       <c r="E125" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F125" t="s">
         <v>1394</v>
       </c>
       <c r="G125" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H125" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I125" t="s">
         <v>1403</v>
@@ -13132,19 +13128,19 @@
         <v>1408</v>
       </c>
       <c r="Q125" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R125" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="S125" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="T125" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="U125" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V125"/>
     </row>
@@ -13159,19 +13155,19 @@
         <v>192</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E126" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F126" t="s">
         <v>1410</v>
       </c>
       <c r="G126" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H126" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I126" t="s">
         <v>1411</v>
@@ -13196,19 +13192,19 @@
         <v>1416</v>
       </c>
       <c r="Q126" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R126" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="S126" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="T126" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="U126" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V126"/>
     </row>
@@ -13220,7 +13216,7 @@
         <v>1417</v>
       </c>
       <c r="C127" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D127" t="s">
         <v>1418</v>
@@ -13230,10 +13226,10 @@
         <v>1419</v>
       </c>
       <c r="G127" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H127" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I127" t="s">
         <v>1420</v>
@@ -13260,7 +13256,7 @@
         <v>1426</v>
       </c>
       <c r="Q127" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R127" t="s">
         <v>1427</v>
@@ -13272,7 +13268,7 @@
         <v>1429</v>
       </c>
       <c r="U127" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V127"/>
     </row>
@@ -13284,22 +13280,22 @@
         <v>1430</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D128" t="s">
         <v>724</v>
       </c>
       <c r="E128" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F128" t="s">
         <v>1431</v>
       </c>
       <c r="G128" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H128" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I128" t="s">
         <v>1432</v>
@@ -13326,7 +13322,7 @@
         <v>1438</v>
       </c>
       <c r="Q128" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R128" t="s">
         <v>1439</v>
@@ -13338,7 +13334,7 @@
         <v>1441</v>
       </c>
       <c r="U128" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V128"/>
     </row>
@@ -13350,22 +13346,22 @@
         <v>1442</v>
       </c>
       <c r="C129" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D129" t="s">
         <v>549</v>
       </c>
       <c r="E129" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F129" t="s">
         <v>1431</v>
       </c>
       <c r="G129" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H129" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I129" t="s">
         <v>1443</v>
@@ -13392,7 +13388,7 @@
         <v>1449</v>
       </c>
       <c r="Q129" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R129" t="s">
         <v>1450</v>
@@ -13404,7 +13400,7 @@
         <v>1452</v>
       </c>
       <c r="U129" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V129"/>
     </row>
@@ -13416,19 +13412,19 @@
         <v>1453</v>
       </c>
       <c r="C130" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D130" t="s">
         <v>1454</v>
       </c>
       <c r="E130" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F130" t="s">
         <v>1455</v>
       </c>
       <c r="G130" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H130" t="s">
         <v>700</v>
@@ -13458,7 +13454,7 @@
         <v>1462</v>
       </c>
       <c r="Q130" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R130" t="s">
         <v>1463</v>
@@ -13470,7 +13466,7 @@
         <v>1465</v>
       </c>
       <c r="U130" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V130"/>
     </row>
@@ -13482,19 +13478,19 @@
         <v>1466</v>
       </c>
       <c r="C131" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D131" t="s">
         <v>854</v>
       </c>
       <c r="E131" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F131" t="s">
         <v>1455</v>
       </c>
       <c r="G131" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H131" t="s">
         <v>700</v>
@@ -13524,7 +13520,7 @@
         <v>1468</v>
       </c>
       <c r="Q131" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R131" t="s">
         <v>1469</v>
@@ -13536,7 +13532,7 @@
         <v>1471</v>
       </c>
       <c r="U131" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V131"/>
     </row>
@@ -13548,7 +13544,7 @@
         <v>1472</v>
       </c>
       <c r="C132" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D132" t="s">
         <v>1473</v>
@@ -13560,10 +13556,10 @@
         <v>1474</v>
       </c>
       <c r="G132" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H132" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I132" t="s">
         <v>1475</v>
@@ -13590,7 +13586,7 @@
         <v>1481</v>
       </c>
       <c r="Q132" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R132" t="s">
         <v>479</v>
@@ -13602,7 +13598,7 @@
         <v>481</v>
       </c>
       <c r="U132" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V132"/>
     </row>
@@ -13614,22 +13610,22 @@
         <v>1482</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E133" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F133" t="s">
         <v>1483</v>
       </c>
       <c r="G133" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H133" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I133" t="s">
         <v>1484</v>
@@ -13656,7 +13652,7 @@
         <v>1490</v>
       </c>
       <c r="Q133" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R133" t="s">
         <v>1491</v>
@@ -13668,7 +13664,7 @@
         <v>1493</v>
       </c>
       <c r="U133" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V133"/>
     </row>
@@ -13680,22 +13676,22 @@
         <v>1494</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D134" t="s">
         <v>514</v>
       </c>
       <c r="E134" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F134" t="s">
         <v>1495</v>
       </c>
       <c r="G134" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H134" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I134" t="s">
         <v>1496</v>
@@ -13722,7 +13718,7 @@
         <v>1502</v>
       </c>
       <c r="Q134" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R134" t="s">
         <v>1503</v>
@@ -13734,7 +13730,7 @@
         <v>1505</v>
       </c>
       <c r="U134" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V134"/>
     </row>
@@ -13752,16 +13748,16 @@
         <v>1507</v>
       </c>
       <c r="E135" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F135" t="s">
         <v>1495</v>
       </c>
       <c r="G135" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H135" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I135" t="s">
         <v>1508</v>
@@ -13786,7 +13782,7 @@
         <v>1513</v>
       </c>
       <c r="Q135" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R135" t="s">
         <v>1503</v>
@@ -13798,7 +13794,7 @@
         <v>1505</v>
       </c>
       <c r="U135" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V135"/>
     </row>
@@ -13816,16 +13812,16 @@
         <v>1507</v>
       </c>
       <c r="E136" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F136" t="s">
         <v>1495</v>
       </c>
       <c r="G136" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H136" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I136" t="s">
         <v>1515</v>
@@ -13850,7 +13846,7 @@
         <v>1520</v>
       </c>
       <c r="Q136" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R136" t="s">
         <v>1503</v>
@@ -13862,7 +13858,7 @@
         <v>1505</v>
       </c>
       <c r="U136" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V136"/>
     </row>
@@ -13886,10 +13882,10 @@
         <v>1523</v>
       </c>
       <c r="G137" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H137" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="I137" t="s">
         <v>1524</v>
@@ -13914,7 +13910,7 @@
         <v>1529</v>
       </c>
       <c r="Q137" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="R137" t="s">
         <v>479</v>
@@ -13926,7 +13922,7 @@
         <v>481</v>
       </c>
       <c r="U137" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V137"/>
     </row>
@@ -13944,16 +13940,16 @@
         <v>1306</v>
       </c>
       <c r="E138" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F138" t="s">
         <v>1531</v>
       </c>
       <c r="G138" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I138" t="s">
         <v>1532</v>
@@ -13978,7 +13974,7 @@
         <v>1537</v>
       </c>
       <c r="Q138" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="R138" t="s">
         <v>1538</v>
@@ -13990,7 +13986,7 @@
         <v>1540</v>
       </c>
       <c r="U138" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V138"/>
     </row>
@@ -14013,7 +14009,7 @@
       </c>
       <c r="G139"/>
       <c r="H139" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I139" t="s">
         <v>1543</v>
@@ -14040,7 +14036,7 @@
         <v>1549</v>
       </c>
       <c r="Q139" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="R139" t="s">
         <v>1550</v>
@@ -14052,7 +14048,7 @@
         <v>1552</v>
       </c>
       <c r="U139" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="V139"/>
     </row>

--- a/Objets_parlementaires_Jura.xlsx
+++ b/Objets_parlementaires_Jura.xlsx
@@ -185,18 +185,57 @@
     <t xml:space="preserve">Economia|Questioni sociali|Media e comunicazione|Salute</t>
   </si>
   <si>
+    <t xml:space="preserve">26.3454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stettler Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verbesserte Lebensqualität dank den Umfahrungsprojekten entlang der N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualité de vie améliorée grâce aux projets de contournement de la N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migliore qualità di vita grazie ai progetti di circonvallazione sulla N18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les lignes directrices de «&amp;nbsp;&lt;i&gt;Transports ’45&amp;nbsp;»&lt;/i&gt;. Selon ces derniers, les projets routiers prévus le long de la route nationale 18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufon (horizon 2055) – devraient être reportés à une période postérieure à 2055. Cette perspective suscite une vive incompréhension dans la région. Elle équivaut en effet à renoncer, pour plusieurs décennies, à une amélioration de l’accessibilité et, par conséquent, à de réelles perspectives de développement économique. Elle contredit en outre directement les résultats de l’étude de corridor N18, menée sous la conduite de l’OFROU selon les méthodes les plus récentes et soutenue par un large partenariat.&lt;/p&gt;&lt;p&gt;La N18 constitue un maillon essentiel du réseau routier national. Elle relie l’agglomération bâloise à l’Arc lémanique et dessert le Laufonnais, en plein essor, ainsi que Delémont, chef-lieu cantonal. En raison de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, présentant l’une des charges de trafic et densités de bouchons les plus élevées du pays. La situation actuelle affecte par ailleurs fortement la qualité de vie dans les centres des localités et compromet la sécurité du trafic motorisé et cycliste. La population souffre quotidiennement des embouteillages et du trafic intense des poids lourds traversant les localités, comme en témoignent les nombreux participants aux forums de la mobilité de Laufon. Une évolution rapide du corridor apparaît dès lors indispensable.&lt;/p&gt;&lt;p&gt;Dans ce contexte, le Conseil fédéral est prié de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il les effets du trafic de transit – en particulier des poids lourds – sur le développement du milieu bâti ainsi que sur la qualité de séjour et d’habitation à Delémont, Laufon et Zwingen ?&lt;/li&gt;&lt;li&gt;Considère-t-il les projets de contournement Laufon–Zwingen et Delémont comme des mesures appropriées pour réduire les nuisances dans les zones urbanisées concernées ?&lt;/li&gt;&lt;li&gt;Estime-t-il nécessaires des mesures visant à améliorer la desserte des zones d’emplois à Delémont ainsi que dans le Laufonnais ?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 veröffentlichte der Bundesrat die Eckwerte von &lt;i&gt;«Verkehr ’45»&lt;/i&gt;. Die geplanten Strassenbauprojekte entlang der Nationalstrasse 18 zwischen Basel und Delsberg – mit Ausnahme der Entlastung des Zentrums von Laufen (bis 2055) – sollen auf einen Zeitpunkt nach 2055 verschoben werden. Diese Aussichten stossen in der Region auf grosses Unverständnis. Der Entscheid bedeutet nämlich, dass für mehrere Jahrzehnte auf eine Verbesserung der Erreichbarkeit und damit auf echte Perspektiven für die wirtschaftliche Entwicklung verzichtet wird. Zudem steht er in direktem Widerspruch zu den Ergebnissen der Korridorstudie N18, die unter der Leitung des ASTRA nach den neuesten Methoden durchgeführt und von einer breiten Partnerschaft unterstützt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein wesentlicher Abschnitt des nationalen Strassennetzes. Sie verbindet den Grossraum Basel mit der Genferseeregion und bedient das aufstrebende Laufental sowie die Kantonshauptstadt Delsberg. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zu einem Engpass und weist eine der höchsten Verkehrsbelastungen und Staudichten des Landes auf. Die derzeitige Situation beeinträchtigt zudem erheblich die Lebensqualität in den Ortskernen und gefährdet die Sicherheit des motorisierten Verkers und des Veloverkehrs. Die Bevölkerung leidet täglich unter den Staus und dem starken Lastwagenverkehr, der durch die Ortschaften rollt, wie die zahlreichen Teilnehmer und Teilnehmerinnen der Mobilitätsforen in Laufen bezeugen. Eine rasche Weiterentwicklung des Korridors erscheint daher unerlässlich.&lt;/p&gt;&lt;p&gt;Vor diesem Hintergrund bitte ich den Bundesrat um die Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie bewertet er die Auswirkungen des Transitverkehrs – insbesondere des Schwerverkehrs – auf die Siedlungsentwicklung sowie auf die Lebens- und Wohnqualität in Delsberg, Laufen und Zwingen?&lt;/li&gt;&lt;li&gt;Erachtet er die Umfahrungsprojekte Laufen–Zwingen und Delsberg als geeignete Massnahmen zur Verringerung der Belastungen in den betroffenen Siedlungsgebieten?&lt;/li&gt;&lt;li&gt;Hält er Massnahmen zur Verbesserung der Verkehrsanbindung der Arbeitszonen in Delsberg sowie im Laufental für notwendig?&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trasporti</t>
+  </si>
+  <si>
     <t xml:space="preserve">26.3192</t>
   </si>
   <si>
-    <t xml:space="preserve">Ip.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aeschi Thomas</t>
   </si>
   <si>
-    <t xml:space="preserve">UDC</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-03-18</t>
   </si>
   <si>
@@ -332,9 +371,6 @@
     <t xml:space="preserve">26.3121</t>
   </si>
   <si>
-    <t xml:space="preserve">UVEK</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dank einer leistungsfähigen Nationalstrasse 18 Kultur- und Wirtschaftsräume effektiv miteinander verbinden</t>
   </si>
   <si>
@@ -395,15 +431,6 @@
     <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263069</t>
   </si>
   <si>
-    <t xml:space="preserve">Verkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trasporti</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.4774</t>
   </si>
   <si>
@@ -444,33 +471,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026-04-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stettler Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbesserte Lebensqualität dank den Umfahrungsprojekten entlang der N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualité de vie améliorée grâce aux projets de contournement de la N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migliore qualità di vita grazie ai progetti di circonvallazione sulla N18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Fin janvier 2026, le Conseil fédéral a publié les lignes directrices de «&amp;nbsp;&lt;i&gt;Transports ’45&amp;nbsp;»&lt;/i&gt;. Selon ces derniers, les projets routiers prévus le long de la route nationale 18 entre Bâle et Delémont – à l’exception de la décharge du centre de Laufon (horizon 2055) – devraient être reportés à une période postérieure à 2055. Cette perspective suscite une vive incompréhension dans la région. Elle équivaut en effet à renoncer, pour plusieurs décennies, à une amélioration de l’accessibilité et, par conséquent, à de réelles perspectives de développement économique. Elle contredit en outre directement les résultats de l’étude de corridor N18, menée sous la conduite de l’OFROU selon les méthodes les plus récentes et soutenue par un large partenariat.&lt;/p&gt;&lt;p&gt;La N18 constitue un maillon essentiel du réseau routier national. Elle relie l’agglomération bâloise à l’Arc lémanique et dessert le Laufonnais, en plein essor, ainsi que Delémont, chef-lieu cantonal. En raison de la croissance démographique, ce tronçon devient toutefois un goulet d’étranglement, présentant l’une des charges de trafic et densités de bouchons les plus élevées du pays. La situation actuelle affecte par ailleurs fortement la qualité de vie dans les centres des localités et compromet la sécurité du trafic motorisé et cycliste. La population souffre quotidiennement des embouteillages et du trafic intense des poids lourds traversant les localités, comme en témoignent les nombreux participants aux forums de la mobilité de Laufon. Une évolution rapide du corridor apparaît dès lors indispensable.&lt;/p&gt;&lt;p&gt;Dans ce contexte, le Conseil fédéral est prié de répondre aux questions suivantes :&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Comment évalue-t-il les effets du trafic de transit – en particulier des poids lourds – sur le développement du milieu bâti ainsi que sur la qualité de séjour et d’habitation à Delémont, Laufon et Zwingen ?&lt;/li&gt;&lt;li&gt;Considère-t-il les projets de contournement Laufon–Zwingen et Delémont comme des mesures appropriées pour réduire les nuisances dans les zones urbanisées concernées ?&lt;/li&gt;&lt;li&gt;Estime-t-il nécessaires des mesures visant à améliorer la desserte des zones d’emplois à Delémont ainsi que dans le Laufonnais ?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Ende Januar 2026 veröffentlichte der Bundesrat die Eckwerte von &lt;i&gt;«Verkehr ’45»&lt;/i&gt;. Die geplanten Strassenbauprojekte entlang der Nationalstrasse 18 zwischen Basel und Delsberg – mit Ausnahme der Entlastung des Zentrums von Laufen (bis 2055) – sollen auf einen Zeitpunkt nach 2055 verschoben werden. Diese Aussichten stossen in der Region auf grosses Unverständnis. Der Entscheid bedeutet nämlich, dass für mehrere Jahrzehnte auf eine Verbesserung der Erreichbarkeit und damit auf echte Perspektiven für die wirtschaftliche Entwicklung verzichtet wird. Zudem steht er in direktem Widerspruch zu den Ergebnissen der Korridorstudie N18, die unter der Leitung des ASTRA nach den neuesten Methoden durchgeführt und von einer breiten Partnerschaft unterstützt wurde.&lt;/p&gt;&lt;p&gt;Die N18 ist ein wesentlicher Abschnitt des nationalen Strassennetzes. Sie verbindet den Grossraum Basel mit der Genferseeregion und bedient das aufstrebende Laufental sowie die Kantonshauptstadt Delsberg. Aufgrund des Bevölkerungswachstums entwickelt sich dieser Abschnitt jedoch zu einem Engpass und weist eine der höchsten Verkehrsbelastungen und Staudichten des Landes auf. Die derzeitige Situation beeinträchtigt zudem erheblich die Lebensqualität in den Ortskernen und gefährdet die Sicherheit des motorisierten Verkers und des Veloverkehrs. Die Bevölkerung leidet täglich unter den Staus und dem starken Lastwagenverkehr, der durch die Ortschaften rollt, wie die zahlreichen Teilnehmer und Teilnehmerinnen der Mobilitätsforen in Laufen bezeugen. Eine rasche Weiterentwicklung des Korridors erscheint daher unerlässlich.&lt;/p&gt;&lt;p&gt;Vor diesem Hintergrund bitte ich den Bundesrat um die Beantwortung der folgenden Fragen:&lt;/p&gt;&lt;ol style="list-style-type:decimal;"&gt;&lt;li&gt;Wie bewertet er die Auswirkungen des Transitverkehrs – insbesondere des Schwerverkehrs – auf die Siedlungsentwicklung sowie auf die Lebens- und Wohnqualität in Delsberg, Laufen und Zwingen?&lt;/li&gt;&lt;li&gt;Erachtet er die Umfahrungsprojekte Laufen–Zwingen und Delsberg als geeignete Massnahmen zur Verringerung der Belastungen in den betroffenen Siedlungsgebieten?&lt;/li&gt;&lt;li&gt;Hält er Massnahmen zur Verbesserung der Verkehrsanbindung der Arbeitszonen in Delsberg sowie im Laufental für notwendig?&lt;/li&gt;&lt;/ol&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/de/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.parlament.ch/fr/ratsbetrieb/suche-curia-vista/geschaeft?AffairId=20263454</t>
   </si>
   <si>
     <t xml:space="preserve">26.3228</t>
@@ -5230,7 +5230,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20263192</v>
+        <v>20263454</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5245,49 +5245,49 @@
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
       <c r="H4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" t="s">
         <v>62</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>63</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>64</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>65</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>66</v>
-      </c>
-      <c r="M4" t="s">
-        <v>67</v>
       </c>
       <c r="N4" t="s">
         <v>33</v>
       </c>
       <c r="O4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" t="s">
         <v>68</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="S4" t="s">
         <v>70</v>
       </c>
-      <c r="R4" t="s">
+      <c r="T4" t="s">
         <v>71</v>
-      </c>
-      <c r="S4" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" t="s">
-        <v>73</v>
       </c>
       <c r="U4" t="s">
         <v>40</v>
@@ -5296,64 +5296,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20263099</v>
+        <v>20263192</v>
       </c>
       <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
         <v>74</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
         <v>75</v>
       </c>
-      <c r="D5" t="s">
+      <c r="I5" t="s">
         <v>76</v>
       </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>77</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
         <v>78</v>
       </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="L5" t="s">
         <v>79</v>
       </c>
-      <c r="I5" t="s">
+      <c r="M5" t="s">
         <v>80</v>
-      </c>
-      <c r="J5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" t="s">
-        <v>83</v>
-      </c>
-      <c r="M5" t="s">
-        <v>84</v>
       </c>
       <c r="N5" t="s">
         <v>33</v>
       </c>
       <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" t="s">
+        <v>84</v>
+      </c>
+      <c r="S5" t="s">
         <v>85</v>
       </c>
-      <c r="P5" t="s">
+      <c r="T5" t="s">
         <v>86</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>53</v>
-      </c>
-      <c r="R5" t="s">
-        <v>87</v>
-      </c>
-      <c r="S5" t="s">
-        <v>88</v>
-      </c>
-      <c r="T5" t="s">
-        <v>89</v>
       </c>
       <c r="U5" t="s">
         <v>40</v>
@@ -5362,28 +5362,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20263120</v>
+        <v>20263099</v>
       </c>
       <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>91</v>
       </c>
-      <c r="E6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
         <v>92</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>45</v>
       </c>
       <c r="I6" t="s">
         <v>93</v>
@@ -5410,73 +5410,73 @@
         <v>99</v>
       </c>
       <c r="Q6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R6" t="s">
         <v>100</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>101</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>102</v>
       </c>
-      <c r="T6" t="s">
-        <v>103</v>
-      </c>
       <c r="U6" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="V6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20263121</v>
+        <v>20263120</v>
       </c>
       <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
         <v>105</v>
       </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" t="s">
-        <v>92</v>
-      </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
         <v>106</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>107</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>108</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>109</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>110</v>
-      </c>
-      <c r="M7" t="s">
-        <v>111</v>
       </c>
       <c r="N7" t="s">
         <v>33</v>
       </c>
       <c r="O7" t="s">
+        <v>111</v>
+      </c>
+      <c r="P7" t="s">
         <v>112</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>113</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>53</v>
       </c>
       <c r="R7" t="s">
         <v>114</v>
@@ -5488,100 +5488,100 @@
         <v>116</v>
       </c>
       <c r="U7" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="V7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20263069</v>
+        <v>20263121</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" t="s">
         <v>119</v>
       </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>120</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>121</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>122</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>123</v>
-      </c>
-      <c r="M8" t="s">
-        <v>124</v>
       </c>
       <c r="N8" t="s">
         <v>33</v>
       </c>
       <c r="O8" t="s">
+        <v>124</v>
+      </c>
+      <c r="P8" t="s">
         <v>125</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" t="s">
         <v>126</v>
       </c>
-      <c r="Q8" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>127</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>128</v>
       </c>
-      <c r="T8" t="s">
-        <v>129</v>
-      </c>
       <c r="U8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="V8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20254774</v>
+        <v>20263069</v>
       </c>
       <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
         <v>130</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>76</v>
-      </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
         <v>131</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
         <v>132</v>
@@ -5599,98 +5599,96 @@
         <v>136</v>
       </c>
       <c r="N9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" t="s">
         <v>137</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>138</v>
       </c>
-      <c r="P9" t="s">
-        <v>139</v>
-      </c>
       <c r="Q9" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="S9" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="T9" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="U9" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="V9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20263454</v>
+        <v>20254774</v>
       </c>
       <c r="B10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" t="s">
+        <v>143</v>
+      </c>
+      <c r="L10" t="s">
         <v>144</v>
       </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="M10" t="s">
         <v>145</v>
       </c>
-      <c r="E10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="N10" t="s">
         <v>146</v>
       </c>
-      <c r="J10" t="s">
+      <c r="O10" t="s">
         <v>147</v>
       </c>
-      <c r="K10" t="s">
+      <c r="P10" t="s">
         <v>148</v>
-      </c>
-      <c r="L10" t="s">
-        <v>149</v>
-      </c>
-      <c r="M10" t="s">
-        <v>150</v>
-      </c>
-      <c r="N10" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" t="s">
-        <v>151</v>
-      </c>
-      <c r="P10" t="s">
-        <v>152</v>
       </c>
       <c r="Q10" t="s">
         <v>53</v>
       </c>
       <c r="R10" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="S10" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="T10" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="U10" t="s">
-        <v>40</v>
-      </c>
-      <c r="V10" t="s">
-        <v>40</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="V10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5715,7 +5713,7 @@
         <v>26</v>
       </c>
       <c r="H11" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
         <v>156</v>
@@ -5742,16 +5740,16 @@
         <v>163</v>
       </c>
       <c r="Q11" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="S11" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="T11" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="U11" t="s">
         <v>164</v>
@@ -5808,7 +5806,7 @@
         <v>175</v>
       </c>
       <c r="Q12" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R12" t="s">
         <v>176</v>
@@ -5839,13 +5837,13 @@
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s">
         <v>181</v>
@@ -5872,7 +5870,7 @@
         <v>187</v>
       </c>
       <c r="Q13" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R13" t="s">
         <v>188</v>
@@ -5969,13 +5967,13 @@
         <v>207</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G15" t="s">
         <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
         <v>208</v>
@@ -6000,7 +5998,7 @@
         <v>213</v>
       </c>
       <c r="Q15" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R15" t="s">
         <v>214</v>
@@ -6033,7 +6031,7 @@
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
         <v>220</v>
@@ -6059,13 +6057,13 @@
         <v>53</v>
       </c>
       <c r="R16" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S16" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="T16" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U16" t="s">
         <v>164</v>
@@ -6120,7 +6118,7 @@
         <v>234</v>
       </c>
       <c r="Q17" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R17" t="s">
         <v>235</v>
@@ -6184,7 +6182,7 @@
         <v>247</v>
       </c>
       <c r="Q18" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R18" t="s">
         <v>248</v>
@@ -6217,7 +6215,7 @@
         <v>253</v>
       </c>
       <c r="F19" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
@@ -6283,13 +6281,13 @@
         <v>60</v>
       </c>
       <c r="F20" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
         <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I20" t="s">
         <v>266</v>
@@ -6316,7 +6314,7 @@
         <v>272</v>
       </c>
       <c r="Q20" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R20" t="s">
         <v>273</v>
@@ -6343,10 +6341,10 @@
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
         <v>277</v>
@@ -6406,13 +6404,13 @@
         <v>290</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
         <v>277</v>
@@ -6421,7 +6419,7 @@
         <v>44</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s">
         <v>291</v>
@@ -6478,7 +6476,7 @@
         <v>303</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
         <v>304</v>
@@ -6514,7 +6512,7 @@
         <v>311</v>
       </c>
       <c r="Q23" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R23" t="s">
         <v>312</v>
@@ -6541,7 +6539,7 @@
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
         <v>60</v>
@@ -6580,7 +6578,7 @@
         <v>323</v>
       </c>
       <c r="Q24" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R24" t="s">
         <v>248</v>
@@ -6710,7 +6708,7 @@
         <v>343</v>
       </c>
       <c r="Q26" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R26" t="s">
         <v>344</v>
@@ -6737,7 +6735,7 @@
         <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s">
         <v>60</v>
@@ -6749,7 +6747,7 @@
         <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s">
         <v>348</v>
@@ -6774,7 +6772,7 @@
         <v>353</v>
       </c>
       <c r="Q27" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R27" t="s">
         <v>188</v>
@@ -6798,7 +6796,7 @@
         <v>354</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>355</v>
@@ -6838,7 +6836,7 @@
         <v>363</v>
       </c>
       <c r="Q28" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R28" t="s">
         <v>364</v>
@@ -6904,7 +6902,7 @@
         <v>376</v>
       </c>
       <c r="Q29" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R29" t="s">
         <v>377</v>
@@ -6928,7 +6926,7 @@
         <v>380</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
         <v>381</v>
@@ -6970,16 +6968,16 @@
         <v>388</v>
       </c>
       <c r="Q30" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R30" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S30" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="T30" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U30" t="s">
         <v>164</v>
@@ -7009,7 +7007,7 @@
         <v>26</v>
       </c>
       <c r="H31" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I31" t="s">
         <v>390</v>
@@ -7039,13 +7037,13 @@
         <v>36</v>
       </c>
       <c r="R31" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="S31" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="T31" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="U31" t="s">
         <v>164</v>
@@ -7132,7 +7130,7 @@
         <v>409</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F33" t="s">
         <v>410</v>
@@ -7195,10 +7193,10 @@
         <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
         <v>419</v>
@@ -7300,7 +7298,7 @@
         <v>438</v>
       </c>
       <c r="Q35" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R35" t="s">
         <v>439</v>
@@ -7330,7 +7328,7 @@
         <v>443</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F36" t="s">
         <v>444</v>
@@ -7393,7 +7391,7 @@
         <v>456</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
         <v>60</v>
@@ -7471,7 +7469,7 @@
         <v>26</v>
       </c>
       <c r="H38" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
         <v>472</v>
@@ -7498,7 +7496,7 @@
         <v>478</v>
       </c>
       <c r="Q38" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R38" t="s">
         <v>479</v>
@@ -7592,7 +7590,7 @@
         <v>492</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F40" t="s">
         <v>471</v>
@@ -7626,7 +7624,7 @@
         <v>498</v>
       </c>
       <c r="Q40" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R40" t="s">
         <v>499</v>
@@ -7665,7 +7663,7 @@
         <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s">
         <v>504</v>
@@ -7756,7 +7754,7 @@
         <v>522</v>
       </c>
       <c r="Q42" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R42" t="s">
         <v>523</v>
@@ -7820,7 +7818,7 @@
         <v>532</v>
       </c>
       <c r="Q43" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R43" t="s">
         <v>533</v>
@@ -7882,7 +7880,7 @@
         <v>547</v>
       </c>
       <c r="Q44" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R44"/>
       <c r="S44"/>
@@ -7915,7 +7913,7 @@
         <v>26</v>
       </c>
       <c r="H45" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I45" t="s">
         <v>551</v>
@@ -7942,7 +7940,7 @@
         <v>557</v>
       </c>
       <c r="Q45" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R45" t="s">
         <v>558</v>
@@ -7981,7 +7979,7 @@
         <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I46" t="s">
         <v>563</v>
@@ -8008,7 +8006,7 @@
         <v>569</v>
       </c>
       <c r="Q46" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R46" t="s">
         <v>570</v>
@@ -8032,13 +8030,13 @@
         <v>573</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D47" t="s">
         <v>574</v>
       </c>
       <c r="E47" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F47" t="s">
         <v>550</v>
@@ -8074,7 +8072,7 @@
         <v>582</v>
       </c>
       <c r="Q47" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R47" t="s">
         <v>583</v>
@@ -8204,7 +8202,7 @@
         <v>606</v>
       </c>
       <c r="Q49" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R49" t="s">
         <v>607</v>
@@ -8243,7 +8241,7 @@
         <v>26</v>
       </c>
       <c r="H50" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I50" t="s">
         <v>613</v>
@@ -8273,13 +8271,13 @@
         <v>36</v>
       </c>
       <c r="R50" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="S50" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="T50" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="U50" t="s">
         <v>164</v>
@@ -8294,7 +8292,7 @@
         <v>620</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D51" t="s">
         <v>621</v>
@@ -8307,7 +8305,7 @@
         <v>26</v>
       </c>
       <c r="H51" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I51" t="s">
         <v>622</v>
@@ -8334,7 +8332,7 @@
         <v>628</v>
       </c>
       <c r="Q51" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R51" t="s">
         <v>629</v>
@@ -8373,7 +8371,7 @@
         <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I52" t="s">
         <v>633</v>
@@ -8439,7 +8437,7 @@
         <v>44</v>
       </c>
       <c r="H53" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I53" t="s">
         <v>646</v>
@@ -8466,7 +8464,7 @@
         <v>652</v>
       </c>
       <c r="Q53" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R53" t="s">
         <v>558</v>
@@ -8505,7 +8503,7 @@
         <v>26</v>
       </c>
       <c r="H54" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I54" t="s">
         <v>656</v>
@@ -8532,16 +8530,16 @@
         <v>662</v>
       </c>
       <c r="Q54" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R54" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="S54" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="T54" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="U54" t="s">
         <v>164</v>
@@ -8598,7 +8596,7 @@
         <v>673</v>
       </c>
       <c r="Q55" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R55" t="s">
         <v>674</v>
@@ -8752,13 +8750,13 @@
         <v>697</v>
       </c>
       <c r="C58" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D58" t="s">
         <v>698</v>
       </c>
       <c r="E58" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F58" t="s">
         <v>699</v>
@@ -8794,7 +8792,7 @@
         <v>707</v>
       </c>
       <c r="Q58" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R58" t="s">
         <v>708</v>
@@ -8824,7 +8822,7 @@
         <v>712</v>
       </c>
       <c r="E59" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F59" t="s">
         <v>699</v>
@@ -8860,7 +8858,7 @@
         <v>719</v>
       </c>
       <c r="Q59" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R59" t="s">
         <v>720</v>
@@ -8899,7 +8897,7 @@
         <v>26</v>
       </c>
       <c r="H60" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I60" t="s">
         <v>725</v>
@@ -8926,7 +8924,7 @@
         <v>731</v>
       </c>
       <c r="Q60" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R60" t="s">
         <v>479</v>
@@ -8956,7 +8954,7 @@
         <v>733</v>
       </c>
       <c r="E61" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F61" t="s">
         <v>734</v>
@@ -9019,10 +9017,10 @@
         <v>23</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F62" t="s">
         <v>734</v>
@@ -9088,7 +9086,7 @@
         <v>303</v>
       </c>
       <c r="E63" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
         <v>754</v>
@@ -9097,7 +9095,7 @@
         <v>44</v>
       </c>
       <c r="H63" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I63" t="s">
         <v>755</v>
@@ -9124,7 +9122,7 @@
         <v>761</v>
       </c>
       <c r="Q63" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R63" t="s">
         <v>762</v>
@@ -9190,7 +9188,7 @@
         <v>773</v>
       </c>
       <c r="Q64" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R64" t="s">
         <v>774</v>
@@ -9225,7 +9223,7 @@
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I65" t="s">
         <v>780</v>
@@ -9243,7 +9241,7 @@
         <v>784</v>
       </c>
       <c r="N65" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O65" t="s">
         <v>785</v>
@@ -9252,7 +9250,7 @@
         <v>786</v>
       </c>
       <c r="Q65" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R65"/>
       <c r="S65"/>
@@ -9281,7 +9279,7 @@
       </c>
       <c r="G66"/>
       <c r="H66" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I66" t="s">
         <v>541</v>
@@ -9308,7 +9306,7 @@
         <v>793</v>
       </c>
       <c r="Q66" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R66"/>
       <c r="S66"/>
@@ -9339,7 +9337,7 @@
         <v>44</v>
       </c>
       <c r="H67" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I67" t="s">
         <v>797</v>
@@ -9357,7 +9355,7 @@
         <v>801</v>
       </c>
       <c r="N67" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O67" t="s">
         <v>802</v>
@@ -9366,7 +9364,7 @@
         <v>803</v>
       </c>
       <c r="Q67" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R67" t="s">
         <v>804</v>
@@ -9405,7 +9403,7 @@
         <v>26</v>
       </c>
       <c r="H68" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I68" t="s">
         <v>809</v>
@@ -9432,7 +9430,7 @@
         <v>815</v>
       </c>
       <c r="Q68" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R68" t="s">
         <v>816</v>
@@ -9528,7 +9526,7 @@
         <v>831</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F70" t="s">
         <v>808</v>
@@ -9537,7 +9535,7 @@
         <v>26</v>
       </c>
       <c r="H70" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I70" t="s">
         <v>832</v>
@@ -9564,7 +9562,7 @@
         <v>838</v>
       </c>
       <c r="Q70" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R70" t="s">
         <v>839</v>
@@ -9669,7 +9667,7 @@
         <v>26</v>
       </c>
       <c r="H72" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I72" t="s">
         <v>855</v>
@@ -9696,7 +9694,7 @@
         <v>861</v>
       </c>
       <c r="Q72" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R72" t="s">
         <v>862</v>
@@ -9792,7 +9790,7 @@
         <v>492</v>
       </c>
       <c r="E74" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>878</v>
@@ -9801,7 +9799,7 @@
         <v>26</v>
       </c>
       <c r="H74" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I74" t="s">
         <v>879</v>
@@ -9828,7 +9826,7 @@
         <v>885</v>
       </c>
       <c r="Q74" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R74" t="s">
         <v>886</v>
@@ -9867,7 +9865,7 @@
         <v>26</v>
       </c>
       <c r="H75" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I75" t="s">
         <v>891</v>
@@ -9894,7 +9892,7 @@
         <v>897</v>
       </c>
       <c r="Q75" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R75" t="s">
         <v>898</v>
@@ -9929,7 +9927,7 @@
       </c>
       <c r="G76"/>
       <c r="H76" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I76" t="s">
         <v>903</v>
@@ -9956,7 +9954,7 @@
         <v>910</v>
       </c>
       <c r="Q76" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R76"/>
       <c r="S76"/>
@@ -9977,7 +9975,7 @@
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="E77" t="s">
         <v>60</v>
@@ -10016,7 +10014,7 @@
         <v>918</v>
       </c>
       <c r="Q77" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R77" t="s">
         <v>377</v>
@@ -10055,7 +10053,7 @@
         <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I78" t="s">
         <v>922</v>
@@ -10080,7 +10078,7 @@
         <v>927</v>
       </c>
       <c r="Q78" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R78" t="s">
         <v>928</v>
@@ -10119,7 +10117,7 @@
         <v>26</v>
       </c>
       <c r="H79" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I79" t="s">
         <v>934</v>
@@ -10144,7 +10142,7 @@
         <v>939</v>
       </c>
       <c r="Q79" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R79" t="s">
         <v>816</v>
@@ -10177,7 +10175,7 @@
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I80" t="s">
         <v>942</v>
@@ -10253,7 +10251,7 @@
         <v>956</v>
       </c>
       <c r="N81" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O81" t="s">
         <v>957</v>
@@ -10262,7 +10260,7 @@
         <v>958</v>
       </c>
       <c r="Q81" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R81" t="s">
         <v>959</v>
@@ -10297,7 +10295,7 @@
       </c>
       <c r="G82"/>
       <c r="H82" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I82" t="s">
         <v>963</v>
@@ -10324,7 +10322,7 @@
         <v>969</v>
       </c>
       <c r="Q82" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R82" t="s">
         <v>970</v>
@@ -10390,7 +10388,7 @@
         <v>981</v>
       </c>
       <c r="Q83" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R83" t="s">
         <v>982</v>
@@ -10420,7 +10418,7 @@
         <v>986</v>
       </c>
       <c r="E84" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F84" t="s">
         <v>987</v>
@@ -10456,7 +10454,7 @@
         <v>994</v>
       </c>
       <c r="Q84" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R84" t="s">
         <v>995</v>
@@ -10495,7 +10493,7 @@
         <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I85" t="s">
         <v>1000</v>
@@ -10522,7 +10520,7 @@
         <v>1006</v>
       </c>
       <c r="Q85" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R85" t="s">
         <v>640</v>
@@ -10618,7 +10616,7 @@
         <v>1020</v>
       </c>
       <c r="E87" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F87" t="s">
         <v>987</v>
@@ -10720,7 +10718,7 @@
         <v>1037</v>
       </c>
       <c r="Q88" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R88" t="s">
         <v>344</v>
@@ -10759,7 +10757,7 @@
         <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I89" t="s">
         <v>1040</v>
@@ -10787,13 +10785,13 @@
         <v>36</v>
       </c>
       <c r="R89" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S89" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="T89" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U89" t="s">
         <v>164</v>
@@ -10823,7 +10821,7 @@
         <v>26</v>
       </c>
       <c r="H90" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I90" t="s">
         <v>1048</v>
@@ -10853,13 +10851,13 @@
         <v>36</v>
       </c>
       <c r="R90" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="S90" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="T90" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="U90" t="s">
         <v>164</v>
@@ -10880,7 +10878,7 @@
         <v>1020</v>
       </c>
       <c r="E91" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F91" t="s">
         <v>1056</v>
@@ -10889,7 +10887,7 @@
         <v>26</v>
       </c>
       <c r="H91" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I91" t="s">
         <v>1057</v>
@@ -10914,7 +10912,7 @@
         <v>1062</v>
       </c>
       <c r="Q91" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R91" t="s">
         <v>479</v>
@@ -10953,7 +10951,7 @@
         <v>26</v>
       </c>
       <c r="H92" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I92" t="s">
         <v>1064</v>
@@ -10981,13 +10979,13 @@
         <v>36</v>
       </c>
       <c r="R92" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S92" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="T92" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U92" t="s">
         <v>164</v>
@@ -11017,7 +11015,7 @@
         <v>26</v>
       </c>
       <c r="H93" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s">
         <v>1064</v>
@@ -11045,13 +11043,13 @@
         <v>36</v>
       </c>
       <c r="R93" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S93" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="T93" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U93" t="s">
         <v>164</v>
@@ -11081,7 +11079,7 @@
         <v>26</v>
       </c>
       <c r="H94" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I94" t="s">
         <v>1064</v>
@@ -11109,13 +11107,13 @@
         <v>36</v>
       </c>
       <c r="R94" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S94" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="T94" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U94" t="s">
         <v>164</v>
@@ -11172,7 +11170,7 @@
         <v>1088</v>
       </c>
       <c r="Q95" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R95" t="s">
         <v>1089</v>
@@ -11202,7 +11200,7 @@
         <v>574</v>
       </c>
       <c r="E96" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F96" t="s">
         <v>1093</v>
@@ -11238,7 +11236,7 @@
         <v>1100</v>
       </c>
       <c r="Q96" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R96" t="s">
         <v>37</v>
@@ -11277,7 +11275,7 @@
         <v>26</v>
       </c>
       <c r="H97" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I97" t="s">
         <v>1103</v>
@@ -11304,7 +11302,7 @@
         <v>1109</v>
       </c>
       <c r="Q97" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R97" t="s">
         <v>1110</v>
@@ -11370,7 +11368,7 @@
         <v>1121</v>
       </c>
       <c r="Q98" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R98" t="s">
         <v>1122</v>
@@ -11423,7 +11421,7 @@
         <v>1131</v>
       </c>
       <c r="N99" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O99" t="s">
         <v>1132</v>
@@ -11432,7 +11430,7 @@
         <v>1133</v>
       </c>
       <c r="Q99" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R99" t="s">
         <v>1134</v>
@@ -11462,7 +11460,7 @@
         <v>409</v>
       </c>
       <c r="E100" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F100" t="s">
         <v>1126</v>
@@ -11498,7 +11496,7 @@
         <v>1144</v>
       </c>
       <c r="Q100" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R100" t="s">
         <v>1145</v>
@@ -11564,7 +11562,7 @@
         <v>1156</v>
       </c>
       <c r="Q101" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R101" t="s">
         <v>1157</v>
@@ -11669,7 +11667,7 @@
         <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I103" t="s">
         <v>1170</v>
@@ -11696,7 +11694,7 @@
         <v>1176</v>
       </c>
       <c r="Q103" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R103" t="s">
         <v>1177</v>
@@ -11762,7 +11760,7 @@
         <v>1188</v>
       </c>
       <c r="Q104" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R104" t="s">
         <v>1189</v>
@@ -11789,7 +11787,7 @@
         <v>58</v>
       </c>
       <c r="D105" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="E105" t="s">
         <v>60</v>
@@ -11801,7 +11799,7 @@
         <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I105" t="s">
         <v>1194</v>
@@ -11828,16 +11826,16 @@
         <v>1200</v>
       </c>
       <c r="Q105" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R105" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="S105" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="T105" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="U105" t="s">
         <v>164</v>
@@ -11958,7 +11956,7 @@
         <v>1218</v>
       </c>
       <c r="Q107" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R107" t="s">
         <v>685</v>
@@ -11997,7 +11995,7 @@
         <v>26</v>
       </c>
       <c r="H108" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I108" t="s">
         <v>1221</v>
@@ -12022,7 +12020,7 @@
         <v>1226</v>
       </c>
       <c r="Q108" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R108" t="s">
         <v>1227</v>
@@ -12046,7 +12044,7 @@
         <v>1230</v>
       </c>
       <c r="C109" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D109" t="s">
         <v>154</v>
@@ -12061,7 +12059,7 @@
         <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I109" t="s">
         <v>1232</v>
@@ -12121,7 +12119,7 @@
       </c>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I110" t="s">
         <v>1241</v>
@@ -12179,7 +12177,7 @@
       </c>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I111" t="s">
         <v>1252</v>
@@ -12206,7 +12204,7 @@
         <v>1258</v>
       </c>
       <c r="Q111" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R111" t="s">
         <v>1259</v>
@@ -12245,7 +12243,7 @@
         <v>26</v>
       </c>
       <c r="H112" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I112" t="s">
         <v>1265</v>
@@ -12377,7 +12375,7 @@
         <v>44</v>
       </c>
       <c r="H114" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I114" t="s">
         <v>1289</v>
@@ -12404,7 +12402,7 @@
         <v>1295</v>
       </c>
       <c r="Q114" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R114" t="s">
         <v>640</v>
@@ -12428,13 +12426,13 @@
         <v>1296</v>
       </c>
       <c r="C115" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D115" t="s">
         <v>303</v>
       </c>
       <c r="E115" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F115" t="s">
         <v>1297</v>
@@ -12470,7 +12468,7 @@
         <v>1304</v>
       </c>
       <c r="Q115" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R115" t="s">
         <v>1134</v>
@@ -12500,7 +12498,7 @@
         <v>1306</v>
       </c>
       <c r="E116" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F116" t="s">
         <v>1297</v>
@@ -12509,7 +12507,7 @@
         <v>26</v>
       </c>
       <c r="H116" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I116" t="s">
         <v>1307</v>
@@ -12602,7 +12600,7 @@
         <v>1326</v>
       </c>
       <c r="Q117" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R117" t="s">
         <v>1327</v>
@@ -12641,7 +12639,7 @@
         <v>26</v>
       </c>
       <c r="H118" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I118" t="s">
         <v>1331</v>
@@ -12668,7 +12666,7 @@
         <v>1337</v>
       </c>
       <c r="Q118" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R118" t="s">
         <v>1338</v>
@@ -12698,7 +12696,7 @@
         <v>1306</v>
       </c>
       <c r="E119" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F119" t="s">
         <v>1297</v>
@@ -12734,7 +12732,7 @@
         <v>1348</v>
       </c>
       <c r="Q119" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R119" t="s">
         <v>1349</v>
@@ -12800,7 +12798,7 @@
         <v>1359</v>
       </c>
       <c r="Q120" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R120" t="s">
         <v>1360</v>
@@ -12830,7 +12828,7 @@
         <v>1364</v>
       </c>
       <c r="E121" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F121" t="s">
         <v>1365</v>
@@ -12866,7 +12864,7 @@
         <v>1372</v>
       </c>
       <c r="Q121" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R121" t="s">
         <v>685</v>
@@ -12893,7 +12891,7 @@
         <v>58</v>
       </c>
       <c r="D122" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E122" t="s">
         <v>60</v>
@@ -12932,7 +12930,7 @@
         <v>1381</v>
       </c>
       <c r="Q122" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R122" t="s">
         <v>261</v>
@@ -12998,7 +12996,7 @@
         <v>1391</v>
       </c>
       <c r="Q123" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R123" t="s">
         <v>607</v>
@@ -13022,7 +13020,7 @@
         <v>1392</v>
       </c>
       <c r="C124" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D124" t="s">
         <v>1393</v>
@@ -13064,7 +13062,7 @@
         <v>1401</v>
       </c>
       <c r="Q124" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R124" t="s">
         <v>1157</v>
@@ -13103,7 +13101,7 @@
         <v>26</v>
       </c>
       <c r="H125" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I125" t="s">
         <v>1403</v>
@@ -13131,13 +13129,13 @@
         <v>36</v>
       </c>
       <c r="R125" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="S125" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="T125" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="U125" t="s">
         <v>164</v>
@@ -13167,7 +13165,7 @@
         <v>26</v>
       </c>
       <c r="H126" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I126" t="s">
         <v>1411</v>
@@ -13192,16 +13190,16 @@
         <v>1416</v>
       </c>
       <c r="Q126" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R126" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="S126" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="T126" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="U126" t="s">
         <v>164</v>
@@ -13295,7 +13293,7 @@
         <v>26</v>
       </c>
       <c r="H128" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I128" t="s">
         <v>1432</v>
@@ -13322,7 +13320,7 @@
         <v>1438</v>
       </c>
       <c r="Q128" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R128" t="s">
         <v>1439</v>
@@ -13388,7 +13386,7 @@
         <v>1449</v>
       </c>
       <c r="Q129" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R129" t="s">
         <v>1450</v>
@@ -13454,7 +13452,7 @@
         <v>1462</v>
       </c>
       <c r="Q130" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R130" t="s">
         <v>1463</v>
@@ -13520,7 +13518,7 @@
         <v>1468</v>
       </c>
       <c r="Q131" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R131" t="s">
         <v>1469</v>
@@ -13586,7 +13584,7 @@
         <v>1481</v>
       </c>
       <c r="Q132" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R132" t="s">
         <v>479</v>
@@ -13613,10 +13611,10 @@
         <v>58</v>
       </c>
       <c r="D133" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E133" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F133" t="s">
         <v>1483</v>
@@ -13625,7 +13623,7 @@
         <v>44</v>
       </c>
       <c r="H133" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I133" t="s">
         <v>1484</v>
@@ -13652,7 +13650,7 @@
         <v>1490</v>
       </c>
       <c r="Q133" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R133" t="s">
         <v>1491</v>
@@ -13691,7 +13689,7 @@
         <v>26</v>
       </c>
       <c r="H134" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I134" t="s">
         <v>1496</v>
@@ -13718,7 +13716,7 @@
         <v>1502</v>
       </c>
       <c r="Q134" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R134" t="s">
         <v>1503</v>
@@ -13757,7 +13755,7 @@
         <v>26</v>
       </c>
       <c r="H135" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I135" t="s">
         <v>1508</v>
@@ -13782,7 +13780,7 @@
         <v>1513</v>
       </c>
       <c r="Q135" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R135" t="s">
         <v>1503</v>
@@ -13821,7 +13819,7 @@
         <v>26</v>
       </c>
       <c r="H136" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I136" t="s">
         <v>1515</v>
@@ -13885,7 +13883,7 @@
         <v>26</v>
       </c>
       <c r="H137" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="I137" t="s">
         <v>1524</v>
@@ -13940,7 +13938,7 @@
         <v>1306</v>
       </c>
       <c r="E138" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F138" t="s">
         <v>1531</v>
@@ -13974,7 +13972,7 @@
         <v>1537</v>
       </c>
       <c r="Q138" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="R138" t="s">
         <v>1538</v>
@@ -14036,7 +14034,7 @@
         <v>1549</v>
       </c>
       <c r="Q139" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="R139" t="s">
         <v>1550</v>
